--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCEF9A8-1C11-2A47-830A-CEFCA9CCC6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DCD687-727D-A445-99C8-9FE0FC97BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11240" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="26Q2" sheetId="2" r:id="rId1"/>
+    <sheet name="26Q3" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DCD687-727D-A445-99C8-9FE0FC97BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DC7A74-2B78-0D45-82B6-9FBA8EF93CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11240" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1554,6 +1554,9 @@
       <c r="B6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="C6" s="15">
+        <v>29</v>
+      </c>
       <c r="D6" s="33"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -1565,7 +1568,7 @@
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -4207,6 +4210,9 @@
       <c r="A18" s="14"/>
       <c r="B18" s="32" t="s">
         <v>21</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
       </c>
       <c r="D18" s="35"/>
       <c r="E18" s="10"/>
@@ -4219,7 +4225,7 @@
       <c r="L18" s="35"/>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
@@ -6860,6 +6866,9 @@
       <c r="A30" s="14"/>
       <c r="B30" s="32" t="s">
         <v>21</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0</v>
       </c>
       <c r="D30" s="35"/>
       <c r="E30" s="10"/>
@@ -9514,6 +9523,9 @@
       <c r="B42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
       <c r="D42" s="35"/>
       <c r="E42" s="10"/>
       <c r="F42" s="12"/>
@@ -9525,7 +9537,7 @@
       <c r="L42" s="35"/>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
@@ -12163,6 +12175,9 @@
       <c r="A54" s="14"/>
       <c r="B54" s="32" t="s">
         <v>21</v>
+      </c>
+      <c r="C54" s="1">
+        <v>4</v>
       </c>
       <c r="D54" s="35"/>
       <c r="E54" s="10"/>
@@ -12175,7 +12190,7 @@
       <c r="L54" s="35"/>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DC7A74-2B78-0D45-82B6-9FBA8EF93CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D59138-AC26-1B4C-80AB-DF8477CD9ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11240" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="11240" yWindow="720" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="26">
   <si>
     <t>總計</t>
   </si>
@@ -152,6 +152,14 @@
   </si>
   <si>
     <t>03/29~04/04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04/05~0411</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -889,7 +897,7 @@
   <dimension ref="A1:CY65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
@@ -958,7 +966,9 @@
       </c>
       <c r="B1" s="26"/>
       <c r="D1" s="25"/>
-      <c r="I1" s="26"/>
+      <c r="I1" s="26" t="s">
+        <v>24</v>
+      </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
       <c r="Q1" s="26"/>
@@ -999,7 +1009,9 @@
       </c>
       <c r="B2" s="22"/>
       <c r="D2" s="21"/>
-      <c r="I2" s="23"/>
+      <c r="I2" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
@@ -1303,11 +1315,13 @@
       <c r="J5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="40"/>
+      <c r="K5" s="40">
+        <v>7674</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="10">
         <f t="shared" ref="M5:N65" si="0">K5-C5</f>
-        <v>-7834</v>
+        <v>-160</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
@@ -1328,7 +1342,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U65" si="2">S5-K5</f>
-        <v>0</v>
+        <v>-7674</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V65" si="3">T5-L5</f>
@@ -1783,18 +1797,23 @@
       <c r="J7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="K7" s="10">
+        <v>268</v>
+      </c>
+      <c r="L7" s="12">
+        <v>268318.09523700998</v>
+      </c>
       <c r="M7" s="10">
         <f t="shared" si="0"/>
-        <v>-275</v>
+        <v>-7</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>-294767.6190465999</v>
+        <v>-26449.523809589911</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-8.9730086008560181E-2</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="13" t="s">
@@ -1803,15 +1822,15 @@
       <c r="T7" s="12"/>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-268</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W7" s="11" t="e">
+        <v>-268318.09523700998</v>
+      </c>
+      <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13" t="s">
@@ -2001,18 +2020,23 @@
       <c r="J8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="K8" s="10">
+        <v>297</v>
+      </c>
+      <c r="L8" s="12">
+        <v>485768.57142833993</v>
+      </c>
       <c r="M8" s="10">
         <f t="shared" si="0"/>
-        <v>-288</v>
+        <v>9</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>-437323.80952360982</v>
+        <v>48444.761904730112</v>
       </c>
       <c r="O8" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.11077549598203325</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="13" t="s">
@@ -2021,15 +2045,15 @@
       <c r="T8" s="12"/>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-297</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="11" t="e">
+        <v>-485768.57142833993</v>
+      </c>
+      <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13" t="s">
@@ -2219,18 +2243,23 @@
       <c r="J9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="K9" s="10">
+        <v>104</v>
+      </c>
+      <c r="L9" s="12">
+        <v>663535.23809521995</v>
+      </c>
       <c r="M9" s="10">
         <f t="shared" si="0"/>
-        <v>-100</v>
+        <v>4</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>-635095.23809521995</v>
+        <v>28440</v>
       </c>
       <c r="O9" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>4.4780685311540606E-2</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="13" t="s">
@@ -2239,15 +2268,15 @@
       <c r="T9" s="12"/>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="11" t="e">
+        <v>-663535.23809521995</v>
+      </c>
+      <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13" t="s">
@@ -2437,18 +2466,23 @@
       <c r="J10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="K10" s="10">
+        <v>71</v>
+      </c>
+      <c r="L10" s="12">
+        <v>871809.52380943997</v>
+      </c>
       <c r="M10" s="10">
         <f t="shared" si="0"/>
-        <v>-68</v>
+        <v>3</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>-1045904.7619047</v>
+        <v>-174095.23809525999</v>
       </c>
       <c r="O10" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.16645419777821327</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="13" t="s">
@@ -2457,15 +2491,15 @@
       <c r="T10" s="12"/>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="11" t="e">
+        <v>-871809.52380943997</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13" t="s">
@@ -2655,18 +2689,23 @@
       <c r="J11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="K11" s="10">
+        <v>9</v>
+      </c>
+      <c r="L11" s="12">
+        <v>25714.285714279999</v>
+      </c>
       <c r="M11" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="0"/>
-        <v>-17714.285714279999</v>
+        <v>8000</v>
       </c>
       <c r="O11" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.45161290322595216</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="13" t="s">
@@ -2675,15 +2714,15 @@
       <c r="T11" s="12"/>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="11" t="e">
+        <v>-25714.285714279999</v>
+      </c>
+      <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13" t="s">
@@ -2873,18 +2912,23 @@
       <c r="J12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="K12" s="10">
+        <v>13</v>
+      </c>
+      <c r="L12" s="12">
+        <v>35770</v>
+      </c>
       <c r="M12" s="10">
         <f t="shared" si="0"/>
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>-54490</v>
+        <v>-18720</v>
       </c>
       <c r="O12" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.34354927509634797</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="13" t="s">
@@ -2893,15 +2937,15 @@
       <c r="T12" s="12"/>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="11" t="e">
+        <v>-35770</v>
+      </c>
+      <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13" t="s">
@@ -3091,18 +3135,23 @@
       <c r="J13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="K13" s="10">
+        <v>10</v>
+      </c>
+      <c r="L13" s="12">
+        <v>492257.14285712002</v>
+      </c>
       <c r="M13" s="10">
         <f t="shared" si="0"/>
-        <v>-19</v>
+        <v>-9</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="0"/>
-        <v>-1005728.5714285101</v>
+        <v>-513471.4285713901</v>
       </c>
       <c r="O13" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.51054672518855548</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="13" t="s">
@@ -3111,15 +3160,15 @@
       <c r="T13" s="12"/>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="11" t="e">
+        <v>-492257.14285712002</v>
+      </c>
+      <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13" t="s">
@@ -3309,18 +3358,23 @@
       <c r="J14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="12"/>
+      <c r="K14" s="10">
+        <v>184</v>
+      </c>
+      <c r="L14" s="12">
+        <v>3023714.2857141499</v>
+      </c>
       <c r="M14" s="10">
         <f t="shared" si="0"/>
-        <v>-152</v>
+        <v>32</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>-2936571.4285712996</v>
+        <v>87142.857142850291</v>
       </c>
       <c r="O14" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>2.9675034053316736E-2</v>
       </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="13" t="s">
@@ -3329,15 +3383,15 @@
       <c r="T14" s="12"/>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-184</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="11" t="e">
+        <v>-3023714.2857141499</v>
+      </c>
+      <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13" t="s">
@@ -3527,18 +3581,23 @@
       <c r="J15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="12"/>
+      <c r="K15" s="10">
+        <v>280</v>
+      </c>
+      <c r="L15" s="12">
+        <v>10843621.90476181</v>
+      </c>
       <c r="M15" s="10">
         <f t="shared" si="0"/>
-        <v>-218</v>
+        <v>62</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="0"/>
-        <v>-8136380.9523808397</v>
+        <v>2707240.9523809701</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.33273281674314753</v>
       </c>
       <c r="Q15" s="14"/>
       <c r="R15" s="13" t="s">
@@ -3547,15 +3606,15 @@
       <c r="T15" s="12"/>
       <c r="U15" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="V15" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="11" t="e">
+        <v>-10843621.90476181</v>
+      </c>
+      <c r="W15" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y15" s="14"/>
       <c r="Z15" s="13" t="s">
@@ -3746,19 +3805,23 @@
         <v>19</v>
       </c>
       <c r="J16" s="9"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="7"/>
+      <c r="K16" s="8">
+        <v>1236</v>
+      </c>
+      <c r="L16" s="7">
+        <v>16710509.047617368</v>
+      </c>
       <c r="M16" s="27">
         <f t="shared" si="0"/>
-        <v>-1133</v>
+        <v>103</v>
       </c>
       <c r="N16" s="28">
         <f t="shared" si="0"/>
-        <v>-14563976.666665059</v>
+        <v>2146532.3809523098</v>
       </c>
       <c r="O16" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.14738641993744933</v>
       </c>
       <c r="Q16" s="9" t="s">
         <v>19</v>
@@ -3768,15 +3831,15 @@
       <c r="T16" s="7"/>
       <c r="U16" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1236</v>
       </c>
       <c r="V16" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="29" t="e">
+        <v>-16710509.047617368</v>
+      </c>
+      <c r="W16" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y16" s="9" t="s">
         <v>19</v>
@@ -3979,10 +4042,13 @@
       <c r="J17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K17" s="1">
+        <v>4508</v>
+      </c>
       <c r="L17" s="35"/>
       <c r="M17" s="10">
         <f t="shared" si="0"/>
-        <v>-4717</v>
+        <v>-209</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
@@ -4001,7 +4067,7 @@
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4508</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -4444,18 +4510,23 @@
       <c r="J19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="12"/>
+      <c r="K19" s="10">
+        <v>172</v>
+      </c>
+      <c r="L19" s="12">
+        <v>160716.19047541992</v>
+      </c>
       <c r="M19" s="10">
         <f t="shared" si="0"/>
-        <v>-148</v>
+        <v>24</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="0"/>
-        <v>-139128.57142802997</v>
+        <v>21587.619047389948</v>
       </c>
       <c r="O19" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.15516308998081707</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="13" t="s">
@@ -4464,15 +4535,15 @@
       <c r="T19" s="12"/>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-172</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="11" t="e">
+        <v>-160716.19047541992</v>
+      </c>
+      <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13" t="s">
@@ -4662,18 +4733,23 @@
       <c r="J20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L20" s="12"/>
+      <c r="K20" s="10">
+        <v>154</v>
+      </c>
+      <c r="L20" s="12">
+        <v>198200.95238083001</v>
+      </c>
       <c r="M20" s="10">
         <f t="shared" si="0"/>
-        <v>-150</v>
+        <v>4</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="0"/>
-        <v>-207807.61904751003</v>
+        <v>-9606.6666666800156</v>
       </c>
       <c r="O20" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-4.622865470819764E-2</v>
       </c>
       <c r="Q20" s="14"/>
       <c r="R20" s="13" t="s">
@@ -4682,15 +4758,15 @@
       <c r="T20" s="12"/>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-154</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="11" t="e">
+        <v>-198200.95238083001</v>
+      </c>
+      <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13" t="s">
@@ -4880,18 +4956,23 @@
       <c r="J21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="12"/>
+      <c r="K21" s="10">
+        <v>43</v>
+      </c>
+      <c r="L21" s="12">
+        <v>253780.95238094</v>
+      </c>
       <c r="M21" s="10">
         <f t="shared" si="0"/>
-        <v>-54</v>
+        <v>-11</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="0"/>
-        <v>-315676.19047618</v>
+        <v>-61895.238095239998</v>
       </c>
       <c r="O21" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.19607192421409569</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="R21" s="13" t="s">
@@ -4900,15 +4981,15 @@
       <c r="T21" s="12"/>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="e">
+        <v>-253780.95238094</v>
+      </c>
+      <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13" t="s">
@@ -5098,18 +5179,23 @@
       <c r="J22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L22" s="12"/>
+      <c r="K22" s="10">
+        <v>30</v>
+      </c>
+      <c r="L22" s="12">
+        <v>373809.52380946005</v>
+      </c>
       <c r="M22" s="10">
         <f t="shared" si="0"/>
-        <v>-33</v>
+        <v>-3</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="0"/>
-        <v>-393999.99999995</v>
+        <v>-20190.47619048995</v>
       </c>
       <c r="O22" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-5.1244863427645969E-2</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="13" t="s">
@@ -5118,15 +5204,15 @@
       <c r="T22" s="12"/>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="11" t="e">
+        <v>-373809.52380946005</v>
+      </c>
+      <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13" t="s">
@@ -5529,18 +5615,23 @@
       <c r="J24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="K24" s="10">
+        <v>7</v>
+      </c>
+      <c r="L24" s="12">
+        <v>39830</v>
+      </c>
       <c r="M24" s="10">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="0"/>
-        <v>-68980</v>
+        <v>-29150</v>
       </c>
       <c r="O24" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.42258625688605395</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="13" t="s">
@@ -5549,15 +5640,15 @@
       <c r="T24" s="12"/>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="11" t="e">
+        <v>-39830</v>
+      </c>
+      <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13" t="s">
@@ -5747,18 +5838,23 @@
       <c r="J25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L25" s="12"/>
+      <c r="K25" s="10">
+        <v>3</v>
+      </c>
+      <c r="L25" s="12">
+        <v>147809.52380950999</v>
+      </c>
       <c r="M25" s="10">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="0"/>
-        <v>-329723.80952378002</v>
+        <v>-181914.28571427002</v>
       </c>
       <c r="O25" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.55171716588198094</v>
       </c>
       <c r="Q25" s="14"/>
       <c r="R25" s="13" t="s">
@@ -5767,15 +5863,15 @@
       <c r="T25" s="12"/>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="e">
+        <v>-147809.52380950999</v>
+      </c>
+      <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13" t="s">
@@ -5965,18 +6061,23 @@
       <c r="J26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="12"/>
+      <c r="K26" s="10">
+        <v>40</v>
+      </c>
+      <c r="L26" s="12">
+        <v>783142.85714277031</v>
+      </c>
       <c r="M26" s="10">
         <f t="shared" si="0"/>
-        <v>-46</v>
+        <v>-6</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="0"/>
-        <v>-945904.76190469018</v>
+        <v>-162761.90476191987</v>
       </c>
       <c r="O26" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.17207007652036732</v>
       </c>
       <c r="Q26" s="14"/>
       <c r="R26" s="13" t="s">
@@ -5985,15 +6086,15 @@
       <c r="T26" s="12"/>
       <c r="U26" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="11" t="e">
+        <v>-783142.85714277031</v>
+      </c>
+      <c r="W26" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y26" s="14"/>
       <c r="Z26" s="13" t="s">
@@ -6183,18 +6284,23 @@
       <c r="J27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="12"/>
+      <c r="K27" s="10">
+        <v>87</v>
+      </c>
+      <c r="L27" s="12">
+        <v>3294571.4285713602</v>
+      </c>
       <c r="M27" s="10">
         <f t="shared" si="0"/>
-        <v>-91</v>
+        <v>-4</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="0"/>
-        <v>-3279904.7619046699</v>
+        <v>14666.66666669026</v>
       </c>
       <c r="O27" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>4.4716745550176266E-3</v>
       </c>
       <c r="Q27" s="14"/>
       <c r="R27" s="13" t="s">
@@ -6203,15 +6309,15 @@
       <c r="T27" s="12"/>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-87</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="11" t="e">
+        <v>-3294571.4285713602</v>
+      </c>
+      <c r="W27" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y27" s="14"/>
       <c r="Z27" s="13" t="s">
@@ -6402,19 +6508,23 @@
         <v>13</v>
       </c>
       <c r="J28" s="9"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
+      <c r="K28" s="8">
+        <v>536</v>
+      </c>
+      <c r="L28" s="7">
+        <v>5251861.428570291</v>
+      </c>
       <c r="M28" s="27">
         <f t="shared" si="0"/>
-        <v>-540</v>
+        <v>-4</v>
       </c>
       <c r="N28" s="28">
         <f t="shared" si="0"/>
-        <v>-5681125.7142848102</v>
+        <v>-429264.28571451921</v>
       </c>
       <c r="O28" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-7.5559723073045704E-2</v>
       </c>
       <c r="Q28" s="9" t="s">
         <v>13</v>
@@ -6424,15 +6534,15 @@
       <c r="T28" s="7"/>
       <c r="U28" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-536</v>
       </c>
       <c r="V28" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="29" t="e">
+        <v>-5251861.428570291</v>
+      </c>
+      <c r="W28" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y28" s="9" t="s">
         <v>13</v>
@@ -6635,10 +6745,13 @@
       <c r="J29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K29" s="1">
+        <v>3931</v>
+      </c>
       <c r="L29" s="35"/>
       <c r="M29" s="10">
         <f t="shared" si="0"/>
-        <v>-4377</v>
+        <v>-446</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="0"/>
@@ -6657,7 +6770,7 @@
       <c r="T29" s="35"/>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3931</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
@@ -7100,18 +7213,23 @@
       <c r="J31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L31" s="12"/>
+      <c r="K31" s="10">
+        <v>135</v>
+      </c>
+      <c r="L31" s="12">
+        <v>125993.33333286998</v>
+      </c>
       <c r="M31" s="10">
         <f t="shared" si="0"/>
-        <v>-102</v>
+        <v>33</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="0"/>
-        <v>-86738.095237659974</v>
+        <v>39255.238095210007</v>
       </c>
       <c r="O31" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.45257205599975125</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="R31" s="13" t="s">
@@ -7120,15 +7238,15 @@
       <c r="T31" s="12"/>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-135</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="11" t="e">
+        <v>-125993.33333286998</v>
+      </c>
+      <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13" t="s">
@@ -7318,18 +7436,23 @@
       <c r="J32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="K32" s="10">
+        <v>71</v>
+      </c>
+      <c r="L32" s="12">
+        <v>84790.476190339992</v>
+      </c>
       <c r="M32" s="10">
         <f t="shared" si="0"/>
-        <v>-49</v>
+        <v>22</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="0"/>
-        <v>-77123.809523739983</v>
+        <v>7666.6666666000092</v>
       </c>
       <c r="O32" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>9.9407261051336973E-2</v>
       </c>
       <c r="Q32" s="14"/>
       <c r="R32" s="13" t="s">
@@ -7338,15 +7461,15 @@
       <c r="T32" s="12"/>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="11" t="e">
+        <v>-84790.476190339992</v>
+      </c>
+      <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13" t="s">
@@ -7536,18 +7659,23 @@
       <c r="J33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="12"/>
+      <c r="K33" s="10">
+        <v>13</v>
+      </c>
+      <c r="L33" s="12">
+        <v>85399.999999990003</v>
+      </c>
       <c r="M33" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="0"/>
-        <v>-73209.523809509992</v>
+        <v>12190.476190480011</v>
       </c>
       <c r="O33" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.16651489527782526</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="R33" s="13" t="s">
@@ -7556,15 +7684,15 @@
       <c r="T33" s="12"/>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="11" t="e">
+        <v>-85399.999999990003</v>
+      </c>
+      <c r="W33" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y33" s="14"/>
       <c r="Z33" s="13" t="s">
@@ -7754,18 +7882,23 @@
       <c r="J34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L34" s="12"/>
+      <c r="K34" s="10">
+        <v>15</v>
+      </c>
+      <c r="L34" s="12">
+        <v>206190.47619043002</v>
+      </c>
       <c r="M34" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="0"/>
-        <v>-138761.90476188</v>
+        <v>67428.571428550029</v>
       </c>
       <c r="O34" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.48592999313651453</v>
       </c>
       <c r="Q34" s="14"/>
       <c r="R34" s="13" t="s">
@@ -7774,15 +7907,15 @@
       <c r="T34" s="12"/>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="11" t="e">
+        <v>-206190.47619043002</v>
+      </c>
+      <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13" t="s">
@@ -7967,14 +8100,19 @@
       <c r="J35" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L35" s="12"/>
+      <c r="K35" s="10">
+        <v>1</v>
+      </c>
+      <c r="L35" s="12">
+        <v>2857.1428571400002</v>
+      </c>
       <c r="M35" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2857.1428571400002</v>
       </c>
       <c r="O35" s="11" t="e">
         <f t="shared" si="1"/>
@@ -7987,15 +8125,15 @@
       <c r="T35" s="12"/>
       <c r="U35" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="11" t="e">
+        <v>-2857.1428571400002</v>
+      </c>
+      <c r="W35" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y35" s="14"/>
       <c r="Z35" s="13" t="s">
@@ -8185,18 +8323,23 @@
       <c r="J36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L36" s="12"/>
+      <c r="K36" s="10">
+        <v>3</v>
+      </c>
+      <c r="L36" s="12">
+        <v>14870</v>
+      </c>
       <c r="M36" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="0"/>
-        <v>-4780</v>
+        <v>10090</v>
       </c>
       <c r="O36" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>2.1108786610878663</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="13" t="s">
@@ -8205,15 +8348,15 @@
       <c r="T36" s="12"/>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="11" t="e">
+        <v>-14870</v>
+      </c>
+      <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13" t="s">
@@ -8403,18 +8546,23 @@
       <c r="J37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L37" s="12"/>
+      <c r="K37" s="10">
+        <v>1</v>
+      </c>
+      <c r="L37" s="12">
+        <v>48625.714285709997</v>
+      </c>
       <c r="M37" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="0"/>
-        <v>-83419.047619040008</v>
+        <v>-34793.333333330011</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.41709099212238665</v>
       </c>
       <c r="Q37" s="14"/>
       <c r="R37" s="13" t="s">
@@ -8423,15 +8571,15 @@
       <c r="T37" s="12"/>
       <c r="U37" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="11" t="e">
+        <v>-48625.714285709997</v>
+      </c>
+      <c r="W37" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y37" s="14"/>
       <c r="Z37" s="13" t="s">
@@ -8621,18 +8769,23 @@
       <c r="J38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="12"/>
+      <c r="K38" s="10">
+        <v>10</v>
+      </c>
+      <c r="L38" s="12">
+        <v>189047.61904759999</v>
+      </c>
       <c r="M38" s="10">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="0"/>
-        <v>-341047.61904758</v>
+        <v>-151999.99999998001</v>
       </c>
       <c r="O38" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.4456855626919779</v>
       </c>
       <c r="Q38" s="14"/>
       <c r="R38" s="13" t="s">
@@ -8641,15 +8794,15 @@
       <c r="T38" s="12"/>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W38" s="11" t="e">
+        <v>-189047.61904759999</v>
+      </c>
+      <c r="W38" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y38" s="14"/>
       <c r="Z38" s="13" t="s">
@@ -8839,18 +8992,23 @@
       <c r="J39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L39" s="12"/>
+      <c r="K39" s="10">
+        <v>17</v>
+      </c>
+      <c r="L39" s="12">
+        <v>615523.80952378991</v>
+      </c>
       <c r="M39" s="10">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>-3</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="0"/>
-        <v>-696190.47619043989</v>
+        <v>-80666.66666664998</v>
       </c>
       <c r="O39" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.11586867305059767</v>
       </c>
       <c r="Q39" s="14"/>
       <c r="R39" s="13" t="s">
@@ -8859,15 +9017,15 @@
       <c r="T39" s="12"/>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W39" s="11" t="e">
+        <v>-615523.80952378991</v>
+      </c>
+      <c r="W39" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y39" s="14"/>
       <c r="Z39" s="13" t="s">
@@ -9058,19 +9216,23 @@
         <v>12</v>
       </c>
       <c r="J40" s="9"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="7"/>
+      <c r="K40" s="8">
+        <v>266</v>
+      </c>
+      <c r="L40" s="7">
+        <v>1373298.5714278698</v>
+      </c>
       <c r="M40" s="27">
         <f t="shared" si="0"/>
-        <v>-221</v>
+        <v>45</v>
       </c>
       <c r="N40" s="28">
         <f t="shared" si="0"/>
-        <v>-1501270.4761898499</v>
+        <v>-127971.90476198005</v>
       </c>
       <c r="O40" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-8.5242404211375966E-2</v>
       </c>
       <c r="Q40" s="9" t="s">
         <v>12</v>
@@ -9080,15 +9242,15 @@
       <c r="T40" s="7"/>
       <c r="U40" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-266</v>
       </c>
       <c r="V40" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="29" t="e">
+        <v>-1373298.5714278698</v>
+      </c>
+      <c r="W40" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y40" s="9" t="s">
         <v>12</v>
@@ -9291,10 +9453,13 @@
       <c r="J41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K41" s="1">
+        <v>1283</v>
+      </c>
       <c r="L41" s="35"/>
       <c r="M41" s="10">
         <f t="shared" si="0"/>
-        <v>-1419</v>
+        <v>-136</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="0"/>
@@ -9313,7 +9478,7 @@
       <c r="T41" s="35"/>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1283</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
@@ -9756,18 +9921,23 @@
       <c r="J43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L43" s="12"/>
+      <c r="K43" s="10">
+        <v>109</v>
+      </c>
+      <c r="L43" s="12">
+        <v>100957.14285668997</v>
+      </c>
       <c r="M43" s="10">
         <f t="shared" si="0"/>
-        <v>-114</v>
+        <v>-5</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="0"/>
-        <v>-97707.619047069966</v>
+        <v>3249.5238096200046</v>
       </c>
       <c r="O43" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>3.325762966401391E-2</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="13" t="s">
@@ -9776,15 +9946,15 @@
       <c r="T43" s="12"/>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W43" s="11" t="e">
+        <v>-100957.14285668997</v>
+      </c>
+      <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13" t="s">
@@ -9974,18 +10144,23 @@
       <c r="J44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="K44" s="10">
+        <v>74</v>
+      </c>
+      <c r="L44" s="12">
+        <v>77676.190476089992</v>
+      </c>
       <c r="M44" s="10">
         <f t="shared" si="0"/>
-        <v>-74</v>
+        <v>0</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="0"/>
-        <v>-80771.428571329991</v>
+        <v>-3095.2380952399981</v>
       </c>
       <c r="O44" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-3.8320952717910209E-2</v>
       </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="13" t="s">
@@ -9994,15 +10169,15 @@
       <c r="T44" s="12"/>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="11" t="e">
+        <v>-77676.190476089992</v>
+      </c>
+      <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13" t="s">
@@ -10192,18 +10367,23 @@
       <c r="J45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="12"/>
+      <c r="K45" s="10">
+        <v>15</v>
+      </c>
+      <c r="L45" s="12">
+        <v>91285.714285709983</v>
+      </c>
       <c r="M45" s="10">
         <f t="shared" si="0"/>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="0"/>
-        <v>-125361.90476189001</v>
+        <v>-34076.190476180025</v>
       </c>
       <c r="O45" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.27182253285720004</v>
       </c>
       <c r="Q45" s="14"/>
       <c r="R45" s="13" t="s">
@@ -10212,15 +10392,15 @@
       <c r="T45" s="12"/>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W45" s="11" t="e">
+        <v>-91285.714285709983</v>
+      </c>
+      <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13" t="s">
@@ -10410,18 +10590,23 @@
       <c r="J46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="12"/>
+      <c r="K46" s="10">
+        <v>16</v>
+      </c>
+      <c r="L46" s="12">
+        <v>182761.90476186998</v>
+      </c>
       <c r="M46" s="10">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="0"/>
-        <v>-137904.76190474001</v>
+        <v>44857.142857129977</v>
       </c>
       <c r="O46" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.32527624309388092</v>
       </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="13" t="s">
@@ -10430,15 +10615,15 @@
       <c r="T46" s="12"/>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W46" s="11" t="e">
+        <v>-182761.90476186998</v>
+      </c>
+      <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13" t="s">
@@ -10841,18 +11026,23 @@
       <c r="J48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="12"/>
+      <c r="K48" s="10">
+        <v>3</v>
+      </c>
+      <c r="L48" s="12">
+        <v>14070</v>
+      </c>
       <c r="M48" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="N48" s="12">
         <f t="shared" si="0"/>
-        <v>-12780</v>
+        <v>1290</v>
       </c>
       <c r="O48" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.10093896713615023</v>
       </c>
       <c r="Q48" s="14"/>
       <c r="R48" s="13" t="s">
@@ -10861,15 +11051,15 @@
       <c r="T48" s="12"/>
       <c r="U48" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W48" s="11" t="e">
+        <v>-14070</v>
+      </c>
+      <c r="W48" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y48" s="14"/>
       <c r="Z48" s="13" t="s">
@@ -11277,18 +11467,23 @@
       <c r="J50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L50" s="12"/>
+      <c r="K50" s="10">
+        <v>8</v>
+      </c>
+      <c r="L50" s="12">
+        <v>144476.19047616998</v>
+      </c>
       <c r="M50" s="10">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="0"/>
-        <v>-150285.7142857</v>
+        <v>-5809.5238095300156</v>
       </c>
       <c r="O50" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-3.8656527249728116E-2</v>
       </c>
       <c r="Q50" s="14"/>
       <c r="R50" s="13" t="s">
@@ -11297,15 +11492,15 @@
       <c r="T50" s="12"/>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W50" s="11" t="e">
+        <v>-144476.19047616998</v>
+      </c>
+      <c r="W50" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y50" s="14"/>
       <c r="Z50" s="13" t="s">
@@ -11495,18 +11690,23 @@
       <c r="J51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L51" s="12"/>
+      <c r="K51" s="10">
+        <v>20</v>
+      </c>
+      <c r="L51" s="12">
+        <v>656190.47619043</v>
+      </c>
       <c r="M51" s="10">
         <f t="shared" si="0"/>
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="N51" s="12">
         <f t="shared" si="0"/>
-        <v>-992571.42857138999</v>
+        <v>-336380.95238095999</v>
       </c>
       <c r="O51" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.33889848397622502</v>
       </c>
       <c r="Q51" s="14"/>
       <c r="R51" s="13" t="s">
@@ -11515,15 +11715,15 @@
       <c r="T51" s="12"/>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="11" t="e">
+        <v>-656190.47619043</v>
+      </c>
+      <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13" t="s">
@@ -11714,19 +11914,23 @@
         <v>11</v>
       </c>
       <c r="J52" s="9"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="7"/>
+      <c r="K52" s="8">
+        <v>245</v>
+      </c>
+      <c r="L52" s="7">
+        <v>1267417.61904696</v>
+      </c>
       <c r="M52" s="27">
         <f t="shared" si="0"/>
-        <v>-256</v>
+        <v>-11</v>
       </c>
       <c r="N52" s="28">
         <f t="shared" si="0"/>
-        <v>-1649668.57142783</v>
+        <v>-382250.95238087</v>
       </c>
       <c r="O52" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.23171378724274422</v>
       </c>
       <c r="Q52" s="9" t="s">
         <v>11</v>
@@ -11736,15 +11940,15 @@
       <c r="T52" s="7"/>
       <c r="U52" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-245</v>
       </c>
       <c r="V52" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="29" t="e">
+        <v>-1267417.61904696</v>
+      </c>
+      <c r="W52" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y52" s="9" t="s">
         <v>11</v>
@@ -12409,18 +12613,23 @@
       <c r="J55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L55" s="12"/>
+      <c r="K55" s="10">
+        <v>122</v>
+      </c>
+      <c r="L55" s="12">
+        <v>97163.809523340009</v>
+      </c>
       <c r="M55" s="10">
         <f t="shared" si="0"/>
-        <v>-124</v>
+        <v>-2</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="0"/>
-        <v>-106086.66666614998</v>
+        <v>-8922.8571428099676</v>
       </c>
       <c r="O55" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-8.4109129103752525E-2</v>
       </c>
       <c r="Q55" s="14"/>
       <c r="R55" s="13" t="s">
@@ -12429,15 +12638,15 @@
       <c r="T55" s="12"/>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="11" t="e">
+        <v>-97163.809523340009</v>
+      </c>
+      <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13" t="s">
@@ -12627,18 +12836,23 @@
       <c r="J56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L56" s="12"/>
+      <c r="K56" s="10">
+        <v>94</v>
+      </c>
+      <c r="L56" s="12">
+        <v>80542.857142770008</v>
+      </c>
       <c r="M56" s="10">
         <f t="shared" si="0"/>
-        <v>-67</v>
+        <v>27</v>
       </c>
       <c r="N56" s="12">
         <f t="shared" si="0"/>
-        <v>-80907.619047550004</v>
+        <v>-364.76190477999626</v>
       </c>
       <c r="O56" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-4.5083752194663273E-3</v>
       </c>
       <c r="Q56" s="14"/>
       <c r="R56" s="13" t="s">
@@ -12647,15 +12861,15 @@
       <c r="T56" s="12"/>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-94</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W56" s="11" t="e">
+        <v>-80542.857142770008</v>
+      </c>
+      <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13" t="s">
@@ -12845,18 +13059,23 @@
       <c r="J57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="12"/>
+      <c r="K57" s="10">
+        <v>14</v>
+      </c>
+      <c r="L57" s="12">
+        <v>90342.857142840003</v>
+      </c>
       <c r="M57" s="10">
         <f t="shared" si="0"/>
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="0"/>
-        <v>-89571.428571419994</v>
+        <v>771.42857142000867</v>
       </c>
       <c r="O57" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>8.6124401912927879E-3</v>
       </c>
       <c r="Q57" s="14"/>
       <c r="R57" s="13" t="s">
@@ -12865,15 +13084,15 @@
       <c r="T57" s="12"/>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W57" s="11" t="e">
+        <v>-90342.857142840003</v>
+      </c>
+      <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13" t="s">
@@ -13063,18 +13282,23 @@
       <c r="J58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L58" s="12"/>
+      <c r="K58" s="10">
+        <v>8</v>
+      </c>
+      <c r="L58" s="12">
+        <v>103047.61904759001</v>
+      </c>
       <c r="M58" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="N58" s="12">
         <f t="shared" si="0"/>
-        <v>-170666.66666660001</v>
+        <v>-67619.047619010002</v>
       </c>
       <c r="O58" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.39620535714279148</v>
       </c>
       <c r="Q58" s="14"/>
       <c r="R58" s="13" t="s">
@@ -13083,15 +13307,15 @@
       <c r="T58" s="12"/>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W58" s="11" t="e">
+        <v>-103047.61904759001</v>
+      </c>
+      <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13" t="s">
@@ -13494,18 +13718,23 @@
       <c r="J60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="12"/>
+      <c r="K60" s="10">
+        <v>1</v>
+      </c>
+      <c r="L60" s="12">
+        <v>2590</v>
+      </c>
       <c r="M60" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N60" s="12">
         <f t="shared" si="0"/>
-        <v>-8580</v>
+        <v>-5990</v>
       </c>
       <c r="O60" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.69813519813519809</v>
       </c>
       <c r="Q60" s="14"/>
       <c r="R60" s="13" t="s">
@@ -13514,15 +13743,15 @@
       <c r="T60" s="12"/>
       <c r="U60" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V60" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W60" s="11" t="e">
+        <v>-2590</v>
+      </c>
+      <c r="W60" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y60" s="14"/>
       <c r="Z60" s="13" t="s">
@@ -13712,18 +13941,23 @@
       <c r="J61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="12"/>
+      <c r="K61" s="10">
+        <v>1</v>
+      </c>
+      <c r="L61" s="12">
+        <v>47523.809523800002</v>
+      </c>
       <c r="M61" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N61" s="12">
         <f t="shared" si="0"/>
-        <v>-95047.619047600005</v>
+        <v>-47523.809523800002</v>
       </c>
       <c r="O61" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="Q61" s="14"/>
       <c r="R61" s="13" t="s">
@@ -13732,15 +13966,15 @@
       <c r="T61" s="12"/>
       <c r="U61" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V61" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W61" s="11" t="e">
+        <v>-47523.809523800002</v>
+      </c>
+      <c r="W61" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y61" s="14"/>
       <c r="Z61" s="13" t="s">
@@ -13930,18 +14164,23 @@
       <c r="J62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="12"/>
+      <c r="K62" s="10">
+        <v>21</v>
+      </c>
+      <c r="L62" s="12">
+        <v>385619.04761900002</v>
+      </c>
       <c r="M62" s="10">
         <f t="shared" si="0"/>
-        <v>-22</v>
+        <v>-1</v>
       </c>
       <c r="N62" s="12">
         <f t="shared" si="0"/>
-        <v>-475999.99999993999</v>
+        <v>-90380.952380939969</v>
       </c>
       <c r="O62" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.18987595038014993</v>
       </c>
       <c r="Q62" s="14"/>
       <c r="R62" s="13" t="s">
@@ -13950,15 +14189,15 @@
       <c r="T62" s="12"/>
       <c r="U62" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="V62" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W62" s="11" t="e">
+        <v>-385619.04761900002</v>
+      </c>
+      <c r="W62" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y62" s="14"/>
       <c r="Z62" s="13" t="s">
@@ -14148,18 +14387,23 @@
       <c r="J63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L63" s="12"/>
+      <c r="K63" s="10">
+        <v>21</v>
+      </c>
+      <c r="L63" s="12">
+        <v>722761.90476188995</v>
+      </c>
       <c r="M63" s="10">
         <f t="shared" si="0"/>
-        <v>-26</v>
+        <v>-5</v>
       </c>
       <c r="N63" s="12">
         <f t="shared" si="0"/>
-        <v>-895619.0476190201</v>
+        <v>-172857.14285713015</v>
       </c>
       <c r="O63" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.19300297745639328</v>
       </c>
       <c r="Q63" s="14"/>
       <c r="R63" s="13" t="s">
@@ -14168,15 +14412,15 @@
       <c r="T63" s="12"/>
       <c r="U63" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="V63" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W63" s="11" t="e">
+        <v>-722761.90476188995</v>
+      </c>
+      <c r="W63" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y63" s="14"/>
       <c r="Z63" s="13" t="s">
@@ -14367,19 +14611,23 @@
         <v>1</v>
       </c>
       <c r="J64" s="9"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
+      <c r="K64" s="8">
+        <v>282</v>
+      </c>
+      <c r="L64" s="7">
+        <v>1529591.9047612301</v>
+      </c>
       <c r="M64" s="27">
         <f t="shared" si="0"/>
-        <v>-271</v>
+        <v>11</v>
       </c>
       <c r="N64" s="28">
         <f t="shared" si="0"/>
-        <v>-1922479.0476182802</v>
+        <v>-392887.14285705006</v>
       </c>
       <c r="O64" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.20436485034455376</v>
       </c>
       <c r="Q64" s="9" t="s">
         <v>1</v>
@@ -14389,15 +14637,15 @@
       <c r="T64" s="7"/>
       <c r="U64" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-282</v>
       </c>
       <c r="V64" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W64" s="29" t="e">
+        <v>-1529591.9047612301</v>
+      </c>
+      <c r="W64" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y64" s="9" t="s">
         <v>1</v>
@@ -14598,19 +14846,23 @@
         <v>0</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="2"/>
+      <c r="K65" s="3">
+        <v>2565</v>
+      </c>
+      <c r="L65" s="2">
+        <v>26132678.571423709</v>
+      </c>
       <c r="M65" s="6">
         <f t="shared" si="0"/>
-        <v>-2421</v>
+        <v>144</v>
       </c>
       <c r="N65" s="5">
         <f t="shared" si="0"/>
-        <v>-25318520.476185832</v>
+        <v>814158.09523787722</v>
       </c>
       <c r="O65" s="30">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>3.2156622106084769E-2</v>
       </c>
       <c r="Q65" s="4" t="s">
         <v>0</v>
@@ -14620,15 +14872,15 @@
       <c r="T65" s="2"/>
       <c r="U65" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2565</v>
       </c>
       <c r="V65" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W65" s="30" t="e">
+        <v>-26132678.571423709</v>
+      </c>
+      <c r="W65" s="30">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D59138-AC26-1B4C-80AB-DF8477CD9ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313F65CF-036B-0D48-971A-82BE2EF2B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11240" yWindow="720" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1579,10 +1579,13 @@
       <c r="J6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K6" s="15">
+        <v>12</v>
+      </c>
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>-29</v>
+        <v>-17</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -1599,7 +1602,7 @@
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -4288,10 +4291,13 @@
       <c r="J18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
       <c r="L18" s="35"/>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
@@ -4308,7 +4314,7 @@
       <c r="T18" s="35"/>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
@@ -6991,10 +6997,13 @@
       <c r="J30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
       <c r="L30" s="35"/>
       <c r="M30" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="0"/>
@@ -7011,7 +7020,7 @@
       <c r="T30" s="35"/>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
@@ -9699,10 +9708,13 @@
       <c r="J42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K42" s="1">
+        <v>4</v>
+      </c>
       <c r="L42" s="35"/>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
@@ -9719,7 +9731,7 @@
       <c r="T42" s="35"/>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
@@ -12391,10 +12403,13 @@
       <c r="J54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K54" s="1">
+        <v>3</v>
+      </c>
       <c r="L54" s="35"/>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>
@@ -12411,7 +12426,7 @@
       <c r="T54" s="35"/>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313F65CF-036B-0D48-971A-82BE2EF2B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123FE991-028D-C841-B3AF-9B5B512223E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11240" yWindow="720" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="14000" yWindow="720" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="28">
   <si>
     <t>總計</t>
   </si>
@@ -160,6 +160,14 @@
   </si>
   <si>
     <t>04/05~0411</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04/12~0418</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -971,7 +979,9 @@
       </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
-      <c r="Q1" s="26"/>
+      <c r="Q1" s="26" t="s">
+        <v>26</v>
+      </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
       <c r="Y1" s="26"/>
@@ -1015,7 +1025,9 @@
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
-      <c r="Q2" s="22"/>
+      <c r="Q2" s="23" t="s">
+        <v>27</v>
+      </c>
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
@@ -1338,11 +1350,13 @@
       <c r="R5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="40"/>
+      <c r="S5" s="40">
+        <v>5227</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U65" si="2">S5-K5</f>
-        <v>-7674</v>
+        <v>-2447</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V65" si="3">T5-L5</f>
@@ -1363,7 +1377,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD65" si="5">AA5-S5</f>
-        <v>0</v>
+        <v>-5227</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1579,13 +1593,10 @@
       <c r="J6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="15">
-        <v>12</v>
-      </c>
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -1602,7 +1613,7 @@
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -1822,18 +1833,23 @@
       <c r="R7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T7" s="12"/>
+      <c r="S7" s="10">
+        <v>193</v>
+      </c>
+      <c r="T7" s="12">
+        <v>201697.14285629994</v>
+      </c>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>-268</v>
+        <v>-75</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>-268318.09523700998</v>
+        <v>-66620.952380710049</v>
       </c>
       <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.24829094110057176</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13" t="s">
@@ -1842,15 +1858,15 @@
       <c r="AB7" s="12"/>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-193</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="11" t="e">
+        <v>-201697.14285629994</v>
+      </c>
+      <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -2045,18 +2061,23 @@
       <c r="R8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="12"/>
+      <c r="S8" s="10">
+        <v>206</v>
+      </c>
+      <c r="T8" s="12">
+        <v>374962.85714272998</v>
+      </c>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>-297</v>
+        <v>-91</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>-485768.57142833993</v>
+        <v>-110805.71428560995</v>
       </c>
       <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.22810391779731656</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13" t="s">
@@ -2065,15 +2086,15 @@
       <c r="AB8" s="12"/>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-206</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="11" t="e">
+        <v>-374962.85714272998</v>
+      </c>
+      <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2268,18 +2289,23 @@
       <c r="R9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="12"/>
+      <c r="S9" s="10">
+        <v>62</v>
+      </c>
+      <c r="T9" s="12">
+        <v>390647.61904759996</v>
+      </c>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>-104</v>
+        <v>-42</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>-663535.23809521995</v>
+        <v>-272887.61904761998</v>
       </c>
       <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.41126319052924137</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13" t="s">
@@ -2288,15 +2314,15 @@
       <c r="AB9" s="12"/>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE9" s="11" t="e">
+        <v>-390647.61904759996</v>
+      </c>
+      <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2491,18 +2517,23 @@
       <c r="R10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T10" s="12"/>
+      <c r="S10" s="10">
+        <v>56</v>
+      </c>
+      <c r="T10" s="12">
+        <v>809428.5714284901</v>
+      </c>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>-71</v>
+        <v>-15</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>-871809.52380943997</v>
+        <v>-62380.952380949864</v>
       </c>
       <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-7.1553419270268356E-2</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13" t="s">
@@ -2511,15 +2542,15 @@
       <c r="AB10" s="12"/>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="11" t="e">
+        <v>-809428.5714284901</v>
+      </c>
+      <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2714,18 +2745,23 @@
       <c r="R11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="12"/>
+      <c r="S11" s="10">
+        <v>1</v>
+      </c>
+      <c r="T11" s="12">
+        <v>2657.1428571400002</v>
+      </c>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>-25714.285714279999</v>
+        <v>-23057.142857139999</v>
       </c>
       <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.89666666666675487</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13" t="s">
@@ -2734,15 +2770,15 @@
       <c r="AB11" s="12"/>
       <c r="AC11" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD11" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="11" t="e">
+        <v>-2657.1428571400002</v>
+      </c>
+      <c r="AE11" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG11" s="14"/>
       <c r="AH11" s="13" t="s">
@@ -2937,18 +2973,23 @@
       <c r="R12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T12" s="12"/>
+      <c r="S12" s="10">
+        <v>5</v>
+      </c>
+      <c r="T12" s="12">
+        <v>26750</v>
+      </c>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>-35770</v>
+        <v>-9020</v>
       </c>
       <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.25216662007268659</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13" t="s">
@@ -2957,15 +2998,15 @@
       <c r="AB12" s="12"/>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="11" t="e">
+        <v>-26750</v>
+      </c>
+      <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3160,18 +3201,23 @@
       <c r="R13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T13" s="12"/>
+      <c r="S13" s="10">
+        <v>5</v>
+      </c>
+      <c r="T13" s="12">
+        <v>275757.14285712998</v>
+      </c>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>-492257.14285712002</v>
+        <v>-216499.99999999005</v>
       </c>
       <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.43981078414301489</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13" t="s">
@@ -3180,15 +3226,15 @@
       <c r="AB13" s="12"/>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="11" t="e">
+        <v>-275757.14285712998</v>
+      </c>
+      <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3383,18 +3429,23 @@
       <c r="R14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="12"/>
+      <c r="S14" s="10">
+        <v>118</v>
+      </c>
+      <c r="T14" s="12">
+        <v>2440666.6666665301</v>
+      </c>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>-184</v>
+        <v>-66</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>-3023714.2857141499</v>
+        <v>-583047.61904761987</v>
       </c>
       <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.19282497086523304</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13" t="s">
@@ -3403,15 +3454,15 @@
       <c r="AB14" s="12"/>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-118</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="11" t="e">
+        <v>-2440666.6666665301</v>
+      </c>
+      <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3606,18 +3657,23 @@
       <c r="R15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T15" s="12"/>
+      <c r="S15" s="10">
+        <v>163</v>
+      </c>
+      <c r="T15" s="12">
+        <v>6496857.1428570598</v>
+      </c>
       <c r="U15" s="10">
         <f t="shared" si="2"/>
-        <v>-280</v>
+        <v>-117</v>
       </c>
       <c r="V15" s="12">
         <f t="shared" si="3"/>
-        <v>-10843621.90476181</v>
+        <v>-4346764.76190475</v>
       </c>
       <c r="W15" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.40085912254059092</v>
       </c>
       <c r="Y15" s="14"/>
       <c r="Z15" s="13" t="s">
@@ -3626,15 +3682,15 @@
       <c r="AB15" s="12"/>
       <c r="AC15" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-163</v>
       </c>
       <c r="AD15" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="11" t="e">
+        <v>-6496857.1428570598</v>
+      </c>
+      <c r="AE15" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG15" s="14"/>
       <c r="AH15" s="13" t="s">
@@ -3830,19 +3886,23 @@
         <v>19</v>
       </c>
       <c r="R16" s="9"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="7"/>
+      <c r="S16" s="8">
+        <v>809</v>
+      </c>
+      <c r="T16" s="7">
+        <v>11019424.28571298</v>
+      </c>
       <c r="U16" s="27">
         <f t="shared" si="2"/>
-        <v>-1236</v>
+        <v>-427</v>
       </c>
       <c r="V16" s="28">
         <f t="shared" si="3"/>
-        <v>-16710509.047617368</v>
+        <v>-5691084.7619043887</v>
       </c>
       <c r="W16" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.34056920382780559</v>
       </c>
       <c r="Y16" s="9" t="s">
         <v>19</v>
@@ -3852,15 +3912,15 @@
       <c r="AB16" s="7"/>
       <c r="AC16" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-809</v>
       </c>
       <c r="AD16" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="29" t="e">
+        <v>-11019424.28571298</v>
+      </c>
+      <c r="AE16" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG16" s="9" t="s">
         <v>19</v>
@@ -4067,10 +4127,13 @@
       <c r="R17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S17" s="1">
+        <v>3855</v>
+      </c>
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>-4508</v>
+        <v>-653</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -4089,7 +4152,7 @@
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3855</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -4291,13 +4354,10 @@
       <c r="J18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="1">
-        <v>12</v>
-      </c>
       <c r="L18" s="35"/>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
@@ -4314,7 +4374,7 @@
       <c r="T18" s="35"/>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
@@ -4538,18 +4598,23 @@
       <c r="R19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T19" s="12"/>
+      <c r="S19" s="10">
+        <v>142</v>
+      </c>
+      <c r="T19" s="12">
+        <v>156208.57142790995</v>
+      </c>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>-172</v>
+        <v>-30</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>-160716.19047541992</v>
+        <v>-4507.619047509972</v>
       </c>
       <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-2.8047074997085444E-2</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13" t="s">
@@ -4558,15 +4623,15 @@
       <c r="AB19" s="12"/>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-142</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="11" t="e">
+        <v>-156208.57142790995</v>
+      </c>
+      <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4761,18 +4826,23 @@
       <c r="R20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T20" s="12"/>
+      <c r="S20" s="10">
+        <v>173</v>
+      </c>
+      <c r="T20" s="12">
+        <v>251306.66666651997</v>
+      </c>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>-154</v>
+        <v>19</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>-198200.95238083001</v>
+        <v>53105.714285689959</v>
       </c>
       <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.26793874422788261</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13" t="s">
@@ -4781,15 +4851,15 @@
       <c r="AB20" s="12"/>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-173</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE20" s="11" t="e">
+        <v>-251306.66666651997</v>
+      </c>
+      <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -4984,18 +5054,23 @@
       <c r="R21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="S21" s="10">
+        <v>42</v>
+      </c>
+      <c r="T21" s="12">
+        <v>252552.38095237</v>
+      </c>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>-43</v>
+        <v>-1</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>-253780.95238094</v>
+        <v>-1228.5714285699942</v>
       </c>
       <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-4.841070289332971E-3</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13" t="s">
@@ -5004,15 +5079,15 @@
       <c r="AB21" s="12"/>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="11" t="e">
+        <v>-252552.38095237</v>
+      </c>
+      <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5207,18 +5282,23 @@
       <c r="R22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T22" s="12"/>
+      <c r="S22" s="10">
+        <v>24</v>
+      </c>
+      <c r="T22" s="12">
+        <v>322095.23809518002</v>
+      </c>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>-30</v>
+        <v>-6</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>-373809.52380946005</v>
+        <v>-51714.285714280035</v>
       </c>
       <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.13834394904459438</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13" t="s">
@@ -5227,15 +5307,15 @@
       <c r="AB22" s="12"/>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="11" t="e">
+        <v>-322095.23809518002</v>
+      </c>
+      <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5420,14 +5500,19 @@
       <c r="R23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T23" s="12"/>
+      <c r="S23" s="10">
+        <v>1</v>
+      </c>
+      <c r="T23" s="12">
+        <v>8857.1428571399993</v>
+      </c>
       <c r="U23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8857.1428571399993</v>
       </c>
       <c r="W23" s="11" t="e">
         <f t="shared" si="4"/>
@@ -5440,15 +5525,15 @@
       <c r="AB23" s="12"/>
       <c r="AC23" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD23" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="11" t="e">
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="AE23" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG23" s="14"/>
       <c r="AH23" s="13" t="s">
@@ -5643,18 +5728,23 @@
       <c r="R24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T24" s="12"/>
+      <c r="S24" s="10">
+        <v>11</v>
+      </c>
+      <c r="T24" s="12">
+        <v>59490</v>
+      </c>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>-39830</v>
+        <v>19660</v>
       </c>
       <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.4935977906100929</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13" t="s">
@@ -5663,15 +5753,15 @@
       <c r="AB24" s="12"/>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="11" t="e">
+        <v>-59490</v>
+      </c>
+      <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5866,18 +5956,23 @@
       <c r="R25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T25" s="12"/>
+      <c r="S25" s="10">
+        <v>4</v>
+      </c>
+      <c r="T25" s="12">
+        <v>224290.47619046</v>
+      </c>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>-147809.52380950999</v>
+        <v>76480.95238095001</v>
       </c>
       <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.51742912371137251</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13" t="s">
@@ -5886,15 +5981,15 @@
       <c r="AB25" s="12"/>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="11" t="e">
+        <v>-224290.47619046</v>
+      </c>
+      <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6089,18 +6184,23 @@
       <c r="R26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T26" s="12"/>
+      <c r="S26" s="10">
+        <v>30</v>
+      </c>
+      <c r="T26" s="12">
+        <v>579999.99999992014</v>
+      </c>
       <c r="U26" s="10">
         <f t="shared" si="2"/>
-        <v>-40</v>
+        <v>-10</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="3"/>
-        <v>-783142.85714277031</v>
+        <v>-203142.85714285017</v>
       </c>
       <c r="W26" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.25939438161257</v>
       </c>
       <c r="Y26" s="14"/>
       <c r="Z26" s="13" t="s">
@@ -6109,15 +6209,15 @@
       <c r="AB26" s="12"/>
       <c r="AC26" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AD26" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="11" t="e">
+        <v>-579999.99999992014</v>
+      </c>
+      <c r="AE26" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG26" s="14"/>
       <c r="AH26" s="13" t="s">
@@ -6312,18 +6412,23 @@
       <c r="R27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T27" s="12"/>
+      <c r="S27" s="10">
+        <v>83</v>
+      </c>
+      <c r="T27" s="12">
+        <v>3150190.4761903705</v>
+      </c>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>-87</v>
+        <v>-4</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
-        <v>-3294571.4285713602</v>
+        <v>-144380.95238098968</v>
       </c>
       <c r="W27" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-4.3823895007672739E-2</v>
       </c>
       <c r="Y27" s="14"/>
       <c r="Z27" s="13" t="s">
@@ -6332,15 +6437,15 @@
       <c r="AB27" s="12"/>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="11" t="e">
+        <v>-3150190.4761903705</v>
+      </c>
+      <c r="AE27" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG27" s="14"/>
       <c r="AH27" s="13" t="s">
@@ -6536,19 +6641,23 @@
         <v>13</v>
       </c>
       <c r="R28" s="9"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="7"/>
+      <c r="S28" s="8">
+        <v>510</v>
+      </c>
+      <c r="T28" s="7">
+        <v>5004990.9523798702</v>
+      </c>
       <c r="U28" s="27">
         <f t="shared" si="2"/>
-        <v>-536</v>
+        <v>-26</v>
       </c>
       <c r="V28" s="28">
         <f t="shared" si="3"/>
-        <v>-5251861.428570291</v>
+        <v>-246870.4761904208</v>
       </c>
       <c r="W28" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-4.7006281400997683E-2</v>
       </c>
       <c r="Y28" s="9" t="s">
         <v>13</v>
@@ -6558,15 +6667,15 @@
       <c r="AB28" s="7"/>
       <c r="AC28" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-510</v>
       </c>
       <c r="AD28" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE28" s="29" t="e">
+        <v>-5004990.9523798702</v>
+      </c>
+      <c r="AE28" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG28" s="9" t="s">
         <v>13</v>
@@ -6773,10 +6882,13 @@
       <c r="R29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S29" s="1">
+        <v>2898</v>
+      </c>
       <c r="T29" s="35"/>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>-3931</v>
+        <v>-1033</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
@@ -6795,7 +6907,7 @@
       <c r="AB29" s="35"/>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2898</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
@@ -6997,13 +7109,10 @@
       <c r="J30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="1">
-        <v>3</v>
-      </c>
       <c r="L30" s="35"/>
       <c r="M30" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="0"/>
@@ -7020,7 +7129,7 @@
       <c r="T30" s="35"/>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
@@ -7244,18 +7353,23 @@
       <c r="R31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T31" s="12"/>
+      <c r="S31" s="10">
+        <v>137</v>
+      </c>
+      <c r="T31" s="12">
+        <v>125499.04761861001</v>
+      </c>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>-135</v>
+        <v>2</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>-125993.33333286998</v>
+        <v>-494.28571425996779</v>
       </c>
       <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-3.9231100661023246E-3</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13" t="s">
@@ -7264,15 +7378,15 @@
       <c r="AB31" s="12"/>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-137</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="11" t="e">
+        <v>-125499.04761861001</v>
+      </c>
+      <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7467,18 +7581,23 @@
       <c r="R32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T32" s="12"/>
+      <c r="S32" s="10">
+        <v>60</v>
+      </c>
+      <c r="T32" s="12">
+        <v>75809.523809429986</v>
+      </c>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>-71</v>
+        <v>-11</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>-84790.476190339992</v>
+        <v>-8980.9523809100065</v>
       </c>
       <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.10591935302673991</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13" t="s">
@@ -7487,15 +7606,15 @@
       <c r="AB32" s="12"/>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE32" s="11" t="e">
+        <v>-75809.523809429986</v>
+      </c>
+      <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7690,18 +7809,23 @@
       <c r="R33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T33" s="12"/>
+      <c r="S33" s="10">
+        <v>14</v>
+      </c>
+      <c r="T33" s="12">
+        <v>86152.380952370004</v>
+      </c>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>1</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="3"/>
-        <v>-85399.999999990003</v>
+        <v>752.38095238000096</v>
       </c>
       <c r="W33" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>8.8100814096029167E-3</v>
       </c>
       <c r="Y33" s="14"/>
       <c r="Z33" s="13" t="s">
@@ -7710,15 +7834,15 @@
       <c r="AB33" s="12"/>
       <c r="AC33" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AD33" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="11" t="e">
+        <v>-86152.380952370004</v>
+      </c>
+      <c r="AE33" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG33" s="14"/>
       <c r="AH33" s="13" t="s">
@@ -7913,18 +8037,23 @@
       <c r="R34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T34" s="12"/>
+      <c r="S34" s="10">
+        <v>16</v>
+      </c>
+      <c r="T34" s="12">
+        <v>188476.19047615002</v>
+      </c>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>-206190.47619043002</v>
+        <v>-17714.285714280006</v>
       </c>
       <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-8.591224018474905E-2</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13" t="s">
@@ -7933,15 +8062,15 @@
       <c r="AB34" s="12"/>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="11" t="e">
+        <v>-188476.19047615002</v>
+      </c>
+      <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8354,18 +8483,23 @@
       <c r="R36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T36" s="12"/>
+      <c r="S36" s="10">
+        <v>5</v>
+      </c>
+      <c r="T36" s="12">
+        <v>10350</v>
+      </c>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>-14870</v>
+        <v>-4520</v>
       </c>
       <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.30396772024209817</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13" t="s">
@@ -8374,15 +8508,15 @@
       <c r="AB36" s="12"/>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE36" s="11" t="e">
+        <v>-10350</v>
+      </c>
+      <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8577,18 +8711,23 @@
       <c r="R37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T37" s="12"/>
+      <c r="S37" s="10">
+        <v>1</v>
+      </c>
+      <c r="T37" s="12">
+        <v>47523.809523800002</v>
+      </c>
       <c r="U37" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="3"/>
-        <v>-48625.714285709997</v>
+        <v>-1101.9047619099947</v>
       </c>
       <c r="W37" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-2.2660947568513553E-2</v>
       </c>
       <c r="Y37" s="14"/>
       <c r="Z37" s="13" t="s">
@@ -8597,15 +8736,15 @@
       <c r="AB37" s="12"/>
       <c r="AC37" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD37" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE37" s="11" t="e">
+        <v>-47523.809523800002</v>
+      </c>
+      <c r="AE37" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG37" s="14"/>
       <c r="AH37" s="13" t="s">
@@ -8800,18 +8939,23 @@
       <c r="R38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T38" s="12"/>
+      <c r="S38" s="10">
+        <v>9</v>
+      </c>
+      <c r="T38" s="12">
+        <v>178666.66666662999</v>
+      </c>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
-        <v>-189047.61904759999</v>
+        <v>-10380.952380970004</v>
       </c>
       <c r="W38" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-5.4911838791030745E-2</v>
       </c>
       <c r="Y38" s="14"/>
       <c r="Z38" s="13" t="s">
@@ -8820,15 +8964,15 @@
       <c r="AB38" s="12"/>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE38" s="11" t="e">
+        <v>-178666.66666662999</v>
+      </c>
+      <c r="AE38" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG38" s="14"/>
       <c r="AH38" s="13" t="s">
@@ -9023,18 +9167,23 @@
       <c r="R39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T39" s="12"/>
+      <c r="S39" s="10">
+        <v>17</v>
+      </c>
+      <c r="T39" s="12">
+        <v>561238.09523807</v>
+      </c>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
-        <v>-615523.80952378991</v>
+        <v>-54285.714285719907</v>
       </c>
       <c r="W39" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-8.8194336995215408E-2</v>
       </c>
       <c r="Y39" s="14"/>
       <c r="Z39" s="13" t="s">
@@ -9043,15 +9192,15 @@
       <c r="AB39" s="12"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE39" s="11" t="e">
+        <v>-561238.09523807</v>
+      </c>
+      <c r="AE39" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG39" s="14"/>
       <c r="AH39" s="13" t="s">
@@ -9247,19 +9396,23 @@
         <v>12</v>
       </c>
       <c r="R40" s="9"/>
-      <c r="S40" s="8"/>
-      <c r="T40" s="7"/>
+      <c r="S40" s="8">
+        <v>259</v>
+      </c>
+      <c r="T40" s="7">
+        <v>1273715.7142850598</v>
+      </c>
       <c r="U40" s="27">
         <f t="shared" si="2"/>
-        <v>-266</v>
+        <v>-7</v>
       </c>
       <c r="V40" s="28">
         <f t="shared" si="3"/>
-        <v>-1373298.5714278698</v>
+        <v>-99582.857142810011</v>
       </c>
       <c r="W40" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-7.2513624651389538E-2</v>
       </c>
       <c r="Y40" s="9" t="s">
         <v>12</v>
@@ -9269,15 +9422,15 @@
       <c r="AB40" s="7"/>
       <c r="AC40" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="AD40" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE40" s="29" t="e">
+        <v>-1273715.7142850598</v>
+      </c>
+      <c r="AE40" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG40" s="9" t="s">
         <v>12</v>
@@ -9484,10 +9637,13 @@
       <c r="R41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S41" s="1">
+        <v>1049</v>
+      </c>
       <c r="T41" s="35"/>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>-1283</v>
+        <v>-234</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
@@ -9506,7 +9662,7 @@
       <c r="AB41" s="35"/>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1049</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
@@ -9708,13 +9864,10 @@
       <c r="J42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="1">
-        <v>4</v>
-      </c>
       <c r="L42" s="35"/>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
@@ -9731,7 +9884,7 @@
       <c r="T42" s="35"/>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
@@ -9955,18 +10108,23 @@
       <c r="R43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T43" s="12"/>
+      <c r="S43" s="10">
+        <v>110</v>
+      </c>
+      <c r="T43" s="12">
+        <v>109499.04761855995</v>
+      </c>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>-109</v>
+        <v>1</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>-100957.14285668997</v>
+        <v>8541.9047618699842</v>
       </c>
       <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>8.4609216546424393E-2</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13" t="s">
@@ -9975,15 +10133,15 @@
       <c r="AB43" s="12"/>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-110</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE43" s="11" t="e">
+        <v>-109499.04761855995</v>
+      </c>
+      <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10178,18 +10336,23 @@
       <c r="R44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="12"/>
+      <c r="S44" s="10">
+        <v>60</v>
+      </c>
+      <c r="T44" s="12">
+        <v>82553.333333219998</v>
+      </c>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>-74</v>
+        <v>-14</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>-77676.190476089992</v>
+        <v>4877.1428571300057</v>
       </c>
       <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>6.2788131436894684E-2</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13" t="s">
@@ -10198,15 +10361,15 @@
       <c r="AB44" s="12"/>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE44" s="11" t="e">
+        <v>-82553.333333219998</v>
+      </c>
+      <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10401,18 +10564,23 @@
       <c r="R45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="12"/>
+      <c r="S45" s="10">
+        <v>9</v>
+      </c>
+      <c r="T45" s="12">
+        <v>42771.428571419994</v>
+      </c>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>-91285.714285709983</v>
+        <v>-48514.285714289988</v>
       </c>
       <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.53145539906110473</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13" t="s">
@@ -10421,15 +10589,15 @@
       <c r="AB45" s="12"/>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE45" s="11" t="e">
+        <v>-42771.428571419994</v>
+      </c>
+      <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10624,18 +10792,23 @@
       <c r="R46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T46" s="12"/>
+      <c r="S46" s="10">
+        <v>11</v>
+      </c>
+      <c r="T46" s="12">
+        <v>111333.33333329001</v>
+      </c>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>-182761.90476186998</v>
+        <v>-71428.571428579977</v>
       </c>
       <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.39082855653998566</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13" t="s">
@@ -10644,15 +10817,15 @@
       <c r="AB46" s="12"/>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE46" s="11" t="e">
+        <v>-111333.33333329001</v>
+      </c>
+      <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10837,14 +11010,19 @@
       <c r="R47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T47" s="12"/>
+      <c r="S47" s="10">
+        <v>2</v>
+      </c>
+      <c r="T47" s="12">
+        <v>5714.2857142800003</v>
+      </c>
       <c r="U47" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5714.2857142800003</v>
       </c>
       <c r="W47" s="11" t="e">
         <f t="shared" si="4"/>
@@ -10857,15 +11035,15 @@
       <c r="AB47" s="12"/>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE47" s="11" t="e">
+        <v>-5714.2857142800003</v>
+      </c>
+      <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11278,14 +11456,19 @@
       <c r="R49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T49" s="12"/>
+      <c r="S49" s="10">
+        <v>1</v>
+      </c>
+      <c r="T49" s="12">
+        <v>47523.809523800002</v>
+      </c>
       <c r="U49" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>47523.809523800002</v>
       </c>
       <c r="W49" s="11" t="e">
         <f t="shared" si="4"/>
@@ -11298,15 +11481,15 @@
       <c r="AB49" s="12"/>
       <c r="AC49" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD49" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE49" s="11" t="e">
+        <v>-47523.809523800002</v>
+      </c>
+      <c r="AE49" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG49" s="14"/>
       <c r="AH49" s="13" t="s">
@@ -11501,18 +11684,23 @@
       <c r="R50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T50" s="12"/>
+      <c r="S50" s="10">
+        <v>19</v>
+      </c>
+      <c r="T50" s="12">
+        <v>335619.04761899996</v>
+      </c>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>-8</v>
+        <v>11</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>
-        <v>-144476.19047616998</v>
+        <v>191142.85714282998</v>
       </c>
       <c r="W50" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>1.32300593276203</v>
       </c>
       <c r="Y50" s="14"/>
       <c r="Z50" s="13" t="s">
@@ -11521,15 +11709,15 @@
       <c r="AB50" s="12"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE50" s="11" t="e">
+        <v>-335619.04761899996</v>
+      </c>
+      <c r="AE50" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG50" s="14"/>
       <c r="AH50" s="13" t="s">
@@ -11724,18 +11912,23 @@
       <c r="R51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T51" s="12"/>
+      <c r="S51" s="10">
+        <v>25</v>
+      </c>
+      <c r="T51" s="12">
+        <v>980476.1904761499</v>
+      </c>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>-656190.47619043</v>
+        <v>324285.71428571991</v>
       </c>
       <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.49419448476056588</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13" t="s">
@@ -11744,15 +11937,15 @@
       <c r="AB51" s="12"/>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE51" s="11" t="e">
+        <v>-980476.1904761499</v>
+      </c>
+      <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -11948,19 +12141,23 @@
         <v>11</v>
       </c>
       <c r="R52" s="9"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="7"/>
+      <c r="S52" s="8">
+        <v>237</v>
+      </c>
+      <c r="T52" s="7">
+        <v>1715490.47618972</v>
+      </c>
       <c r="U52" s="27">
         <f t="shared" si="2"/>
-        <v>-245</v>
+        <v>-8</v>
       </c>
       <c r="V52" s="28">
         <f t="shared" si="3"/>
-        <v>-1267417.61904696</v>
+        <v>448072.85714275995</v>
       </c>
       <c r="W52" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.35353213527179006</v>
       </c>
       <c r="Y52" s="9" t="s">
         <v>11</v>
@@ -11970,15 +12167,15 @@
       <c r="AB52" s="7"/>
       <c r="AC52" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-237</v>
       </c>
       <c r="AD52" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE52" s="29" t="e">
+        <v>-1715490.47618972</v>
+      </c>
+      <c r="AE52" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG52" s="9" t="s">
         <v>11</v>
@@ -12403,13 +12600,10 @@
       <c r="J54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K54" s="1">
-        <v>3</v>
-      </c>
       <c r="L54" s="35"/>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>
@@ -12426,7 +12620,7 @@
       <c r="T54" s="35"/>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
@@ -12650,18 +12844,23 @@
       <c r="R55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="T55" s="12"/>
+      <c r="S55" s="10">
+        <v>92</v>
+      </c>
+      <c r="T55" s="12">
+        <v>87358.095237700007</v>
+      </c>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>-122</v>
+        <v>-30</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>-97163.809523340009</v>
+        <v>-9805.7142856400023</v>
       </c>
       <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.10091940953884215</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13" t="s">
@@ -12670,15 +12869,15 @@
       <c r="AB55" s="12"/>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE55" s="11" t="e">
+        <v>-87358.095237700007</v>
+      </c>
+      <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -12873,18 +13072,23 @@
       <c r="R56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T56" s="12"/>
+      <c r="S56" s="10">
+        <v>53</v>
+      </c>
+      <c r="T56" s="12">
+        <v>56161.90476184</v>
+      </c>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>-94</v>
+        <v>-41</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>-80542.857142770008</v>
+        <v>-24380.952380930008</v>
       </c>
       <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.30270781601045527</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13" t="s">
@@ -12893,15 +13097,15 @@
       <c r="AB56" s="12"/>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE56" s="11" t="e">
+        <v>-56161.90476184</v>
+      </c>
+      <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13096,18 +13300,23 @@
       <c r="R57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T57" s="12"/>
+      <c r="S57" s="10">
+        <v>17</v>
+      </c>
+      <c r="T57" s="12">
+        <v>104409.52380952</v>
+      </c>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>-14</v>
+        <v>3</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>-90342.857142840003</v>
+        <v>14066.666666680001</v>
       </c>
       <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.15570314147181955</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13" t="s">
@@ -13116,15 +13325,15 @@
       <c r="AB57" s="12"/>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE57" s="11" t="e">
+        <v>-104409.52380952</v>
+      </c>
+      <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13319,18 +13528,23 @@
       <c r="R58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T58" s="12"/>
+      <c r="S58" s="10">
+        <v>10</v>
+      </c>
+      <c r="T58" s="12">
+        <v>115238.09523805999</v>
+      </c>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>-103047.61904759001</v>
+        <v>12190.476190469984</v>
       </c>
       <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.11829944547132247</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13" t="s">
@@ -13339,15 +13553,15 @@
       <c r="AB58" s="12"/>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE58" s="11" t="e">
+        <v>-115238.09523805999</v>
+      </c>
+      <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13755,18 +13969,23 @@
       <c r="R60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T60" s="12"/>
+      <c r="S60" s="10">
+        <v>6</v>
+      </c>
+      <c r="T60" s="12">
+        <v>22940</v>
+      </c>
       <c r="U60" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V60" s="12">
         <f t="shared" si="3"/>
-        <v>-2590</v>
+        <v>20350</v>
       </c>
       <c r="W60" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>7.8571428571428568</v>
       </c>
       <c r="Y60" s="14"/>
       <c r="Z60" s="13" t="s">
@@ -13775,15 +13994,15 @@
       <c r="AB60" s="12"/>
       <c r="AC60" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD60" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE60" s="11" t="e">
+        <v>-22940</v>
+      </c>
+      <c r="AE60" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG60" s="14"/>
       <c r="AH60" s="13" t="s">
@@ -13978,18 +14197,23 @@
       <c r="R61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T61" s="12"/>
+      <c r="S61" s="10">
+        <v>1</v>
+      </c>
+      <c r="T61" s="12">
+        <v>49671.428571420001</v>
+      </c>
       <c r="U61" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="12">
         <f t="shared" si="3"/>
-        <v>-47523.809523800002</v>
+        <v>2147.619047619999</v>
       </c>
       <c r="W61" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>4.5190380761552122E-2</v>
       </c>
       <c r="Y61" s="14"/>
       <c r="Z61" s="13" t="s">
@@ -13998,15 +14222,15 @@
       <c r="AB61" s="12"/>
       <c r="AC61" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD61" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE61" s="11" t="e">
+        <v>-49671.428571420001</v>
+      </c>
+      <c r="AE61" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG61" s="14"/>
       <c r="AH61" s="13" t="s">
@@ -14201,18 +14425,23 @@
       <c r="R62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="12"/>
+      <c r="S62" s="10">
+        <v>7</v>
+      </c>
+      <c r="T62" s="12">
+        <v>120761.90476188001</v>
+      </c>
       <c r="U62" s="10">
         <f t="shared" si="2"/>
-        <v>-21</v>
+        <v>-14</v>
       </c>
       <c r="V62" s="12">
         <f t="shared" si="3"/>
-        <v>-385619.04761900002</v>
+        <v>-264857.14285712002</v>
       </c>
       <c r="W62" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.68683625586567143</v>
       </c>
       <c r="Y62" s="14"/>
       <c r="Z62" s="13" t="s">
@@ -14221,15 +14450,15 @@
       <c r="AB62" s="12"/>
       <c r="AC62" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AD62" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE62" s="11" t="e">
+        <v>-120761.90476188001</v>
+      </c>
+      <c r="AE62" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG62" s="14"/>
       <c r="AH62" s="13" t="s">
@@ -14424,18 +14653,23 @@
       <c r="R63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T63" s="12"/>
+      <c r="S63" s="10">
+        <v>13</v>
+      </c>
+      <c r="T63" s="12">
+        <v>479812.38095233997</v>
+      </c>
       <c r="U63" s="10">
         <f t="shared" si="2"/>
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="V63" s="12">
         <f t="shared" si="3"/>
-        <v>-722761.90476188995</v>
+        <v>-242949.52380954998</v>
       </c>
       <c r="W63" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.33614046646466295</v>
       </c>
       <c r="Y63" s="14"/>
       <c r="Z63" s="13" t="s">
@@ -14444,15 +14678,15 @@
       <c r="AB63" s="12"/>
       <c r="AC63" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AD63" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE63" s="11" t="e">
+        <v>-479812.38095233997</v>
+      </c>
+      <c r="AE63" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG63" s="14"/>
       <c r="AH63" s="13" t="s">
@@ -14648,19 +14882,23 @@
         <v>1</v>
       </c>
       <c r="R64" s="9"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="7"/>
+      <c r="S64" s="8">
+        <v>199</v>
+      </c>
+      <c r="T64" s="7">
+        <v>1036353.33333276</v>
+      </c>
       <c r="U64" s="27">
         <f t="shared" si="2"/>
-        <v>-282</v>
+        <v>-83</v>
       </c>
       <c r="V64" s="28">
         <f t="shared" si="3"/>
-        <v>-1529591.9047612301</v>
+        <v>-493238.57142847008</v>
       </c>
       <c r="W64" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.3224641617761862</v>
       </c>
       <c r="Y64" s="9" t="s">
         <v>1</v>
@@ -14670,15 +14908,15 @@
       <c r="AB64" s="7"/>
       <c r="AC64" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-199</v>
       </c>
       <c r="AD64" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE64" s="29" t="e">
+        <v>-1036353.33333276</v>
+      </c>
+      <c r="AE64" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG64" s="9" t="s">
         <v>1</v>
@@ -14883,19 +15121,23 @@
         <v>0</v>
       </c>
       <c r="R65" s="4"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="2"/>
+      <c r="S65" s="3">
+        <v>2014</v>
+      </c>
+      <c r="T65" s="2">
+        <v>20049974.761900391</v>
+      </c>
       <c r="U65" s="6">
         <f t="shared" si="2"/>
-        <v>-2565</v>
+        <v>-551</v>
       </c>
       <c r="V65" s="5">
         <f t="shared" si="3"/>
-        <v>-26132678.571423709</v>
+        <v>-6082703.809523318</v>
       </c>
       <c r="W65" s="30">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.232762355106407</v>
       </c>
       <c r="Y65" s="4" t="s">
         <v>0</v>
@@ -14905,15 +15147,15 @@
       <c r="AB65" s="2"/>
       <c r="AC65" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2014</v>
       </c>
       <c r="AD65" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE65" s="30" t="e">
+        <v>-20049974.761900391</v>
+      </c>
+      <c r="AE65" s="30">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123FE991-028D-C841-B3AF-9B5B512223E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF5A7EB-4BFA-564F-B2A4-5F2D14B9B8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14000" yWindow="720" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="14000" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -1593,10 +1593,13 @@
       <c r="J6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K6" s="15">
+        <v>12</v>
+      </c>
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>-29</v>
+        <v>-17</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -1610,10 +1613,13 @@
       <c r="R6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="S6" s="15">
+        <v>8</v>
+      </c>
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -1630,7 +1636,7 @@
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -4354,10 +4360,13 @@
       <c r="J18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
       <c r="L18" s="35"/>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
@@ -4371,10 +4380,13 @@
       <c r="R18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="S18" s="1">
+        <v>9</v>
+      </c>
       <c r="T18" s="35"/>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
@@ -4391,7 +4403,7 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
@@ -7109,10 +7121,13 @@
       <c r="J30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
       <c r="L30" s="35"/>
       <c r="M30" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="0"/>
@@ -7126,10 +7141,13 @@
       <c r="R30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="S30" s="1">
+        <v>1</v>
+      </c>
       <c r="T30" s="35"/>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
@@ -7146,7 +7164,7 @@
       <c r="AB30" s="35"/>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
@@ -9864,10 +9882,13 @@
       <c r="J42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K42" s="1">
+        <v>4</v>
+      </c>
       <c r="L42" s="35"/>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
@@ -9881,10 +9902,13 @@
       <c r="R42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="S42" s="1">
+        <v>5</v>
+      </c>
       <c r="T42" s="35"/>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
@@ -9901,7 +9925,7 @@
       <c r="AB42" s="35"/>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
@@ -12600,10 +12624,13 @@
       <c r="J54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="K54" s="1">
+        <v>3</v>
+      </c>
       <c r="L54" s="35"/>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>
@@ -12617,10 +12644,13 @@
       <c r="R54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="S54" s="1">
+        <v>4</v>
+      </c>
       <c r="T54" s="35"/>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
@@ -12637,7 +12667,7 @@
       <c r="AB54" s="35"/>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF5A7EB-4BFA-564F-B2A4-5F2D14B9B8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08162E52-B231-864F-871A-12C4387F8200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14000" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -159,15 +159,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>04/05~0411</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>26Q3W3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>04/12~0418</t>
+    <t>04/12~04/18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04/05~04/11</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -980,7 +980,7 @@
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
       <c r="Q1" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
@@ -1020,13 +1020,13 @@
       <c r="B2" s="22"/>
       <c r="D2" s="21"/>
       <c r="I2" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
       <c r="Q2" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08162E52-B231-864F-871A-12C4387F8200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A3314-C4D3-8D40-90EC-91DA934FEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14000" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="30">
   <si>
     <t>總計</t>
   </si>
@@ -168,6 +168,14 @@
   </si>
   <si>
     <t>04/05~04/11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04/19~04/25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -984,7 +992,9 @@
       </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
-      <c r="Y1" s="26"/>
+      <c r="Y1" s="26" t="s">
+        <v>28</v>
+      </c>
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
       <c r="AG1" s="26"/>
@@ -1031,6 +1041,9 @@
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
+      <c r="Y2" s="23" t="s">
+        <v>29</v>
+      </c>
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
       <c r="AK2" s="22"/>
@@ -1373,11 +1386,13 @@
       <c r="Z5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AA5" s="40"/>
+      <c r="AA5" s="40">
+        <v>5617</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD65" si="5">AA5-S5</f>
-        <v>-5227</v>
+        <v>390</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1398,7 +1413,7 @@
       <c r="AJ5" s="40"/>
       <c r="AK5" s="10">
         <f t="shared" ref="AK5:AL65" si="7">AI5-AA5</f>
-        <v>0</v>
+        <v>-5617</v>
       </c>
       <c r="AL5" s="12">
         <f t="shared" si="7"/>
@@ -1861,18 +1876,23 @@
       <c r="Z7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AB7" s="12"/>
+      <c r="AA7" s="10">
+        <v>194</v>
+      </c>
+      <c r="AB7" s="12">
+        <v>201242.85714209004</v>
+      </c>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>-193</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>-201697.14285629994</v>
+        <v>-454.28571420989465</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-2.2523160604885346E-3</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -1881,15 +1901,15 @@
       <c r="AI7" s="13"/>
       <c r="AK7" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-194</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM7" s="11" t="e">
+        <v>-201242.85714209004</v>
+      </c>
+      <c r="AM7" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO7" s="14"/>
       <c r="AP7" s="13" t="s">
@@ -2089,18 +2109,23 @@
       <c r="Z8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="12"/>
+      <c r="AA8" s="10">
+        <v>251</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>475849.52380930987</v>
+      </c>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>-206</v>
+        <v>45</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>-374962.85714272998</v>
+        <v>100886.6666665799</v>
       </c>
       <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.26905776064154879</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2109,15 +2134,15 @@
       <c r="AI8" s="13"/>
       <c r="AK8" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-251</v>
       </c>
       <c r="AL8" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="11" t="e">
+        <v>-475849.52380930987</v>
+      </c>
+      <c r="AM8" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO8" s="14"/>
       <c r="AP8" s="13" t="s">
@@ -2317,18 +2342,23 @@
       <c r="Z9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB9" s="12"/>
+      <c r="AA9" s="10">
+        <v>69</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>426009.52380950004</v>
+      </c>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>-62</v>
+        <v>7</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>-390647.61904759996</v>
+        <v>35361.904761900078</v>
       </c>
       <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>9.0521234579932941E-2</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2337,15 +2367,15 @@
       <c r="AI9" s="13"/>
       <c r="AK9" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="AL9" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM9" s="11" t="e">
+        <v>-426009.52380950004</v>
+      </c>
+      <c r="AM9" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO9" s="14"/>
       <c r="AP9" s="13" t="s">
@@ -2545,18 +2575,23 @@
       <c r="Z10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB10" s="12"/>
+      <c r="AA10" s="10">
+        <v>58</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>787523.80952371005</v>
+      </c>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>-56</v>
+        <v>2</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>-809428.5714284901</v>
+        <v>-21904.761904780054</v>
       </c>
       <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-2.7062007295001023E-2</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2565,15 +2600,15 @@
       <c r="AI10" s="13"/>
       <c r="AK10" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="11" t="e">
+        <v>-787523.80952371005</v>
+      </c>
+      <c r="AM10" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO10" s="14"/>
       <c r="AP10" s="13" t="s">
@@ -3001,18 +3036,23 @@
       <c r="Z12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB12" s="12"/>
+      <c r="AA12" s="10">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>26860</v>
+      </c>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>-26750</v>
+        <v>110</v>
       </c>
       <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>4.1121495327102802E-3</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3021,15 +3061,15 @@
       <c r="AI12" s="13"/>
       <c r="AK12" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM12" s="11" t="e">
+        <v>-26860</v>
+      </c>
+      <c r="AM12" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO12" s="14"/>
       <c r="AP12" s="13" t="s">
@@ -3229,18 +3269,23 @@
       <c r="Z13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB13" s="12"/>
+      <c r="AA13" s="10">
+        <v>44</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>1773776.1904760499</v>
+      </c>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>39</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>-275757.14285712998</v>
+        <v>1498019.04761892</v>
       </c>
       <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>5.4323852941682276</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3249,15 +3294,15 @@
       <c r="AI13" s="13"/>
       <c r="AK13" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM13" s="11" t="e">
+        <v>-1773776.1904760499</v>
+      </c>
+      <c r="AM13" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO13" s="14"/>
       <c r="AP13" s="13" t="s">
@@ -3457,18 +3502,23 @@
       <c r="Z14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="12"/>
+      <c r="AA14" s="10">
+        <v>72</v>
+      </c>
+      <c r="AB14" s="12">
+        <v>1379619.0476189305</v>
+      </c>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>-118</v>
+        <v>-46</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>-2440666.6666665301</v>
+        <v>-1061047.6190475996</v>
       </c>
       <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.43473680103017986</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3477,15 +3527,15 @@
       <c r="AI14" s="13"/>
       <c r="AK14" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11" t="e">
+        <v>-1379619.0476189305</v>
+      </c>
+      <c r="AM14" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO14" s="14"/>
       <c r="AP14" s="13" t="s">
@@ -3685,18 +3735,23 @@
       <c r="Z15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB15" s="12"/>
+      <c r="AA15" s="10">
+        <v>81</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>2842761.9047618099</v>
+      </c>
       <c r="AC15" s="10">
         <f t="shared" si="5"/>
-        <v>-163</v>
+        <v>-82</v>
       </c>
       <c r="AD15" s="12">
         <f t="shared" si="5"/>
-        <v>-6496857.1428570598</v>
+        <v>-3654095.23809525</v>
       </c>
       <c r="AE15" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.56244044739581944</v>
       </c>
       <c r="AG15" s="14"/>
       <c r="AH15" s="13" t="s">
@@ -3705,15 +3760,15 @@
       <c r="AI15" s="13"/>
       <c r="AK15" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-81</v>
       </c>
       <c r="AL15" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="11" t="e">
+        <v>-2842761.9047618099</v>
+      </c>
+      <c r="AM15" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO15" s="14"/>
       <c r="AP15" s="13" t="s">
@@ -3914,19 +3969,23 @@
         <v>19</v>
       </c>
       <c r="Z16" s="9"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="7"/>
+      <c r="AA16" s="8">
+        <v>773</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>7913642.8571413998</v>
+      </c>
       <c r="AC16" s="27">
         <f t="shared" si="5"/>
-        <v>-809</v>
+        <v>-36</v>
       </c>
       <c r="AD16" s="28">
         <f t="shared" si="5"/>
-        <v>-11019424.28571298</v>
+        <v>-3105781.42857158</v>
       </c>
       <c r="AE16" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.2818460699982594</v>
       </c>
       <c r="AG16" s="9" t="s">
         <v>19</v>
@@ -3936,15 +3995,15 @@
       <c r="AJ16" s="8"/>
       <c r="AK16" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-773</v>
       </c>
       <c r="AL16" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="29" t="e">
+        <v>-7913642.8571413998</v>
+      </c>
+      <c r="AM16" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO16" s="9" t="s">
         <v>19</v>
@@ -4155,10 +4214,13 @@
       <c r="Z17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA17" s="1">
+        <v>3858</v>
+      </c>
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>-3855</v>
+        <v>3</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -4177,7 +4239,7 @@
       <c r="AI17" s="32"/>
       <c r="AK17" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3858</v>
       </c>
       <c r="AL17" s="12">
         <f t="shared" si="7"/>
@@ -4632,18 +4694,23 @@
       <c r="Z19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AB19" s="12"/>
+      <c r="AA19" s="10">
+        <v>146</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>152445.71428508</v>
+      </c>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>-142</v>
+        <v>4</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>-156208.57142790995</v>
+        <v>-3762.8571428299474</v>
       </c>
       <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-2.4088672653705824E-2</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4652,15 +4719,15 @@
       <c r="AI19" s="13"/>
       <c r="AK19" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-146</v>
       </c>
       <c r="AL19" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="11" t="e">
+        <v>-152445.71428508</v>
+      </c>
+      <c r="AM19" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO19" s="14"/>
       <c r="AP19" s="13" t="s">
@@ -4860,18 +4927,23 @@
       <c r="Z20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB20" s="12"/>
+      <c r="AA20" s="10">
+        <v>173</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>205209.52380940001</v>
+      </c>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>-173</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>-251306.66666651997</v>
+        <v>-46097.142857119965</v>
       </c>
       <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.18342984477323937</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -4880,15 +4952,15 @@
       <c r="AI20" s="13"/>
       <c r="AK20" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-173</v>
       </c>
       <c r="AL20" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM20" s="11" t="e">
+        <v>-205209.52380940001</v>
+      </c>
+      <c r="AM20" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO20" s="14"/>
       <c r="AP20" s="13" t="s">
@@ -5088,18 +5160,23 @@
       <c r="Z21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="12"/>
+      <c r="AA21" s="10">
+        <v>46</v>
+      </c>
+      <c r="AB21" s="12">
+        <v>269276.19047617004</v>
+      </c>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>-42</v>
+        <v>4</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>-252552.38095237</v>
+        <v>16723.809523800039</v>
       </c>
       <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>6.6219171883214425E-2</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5108,15 +5185,15 @@
       <c r="AI21" s="13"/>
       <c r="AK21" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="AL21" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="11" t="e">
+        <v>-269276.19047617004</v>
+      </c>
+      <c r="AM21" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO21" s="14"/>
       <c r="AP21" s="13" t="s">
@@ -5316,18 +5393,23 @@
       <c r="Z22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB22" s="12"/>
+      <c r="AA22" s="10">
+        <v>39</v>
+      </c>
+      <c r="AB22" s="12">
+        <v>479142.85714278999</v>
+      </c>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>-24</v>
+        <v>15</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>-322095.23809518002</v>
+        <v>157047.61904760997</v>
       </c>
       <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.48758131283270317</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5336,15 +5418,15 @@
       <c r="AI22" s="13"/>
       <c r="AK22" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="AL22" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="11" t="e">
+        <v>-479142.85714278999</v>
+      </c>
+      <c r="AM22" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO22" s="14"/>
       <c r="AP22" s="13" t="s">
@@ -5762,18 +5844,23 @@
       <c r="Z24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB24" s="12"/>
+      <c r="AA24" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB24" s="12">
+        <v>59080</v>
+      </c>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>-59490</v>
+        <v>-410</v>
       </c>
       <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-6.8919146074970586E-3</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5782,15 +5869,15 @@
       <c r="AI24" s="13"/>
       <c r="AK24" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL24" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM24" s="11" t="e">
+        <v>-59080</v>
+      </c>
+      <c r="AM24" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO24" s="14"/>
       <c r="AP24" s="13" t="s">
@@ -5990,18 +6077,23 @@
       <c r="Z25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB25" s="12"/>
+      <c r="AA25" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB25" s="12">
+        <v>974552.38095230004</v>
+      </c>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>21</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>-224290.47619046</v>
+        <v>750261.90476184001</v>
       </c>
       <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>3.3450457527440558</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6010,15 +6102,15 @@
       <c r="AI25" s="13"/>
       <c r="AK25" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AL25" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM25" s="11" t="e">
+        <v>-974552.38095230004</v>
+      </c>
+      <c r="AM25" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO25" s="14"/>
       <c r="AP25" s="13" t="s">
@@ -6218,18 +6310,23 @@
       <c r="Z26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB26" s="12"/>
+      <c r="AA26" s="10">
+        <v>22</v>
+      </c>
+      <c r="AB26" s="12">
+        <v>385999.99999995006</v>
+      </c>
       <c r="AC26" s="10">
         <f t="shared" si="5"/>
-        <v>-30</v>
+        <v>-8</v>
       </c>
       <c r="AD26" s="12">
         <f t="shared" si="5"/>
-        <v>-579999.99999992014</v>
+        <v>-193999.99999997008</v>
       </c>
       <c r="AE26" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.33448275862068411</v>
       </c>
       <c r="AG26" s="14"/>
       <c r="AH26" s="13" t="s">
@@ -6238,15 +6335,15 @@
       <c r="AI26" s="13"/>
       <c r="AK26" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AL26" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM26" s="11" t="e">
+        <v>-385999.99999995006</v>
+      </c>
+      <c r="AM26" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO26" s="14"/>
       <c r="AP26" s="13" t="s">
@@ -6446,18 +6543,23 @@
       <c r="Z27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB27" s="12"/>
+      <c r="AA27" s="10">
+        <v>72</v>
+      </c>
+      <c r="AB27" s="12">
+        <v>2358857.1428570701</v>
+      </c>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>-83</v>
+        <v>-11</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
-        <v>-3150190.4761903705</v>
+        <v>-791333.33333330043</v>
       </c>
       <c r="AE27" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.25120174139129708</v>
       </c>
       <c r="AG27" s="14"/>
       <c r="AH27" s="13" t="s">
@@ -6466,15 +6568,15 @@
       <c r="AI27" s="13"/>
       <c r="AK27" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="AL27" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM27" s="11" t="e">
+        <v>-2358857.1428570701</v>
+      </c>
+      <c r="AM27" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO27" s="14"/>
       <c r="AP27" s="13" t="s">
@@ -6675,19 +6777,23 @@
         <v>13</v>
       </c>
       <c r="Z28" s="9"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="7"/>
+      <c r="AA28" s="8">
+        <v>535</v>
+      </c>
+      <c r="AB28" s="7">
+        <v>4884563.809522761</v>
+      </c>
       <c r="AC28" s="27">
         <f t="shared" si="5"/>
-        <v>-510</v>
+        <v>25</v>
       </c>
       <c r="AD28" s="28">
         <f t="shared" si="5"/>
-        <v>-5004990.9523798702</v>
+        <v>-120427.1428571092</v>
       </c>
       <c r="AE28" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-2.4061410700422177E-2</v>
       </c>
       <c r="AG28" s="9" t="s">
         <v>13</v>
@@ -6697,15 +6803,15 @@
       <c r="AJ28" s="8"/>
       <c r="AK28" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-535</v>
       </c>
       <c r="AL28" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM28" s="29" t="e">
+        <v>-4884563.809522761</v>
+      </c>
+      <c r="AM28" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO28" s="9" t="s">
         <v>13</v>
@@ -6916,10 +7022,13 @@
       <c r="Z29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA29" s="1">
+        <v>2979</v>
+      </c>
       <c r="AB29" s="35"/>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>-2898</v>
+        <v>81</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
@@ -6938,7 +7047,7 @@
       <c r="AI29" s="32"/>
       <c r="AK29" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2979</v>
       </c>
       <c r="AL29" s="12">
         <f t="shared" si="7"/>
@@ -7393,18 +7502,23 @@
       <c r="Z31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AB31" s="12"/>
+      <c r="AA31" s="10">
+        <v>97</v>
+      </c>
+      <c r="AB31" s="12">
+        <v>92987.619047320011</v>
+      </c>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>-137</v>
+        <v>-40</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>-125499.04761861001</v>
+        <v>-32511.428571290002</v>
       </c>
       <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.25905717364558667</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7413,15 +7527,15 @@
       <c r="AI31" s="13"/>
       <c r="AK31" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="AL31" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM31" s="11" t="e">
+        <v>-92987.619047320011</v>
+      </c>
+      <c r="AM31" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO31" s="14"/>
       <c r="AP31" s="13" t="s">
@@ -7621,18 +7735,23 @@
       <c r="Z32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB32" s="12"/>
+      <c r="AA32" s="10">
+        <v>45</v>
+      </c>
+      <c r="AB32" s="12">
+        <v>37430.476190390007</v>
+      </c>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>-60</v>
+        <v>-15</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>-75809.523809429986</v>
+        <v>-38379.047619039979</v>
       </c>
       <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.50625628140756096</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7641,15 +7760,15 @@
       <c r="AI32" s="13"/>
       <c r="AK32" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="AL32" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM32" s="11" t="e">
+        <v>-37430.476190390007</v>
+      </c>
+      <c r="AM32" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO32" s="14"/>
       <c r="AP32" s="13" t="s">
@@ -7849,18 +7968,23 @@
       <c r="Z33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB33" s="12"/>
+      <c r="AA33" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB33" s="12">
+        <v>74076.190476179996</v>
+      </c>
       <c r="AC33" s="10">
         <f t="shared" si="5"/>
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="AD33" s="12">
         <f t="shared" si="5"/>
-        <v>-86152.380952370004</v>
+        <v>-12076.190476190008</v>
       </c>
       <c r="AE33" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.14017245191245986</v>
       </c>
       <c r="AG33" s="14"/>
       <c r="AH33" s="13" t="s">
@@ -7869,15 +7993,15 @@
       <c r="AI33" s="13"/>
       <c r="AK33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL33" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM33" s="11" t="e">
+        <v>-74076.190476179996</v>
+      </c>
+      <c r="AM33" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO33" s="14"/>
       <c r="AP33" s="13" t="s">
@@ -8077,18 +8201,23 @@
       <c r="Z34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB34" s="12"/>
+      <c r="AA34" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB34" s="12">
+        <v>142666.66666663002</v>
+      </c>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>-188476.19047615002</v>
+        <v>-45809.523809520004</v>
       </c>
       <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.24305204648815729</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8097,15 +8226,15 @@
       <c r="AI34" s="13"/>
       <c r="AK34" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL34" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM34" s="11" t="e">
+        <v>-142666.66666663002</v>
+      </c>
+      <c r="AM34" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO34" s="14"/>
       <c r="AP34" s="13" t="s">
@@ -8523,18 +8652,23 @@
       <c r="Z36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB36" s="12"/>
+      <c r="AA36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>2857.1428571400002</v>
+      </c>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>-10350</v>
+        <v>-7492.8571428599998</v>
       </c>
       <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.72394755003478262</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8543,15 +8677,15 @@
       <c r="AI36" s="13"/>
       <c r="AK36" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL36" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM36" s="11" t="e">
+        <v>-2857.1428571400002</v>
+      </c>
+      <c r="AM36" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO36" s="14"/>
       <c r="AP36" s="13" t="s">
@@ -8751,18 +8885,23 @@
       <c r="Z37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB37" s="12"/>
+      <c r="AA37" s="10">
+        <v>5</v>
+      </c>
+      <c r="AB37" s="12">
+        <v>19650</v>
+      </c>
       <c r="AC37" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AD37" s="12">
         <f t="shared" si="5"/>
-        <v>-47523.809523800002</v>
+        <v>-27873.809523800002</v>
       </c>
       <c r="AE37" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.58652304609210149</v>
       </c>
       <c r="AG37" s="14"/>
       <c r="AH37" s="13" t="s">
@@ -8771,15 +8910,15 @@
       <c r="AI37" s="13"/>
       <c r="AK37" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AL37" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM37" s="11" t="e">
+        <v>-19650</v>
+      </c>
+      <c r="AM37" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO37" s="14"/>
       <c r="AP37" s="13" t="s">
@@ -8979,18 +9118,23 @@
       <c r="Z38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB38" s="12"/>
+      <c r="AA38" s="10">
+        <v>11</v>
+      </c>
+      <c r="AB38" s="12">
+        <v>154952.38095235999</v>
+      </c>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
-        <v>-178666.66666662999</v>
+        <v>-23714.285714269994</v>
       </c>
       <c r="AE38" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.1327292110873593</v>
       </c>
       <c r="AG38" s="14"/>
       <c r="AH38" s="13" t="s">
@@ -8999,15 +9143,15 @@
       <c r="AI38" s="13"/>
       <c r="AK38" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AL38" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM38" s="11" t="e">
+        <v>-154952.38095235999</v>
+      </c>
+      <c r="AM38" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO38" s="14"/>
       <c r="AP38" s="13" t="s">
@@ -9207,18 +9351,23 @@
       <c r="Z39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB39" s="12"/>
+      <c r="AA39" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB39" s="12">
+        <v>236571.42857142002</v>
+      </c>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
-        <v>-561238.09523807</v>
+        <v>-324666.66666664998</v>
       </c>
       <c r="AE39" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.57848294586797522</v>
       </c>
       <c r="AG39" s="14"/>
       <c r="AH39" s="13" t="s">
@@ -9227,15 +9376,15 @@
       <c r="AI39" s="13"/>
       <c r="AK39" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL39" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM39" s="11" t="e">
+        <v>-236571.42857142002</v>
+      </c>
+      <c r="AM39" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO39" s="14"/>
       <c r="AP39" s="13" t="s">
@@ -9436,19 +9585,23 @@
         <v>12</v>
       </c>
       <c r="Z40" s="9"/>
-      <c r="AA40" s="8"/>
-      <c r="AB40" s="7"/>
+      <c r="AA40" s="8">
+        <v>189</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>761191.90476144012</v>
+      </c>
       <c r="AC40" s="27">
         <f t="shared" si="5"/>
-        <v>-259</v>
+        <v>-70</v>
       </c>
       <c r="AD40" s="28">
         <f t="shared" si="5"/>
-        <v>-1273715.7142850598</v>
+        <v>-512523.80952361971</v>
       </c>
       <c r="AE40" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.40238477375722786</v>
       </c>
       <c r="AG40" s="9" t="s">
         <v>12</v>
@@ -9458,15 +9611,15 @@
       <c r="AJ40" s="8"/>
       <c r="AK40" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-189</v>
       </c>
       <c r="AL40" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM40" s="29" t="e">
+        <v>-761191.90476144012</v>
+      </c>
+      <c r="AM40" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO40" s="9" t="s">
         <v>12</v>
@@ -9677,10 +9830,13 @@
       <c r="Z41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA41" s="1">
+        <v>1019</v>
+      </c>
       <c r="AB41" s="35"/>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>-1049</v>
+        <v>-30</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
@@ -9699,7 +9855,7 @@
       <c r="AI41" s="32"/>
       <c r="AK41" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1019</v>
       </c>
       <c r="AL41" s="12">
         <f t="shared" si="7"/>
@@ -10154,18 +10310,23 @@
       <c r="Z43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AB43" s="12"/>
+      <c r="AA43" s="10">
+        <v>72</v>
+      </c>
+      <c r="AB43" s="12">
+        <v>64970.47619015001</v>
+      </c>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>-110</v>
+        <v>-38</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>-109499.04761855995</v>
+        <v>-44528.571428409945</v>
       </c>
       <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.4066571572706757</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10174,15 +10335,15 @@
       <c r="AI43" s="13"/>
       <c r="AK43" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="AL43" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM43" s="11" t="e">
+        <v>-64970.47619015001</v>
+      </c>
+      <c r="AM43" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO43" s="14"/>
       <c r="AP43" s="13" t="s">
@@ -10382,18 +10543,23 @@
       <c r="Z44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB44" s="12"/>
+      <c r="AA44" s="10">
+        <v>83</v>
+      </c>
+      <c r="AB44" s="12">
+        <v>83323.809523720003</v>
+      </c>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>-60</v>
+        <v>23</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>-82553.333333219998</v>
+        <v>770.47619050000503</v>
       </c>
       <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>9.3330718384203679E-3</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10402,15 +10568,15 @@
       <c r="AI44" s="13"/>
       <c r="AK44" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="AL44" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM44" s="11" t="e">
+        <v>-83323.809523720003</v>
+      </c>
+      <c r="AM44" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO44" s="14"/>
       <c r="AP44" s="13" t="s">
@@ -10610,18 +10776,23 @@
       <c r="Z45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="12"/>
+      <c r="AA45" s="10">
+        <v>16</v>
+      </c>
+      <c r="AB45" s="12">
+        <v>100704.76190474999</v>
+      </c>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>7</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>-42771.428571419994</v>
+        <v>57933.333333329996</v>
       </c>
       <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>1.3544867512805321</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10630,15 +10801,15 @@
       <c r="AI45" s="13"/>
       <c r="AK45" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AL45" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM45" s="11" t="e">
+        <v>-100704.76190474999</v>
+      </c>
+      <c r="AM45" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO45" s="14"/>
       <c r="AP45" s="13" t="s">
@@ -10838,18 +11009,23 @@
       <c r="Z46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB46" s="12"/>
+      <c r="AA46" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB46" s="12">
+        <v>129333.33333331</v>
+      </c>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>-111333.33333329001</v>
+        <v>18000.000000019994</v>
       </c>
       <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.16167664670682932</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10858,15 +11034,15 @@
       <c r="AI46" s="13"/>
       <c r="AK46" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL46" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM46" s="11" t="e">
+        <v>-129333.33333331</v>
+      </c>
+      <c r="AM46" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO46" s="14"/>
       <c r="AP46" s="13" t="s">
@@ -11056,18 +11232,23 @@
       <c r="Z47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB47" s="12"/>
+      <c r="AA47" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="12">
+        <v>2857.1428571400002</v>
+      </c>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>-5714.2857142800003</v>
+        <v>-2857.1428571400002</v>
       </c>
       <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11076,15 +11257,15 @@
       <c r="AI47" s="13"/>
       <c r="AK47" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL47" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM47" s="11" t="e">
+        <v>-2857.1428571400002</v>
+      </c>
+      <c r="AM47" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO47" s="14"/>
       <c r="AP47" s="13" t="s">
@@ -11279,14 +11460,19 @@
       <c r="Z48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="12"/>
+      <c r="AA48" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="12">
+        <v>12990</v>
+      </c>
       <c r="AC48" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12990</v>
       </c>
       <c r="AE48" s="11" t="e">
         <f t="shared" si="6"/>
@@ -11299,15 +11485,15 @@
       <c r="AI48" s="13"/>
       <c r="AK48" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL48" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM48" s="11" t="e">
+        <v>-12990</v>
+      </c>
+      <c r="AM48" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO48" s="14"/>
       <c r="AP48" s="13" t="s">
@@ -11502,18 +11688,23 @@
       <c r="Z49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB49" s="12"/>
+      <c r="AA49" s="10">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="12">
+        <v>224006.66666664</v>
+      </c>
       <c r="AC49" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AD49" s="12">
         <f t="shared" si="5"/>
-        <v>-47523.809523800002</v>
+        <v>176482.85714283999</v>
       </c>
       <c r="AE49" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>3.7135671342689203</v>
       </c>
       <c r="AG49" s="14"/>
       <c r="AH49" s="13" t="s">
@@ -11522,15 +11713,15 @@
       <c r="AI49" s="13"/>
       <c r="AK49" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AL49" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM49" s="11" t="e">
+        <v>-224006.66666664</v>
+      </c>
+      <c r="AM49" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO49" s="14"/>
       <c r="AP49" s="13" t="s">
@@ -11730,18 +11921,23 @@
       <c r="Z50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB50" s="12"/>
+      <c r="AA50" s="10">
+        <v>15</v>
+      </c>
+      <c r="AB50" s="12">
+        <v>330909.52380948002</v>
+      </c>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>-19</v>
+        <v>-4</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>
-        <v>-335619.04761899996</v>
+        <v>-4709.5238095199456</v>
       </c>
       <c r="AE50" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-1.4032349602714657E-2</v>
       </c>
       <c r="AG50" s="14"/>
       <c r="AH50" s="13" t="s">
@@ -11750,15 +11946,15 @@
       <c r="AI50" s="13"/>
       <c r="AK50" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AL50" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM50" s="11" t="e">
+        <v>-330909.52380948002</v>
+      </c>
+      <c r="AM50" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO50" s="14"/>
       <c r="AP50" s="13" t="s">
@@ -11958,18 +12154,23 @@
       <c r="Z51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB51" s="12"/>
+      <c r="AA51" s="10">
+        <v>13</v>
+      </c>
+      <c r="AB51" s="12">
+        <v>396857.14285711991</v>
+      </c>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>-25</v>
+        <v>-12</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>-980476.1904761499</v>
+        <v>-583619.04761903</v>
       </c>
       <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.59524040796503819</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -11978,15 +12179,15 @@
       <c r="AI51" s="13"/>
       <c r="AK51" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL51" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM51" s="11" t="e">
+        <v>-396857.14285711991</v>
+      </c>
+      <c r="AM51" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO51" s="14"/>
       <c r="AP51" s="13" t="s">
@@ -12187,19 +12388,23 @@
         <v>11</v>
       </c>
       <c r="Z52" s="9"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="7"/>
+      <c r="AA52" s="8">
+        <v>218</v>
+      </c>
+      <c r="AB52" s="7">
+        <v>1345952.8571423099</v>
+      </c>
       <c r="AC52" s="27">
         <f t="shared" si="5"/>
-        <v>-237</v>
+        <v>-19</v>
       </c>
       <c r="AD52" s="28">
         <f t="shared" si="5"/>
-        <v>-1715490.47618972</v>
+        <v>-369537.61904741009</v>
       </c>
       <c r="AE52" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.21541222418686404</v>
       </c>
       <c r="AG52" s="9" t="s">
         <v>11</v>
@@ -12209,15 +12414,15 @@
       <c r="AJ52" s="8"/>
       <c r="AK52" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-218</v>
       </c>
       <c r="AL52" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM52" s="29" t="e">
+        <v>-1345952.8571423099</v>
+      </c>
+      <c r="AM52" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO52" s="9" t="s">
         <v>11</v>
@@ -12896,18 +13101,23 @@
       <c r="Z55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AB55" s="12"/>
+      <c r="AA55" s="10">
+        <v>82</v>
+      </c>
+      <c r="AB55" s="12">
+        <v>73125.714285359994</v>
+      </c>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>-92</v>
+        <v>-10</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>-87358.095237700007</v>
+        <v>-14232.380952340012</v>
       </c>
       <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.16292000087243119</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -12916,15 +13126,15 @@
       <c r="AI55" s="13"/>
       <c r="AK55" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="AL55" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM55" s="11" t="e">
+        <v>-73125.714285359994</v>
+      </c>
+      <c r="AM55" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO55" s="14"/>
       <c r="AP55" s="13" t="s">
@@ -13124,18 +13334,23 @@
       <c r="Z56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB56" s="12"/>
+      <c r="AA56" s="10">
+        <v>77</v>
+      </c>
+      <c r="AB56" s="12">
+        <v>79457.142857069994</v>
+      </c>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>-53</v>
+        <v>24</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>-56161.90476184</v>
+        <v>23295.238095229994</v>
       </c>
       <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.41478717992232828</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13144,15 +13359,15 @@
       <c r="AI56" s="13"/>
       <c r="AK56" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-77</v>
       </c>
       <c r="AL56" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM56" s="11" t="e">
+        <v>-79457.142857069994</v>
+      </c>
+      <c r="AM56" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO56" s="14"/>
       <c r="AP56" s="13" t="s">
@@ -13352,18 +13567,23 @@
       <c r="Z57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB57" s="12"/>
+      <c r="AA57" s="10">
+        <v>14</v>
+      </c>
+      <c r="AB57" s="12">
+        <v>86152.380952370004</v>
+      </c>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>-104409.52380952</v>
+        <v>-18257.14285715</v>
       </c>
       <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.17486089574029187</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13372,15 +13592,15 @@
       <c r="AI57" s="13"/>
       <c r="AK57" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AL57" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM57" s="11" t="e">
+        <v>-86152.380952370004</v>
+      </c>
+      <c r="AM57" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO57" s="14"/>
       <c r="AP57" s="13" t="s">
@@ -13580,18 +13800,23 @@
       <c r="Z58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB58" s="12"/>
+      <c r="AA58" s="10">
+        <v>8</v>
+      </c>
+      <c r="AB58" s="12">
+        <v>118285.71428567999</v>
+      </c>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>-115238.09523805999</v>
+        <v>3047.619047619999</v>
       </c>
       <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>2.6446280991751881E-2</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13600,15 +13825,15 @@
       <c r="AI58" s="13"/>
       <c r="AK58" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AL58" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM58" s="11" t="e">
+        <v>-118285.71428567999</v>
+      </c>
+      <c r="AM58" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO58" s="14"/>
       <c r="AP58" s="13" t="s">
@@ -14021,18 +14246,23 @@
       <c r="Z60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB60" s="12"/>
+      <c r="AA60" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB60" s="12">
+        <v>5880</v>
+      </c>
       <c r="AC60" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD60" s="12">
         <f t="shared" si="5"/>
-        <v>-22940</v>
+        <v>-17060</v>
       </c>
       <c r="AE60" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.74367916303400172</v>
       </c>
       <c r="AG60" s="14"/>
       <c r="AH60" s="13" t="s">
@@ -14041,15 +14271,15 @@
       <c r="AI60" s="13"/>
       <c r="AK60" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL60" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM60" s="11" t="e">
+        <v>-5880</v>
+      </c>
+      <c r="AM60" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO60" s="14"/>
       <c r="AP60" s="13" t="s">
@@ -14249,18 +14479,23 @@
       <c r="Z61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB61" s="12"/>
+      <c r="AA61" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB61" s="12">
+        <v>55999.999999990003</v>
+      </c>
       <c r="AC61" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD61" s="12">
         <f t="shared" si="5"/>
-        <v>-49671.428571420001</v>
+        <v>6328.5714285700014</v>
       </c>
       <c r="AE61" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.12740868564854085</v>
       </c>
       <c r="AG61" s="14"/>
       <c r="AH61" s="13" t="s">
@@ -14269,15 +14504,15 @@
       <c r="AI61" s="13"/>
       <c r="AK61" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL61" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM61" s="11" t="e">
+        <v>-55999.999999990003</v>
+      </c>
+      <c r="AM61" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO61" s="14"/>
       <c r="AP61" s="13" t="s">
@@ -14477,18 +14712,23 @@
       <c r="Z62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="12"/>
+      <c r="AA62" s="10">
+        <v>20</v>
+      </c>
+      <c r="AB62" s="12">
+        <v>321904.76190471998</v>
+      </c>
       <c r="AC62" s="10">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>13</v>
       </c>
       <c r="AD62" s="12">
         <f t="shared" si="5"/>
-        <v>-120761.90476188001</v>
+        <v>201142.85714283999</v>
       </c>
       <c r="AE62" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>1.6656151419560352</v>
       </c>
       <c r="AG62" s="14"/>
       <c r="AH62" s="13" t="s">
@@ -14497,15 +14737,15 @@
       <c r="AI62" s="13"/>
       <c r="AK62" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AL62" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM62" s="11" t="e">
+        <v>-321904.76190471998</v>
+      </c>
+      <c r="AM62" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO62" s="14"/>
       <c r="AP62" s="13" t="s">
@@ -14705,18 +14945,23 @@
       <c r="Z63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB63" s="12"/>
+      <c r="AA63" s="10">
+        <v>23</v>
+      </c>
+      <c r="AB63" s="12">
+        <v>858761.90476186003</v>
+      </c>
       <c r="AC63" s="10">
         <f t="shared" si="5"/>
-        <v>-13</v>
+        <v>10</v>
       </c>
       <c r="AD63" s="12">
         <f t="shared" si="5"/>
-        <v>-479812.38095233997</v>
+        <v>378949.52380952006</v>
       </c>
       <c r="AE63" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.78978688098330108</v>
       </c>
       <c r="AG63" s="14"/>
       <c r="AH63" s="13" t="s">
@@ -14725,15 +14970,15 @@
       <c r="AI63" s="13"/>
       <c r="AK63" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AL63" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM63" s="11" t="e">
+        <v>-858761.90476186003</v>
+      </c>
+      <c r="AM63" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO63" s="14"/>
       <c r="AP63" s="13" t="s">
@@ -14934,19 +15179,23 @@
         <v>1</v>
       </c>
       <c r="Z64" s="9"/>
-      <c r="AA64" s="8"/>
-      <c r="AB64" s="7"/>
+      <c r="AA64" s="8">
+        <v>228</v>
+      </c>
+      <c r="AB64" s="7">
+        <v>1599567.6190470499</v>
+      </c>
       <c r="AC64" s="27">
         <f t="shared" si="5"/>
-        <v>-199</v>
+        <v>29</v>
       </c>
       <c r="AD64" s="28">
         <f t="shared" si="5"/>
-        <v>-1036353.33333276</v>
+        <v>563214.28571428987</v>
       </c>
       <c r="AE64" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.54345778374936615</v>
       </c>
       <c r="AG64" s="9" t="s">
         <v>1</v>
@@ -14956,15 +15205,15 @@
       <c r="AJ64" s="8"/>
       <c r="AK64" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-228</v>
       </c>
       <c r="AL64" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM64" s="29" t="e">
+        <v>-1599567.6190470499</v>
+      </c>
+      <c r="AM64" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO64" s="9" t="s">
         <v>1</v>
@@ -15173,19 +15422,23 @@
         <v>0</v>
       </c>
       <c r="Z65" s="4"/>
-      <c r="AA65" s="3"/>
-      <c r="AB65" s="2"/>
+      <c r="AA65" s="3">
+        <v>1943</v>
+      </c>
+      <c r="AB65" s="2">
+        <v>16504919.047614958</v>
+      </c>
       <c r="AC65" s="6">
         <f t="shared" si="5"/>
-        <v>-2014</v>
+        <v>-71</v>
       </c>
       <c r="AD65" s="5">
         <f t="shared" si="5"/>
-        <v>-20049974.761900391</v>
+        <v>-3545055.7142854333</v>
       </c>
       <c r="AE65" s="30">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.17681098137948095</v>
       </c>
       <c r="AG65" s="4" t="s">
         <v>0</v>
@@ -15195,15 +15448,15 @@
       <c r="AJ65" s="3"/>
       <c r="AK65" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1943</v>
       </c>
       <c r="AL65" s="5">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM65" s="30" t="e">
+        <v>-16504919.047614958</v>
+      </c>
+      <c r="AM65" s="30">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A3314-C4D3-8D40-90EC-91DA934FEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5417B6DA-ED52-1D44-B895-E29C08ECE9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14000" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1648,10 +1648,13 @@
       <c r="Z6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AA6" s="15">
+        <v>5</v>
+      </c>
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -1668,7 +1671,7 @@
       <c r="AI6" s="32"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="7"/>
@@ -4462,10 +4465,13 @@
       <c r="Z18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AA18" s="1">
+        <v>9</v>
+      </c>
       <c r="AB18" s="35"/>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
@@ -4482,7 +4488,7 @@
       <c r="AI18" s="32"/>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AL18" s="12">
         <f t="shared" si="7"/>
@@ -7270,10 +7276,13 @@
       <c r="Z30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AA30" s="1">
+        <v>1</v>
+      </c>
       <c r="AB30" s="35"/>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
@@ -7290,7 +7299,7 @@
       <c r="AI30" s="32"/>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL30" s="12">
         <f t="shared" si="7"/>
@@ -10078,10 +10087,13 @@
       <c r="Z42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AA42" s="1">
+        <v>1</v>
+      </c>
       <c r="AB42" s="35"/>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
@@ -10098,7 +10110,7 @@
       <c r="AI42" s="32"/>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL42" s="12">
         <f t="shared" si="7"/>
@@ -12869,10 +12881,13 @@
       <c r="Z54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AA54" s="1">
+        <v>4</v>
+      </c>
       <c r="AB54" s="35"/>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
@@ -12889,7 +12904,7 @@
       <c r="AI54" s="32"/>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AL54" s="12">
         <f t="shared" si="7"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5417B6DA-ED52-1D44-B895-E29C08ECE9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557A328E-D1D5-9648-AFDD-2BFE4F50F625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14000" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="11720" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="32">
   <si>
     <t>總計</t>
   </si>
@@ -176,6 +176,14 @@
   </si>
   <si>
     <t>04/19~04/25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04/26~0502</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -377,7 +385,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -499,6 +507,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -943,7 +981,7 @@
     <col min="32" max="32" width="5" customWidth="1"/>
     <col min="33" max="33" width="11" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.1640625" style="50" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="11" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13.5" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="11" bestFit="1" customWidth="1"/>
@@ -997,9 +1035,11 @@
       </c>
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
-      <c r="AG1" s="26"/>
+      <c r="AG1" s="26" t="s">
+        <v>31</v>
+      </c>
       <c r="AH1" s="26"/>
-      <c r="AJ1" s="25"/>
+      <c r="AJ1" s="41"/>
       <c r="AO1" s="26"/>
       <c r="AP1" s="26"/>
       <c r="AR1" s="25"/>
@@ -1046,6 +1086,10 @@
       </c>
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
+      <c r="AG2" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ2" s="42"/>
       <c r="AK2" s="22"/>
       <c r="AL2" s="22"/>
       <c r="AN2" s="21"/>
@@ -1091,6 +1135,7 @@
       <c r="Y3" s="31"/>
       <c r="AB3" s="31"/>
       <c r="AG3" s="31"/>
+      <c r="AJ3" s="42"/>
     </row>
     <row r="4" spans="1:103" s="15" customFormat="1" ht="22" customHeight="1">
       <c r="A4" s="19" t="s">
@@ -1172,7 +1217,7 @@
         <v>17</v>
       </c>
       <c r="AI4" s="18"/>
-      <c r="AJ4" s="17"/>
+      <c r="AJ4" s="43"/>
       <c r="AK4" s="16" t="s">
         <v>14</v>
       </c>
@@ -1409,11 +1454,13 @@
       <c r="AH5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI5" s="32"/>
-      <c r="AJ5" s="40"/>
+      <c r="AI5" s="32">
+        <v>7979</v>
+      </c>
+      <c r="AJ5" s="44"/>
       <c r="AK5" s="10">
         <f t="shared" ref="AK5:AL65" si="7">AI5-AA5</f>
-        <v>-5617</v>
+        <v>2362</v>
       </c>
       <c r="AL5" s="12">
         <f t="shared" si="7"/>
@@ -1434,7 +1481,7 @@
       <c r="AR5" s="1"/>
       <c r="AS5" s="10">
         <f t="shared" ref="AS5:AT65" si="9">AQ5-AI5</f>
-        <v>0</v>
+        <v>-7979</v>
       </c>
       <c r="AT5" s="12">
         <f t="shared" si="9"/>
@@ -1669,6 +1716,7 @@
         <v>21</v>
       </c>
       <c r="AI6" s="32"/>
+      <c r="AJ6" s="45"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
         <v>-5</v>
@@ -1901,18 +1949,23 @@
       <c r="AH7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI7" s="13"/>
+      <c r="AI7" s="13">
+        <v>228</v>
+      </c>
+      <c r="AJ7" s="46">
+        <v>274511.42857061001</v>
+      </c>
       <c r="AK7" s="10">
         <f t="shared" si="7"/>
-        <v>-194</v>
+        <v>34</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="7"/>
-        <v>-201242.85714209004</v>
+        <v>73268.571428519965</v>
       </c>
       <c r="AM7" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.36408035777780562</v>
       </c>
       <c r="AO7" s="14"/>
       <c r="AP7" s="13" t="s">
@@ -1921,15 +1974,15 @@
       <c r="AR7" s="12"/>
       <c r="AS7" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-228</v>
       </c>
       <c r="AT7" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU7" s="11" t="e">
+        <v>-274511.42857061001</v>
+      </c>
+      <c r="AU7" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW7" s="14"/>
       <c r="AX7" s="13" t="s">
@@ -2134,18 +2187,23 @@
       <c r="AH8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI8" s="13"/>
+      <c r="AI8" s="13">
+        <v>286</v>
+      </c>
+      <c r="AJ8" s="46">
+        <v>419689.52380937996</v>
+      </c>
       <c r="AK8" s="10">
         <f t="shared" si="7"/>
-        <v>-251</v>
+        <v>35</v>
       </c>
       <c r="AL8" s="12">
         <f t="shared" si="7"/>
-        <v>-475849.52380930987</v>
+        <v>-56159.999999929918</v>
       </c>
       <c r="AM8" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.1180205026798246</v>
       </c>
       <c r="AO8" s="14"/>
       <c r="AP8" s="13" t="s">
@@ -2154,15 +2212,15 @@
       <c r="AR8" s="12"/>
       <c r="AS8" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-286</v>
       </c>
       <c r="AT8" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU8" s="11" t="e">
+        <v>-419689.52380937996</v>
+      </c>
+      <c r="AU8" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW8" s="14"/>
       <c r="AX8" s="13" t="s">
@@ -2367,18 +2425,23 @@
       <c r="AH9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI9" s="13"/>
+      <c r="AI9" s="13">
+        <v>83</v>
+      </c>
+      <c r="AJ9" s="46">
+        <v>529685.7142857</v>
+      </c>
       <c r="AK9" s="10">
         <f t="shared" si="7"/>
-        <v>-69</v>
+        <v>14</v>
       </c>
       <c r="AL9" s="12">
         <f t="shared" si="7"/>
-        <v>-426009.52380950004</v>
+        <v>103676.19047619996</v>
       </c>
       <c r="AM9" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.2433658983702936</v>
       </c>
       <c r="AO9" s="14"/>
       <c r="AP9" s="13" t="s">
@@ -2387,15 +2450,15 @@
       <c r="AR9" s="12"/>
       <c r="AS9" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="AT9" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU9" s="11" t="e">
+        <v>-529685.7142857</v>
+      </c>
+      <c r="AU9" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW9" s="14"/>
       <c r="AX9" s="13" t="s">
@@ -2600,18 +2663,23 @@
       <c r="AH10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI10" s="13"/>
+      <c r="AI10" s="13">
+        <v>53</v>
+      </c>
+      <c r="AJ10" s="46">
+        <v>707333.33333325002</v>
+      </c>
       <c r="AK10" s="10">
         <f t="shared" si="7"/>
-        <v>-58</v>
+        <v>-5</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="7"/>
-        <v>-787523.80952371005</v>
+        <v>-80190.476190460031</v>
       </c>
       <c r="AM10" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.10182609747247995</v>
       </c>
       <c r="AO10" s="14"/>
       <c r="AP10" s="13" t="s">
@@ -2620,15 +2688,15 @@
       <c r="AR10" s="12"/>
       <c r="AS10" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="AT10" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU10" s="11" t="e">
+        <v>-707333.33333325002</v>
+      </c>
+      <c r="AU10" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW10" s="14"/>
       <c r="AX10" s="13" t="s">
@@ -2828,14 +2896,19 @@
       <c r="AH11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI11" s="13"/>
+      <c r="AI11" s="13">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="46">
+        <v>11514.285714279999</v>
+      </c>
       <c r="AK11" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11514.285714279999</v>
       </c>
       <c r="AM11" s="11" t="e">
         <f t="shared" si="8"/>
@@ -2848,15 +2921,15 @@
       <c r="AR11" s="12"/>
       <c r="AS11" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT11" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="11" t="e">
+        <v>-11514.285714279999</v>
+      </c>
+      <c r="AU11" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW11" s="14"/>
       <c r="AX11" s="13" t="s">
@@ -3061,18 +3134,23 @@
       <c r="AH12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI12" s="13"/>
+      <c r="AI12" s="13">
+        <v>29</v>
+      </c>
+      <c r="AJ12" s="46">
+        <v>148110</v>
+      </c>
       <c r="AK12" s="10">
         <f t="shared" si="7"/>
-        <v>-4</v>
+        <v>25</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="7"/>
-        <v>-26860</v>
+        <v>121250</v>
       </c>
       <c r="AM12" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>4.5141474311243481</v>
       </c>
       <c r="AO12" s="14"/>
       <c r="AP12" s="13" t="s">
@@ -3081,15 +3159,15 @@
       <c r="AR12" s="12"/>
       <c r="AS12" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="AT12" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU12" s="11" t="e">
+        <v>-148110</v>
+      </c>
+      <c r="AU12" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW12" s="14"/>
       <c r="AX12" s="13" t="s">
@@ -3294,18 +3372,23 @@
       <c r="AH13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI13" s="13"/>
+      <c r="AI13" s="13">
+        <v>55</v>
+      </c>
+      <c r="AJ13" s="46">
+        <v>2281052.3809522097</v>
+      </c>
       <c r="AK13" s="10">
         <f t="shared" si="7"/>
-        <v>-44</v>
+        <v>11</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="7"/>
-        <v>-1773776.1904760499</v>
+        <v>507276.1904761598</v>
       </c>
       <c r="AM13" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.28598658229819623</v>
       </c>
       <c r="AO13" s="14"/>
       <c r="AP13" s="13" t="s">
@@ -3314,15 +3397,15 @@
       <c r="AR13" s="12"/>
       <c r="AS13" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AT13" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU13" s="11" t="e">
+        <v>-2281052.3809522097</v>
+      </c>
+      <c r="AU13" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW13" s="14"/>
       <c r="AX13" s="13" t="s">
@@ -3527,18 +3610,23 @@
       <c r="AH14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI14" s="13"/>
+      <c r="AI14" s="13">
+        <v>120</v>
+      </c>
+      <c r="AJ14" s="46">
+        <v>2500095.23809504</v>
+      </c>
       <c r="AK14" s="10">
         <f t="shared" si="7"/>
-        <v>-72</v>
+        <v>48</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="7"/>
-        <v>-1379619.0476189305</v>
+        <v>1120476.1904761095</v>
       </c>
       <c r="AM14" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.81216346817618035</v>
       </c>
       <c r="AO14" s="14"/>
       <c r="AP14" s="13" t="s">
@@ -3547,15 +3635,15 @@
       <c r="AR14" s="12"/>
       <c r="AS14" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="AT14" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU14" s="11" t="e">
+        <v>-2500095.23809504</v>
+      </c>
+      <c r="AU14" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW14" s="14"/>
       <c r="AX14" s="13" t="s">
@@ -3760,18 +3848,23 @@
       <c r="AH15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="13"/>
+      <c r="AI15" s="13">
+        <v>99</v>
+      </c>
+      <c r="AJ15" s="46">
+        <v>3540095.2380951596</v>
+      </c>
       <c r="AK15" s="10">
         <f t="shared" si="7"/>
-        <v>-81</v>
+        <v>18</v>
       </c>
       <c r="AL15" s="12">
         <f t="shared" si="7"/>
-        <v>-2842761.9047618099</v>
+        <v>697333.33333334979</v>
       </c>
       <c r="AM15" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.24530135012899651</v>
       </c>
       <c r="AO15" s="14"/>
       <c r="AP15" s="13" t="s">
@@ -3780,15 +3873,15 @@
       <c r="AR15" s="12"/>
       <c r="AS15" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="AT15" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU15" s="11" t="e">
+        <v>-3540095.2380951596</v>
+      </c>
+      <c r="AU15" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW15" s="14"/>
       <c r="AX15" s="13" t="s">
@@ -3994,19 +4087,23 @@
         <v>19</v>
       </c>
       <c r="AH16" s="9"/>
-      <c r="AI16" s="9"/>
-      <c r="AJ16" s="8"/>
+      <c r="AI16" s="9">
+        <v>955</v>
+      </c>
+      <c r="AJ16" s="47">
+        <v>10412087.142855629</v>
+      </c>
       <c r="AK16" s="27">
         <f t="shared" si="7"/>
-        <v>-773</v>
+        <v>182</v>
       </c>
       <c r="AL16" s="28">
         <f t="shared" si="7"/>
-        <v>-7913642.8571413998</v>
+        <v>2498444.2857142296</v>
       </c>
       <c r="AM16" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.31571355073973206</v>
       </c>
       <c r="AO16" s="9" t="s">
         <v>19</v>
@@ -4016,15 +4113,15 @@
       <c r="AR16" s="7"/>
       <c r="AS16" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-955</v>
       </c>
       <c r="AT16" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU16" s="29" t="e">
+        <v>-10412087.142855629</v>
+      </c>
+      <c r="AU16" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW16" s="9" t="s">
         <v>19</v>
@@ -4239,10 +4336,13 @@
       <c r="AH17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI17" s="32"/>
+      <c r="AI17" s="32">
+        <v>5198</v>
+      </c>
+      <c r="AJ17" s="48"/>
       <c r="AK17" s="10">
         <f t="shared" si="7"/>
-        <v>-3858</v>
+        <v>1340</v>
       </c>
       <c r="AL17" s="12">
         <f t="shared" si="7"/>
@@ -4261,7 +4361,7 @@
       <c r="AR17" s="35"/>
       <c r="AS17" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5198</v>
       </c>
       <c r="AT17" s="12">
         <f t="shared" si="9"/>
@@ -4486,6 +4586,7 @@
         <v>21</v>
       </c>
       <c r="AI18" s="32"/>
+      <c r="AJ18" s="48"/>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
         <v>-9</v>
@@ -4722,18 +4823,23 @@
       <c r="AH19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI19" s="13"/>
+      <c r="AI19" s="13">
+        <v>148</v>
+      </c>
+      <c r="AJ19" s="46">
+        <v>168661.90476126003</v>
+      </c>
       <c r="AK19" s="10">
         <f t="shared" si="7"/>
-        <v>-146</v>
+        <v>2</v>
       </c>
       <c r="AL19" s="12">
         <f t="shared" si="7"/>
-        <v>-152445.71428508</v>
+        <v>16216.190476180025</v>
       </c>
       <c r="AM19" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.10637354124534493</v>
       </c>
       <c r="AO19" s="14"/>
       <c r="AP19" s="13" t="s">
@@ -4742,15 +4848,15 @@
       <c r="AR19" s="12"/>
       <c r="AS19" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-148</v>
       </c>
       <c r="AT19" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU19" s="11" t="e">
+        <v>-168661.90476126003</v>
+      </c>
+      <c r="AU19" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW19" s="14"/>
       <c r="AX19" s="13" t="s">
@@ -4955,18 +5061,23 @@
       <c r="AH20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI20" s="13"/>
+      <c r="AI20" s="13">
+        <v>200</v>
+      </c>
+      <c r="AJ20" s="46">
+        <v>196704.76190463002</v>
+      </c>
       <c r="AK20" s="10">
         <f t="shared" si="7"/>
-        <v>-173</v>
+        <v>27</v>
       </c>
       <c r="AL20" s="12">
         <f t="shared" si="7"/>
-        <v>-205209.52380940001</v>
+        <v>-8504.7619047699845</v>
       </c>
       <c r="AM20" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-4.1444284587245889E-2</v>
       </c>
       <c r="AO20" s="14"/>
       <c r="AP20" s="13" t="s">
@@ -4975,15 +5086,15 @@
       <c r="AR20" s="12"/>
       <c r="AS20" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AT20" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU20" s="11" t="e">
+        <v>-196704.76190463002</v>
+      </c>
+      <c r="AU20" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW20" s="14"/>
       <c r="AX20" s="13" t="s">
@@ -5188,18 +5299,23 @@
       <c r="AH21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI21" s="13"/>
+      <c r="AI21" s="13">
+        <v>36</v>
+      </c>
+      <c r="AJ21" s="46">
+        <v>229657.14285712998</v>
+      </c>
       <c r="AK21" s="10">
         <f t="shared" si="7"/>
-        <v>-46</v>
+        <v>-10</v>
       </c>
       <c r="AL21" s="12">
         <f t="shared" si="7"/>
-        <v>-269276.19047617004</v>
+        <v>-39619.047619040066</v>
       </c>
       <c r="AM21" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.14713164037630058</v>
       </c>
       <c r="AO21" s="14"/>
       <c r="AP21" s="13" t="s">
@@ -5208,15 +5324,15 @@
       <c r="AR21" s="12"/>
       <c r="AS21" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="AT21" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU21" s="11" t="e">
+        <v>-229657.14285712998</v>
+      </c>
+      <c r="AU21" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW21" s="14"/>
       <c r="AX21" s="13" t="s">
@@ -5421,18 +5537,23 @@
       <c r="AH22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI22" s="13"/>
+      <c r="AI22" s="13">
+        <v>39</v>
+      </c>
+      <c r="AJ22" s="46">
+        <v>498761.90476185002</v>
+      </c>
       <c r="AK22" s="10">
         <f t="shared" si="7"/>
-        <v>-39</v>
+        <v>0</v>
       </c>
       <c r="AL22" s="12">
         <f t="shared" si="7"/>
-        <v>-479142.85714278999</v>
+        <v>19619.047619060031</v>
       </c>
       <c r="AM22" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>4.0946133969421428E-2</v>
       </c>
       <c r="AO22" s="14"/>
       <c r="AP22" s="13" t="s">
@@ -5441,15 +5562,15 @@
       <c r="AR22" s="12"/>
       <c r="AS22" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="AT22" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU22" s="11" t="e">
+        <v>-498761.90476185002</v>
+      </c>
+      <c r="AU22" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW22" s="14"/>
       <c r="AX22" s="13" t="s">
@@ -5640,6 +5761,7 @@
         <v>6</v>
       </c>
       <c r="AI23" s="13"/>
+      <c r="AJ23" s="46"/>
       <c r="AK23" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5872,18 +5994,23 @@
       <c r="AH24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI24" s="13"/>
+      <c r="AI24" s="13">
+        <v>21</v>
+      </c>
+      <c r="AJ24" s="46">
+        <v>121490</v>
+      </c>
       <c r="AK24" s="10">
         <f t="shared" si="7"/>
-        <v>-12</v>
+        <v>9</v>
       </c>
       <c r="AL24" s="12">
         <f t="shared" si="7"/>
-        <v>-59080</v>
+        <v>62410</v>
       </c>
       <c r="AM24" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.0563642518618821</v>
       </c>
       <c r="AO24" s="14"/>
       <c r="AP24" s="13" t="s">
@@ -5892,15 +6019,15 @@
       <c r="AR24" s="12"/>
       <c r="AS24" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="AT24" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU24" s="11" t="e">
+        <v>-121490</v>
+      </c>
+      <c r="AU24" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW24" s="14"/>
       <c r="AX24" s="13" t="s">
@@ -6105,18 +6232,23 @@
       <c r="AH25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI25" s="13"/>
+      <c r="AI25" s="13">
+        <v>33</v>
+      </c>
+      <c r="AJ25" s="46">
+        <v>1195909.5238094102</v>
+      </c>
       <c r="AK25" s="10">
         <f t="shared" si="7"/>
-        <v>-25</v>
+        <v>8</v>
       </c>
       <c r="AL25" s="12">
         <f t="shared" si="7"/>
-        <v>-974552.38095230004</v>
+        <v>221357.14285711013</v>
       </c>
       <c r="AM25" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.22713724493783219</v>
       </c>
       <c r="AO25" s="14"/>
       <c r="AP25" s="13" t="s">
@@ -6125,15 +6257,15 @@
       <c r="AR25" s="12"/>
       <c r="AS25" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="AT25" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU25" s="11" t="e">
+        <v>-1195909.5238094102</v>
+      </c>
+      <c r="AU25" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW25" s="14"/>
       <c r="AX25" s="13" t="s">
@@ -6338,18 +6470,23 @@
       <c r="AH26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI26" s="13"/>
+      <c r="AI26" s="13">
+        <v>40</v>
+      </c>
+      <c r="AJ26" s="46">
+        <v>843333.33333324024</v>
+      </c>
       <c r="AK26" s="10">
         <f t="shared" si="7"/>
-        <v>-22</v>
+        <v>18</v>
       </c>
       <c r="AL26" s="12">
         <f t="shared" si="7"/>
-        <v>-385999.99999995006</v>
+        <v>457333.33333329018</v>
       </c>
       <c r="AM26" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.1848013816926148</v>
       </c>
       <c r="AO26" s="14"/>
       <c r="AP26" s="13" t="s">
@@ -6358,15 +6495,15 @@
       <c r="AR26" s="12"/>
       <c r="AS26" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AT26" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU26" s="11" t="e">
+        <v>-843333.33333324024</v>
+      </c>
+      <c r="AU26" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW26" s="14"/>
       <c r="AX26" s="13" t="s">
@@ -6571,18 +6708,23 @@
       <c r="AH27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI27" s="13"/>
+      <c r="AI27" s="13">
+        <v>48</v>
+      </c>
+      <c r="AJ27" s="46">
+        <v>1537333.3333332799</v>
+      </c>
       <c r="AK27" s="10">
         <f t="shared" si="7"/>
-        <v>-72</v>
+        <v>-24</v>
       </c>
       <c r="AL27" s="12">
         <f t="shared" si="7"/>
-        <v>-2358857.1428570701</v>
+        <v>-821523.80952379014</v>
       </c>
       <c r="AM27" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.34827196382429193</v>
       </c>
       <c r="AO27" s="14"/>
       <c r="AP27" s="13" t="s">
@@ -6591,15 +6733,15 @@
       <c r="AR27" s="12"/>
       <c r="AS27" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="AT27" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU27" s="11" t="e">
+        <v>-1537333.3333332799</v>
+      </c>
+      <c r="AU27" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW27" s="14"/>
       <c r="AX27" s="13" t="s">
@@ -6805,19 +6947,23 @@
         <v>13</v>
       </c>
       <c r="AH28" s="9"/>
-      <c r="AI28" s="9"/>
-      <c r="AJ28" s="8"/>
+      <c r="AI28" s="9">
+        <v>565</v>
+      </c>
+      <c r="AJ28" s="47">
+        <v>4791851.9047608003</v>
+      </c>
       <c r="AK28" s="27">
         <f t="shared" si="7"/>
-        <v>-535</v>
+        <v>30</v>
       </c>
       <c r="AL28" s="28">
         <f t="shared" si="7"/>
-        <v>-4884563.809522761</v>
+        <v>-92711.90476196073</v>
       </c>
       <c r="AM28" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-1.8980590361254591E-2</v>
       </c>
       <c r="AO28" s="9" t="s">
         <v>13</v>
@@ -6827,15 +6973,15 @@
       <c r="AR28" s="7"/>
       <c r="AS28" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-565</v>
       </c>
       <c r="AT28" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU28" s="29" t="e">
+        <v>-4791851.9047608003</v>
+      </c>
+      <c r="AU28" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW28" s="9" t="s">
         <v>13</v>
@@ -7050,10 +7196,13 @@
       <c r="AH29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI29" s="32"/>
+      <c r="AI29" s="32">
+        <v>4528</v>
+      </c>
+      <c r="AJ29" s="48"/>
       <c r="AK29" s="10">
         <f t="shared" si="7"/>
-        <v>-2979</v>
+        <v>1549</v>
       </c>
       <c r="AL29" s="12">
         <f t="shared" si="7"/>
@@ -7072,7 +7221,7 @@
       <c r="AR29" s="35"/>
       <c r="AS29" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-4528</v>
       </c>
       <c r="AT29" s="12">
         <f t="shared" si="9"/>
@@ -7297,6 +7446,7 @@
         <v>21</v>
       </c>
       <c r="AI30" s="32"/>
+      <c r="AJ30" s="48"/>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
         <v>-1</v>
@@ -7533,18 +7683,23 @@
       <c r="AH31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI31" s="13"/>
+      <c r="AI31" s="13">
+        <v>118</v>
+      </c>
+      <c r="AJ31" s="46">
+        <v>124480.95238046</v>
+      </c>
       <c r="AK31" s="10">
         <f t="shared" si="7"/>
-        <v>-97</v>
+        <v>21</v>
       </c>
       <c r="AL31" s="12">
         <f t="shared" si="7"/>
-        <v>-92987.619047320011</v>
+        <v>31493.333333139992</v>
       </c>
       <c r="AM31" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.33868308120797785</v>
       </c>
       <c r="AO31" s="14"/>
       <c r="AP31" s="13" t="s">
@@ -7553,15 +7708,15 @@
       <c r="AR31" s="12"/>
       <c r="AS31" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-118</v>
       </c>
       <c r="AT31" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU31" s="11" t="e">
+        <v>-124480.95238046</v>
+      </c>
+      <c r="AU31" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW31" s="14"/>
       <c r="AX31" s="13" t="s">
@@ -7766,18 +7921,23 @@
       <c r="AH32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI32" s="13"/>
+      <c r="AI32" s="13">
+        <v>80</v>
+      </c>
+      <c r="AJ32" s="46">
+        <v>85572.38095224998</v>
+      </c>
       <c r="AK32" s="10">
         <f t="shared" si="7"/>
-        <v>-45</v>
+        <v>35</v>
       </c>
       <c r="AL32" s="12">
         <f t="shared" si="7"/>
-        <v>-37430.476190390007</v>
+        <v>48141.904761859972</v>
       </c>
       <c r="AM32" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.2861686428189243</v>
       </c>
       <c r="AO32" s="14"/>
       <c r="AP32" s="13" t="s">
@@ -7786,15 +7946,15 @@
       <c r="AR32" s="12"/>
       <c r="AS32" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="AT32" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU32" s="11" t="e">
+        <v>-85572.38095224998</v>
+      </c>
+      <c r="AU32" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW32" s="14"/>
       <c r="AX32" s="13" t="s">
@@ -7999,18 +8159,23 @@
       <c r="AH33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI33" s="13"/>
+      <c r="AI33" s="13">
+        <v>29</v>
+      </c>
+      <c r="AJ33" s="46">
+        <v>194009.52380950999</v>
+      </c>
       <c r="AK33" s="10">
         <f t="shared" si="7"/>
-        <v>-12</v>
+        <v>17</v>
       </c>
       <c r="AL33" s="12">
         <f t="shared" si="7"/>
-        <v>-74076.190476179996</v>
+        <v>119933.33333333</v>
       </c>
       <c r="AM33" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.6190537413218606</v>
       </c>
       <c r="AO33" s="14"/>
       <c r="AP33" s="13" t="s">
@@ -8019,15 +8184,15 @@
       <c r="AR33" s="12"/>
       <c r="AS33" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="AT33" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU33" s="11" t="e">
+        <v>-194009.52380950999</v>
+      </c>
+      <c r="AU33" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW33" s="14"/>
       <c r="AX33" s="13" t="s">
@@ -8232,18 +8397,23 @@
       <c r="AH34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI34" s="13"/>
+      <c r="AI34" s="13">
+        <v>18</v>
+      </c>
+      <c r="AJ34" s="46">
+        <v>190666.66666663002</v>
+      </c>
       <c r="AK34" s="10">
         <f t="shared" si="7"/>
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="AL34" s="12">
         <f t="shared" si="7"/>
-        <v>-142666.66666663002</v>
+        <v>48000</v>
       </c>
       <c r="AM34" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.33644859813092753</v>
       </c>
       <c r="AO34" s="14"/>
       <c r="AP34" s="13" t="s">
@@ -8252,15 +8422,15 @@
       <c r="AR34" s="12"/>
       <c r="AS34" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AT34" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU34" s="11" t="e">
+        <v>-190666.66666663002</v>
+      </c>
+      <c r="AU34" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW34" s="14"/>
       <c r="AX34" s="13" t="s">
@@ -8450,14 +8620,19 @@
       <c r="AH35" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI35" s="13"/>
+      <c r="AI35" s="13">
+        <v>2</v>
+      </c>
+      <c r="AJ35" s="46">
+        <v>11714.285714279999</v>
+      </c>
       <c r="AK35" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL35" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11714.285714279999</v>
       </c>
       <c r="AM35" s="11" t="e">
         <f t="shared" si="8"/>
@@ -8470,15 +8645,15 @@
       <c r="AR35" s="12"/>
       <c r="AS35" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT35" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU35" s="11" t="e">
+        <v>-11714.285714279999</v>
+      </c>
+      <c r="AU35" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW35" s="14"/>
       <c r="AX35" s="13" t="s">
@@ -8683,18 +8858,23 @@
       <c r="AH36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI36" s="13"/>
+      <c r="AI36" s="13">
+        <v>8</v>
+      </c>
+      <c r="AJ36" s="46">
+        <v>33320</v>
+      </c>
       <c r="AK36" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AL36" s="12">
         <f t="shared" si="7"/>
-        <v>-2857.1428571400002</v>
+        <v>30462.857142860001</v>
       </c>
       <c r="AM36" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>10.662000000011661</v>
       </c>
       <c r="AO36" s="14"/>
       <c r="AP36" s="13" t="s">
@@ -8703,15 +8883,15 @@
       <c r="AR36" s="12"/>
       <c r="AS36" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AT36" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU36" s="11" t="e">
+        <v>-33320</v>
+      </c>
+      <c r="AU36" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW36" s="14"/>
       <c r="AX36" s="13" t="s">
@@ -8916,18 +9096,23 @@
       <c r="AH37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI37" s="13"/>
+      <c r="AI37" s="13">
+        <v>10</v>
+      </c>
+      <c r="AJ37" s="46">
+        <v>369458.09523806005</v>
+      </c>
       <c r="AK37" s="10">
         <f t="shared" si="7"/>
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AL37" s="12">
         <f t="shared" si="7"/>
-        <v>-19650</v>
+        <v>349808.09523806005</v>
       </c>
       <c r="AM37" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>17.801938688959797</v>
       </c>
       <c r="AO37" s="14"/>
       <c r="AP37" s="13" t="s">
@@ -8936,15 +9121,15 @@
       <c r="AR37" s="12"/>
       <c r="AS37" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AT37" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU37" s="11" t="e">
+        <v>-369458.09523806005</v>
+      </c>
+      <c r="AU37" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW37" s="14"/>
       <c r="AX37" s="13" t="s">
@@ -9149,18 +9334,23 @@
       <c r="AH38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI38" s="13"/>
+      <c r="AI38" s="13">
+        <v>20</v>
+      </c>
+      <c r="AJ38" s="46">
+        <v>379999.99999995995</v>
+      </c>
       <c r="AK38" s="10">
         <f t="shared" si="7"/>
-        <v>-11</v>
+        <v>9</v>
       </c>
       <c r="AL38" s="12">
         <f t="shared" si="7"/>
-        <v>-154952.38095235999</v>
+        <v>225047.61904759996</v>
       </c>
       <c r="AM38" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.4523663183774549</v>
       </c>
       <c r="AO38" s="14"/>
       <c r="AP38" s="13" t="s">
@@ -9169,15 +9359,15 @@
       <c r="AR38" s="12"/>
       <c r="AS38" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AT38" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU38" s="11" t="e">
+        <v>-379999.99999995995</v>
+      </c>
+      <c r="AU38" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW38" s="14"/>
       <c r="AX38" s="13" t="s">
@@ -9382,18 +9572,23 @@
       <c r="AH39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI39" s="13"/>
+      <c r="AI39" s="13">
+        <v>18</v>
+      </c>
+      <c r="AJ39" s="46">
+        <v>651619.04761901998</v>
+      </c>
       <c r="AK39" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>12</v>
       </c>
       <c r="AL39" s="12">
         <f t="shared" si="7"/>
-        <v>-236571.42857142002</v>
+        <v>415047.61904759996</v>
       </c>
       <c r="AM39" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.7544283413848458</v>
       </c>
       <c r="AO39" s="14"/>
       <c r="AP39" s="13" t="s">
@@ -9402,15 +9597,15 @@
       <c r="AR39" s="12"/>
       <c r="AS39" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AT39" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU39" s="11" t="e">
+        <v>-651619.04761901998</v>
+      </c>
+      <c r="AU39" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW39" s="14"/>
       <c r="AX39" s="13" t="s">
@@ -9616,19 +9811,23 @@
         <v>12</v>
       </c>
       <c r="AH40" s="9"/>
-      <c r="AI40" s="9"/>
-      <c r="AJ40" s="8"/>
+      <c r="AI40" s="9">
+        <v>303</v>
+      </c>
+      <c r="AJ40" s="47">
+        <v>2040840.9523801701</v>
+      </c>
       <c r="AK40" s="27">
         <f t="shared" si="7"/>
-        <v>-189</v>
+        <v>114</v>
       </c>
       <c r="AL40" s="28">
         <f t="shared" si="7"/>
-        <v>-761191.90476144012</v>
+        <v>1279649.04761873</v>
       </c>
       <c r="AM40" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1.6811122656641704</v>
       </c>
       <c r="AO40" s="9" t="s">
         <v>12</v>
@@ -9638,15 +9837,15 @@
       <c r="AR40" s="7"/>
       <c r="AS40" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-303</v>
       </c>
       <c r="AT40" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU40" s="29" t="e">
+        <v>-2040840.9523801701</v>
+      </c>
+      <c r="AU40" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW40" s="9" t="s">
         <v>12</v>
@@ -9861,10 +10060,13 @@
       <c r="AH41" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI41" s="32"/>
+      <c r="AI41" s="32">
+        <v>1393</v>
+      </c>
+      <c r="AJ41" s="48"/>
       <c r="AK41" s="10">
         <f t="shared" si="7"/>
-        <v>-1019</v>
+        <v>374</v>
       </c>
       <c r="AL41" s="12">
         <f t="shared" si="7"/>
@@ -9883,7 +10085,7 @@
       <c r="AR41" s="35"/>
       <c r="AS41" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1393</v>
       </c>
       <c r="AT41" s="12">
         <f t="shared" si="9"/>
@@ -10108,6 +10310,7 @@
         <v>21</v>
       </c>
       <c r="AI42" s="32"/>
+      <c r="AJ42" s="48"/>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
         <v>-1</v>
@@ -10344,18 +10547,23 @@
       <c r="AH43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI43" s="13"/>
+      <c r="AI43" s="13">
+        <v>78</v>
+      </c>
+      <c r="AJ43" s="46">
+        <v>80907.619047240005</v>
+      </c>
       <c r="AK43" s="10">
         <f t="shared" si="7"/>
-        <v>-72</v>
+        <v>6</v>
       </c>
       <c r="AL43" s="12">
         <f t="shared" si="7"/>
-        <v>-64970.47619015001</v>
+        <v>15937.142857089995</v>
       </c>
       <c r="AM43" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.24529823069861045</v>
       </c>
       <c r="AO43" s="14"/>
       <c r="AP43" s="13" t="s">
@@ -10364,15 +10572,15 @@
       <c r="AR43" s="12"/>
       <c r="AS43" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="AT43" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU43" s="11" t="e">
+        <v>-80907.619047240005</v>
+      </c>
+      <c r="AU43" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW43" s="14"/>
       <c r="AX43" s="13" t="s">
@@ -10577,18 +10785,23 @@
       <c r="AH44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI44" s="13"/>
+      <c r="AI44" s="13">
+        <v>89</v>
+      </c>
+      <c r="AJ44" s="46">
+        <v>79542.857142760011</v>
+      </c>
       <c r="AK44" s="10">
         <f t="shared" si="7"/>
-        <v>-83</v>
+        <v>6</v>
       </c>
       <c r="AL44" s="12">
         <f t="shared" si="7"/>
-        <v>-83323.809523720003</v>
+        <v>-3780.9523809599923</v>
       </c>
       <c r="AM44" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-4.5376614470365263E-2</v>
       </c>
       <c r="AO44" s="14"/>
       <c r="AP44" s="13" t="s">
@@ -10597,15 +10810,15 @@
       <c r="AR44" s="12"/>
       <c r="AS44" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="AT44" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU44" s="11" t="e">
+        <v>-79542.857142760011</v>
+      </c>
+      <c r="AU44" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW44" s="14"/>
       <c r="AX44" s="13" t="s">
@@ -10810,18 +11023,23 @@
       <c r="AH45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI45" s="13"/>
+      <c r="AI45" s="13">
+        <v>14</v>
+      </c>
+      <c r="AJ45" s="46">
+        <v>84152.380952370004</v>
+      </c>
       <c r="AK45" s="10">
         <f t="shared" si="7"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="AL45" s="12">
         <f t="shared" si="7"/>
-        <v>-100704.76190474999</v>
+        <v>-16552.380952379986</v>
       </c>
       <c r="AM45" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.16436542462645207</v>
       </c>
       <c r="AO45" s="14"/>
       <c r="AP45" s="13" t="s">
@@ -10830,15 +11048,15 @@
       <c r="AR45" s="12"/>
       <c r="AS45" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AT45" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU45" s="11" t="e">
+        <v>-84152.380952370004</v>
+      </c>
+      <c r="AU45" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW45" s="14"/>
       <c r="AX45" s="13" t="s">
@@ -11043,18 +11261,23 @@
       <c r="AH46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI46" s="13"/>
+      <c r="AI46" s="13">
+        <v>9</v>
+      </c>
+      <c r="AJ46" s="46">
+        <v>106761.90476187001</v>
+      </c>
       <c r="AK46" s="10">
         <f t="shared" si="7"/>
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="AL46" s="12">
         <f t="shared" si="7"/>
-        <v>-129333.33333331</v>
+        <v>-22571.428571439988</v>
       </c>
       <c r="AM46" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.17452135493384582</v>
       </c>
       <c r="AO46" s="14"/>
       <c r="AP46" s="13" t="s">
@@ -11063,15 +11286,15 @@
       <c r="AR46" s="12"/>
       <c r="AS46" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AT46" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU46" s="11" t="e">
+        <v>-106761.90476187001</v>
+      </c>
+      <c r="AU46" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW46" s="14"/>
       <c r="AX46" s="13" t="s">
@@ -11266,18 +11489,23 @@
       <c r="AH47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI47" s="13"/>
+      <c r="AI47" s="13">
+        <v>2</v>
+      </c>
+      <c r="AJ47" s="46">
+        <v>5714.2857142800003</v>
+      </c>
       <c r="AK47" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AL47" s="12">
         <f t="shared" si="7"/>
-        <v>-2857.1428571400002</v>
+        <v>2857.1428571400002</v>
       </c>
       <c r="AM47" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO47" s="14"/>
       <c r="AP47" s="13" t="s">
@@ -11286,15 +11514,15 @@
       <c r="AR47" s="12"/>
       <c r="AS47" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT47" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU47" s="11" t="e">
+        <v>-5714.2857142800003</v>
+      </c>
+      <c r="AU47" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW47" s="14"/>
       <c r="AX47" s="13" t="s">
@@ -11494,18 +11722,23 @@
       <c r="AH48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI48" s="13"/>
+      <c r="AI48" s="13">
+        <v>1</v>
+      </c>
+      <c r="AJ48" s="46">
+        <v>7290</v>
+      </c>
       <c r="AK48" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL48" s="12">
         <f t="shared" si="7"/>
-        <v>-12990</v>
+        <v>-5700</v>
       </c>
       <c r="AM48" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.43879907621247111</v>
       </c>
       <c r="AO48" s="14"/>
       <c r="AP48" s="13" t="s">
@@ -11514,15 +11747,15 @@
       <c r="AR48" s="12"/>
       <c r="AS48" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT48" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU48" s="11" t="e">
+        <v>-7290</v>
+      </c>
+      <c r="AU48" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW48" s="14"/>
       <c r="AX48" s="13" t="s">
@@ -11722,18 +11955,23 @@
       <c r="AH49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI49" s="13"/>
+      <c r="AI49" s="13">
+        <v>9</v>
+      </c>
+      <c r="AJ49" s="46">
+        <v>297597.14285711001</v>
+      </c>
       <c r="AK49" s="10">
         <f t="shared" si="7"/>
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="AL49" s="12">
         <f t="shared" si="7"/>
-        <v>-224006.66666664</v>
+        <v>73590.476190470014</v>
       </c>
       <c r="AM49" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.32851913420945256</v>
       </c>
       <c r="AO49" s="14"/>
       <c r="AP49" s="13" t="s">
@@ -11742,15 +11980,15 @@
       <c r="AR49" s="12"/>
       <c r="AS49" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AT49" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU49" s="11" t="e">
+        <v>-297597.14285711001</v>
+      </c>
+      <c r="AU49" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW49" s="14"/>
       <c r="AX49" s="13" t="s">
@@ -11955,18 +12193,23 @@
       <c r="AH50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI50" s="13"/>
+      <c r="AI50" s="13">
+        <v>9</v>
+      </c>
+      <c r="AJ50" s="46">
+        <v>152285.71428568999</v>
+      </c>
       <c r="AK50" s="10">
         <f t="shared" si="7"/>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="AL50" s="12">
         <f t="shared" si="7"/>
-        <v>-330909.52380948002</v>
+        <v>-178623.80952379003</v>
       </c>
       <c r="AM50" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.53979652041272785</v>
       </c>
       <c r="AO50" s="14"/>
       <c r="AP50" s="13" t="s">
@@ -11975,15 +12218,15 @@
       <c r="AR50" s="12"/>
       <c r="AS50" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AT50" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU50" s="11" t="e">
+        <v>-152285.71428568999</v>
+      </c>
+      <c r="AU50" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW50" s="14"/>
       <c r="AX50" s="13" t="s">
@@ -12188,18 +12431,23 @@
       <c r="AH51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI51" s="13"/>
+      <c r="AI51" s="13">
+        <v>21</v>
+      </c>
+      <c r="AJ51" s="46">
+        <v>681809.52380949003</v>
+      </c>
       <c r="AK51" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>8</v>
       </c>
       <c r="AL51" s="12">
         <f t="shared" si="7"/>
-        <v>-396857.14285711991</v>
+        <v>284952.38095237012</v>
       </c>
       <c r="AM51" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.71802255819535865</v>
       </c>
       <c r="AO51" s="14"/>
       <c r="AP51" s="13" t="s">
@@ -12208,15 +12456,15 @@
       <c r="AR51" s="12"/>
       <c r="AS51" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="AT51" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU51" s="11" t="e">
+        <v>-681809.52380949003</v>
+      </c>
+      <c r="AU51" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW51" s="14"/>
       <c r="AX51" s="13" t="s">
@@ -12422,19 +12670,23 @@
         <v>11</v>
       </c>
       <c r="AH52" s="9"/>
-      <c r="AI52" s="9"/>
-      <c r="AJ52" s="8"/>
+      <c r="AI52" s="9">
+        <v>232</v>
+      </c>
+      <c r="AJ52" s="47">
+        <v>1496061.42857081</v>
+      </c>
       <c r="AK52" s="27">
         <f t="shared" si="7"/>
-        <v>-218</v>
+        <v>14</v>
       </c>
       <c r="AL52" s="28">
         <f t="shared" si="7"/>
-        <v>-1345952.8571423099</v>
+        <v>150108.57142850012</v>
       </c>
       <c r="AM52" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.11152587598588445</v>
       </c>
       <c r="AO52" s="9" t="s">
         <v>11</v>
@@ -12444,15 +12696,15 @@
       <c r="AR52" s="7"/>
       <c r="AS52" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-232</v>
       </c>
       <c r="AT52" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU52" s="29" t="e">
+        <v>-1496061.42857081</v>
+      </c>
+      <c r="AU52" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW52" s="9" t="s">
         <v>11</v>
@@ -12656,6 +12908,7 @@
         <v>20</v>
       </c>
       <c r="AI53" s="32"/>
+      <c r="AJ53" s="48"/>
       <c r="AK53" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -12902,6 +13155,7 @@
         <v>21</v>
       </c>
       <c r="AI54" s="32"/>
+      <c r="AJ54" s="48"/>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
         <v>-4</v>
@@ -13138,18 +13392,23 @@
       <c r="AH55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI55" s="13"/>
+      <c r="AI55" s="13">
+        <v>128</v>
+      </c>
+      <c r="AJ55" s="46">
+        <v>119866.66666608992</v>
+      </c>
       <c r="AK55" s="10">
         <f t="shared" si="7"/>
-        <v>-82</v>
+        <v>46</v>
       </c>
       <c r="AL55" s="12">
         <f t="shared" si="7"/>
-        <v>-73125.714285359994</v>
+        <v>46740.952380729927</v>
       </c>
       <c r="AM55" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.6391862676148603</v>
       </c>
       <c r="AO55" s="14"/>
       <c r="AP55" s="13" t="s">
@@ -13158,15 +13417,15 @@
       <c r="AR55" s="12"/>
       <c r="AS55" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-128</v>
       </c>
       <c r="AT55" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU55" s="11" t="e">
+        <v>-119866.66666608992</v>
+      </c>
+      <c r="AU55" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW55" s="14"/>
       <c r="AX55" s="13" t="s">
@@ -13371,18 +13630,23 @@
       <c r="AH56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI56" s="13"/>
+      <c r="AI56" s="13">
+        <v>82</v>
+      </c>
+      <c r="AJ56" s="46">
+        <v>70076.190476100004</v>
+      </c>
       <c r="AK56" s="10">
         <f t="shared" si="7"/>
-        <v>-77</v>
+        <v>5</v>
       </c>
       <c r="AL56" s="12">
         <f t="shared" si="7"/>
-        <v>-79457.142857069994</v>
+        <v>-9380.9523809699895</v>
       </c>
       <c r="AM56" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.11806304686596573</v>
       </c>
       <c r="AO56" s="14"/>
       <c r="AP56" s="13" t="s">
@@ -13391,15 +13655,15 @@
       <c r="AR56" s="12"/>
       <c r="AS56" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="AT56" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU56" s="11" t="e">
+        <v>-70076.190476100004</v>
+      </c>
+      <c r="AU56" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW56" s="14"/>
       <c r="AX56" s="13" t="s">
@@ -13604,18 +13868,23 @@
       <c r="AH57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI57" s="13"/>
+      <c r="AI57" s="13">
+        <v>14</v>
+      </c>
+      <c r="AJ57" s="46">
+        <v>85580.952380939998</v>
+      </c>
       <c r="AK57" s="10">
         <f t="shared" si="7"/>
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AL57" s="12">
         <f t="shared" si="7"/>
-        <v>-86152.380952370004</v>
+        <v>-571.42857143000583</v>
       </c>
       <c r="AM57" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-6.6327658633825153E-3</v>
       </c>
       <c r="AO57" s="14"/>
       <c r="AP57" s="13" t="s">
@@ -13624,15 +13893,15 @@
       <c r="AR57" s="12"/>
       <c r="AS57" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AT57" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU57" s="11" t="e">
+        <v>-85580.952380939998</v>
+      </c>
+      <c r="AU57" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW57" s="14"/>
       <c r="AX57" s="13" t="s">
@@ -13837,18 +14106,23 @@
       <c r="AH58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI58" s="13"/>
+      <c r="AI58" s="13">
+        <v>7</v>
+      </c>
+      <c r="AJ58" s="46">
+        <v>105999.99999996999</v>
+      </c>
       <c r="AK58" s="10">
         <f t="shared" si="7"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="AL58" s="12">
         <f t="shared" si="7"/>
-        <v>-118285.71428567999</v>
+        <v>-12285.714285709997</v>
       </c>
       <c r="AM58" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.10386473429951076</v>
       </c>
       <c r="AO58" s="14"/>
       <c r="AP58" s="13" t="s">
@@ -13857,15 +14131,15 @@
       <c r="AR58" s="12"/>
       <c r="AS58" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AT58" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU58" s="11" t="e">
+        <v>-105999.99999996999</v>
+      </c>
+      <c r="AU58" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW58" s="14"/>
       <c r="AX58" s="13" t="s">
@@ -14051,6 +14325,7 @@
         <v>6</v>
       </c>
       <c r="AI59" s="13"/>
+      <c r="AJ59" s="46"/>
       <c r="AK59" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14283,18 +14558,23 @@
       <c r="AH60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI60" s="13"/>
+      <c r="AI60" s="13">
+        <v>8</v>
+      </c>
+      <c r="AJ60" s="46">
+        <v>36520</v>
+      </c>
       <c r="AK60" s="10">
         <f t="shared" si="7"/>
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="AL60" s="12">
         <f t="shared" si="7"/>
-        <v>-5880</v>
+        <v>30640</v>
       </c>
       <c r="AM60" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>5.2108843537414966</v>
       </c>
       <c r="AO60" s="14"/>
       <c r="AP60" s="13" t="s">
@@ -14303,15 +14583,15 @@
       <c r="AR60" s="12"/>
       <c r="AS60" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AT60" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU60" s="11" t="e">
+        <v>-36520</v>
+      </c>
+      <c r="AU60" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW60" s="14"/>
       <c r="AX60" s="13" t="s">
@@ -14516,18 +14796,23 @@
       <c r="AH61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI61" s="13"/>
+      <c r="AI61" s="13">
+        <v>12</v>
+      </c>
+      <c r="AJ61" s="46">
+        <v>397971.42857137998</v>
+      </c>
       <c r="AK61" s="10">
         <f t="shared" si="7"/>
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="AL61" s="12">
         <f t="shared" si="7"/>
-        <v>-55999.999999990003</v>
+        <v>341971.42857138999</v>
       </c>
       <c r="AM61" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>6.1066326530616255</v>
       </c>
       <c r="AO61" s="14"/>
       <c r="AP61" s="13" t="s">
@@ -14536,15 +14821,15 @@
       <c r="AR61" s="12"/>
       <c r="AS61" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AT61" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU61" s="11" t="e">
+        <v>-397971.42857137998</v>
+      </c>
+      <c r="AU61" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW61" s="14"/>
       <c r="AX61" s="13" t="s">
@@ -14749,18 +15034,23 @@
       <c r="AH62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI62" s="13"/>
+      <c r="AI62" s="13">
+        <v>20</v>
+      </c>
+      <c r="AJ62" s="46">
+        <v>407142.85714280012</v>
+      </c>
       <c r="AK62" s="10">
         <f t="shared" si="7"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AL62" s="12">
         <f t="shared" si="7"/>
-        <v>-321904.76190471998</v>
+        <v>85238.095238080132</v>
       </c>
       <c r="AM62" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.26479289940827155</v>
       </c>
       <c r="AO62" s="14"/>
       <c r="AP62" s="13" t="s">
@@ -14769,15 +15059,15 @@
       <c r="AR62" s="12"/>
       <c r="AS62" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AT62" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU62" s="11" t="e">
+        <v>-407142.85714280012</v>
+      </c>
+      <c r="AU62" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW62" s="14"/>
       <c r="AX62" s="13" t="s">
@@ -14982,18 +15272,23 @@
       <c r="AH63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI63" s="13"/>
+      <c r="AI63" s="13">
+        <v>15</v>
+      </c>
+      <c r="AJ63" s="46">
+        <v>510952.38095235999</v>
+      </c>
       <c r="AK63" s="10">
         <f t="shared" si="7"/>
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="AL63" s="12">
         <f t="shared" si="7"/>
-        <v>-858761.90476186003</v>
+        <v>-347809.52380950004</v>
       </c>
       <c r="AM63" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.40501275368747264</v>
       </c>
       <c r="AO63" s="14"/>
       <c r="AP63" s="13" t="s">
@@ -15002,15 +15297,15 @@
       <c r="AR63" s="12"/>
       <c r="AS63" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AT63" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU63" s="11" t="e">
+        <v>-510952.38095235999</v>
+      </c>
+      <c r="AU63" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW63" s="14"/>
       <c r="AX63" s="13" t="s">
@@ -15216,19 +15511,23 @@
         <v>1</v>
       </c>
       <c r="AH64" s="9"/>
-      <c r="AI64" s="9"/>
-      <c r="AJ64" s="8"/>
+      <c r="AI64" s="9">
+        <v>286</v>
+      </c>
+      <c r="AJ64" s="47">
+        <v>1734110.4761896399</v>
+      </c>
       <c r="AK64" s="27">
         <f t="shared" si="7"/>
-        <v>-228</v>
+        <v>58</v>
       </c>
       <c r="AL64" s="28">
         <f t="shared" si="7"/>
-        <v>-1599567.6190470499</v>
+        <v>134542.85714258999</v>
       </c>
       <c r="AM64" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>8.4112015985135125E-2</v>
       </c>
       <c r="AO64" s="9" t="s">
         <v>1</v>
@@ -15238,15 +15537,15 @@
       <c r="AR64" s="7"/>
       <c r="AS64" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-286</v>
       </c>
       <c r="AT64" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU64" s="29" t="e">
+        <v>-1734110.4761896399</v>
+      </c>
+      <c r="AU64" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW64" s="9" t="s">
         <v>1</v>
@@ -15459,19 +15758,23 @@
         <v>0</v>
       </c>
       <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="3"/>
+      <c r="AI65" s="4">
+        <v>2341</v>
+      </c>
+      <c r="AJ65" s="49">
+        <v>20474951.904757049</v>
+      </c>
       <c r="AK65" s="6">
         <f t="shared" si="7"/>
-        <v>-1943</v>
+        <v>398</v>
       </c>
       <c r="AL65" s="5">
         <f t="shared" si="7"/>
-        <v>-16504919.047614958</v>
+        <v>3970032.8571420908</v>
       </c>
       <c r="AM65" s="30">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.24053634226796042</v>
       </c>
       <c r="AO65" s="4" t="s">
         <v>0</v>
@@ -15481,15 +15784,15 @@
       <c r="AR65" s="2"/>
       <c r="AS65" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2341</v>
       </c>
       <c r="AT65" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU65" s="30" t="e">
+        <v>-20474951.904757049</v>
+      </c>
+      <c r="AU65" s="30">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557A328E-D1D5-9648-AFDD-2BFE4F50F625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52104101-2FED-BC43-868A-E0142020DB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11720" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -179,11 +179,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>04/26~0502</t>
+    <t>26Q3W5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>26Q3W5</t>
+    <t>04/26~05/02</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1036,7 +1036,7 @@
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
       <c r="AG1" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AH1" s="26"/>
       <c r="AJ1" s="41"/>
@@ -1087,7 +1087,7 @@
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
       <c r="AG2" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AJ2" s="42"/>
       <c r="AK2" s="22"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52104101-2FED-BC43-868A-E0142020DB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57395C4C-B42A-9E44-AF4E-E93D9478FD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1715,11 +1715,13 @@
       <c r="AH6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AI6" s="32"/>
+      <c r="AI6" s="32">
+        <v>17</v>
+      </c>
       <c r="AJ6" s="45"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="7"/>
@@ -1736,7 +1738,7 @@
       <c r="AR6" s="33"/>
       <c r="AS6" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AT6" s="12">
         <f t="shared" si="9"/>
@@ -4585,11 +4587,13 @@
       <c r="AH18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AI18" s="32"/>
+      <c r="AI18" s="32">
+        <v>10</v>
+      </c>
       <c r="AJ18" s="48"/>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="AL18" s="12">
         <f t="shared" si="7"/>
@@ -4606,7 +4610,7 @@
       <c r="AR18" s="35"/>
       <c r="AS18" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AT18" s="12">
         <f t="shared" si="9"/>
@@ -7445,11 +7449,13 @@
       <c r="AH30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AI30" s="32"/>
+      <c r="AI30" s="32">
+        <v>2</v>
+      </c>
       <c r="AJ30" s="48"/>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AL30" s="12">
         <f t="shared" si="7"/>
@@ -7466,7 +7472,7 @@
       <c r="AR30" s="35"/>
       <c r="AS30" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT30" s="12">
         <f t="shared" si="9"/>
@@ -10309,11 +10315,13 @@
       <c r="AH42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AI42" s="32"/>
+      <c r="AI42" s="32">
+        <v>3</v>
+      </c>
       <c r="AJ42" s="48"/>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AL42" s="12">
         <f t="shared" si="7"/>
@@ -10330,7 +10338,7 @@
       <c r="AR42" s="35"/>
       <c r="AS42" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AT42" s="12">
         <f t="shared" si="9"/>
@@ -13154,11 +13162,13 @@
       <c r="AH54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AI54" s="32"/>
+      <c r="AI54" s="32">
+        <v>2</v>
+      </c>
       <c r="AJ54" s="48"/>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AL54" s="12">
         <f t="shared" si="7"/>
@@ -13175,7 +13185,7 @@
       <c r="AR54" s="35"/>
       <c r="AS54" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT54" s="12">
         <f t="shared" si="9"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57395C4C-B42A-9E44-AF4E-E93D9478FD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FD10B9-911A-914F-B60C-EAC33B376122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="7940" yWindow="700" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="34">
   <si>
     <t>總計</t>
   </si>
@@ -184,6 +184,14 @@
   </si>
   <si>
     <t>04/26~05/02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/03~05/09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1040,7 +1048,9 @@
       </c>
       <c r="AH1" s="26"/>
       <c r="AJ1" s="41"/>
-      <c r="AO1" s="26"/>
+      <c r="AO1" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="AP1" s="26"/>
       <c r="AR1" s="25"/>
       <c r="AW1" s="26"/>
@@ -1093,6 +1103,9 @@
       <c r="AK2" s="22"/>
       <c r="AL2" s="22"/>
       <c r="AN2" s="21"/>
+      <c r="AO2" s="23" t="s">
+        <v>33</v>
+      </c>
       <c r="AQ2" s="22"/>
       <c r="AR2" s="22"/>
       <c r="AT2" s="21"/>
@@ -1477,11 +1490,13 @@
       <c r="AP5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AQ5" s="40"/>
+      <c r="AQ5" s="40">
+        <v>6004</v>
+      </c>
       <c r="AR5" s="1"/>
       <c r="AS5" s="10">
         <f t="shared" ref="AS5:AT65" si="9">AQ5-AI5</f>
-        <v>-7979</v>
+        <v>-1975</v>
       </c>
       <c r="AT5" s="12">
         <f t="shared" si="9"/>
@@ -1502,7 +1517,7 @@
       <c r="AZ5" s="1"/>
       <c r="BA5" s="10">
         <f t="shared" ref="BA5:BA65" si="11">AY5-AQ5</f>
-        <v>0</v>
+        <v>-6004</v>
       </c>
       <c r="BB5" s="12">
         <f t="shared" ref="BB5:BB65" si="12">AZ5-AR5</f>
@@ -1973,18 +1988,23 @@
       <c r="AP7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AR7" s="12"/>
+      <c r="AQ7" s="10">
+        <v>202</v>
+      </c>
+      <c r="AR7" s="12">
+        <v>198379.04761833997</v>
+      </c>
       <c r="AS7" s="10">
         <f t="shared" si="9"/>
-        <v>-228</v>
+        <v>-26</v>
       </c>
       <c r="AT7" s="12">
         <f t="shared" si="9"/>
-        <v>-274511.42857061001</v>
+        <v>-76132.380952270032</v>
       </c>
       <c r="AU7" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.27733774636886277</v>
       </c>
       <c r="AW7" s="14"/>
       <c r="AX7" s="13" t="s">
@@ -1993,15 +2013,15 @@
       <c r="AZ7" s="12"/>
       <c r="BA7" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-202</v>
       </c>
       <c r="BB7" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="11" t="e">
+        <v>-198379.04761833997</v>
+      </c>
+      <c r="BC7" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE7" s="14"/>
       <c r="BF7" s="13" t="s">
@@ -2211,18 +2231,23 @@
       <c r="AP8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR8" s="12"/>
+      <c r="AQ8" s="10">
+        <v>214</v>
+      </c>
+      <c r="AR8" s="12">
+        <v>356401.90476171992</v>
+      </c>
       <c r="AS8" s="10">
         <f t="shared" si="9"/>
-        <v>-286</v>
+        <v>-72</v>
       </c>
       <c r="AT8" s="12">
         <f t="shared" si="9"/>
-        <v>-419689.52380937996</v>
+        <v>-63287.619047660031</v>
       </c>
       <c r="AU8" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.15079628024359459</v>
       </c>
       <c r="AW8" s="14"/>
       <c r="AX8" s="13" t="s">
@@ -2231,15 +2256,15 @@
       <c r="AZ8" s="12"/>
       <c r="BA8" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-214</v>
       </c>
       <c r="BB8" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="11" t="e">
+        <v>-356401.90476171992</v>
+      </c>
+      <c r="BC8" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE8" s="14"/>
       <c r="BF8" s="13" t="s">
@@ -2449,18 +2474,23 @@
       <c r="AP9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR9" s="12"/>
+      <c r="AQ9" s="10">
+        <v>68</v>
+      </c>
+      <c r="AR9" s="12">
+        <v>427923.80952379003</v>
+      </c>
       <c r="AS9" s="10">
         <f t="shared" si="9"/>
-        <v>-83</v>
+        <v>-15</v>
       </c>
       <c r="AT9" s="12">
         <f t="shared" si="9"/>
-        <v>-529685.7142857</v>
+        <v>-101761.90476190997</v>
       </c>
       <c r="AU9" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.19211751802507929</v>
       </c>
       <c r="AW9" s="14"/>
       <c r="AX9" s="13" t="s">
@@ -2469,15 +2499,15 @@
       <c r="AZ9" s="12"/>
       <c r="BA9" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="BB9" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC9" s="11" t="e">
+        <v>-427923.80952379003</v>
+      </c>
+      <c r="BC9" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE9" s="14"/>
       <c r="BF9" s="13" t="s">
@@ -2687,18 +2717,23 @@
       <c r="AP10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR10" s="12"/>
+      <c r="AQ10" s="10">
+        <v>59</v>
+      </c>
+      <c r="AR10" s="12">
+        <v>820004.76190469007</v>
+      </c>
       <c r="AS10" s="10">
         <f t="shared" si="9"/>
-        <v>-53</v>
+        <v>6</v>
       </c>
       <c r="AT10" s="12">
         <f t="shared" si="9"/>
-        <v>-707333.33333325002</v>
+        <v>112671.42857144005</v>
       </c>
       <c r="AU10" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.15929042682109329</v>
       </c>
       <c r="AW10" s="14"/>
       <c r="AX10" s="13" t="s">
@@ -2707,15 +2742,15 @@
       <c r="AZ10" s="12"/>
       <c r="BA10" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="BB10" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="11" t="e">
+        <v>-820004.76190469007</v>
+      </c>
+      <c r="BC10" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE10" s="14"/>
       <c r="BF10" s="13" t="s">
@@ -2920,18 +2955,23 @@
       <c r="AP11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR11" s="12"/>
+      <c r="AQ11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="12">
+        <v>2657.1428571400002</v>
+      </c>
       <c r="AS11" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT11" s="12">
         <f t="shared" si="9"/>
-        <v>-11514.285714279999</v>
+        <v>-8857.1428571399993</v>
       </c>
       <c r="AU11" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.76923076923090283</v>
       </c>
       <c r="AW11" s="14"/>
       <c r="AX11" s="13" t="s">
@@ -2940,15 +2980,15 @@
       <c r="AZ11" s="12"/>
       <c r="BA11" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BB11" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="11" t="e">
+        <v>-2657.1428571400002</v>
+      </c>
+      <c r="BC11" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE11" s="14"/>
       <c r="BF11" s="13" t="s">
@@ -3158,18 +3198,23 @@
       <c r="AP12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR12" s="12"/>
+      <c r="AQ12" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR12" s="12">
+        <v>40420</v>
+      </c>
       <c r="AS12" s="10">
         <f t="shared" si="9"/>
-        <v>-29</v>
+        <v>-19</v>
       </c>
       <c r="AT12" s="12">
         <f t="shared" si="9"/>
-        <v>-148110</v>
+        <v>-107690</v>
       </c>
       <c r="AU12" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.72709472689217469</v>
       </c>
       <c r="AW12" s="14"/>
       <c r="AX12" s="13" t="s">
@@ -3178,15 +3223,15 @@
       <c r="AZ12" s="12"/>
       <c r="BA12" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB12" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="11" t="e">
+        <v>-40420</v>
+      </c>
+      <c r="BC12" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE12" s="14"/>
       <c r="BF12" s="13" t="s">
@@ -3396,18 +3441,23 @@
       <c r="AP13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR13" s="12"/>
+      <c r="AQ13" s="10">
+        <v>23</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>1014895.2380951601</v>
+      </c>
       <c r="AS13" s="10">
         <f t="shared" si="9"/>
-        <v>-55</v>
+        <v>-32</v>
       </c>
       <c r="AT13" s="12">
         <f t="shared" si="9"/>
-        <v>-2281052.3809522097</v>
+        <v>-1266157.1428570496</v>
       </c>
       <c r="AU13" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.5550758735003275</v>
       </c>
       <c r="AW13" s="14"/>
       <c r="AX13" s="13" t="s">
@@ -3416,15 +3466,15 @@
       <c r="AZ13" s="12"/>
       <c r="BA13" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="BB13" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC13" s="11" t="e">
+        <v>-1014895.2380951601</v>
+      </c>
+      <c r="BC13" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE13" s="14"/>
       <c r="BF13" s="13" t="s">
@@ -3634,18 +3684,23 @@
       <c r="AP14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR14" s="12"/>
+      <c r="AQ14" s="10">
+        <v>80</v>
+      </c>
+      <c r="AR14" s="12">
+        <v>1749238.0952379704</v>
+      </c>
       <c r="AS14" s="10">
         <f t="shared" si="9"/>
-        <v>-120</v>
+        <v>-40</v>
       </c>
       <c r="AT14" s="12">
         <f t="shared" si="9"/>
-        <v>-2500095.23809504</v>
+        <v>-750857.14285706962</v>
       </c>
       <c r="AU14" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.30033141594605373</v>
       </c>
       <c r="AW14" s="14"/>
       <c r="AX14" s="13" t="s">
@@ -3654,15 +3709,15 @@
       <c r="AZ14" s="12"/>
       <c r="BA14" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="BB14" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC14" s="11" t="e">
+        <v>-1749238.0952379704</v>
+      </c>
+      <c r="BC14" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE14" s="14"/>
       <c r="BF14" s="13" t="s">
@@ -3872,18 +3927,23 @@
       <c r="AP15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR15" s="12"/>
+      <c r="AQ15" s="10">
+        <v>137</v>
+      </c>
+      <c r="AR15" s="12">
+        <v>5078379.0476189293</v>
+      </c>
       <c r="AS15" s="10">
         <f t="shared" si="9"/>
-        <v>-99</v>
+        <v>38</v>
       </c>
       <c r="AT15" s="12">
         <f t="shared" si="9"/>
-        <v>-3540095.2380951596</v>
+        <v>1538283.8095237697</v>
       </c>
       <c r="AU15" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.43453175862903715</v>
       </c>
       <c r="AW15" s="14"/>
       <c r="AX15" s="13" t="s">
@@ -3892,15 +3952,15 @@
       <c r="AZ15" s="12"/>
       <c r="BA15" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-137</v>
       </c>
       <c r="BB15" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC15" s="11" t="e">
+        <v>-5078379.0476189293</v>
+      </c>
+      <c r="BC15" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE15" s="14"/>
       <c r="BF15" s="13" t="s">
@@ -4111,19 +4171,23 @@
         <v>19</v>
       </c>
       <c r="AP16" s="9"/>
-      <c r="AQ16" s="8"/>
-      <c r="AR16" s="7"/>
+      <c r="AQ16" s="8">
+        <v>794</v>
+      </c>
+      <c r="AR16" s="7">
+        <v>9688299.0476177391</v>
+      </c>
       <c r="AS16" s="27">
         <f t="shared" si="9"/>
-        <v>-955</v>
+        <v>-161</v>
       </c>
       <c r="AT16" s="28">
         <f t="shared" si="9"/>
-        <v>-10412087.142855629</v>
+        <v>-723788.09523789026</v>
       </c>
       <c r="AU16" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-6.9514217976414619E-2</v>
       </c>
       <c r="AW16" s="9" t="s">
         <v>19</v>
@@ -4133,15 +4197,15 @@
       <c r="AZ16" s="7"/>
       <c r="BA16" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-794</v>
       </c>
       <c r="BB16" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC16" s="29" t="e">
+        <v>-9688299.0476177391</v>
+      </c>
+      <c r="BC16" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE16" s="9" t="s">
         <v>19</v>
@@ -4360,10 +4424,13 @@
       <c r="AP17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AQ17" s="1">
+        <v>4360</v>
+      </c>
       <c r="AR17" s="35"/>
       <c r="AS17" s="10">
         <f t="shared" si="9"/>
-        <v>-5198</v>
+        <v>-838</v>
       </c>
       <c r="AT17" s="12">
         <f t="shared" si="9"/>
@@ -4382,7 +4449,7 @@
       <c r="AZ17" s="35"/>
       <c r="BA17" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-4360</v>
       </c>
       <c r="BB17" s="12">
         <f t="shared" si="12"/>
@@ -4849,18 +4916,23 @@
       <c r="AP19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AR19" s="12"/>
+      <c r="AQ19" s="10">
+        <v>157</v>
+      </c>
+      <c r="AR19" s="12">
+        <v>172610.47618982001</v>
+      </c>
       <c r="AS19" s="10">
         <f t="shared" si="9"/>
-        <v>-148</v>
+        <v>9</v>
       </c>
       <c r="AT19" s="12">
         <f t="shared" si="9"/>
-        <v>-168661.90476126003</v>
+        <v>3948.5714285599825</v>
       </c>
       <c r="AU19" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>2.3411163499838111E-2</v>
       </c>
       <c r="AW19" s="14"/>
       <c r="AX19" s="13" t="s">
@@ -4869,15 +4941,15 @@
       <c r="AZ19" s="12"/>
       <c r="BA19" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-157</v>
       </c>
       <c r="BB19" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC19" s="11" t="e">
+        <v>-172610.47618982001</v>
+      </c>
+      <c r="BC19" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE19" s="14"/>
       <c r="BF19" s="13" t="s">
@@ -5087,18 +5159,23 @@
       <c r="AP20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR20" s="12"/>
+      <c r="AQ20" s="10">
+        <v>174</v>
+      </c>
+      <c r="AR20" s="12">
+        <v>188534.28571418999</v>
+      </c>
       <c r="AS20" s="10">
         <f t="shared" si="9"/>
-        <v>-200</v>
+        <v>-26</v>
       </c>
       <c r="AT20" s="12">
         <f t="shared" si="9"/>
-        <v>-196704.76190463002</v>
+        <v>-8170.4761904400366</v>
       </c>
       <c r="AU20" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-4.1536748329465432E-2</v>
       </c>
       <c r="AW20" s="14"/>
       <c r="AX20" s="13" t="s">
@@ -5107,15 +5184,15 @@
       <c r="AZ20" s="12"/>
       <c r="BA20" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-174</v>
       </c>
       <c r="BB20" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="11" t="e">
+        <v>-188534.28571418999</v>
+      </c>
+      <c r="BC20" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE20" s="14"/>
       <c r="BF20" s="13" t="s">
@@ -5325,18 +5402,23 @@
       <c r="AP21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR21" s="12"/>
+      <c r="AQ21" s="10">
+        <v>42</v>
+      </c>
+      <c r="AR21" s="12">
+        <v>262457.14285713003</v>
+      </c>
       <c r="AS21" s="10">
         <f t="shared" si="9"/>
-        <v>-36</v>
+        <v>6</v>
       </c>
       <c r="AT21" s="12">
         <f t="shared" si="9"/>
-        <v>-229657.14285712998</v>
+        <v>32800.000000000058</v>
       </c>
       <c r="AU21" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.14282159741229988</v>
       </c>
       <c r="AW21" s="14"/>
       <c r="AX21" s="13" t="s">
@@ -5345,15 +5427,15 @@
       <c r="AZ21" s="12"/>
       <c r="BA21" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="BB21" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC21" s="11" t="e">
+        <v>-262457.14285713003</v>
+      </c>
+      <c r="BC21" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE21" s="14"/>
       <c r="BF21" s="13" t="s">
@@ -5563,18 +5645,23 @@
       <c r="AP22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR22" s="12"/>
+      <c r="AQ22" s="10">
+        <v>48</v>
+      </c>
+      <c r="AR22" s="12">
+        <v>592190.47619040008</v>
+      </c>
       <c r="AS22" s="10">
         <f t="shared" si="9"/>
-        <v>-39</v>
+        <v>9</v>
       </c>
       <c r="AT22" s="12">
         <f t="shared" si="9"/>
-        <v>-498761.90476185002</v>
+        <v>93428.571428550058</v>
       </c>
       <c r="AU22" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.18732098529690344</v>
       </c>
       <c r="AW22" s="14"/>
       <c r="AX22" s="13" t="s">
@@ -5583,15 +5670,15 @@
       <c r="AZ22" s="12"/>
       <c r="BA22" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="BB22" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="11" t="e">
+        <v>-592190.47619040008</v>
+      </c>
+      <c r="BC22" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE22" s="14"/>
       <c r="BF22" s="13" t="s">
@@ -6020,18 +6107,23 @@
       <c r="AP24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR24" s="12"/>
+      <c r="AQ24" s="10">
+        <v>15</v>
+      </c>
+      <c r="AR24" s="12">
+        <v>71260</v>
+      </c>
       <c r="AS24" s="10">
         <f t="shared" si="9"/>
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="AT24" s="12">
         <f t="shared" si="9"/>
-        <v>-121490</v>
+        <v>-50230</v>
       </c>
       <c r="AU24" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.41344966663922955</v>
       </c>
       <c r="AW24" s="14"/>
       <c r="AX24" s="13" t="s">
@@ -6040,15 +6132,15 @@
       <c r="AZ24" s="12"/>
       <c r="BA24" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BB24" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="11" t="e">
+        <v>-71260</v>
+      </c>
+      <c r="BC24" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE24" s="14"/>
       <c r="BF24" s="13" t="s">
@@ -6258,18 +6350,23 @@
       <c r="AP25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR25" s="12"/>
+      <c r="AQ25" s="10">
+        <v>11</v>
+      </c>
+      <c r="AR25" s="12">
+        <v>432152.38095233002</v>
+      </c>
       <c r="AS25" s="10">
         <f t="shared" si="9"/>
-        <v>-33</v>
+        <v>-22</v>
       </c>
       <c r="AT25" s="12">
         <f t="shared" si="9"/>
-        <v>-1195909.5238094102</v>
+        <v>-763757.14285708009</v>
       </c>
       <c r="AU25" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.63864124137437561</v>
       </c>
       <c r="AW25" s="14"/>
       <c r="AX25" s="13" t="s">
@@ -6278,15 +6375,15 @@
       <c r="AZ25" s="12"/>
       <c r="BA25" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BB25" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC25" s="11" t="e">
+        <v>-432152.38095233002</v>
+      </c>
+      <c r="BC25" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE25" s="14"/>
       <c r="BF25" s="13" t="s">
@@ -6496,18 +6593,23 @@
       <c r="AP26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR26" s="12"/>
+      <c r="AQ26" s="10">
+        <v>34</v>
+      </c>
+      <c r="AR26" s="12">
+        <v>635809.5238094501</v>
+      </c>
       <c r="AS26" s="10">
         <f t="shared" si="9"/>
-        <v>-40</v>
+        <v>-6</v>
       </c>
       <c r="AT26" s="12">
         <f t="shared" si="9"/>
-        <v>-843333.33333324024</v>
+        <v>-207523.80952379014</v>
       </c>
       <c r="AU26" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.24607566346697199</v>
       </c>
       <c r="AW26" s="14"/>
       <c r="AX26" s="13" t="s">
@@ -6516,15 +6618,15 @@
       <c r="AZ26" s="12"/>
       <c r="BA26" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="BB26" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC26" s="11" t="e">
+        <v>-635809.5238094501</v>
+      </c>
+      <c r="BC26" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE26" s="14"/>
       <c r="BF26" s="13" t="s">
@@ -6734,18 +6836,23 @@
       <c r="AP27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR27" s="12"/>
+      <c r="AQ27" s="10">
+        <v>74</v>
+      </c>
+      <c r="AR27" s="12">
+        <v>2682476.1904761102</v>
+      </c>
       <c r="AS27" s="10">
         <f t="shared" si="9"/>
-        <v>-48</v>
+        <v>26</v>
       </c>
       <c r="AT27" s="12">
         <f t="shared" si="9"/>
-        <v>-1537333.3333332799</v>
+        <v>1145142.8571428303</v>
       </c>
       <c r="AU27" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.74488910915624673</v>
       </c>
       <c r="AW27" s="14"/>
       <c r="AX27" s="13" t="s">
@@ -6754,15 +6861,15 @@
       <c r="AZ27" s="12"/>
       <c r="BA27" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="BB27" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC27" s="11" t="e">
+        <v>-2682476.1904761102</v>
+      </c>
+      <c r="BC27" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE27" s="14"/>
       <c r="BF27" s="13" t="s">
@@ -6973,19 +7080,23 @@
         <v>13</v>
       </c>
       <c r="AP28" s="9"/>
-      <c r="AQ28" s="8"/>
-      <c r="AR28" s="7"/>
+      <c r="AQ28" s="8">
+        <v>555</v>
+      </c>
+      <c r="AR28" s="7">
+        <v>5037490.4761894308</v>
+      </c>
       <c r="AS28" s="27">
         <f t="shared" si="9"/>
-        <v>-565</v>
+        <v>-10</v>
       </c>
       <c r="AT28" s="28">
         <f t="shared" si="9"/>
-        <v>-4791851.9047608003</v>
+        <v>245638.5714286305</v>
       </c>
       <c r="AU28" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>5.1261720168059383E-2</v>
       </c>
       <c r="AW28" s="9" t="s">
         <v>13</v>
@@ -6995,15 +7106,15 @@
       <c r="AZ28" s="7"/>
       <c r="BA28" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-555</v>
       </c>
       <c r="BB28" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC28" s="29" t="e">
+        <v>-5037490.4761894308</v>
+      </c>
+      <c r="BC28" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE28" s="9" t="s">
         <v>13</v>
@@ -7222,10 +7333,13 @@
       <c r="AP29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AQ29" s="1">
+        <v>3298</v>
+      </c>
       <c r="AR29" s="35"/>
       <c r="AS29" s="10">
         <f t="shared" si="9"/>
-        <v>-4528</v>
+        <v>-1230</v>
       </c>
       <c r="AT29" s="12">
         <f t="shared" si="9"/>
@@ -7244,7 +7358,7 @@
       <c r="AZ29" s="35"/>
       <c r="BA29" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3298</v>
       </c>
       <c r="BB29" s="12">
         <f t="shared" si="12"/>
@@ -7711,18 +7825,23 @@
       <c r="AP31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AR31" s="12"/>
+      <c r="AQ31" s="10">
+        <v>85</v>
+      </c>
+      <c r="AR31" s="12">
+        <v>74525.714285370021</v>
+      </c>
       <c r="AS31" s="10">
         <f t="shared" si="9"/>
-        <v>-118</v>
+        <v>-33</v>
       </c>
       <c r="AT31" s="12">
         <f t="shared" si="9"/>
-        <v>-124480.95238046</v>
+        <v>-49955.238095089982</v>
       </c>
       <c r="AU31" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.40130828966031873</v>
       </c>
       <c r="AW31" s="14"/>
       <c r="AX31" s="13" t="s">
@@ -7731,15 +7850,15 @@
       <c r="AZ31" s="12"/>
       <c r="BA31" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="BB31" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="11" t="e">
+        <v>-74525.714285370021</v>
+      </c>
+      <c r="BC31" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE31" s="14"/>
       <c r="BF31" s="13" t="s">
@@ -7949,18 +8068,23 @@
       <c r="AP32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR32" s="12"/>
+      <c r="AQ32" s="10">
+        <v>67</v>
+      </c>
+      <c r="AR32" s="12">
+        <v>65083.80952372001</v>
+      </c>
       <c r="AS32" s="10">
         <f t="shared" si="9"/>
-        <v>-80</v>
+        <v>-13</v>
       </c>
       <c r="AT32" s="12">
         <f t="shared" si="9"/>
-        <v>-85572.38095224998</v>
+        <v>-20488.571428529969</v>
       </c>
       <c r="AU32" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.2394297225405326</v>
       </c>
       <c r="AW32" s="14"/>
       <c r="AX32" s="13" t="s">
@@ -7969,15 +8093,15 @@
       <c r="AZ32" s="12"/>
       <c r="BA32" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-67</v>
       </c>
       <c r="BB32" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="11" t="e">
+        <v>-65083.80952372001</v>
+      </c>
+      <c r="BC32" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE32" s="14"/>
       <c r="BF32" s="13" t="s">
@@ -8187,18 +8311,23 @@
       <c r="AP33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR33" s="12"/>
+      <c r="AQ33" s="10">
+        <v>13</v>
+      </c>
+      <c r="AR33" s="12">
+        <v>79495.238095229986</v>
+      </c>
       <c r="AS33" s="10">
         <f t="shared" si="9"/>
-        <v>-29</v>
+        <v>-16</v>
       </c>
       <c r="AT33" s="12">
         <f t="shared" si="9"/>
-        <v>-194009.52380950999</v>
+        <v>-114514.28571428001</v>
       </c>
       <c r="AU33" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.59025084679202089</v>
       </c>
       <c r="AW33" s="14"/>
       <c r="AX33" s="13" t="s">
@@ -8207,15 +8336,15 @@
       <c r="AZ33" s="12"/>
       <c r="BA33" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BB33" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="11" t="e">
+        <v>-79495.238095229986</v>
+      </c>
+      <c r="BC33" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE33" s="14"/>
       <c r="BF33" s="13" t="s">
@@ -8425,18 +8554,23 @@
       <c r="AP34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR34" s="12"/>
+      <c r="AQ34" s="10">
+        <v>17</v>
+      </c>
+      <c r="AR34" s="12">
+        <v>251714.28571425998</v>
+      </c>
       <c r="AS34" s="10">
         <f t="shared" si="9"/>
-        <v>-18</v>
+        <v>-1</v>
       </c>
       <c r="AT34" s="12">
         <f t="shared" si="9"/>
-        <v>-190666.66666663002</v>
+        <v>61047.619047629967</v>
       </c>
       <c r="AU34" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.32017982017993901</v>
       </c>
       <c r="AW34" s="14"/>
       <c r="AX34" s="13" t="s">
@@ -8445,15 +8579,15 @@
       <c r="AZ34" s="12"/>
       <c r="BA34" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BB34" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="11" t="e">
+        <v>-251714.28571425998</v>
+      </c>
+      <c r="BC34" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE34" s="14"/>
       <c r="BF34" s="13" t="s">
@@ -8886,18 +9020,23 @@
       <c r="AP36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR36" s="12"/>
+      <c r="AQ36" s="10">
+        <v>5</v>
+      </c>
+      <c r="AR36" s="12">
+        <v>17950</v>
+      </c>
       <c r="AS36" s="10">
         <f t="shared" si="9"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="AT36" s="12">
         <f t="shared" si="9"/>
-        <v>-33320</v>
+        <v>-15370</v>
       </c>
       <c r="AU36" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.46128451380552221</v>
       </c>
       <c r="AW36" s="14"/>
       <c r="AX36" s="13" t="s">
@@ -8906,15 +9045,15 @@
       <c r="AZ36" s="12"/>
       <c r="BA36" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BB36" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC36" s="11" t="e">
+        <v>-17950</v>
+      </c>
+      <c r="BC36" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE36" s="14"/>
       <c r="BF36" s="13" t="s">
@@ -9124,18 +9263,23 @@
       <c r="AP37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR37" s="12"/>
+      <c r="AQ37" s="10">
+        <v>2</v>
+      </c>
+      <c r="AR37" s="12">
+        <v>66476.190476179996</v>
+      </c>
       <c r="AS37" s="10">
         <f t="shared" si="9"/>
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AT37" s="12">
         <f t="shared" si="9"/>
-        <v>-369458.09523806005</v>
+        <v>-302981.90476188005</v>
       </c>
       <c r="AU37" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.82007109511744192</v>
       </c>
       <c r="AW37" s="14"/>
       <c r="AX37" s="13" t="s">
@@ -9144,15 +9288,15 @@
       <c r="AZ37" s="12"/>
       <c r="BA37" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BB37" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC37" s="11" t="e">
+        <v>-66476.190476179996</v>
+      </c>
+      <c r="BC37" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE37" s="14"/>
       <c r="BF37" s="13" t="s">
@@ -9362,18 +9506,23 @@
       <c r="AP38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR38" s="12"/>
+      <c r="AQ38" s="10">
+        <v>14</v>
+      </c>
+      <c r="AR38" s="12">
+        <v>245809.52380949</v>
+      </c>
       <c r="AS38" s="10">
         <f t="shared" si="9"/>
-        <v>-20</v>
+        <v>-6</v>
       </c>
       <c r="AT38" s="12">
         <f t="shared" si="9"/>
-        <v>-379999.99999995995</v>
+        <v>-134190.47619046996</v>
       </c>
       <c r="AU38" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.35313283208022128</v>
       </c>
       <c r="AW38" s="14"/>
       <c r="AX38" s="13" t="s">
@@ -9382,15 +9531,15 @@
       <c r="AZ38" s="12"/>
       <c r="BA38" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BB38" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC38" s="11" t="e">
+        <v>-245809.52380949</v>
+      </c>
+      <c r="BC38" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE38" s="14"/>
       <c r="BF38" s="13" t="s">
@@ -9600,18 +9749,23 @@
       <c r="AP39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR39" s="12"/>
+      <c r="AQ39" s="10">
+        <v>12</v>
+      </c>
+      <c r="AR39" s="12">
+        <v>393142.85714282992</v>
+      </c>
       <c r="AS39" s="10">
         <f t="shared" si="9"/>
-        <v>-18</v>
+        <v>-6</v>
       </c>
       <c r="AT39" s="12">
         <f t="shared" si="9"/>
-        <v>-651619.04761901998</v>
+        <v>-258476.19047619007</v>
       </c>
       <c r="AU39" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.39666764104064761</v>
       </c>
       <c r="AW39" s="14"/>
       <c r="AX39" s="13" t="s">
@@ -9620,15 +9774,15 @@
       <c r="AZ39" s="12"/>
       <c r="BA39" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BB39" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC39" s="11" t="e">
+        <v>-393142.85714282992</v>
+      </c>
+      <c r="BC39" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE39" s="14"/>
       <c r="BF39" s="13" t="s">
@@ -9839,19 +9993,23 @@
         <v>12</v>
       </c>
       <c r="AP40" s="9"/>
-      <c r="AQ40" s="8"/>
-      <c r="AR40" s="7"/>
+      <c r="AQ40" s="8">
+        <v>215</v>
+      </c>
+      <c r="AR40" s="7">
+        <v>1194197.6190470799</v>
+      </c>
       <c r="AS40" s="27">
         <f t="shared" si="9"/>
-        <v>-303</v>
+        <v>-88</v>
       </c>
       <c r="AT40" s="28">
         <f t="shared" si="9"/>
-        <v>-2040840.9523801701</v>
+        <v>-846643.33333309018</v>
       </c>
       <c r="AU40" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.41485022747396166</v>
       </c>
       <c r="AW40" s="9" t="s">
         <v>12</v>
@@ -9861,15 +10019,15 @@
       <c r="AZ40" s="7"/>
       <c r="BA40" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-215</v>
       </c>
       <c r="BB40" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC40" s="29" t="e">
+        <v>-1194197.6190470799</v>
+      </c>
+      <c r="BC40" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE40" s="9" t="s">
         <v>12</v>
@@ -10088,10 +10246,13 @@
       <c r="AP41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AQ41" s="1">
+        <v>1188</v>
+      </c>
       <c r="AR41" s="35"/>
       <c r="AS41" s="10">
         <f t="shared" si="9"/>
-        <v>-1393</v>
+        <v>-205</v>
       </c>
       <c r="AT41" s="12">
         <f t="shared" si="9"/>
@@ -10110,7 +10271,7 @@
       <c r="AZ41" s="35"/>
       <c r="BA41" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1188</v>
       </c>
       <c r="BB41" s="12">
         <f t="shared" si="12"/>
@@ -10577,18 +10738,23 @@
       <c r="AP43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AR43" s="12"/>
+      <c r="AQ43" s="10">
+        <v>107</v>
+      </c>
+      <c r="AR43" s="12">
+        <v>97992.380951889994</v>
+      </c>
       <c r="AS43" s="10">
         <f t="shared" si="9"/>
-        <v>-78</v>
+        <v>29</v>
       </c>
       <c r="AT43" s="12">
         <f t="shared" si="9"/>
-        <v>-80907.619047240005</v>
+        <v>17084.761904649989</v>
       </c>
       <c r="AU43" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.21116381999419126</v>
       </c>
       <c r="AW43" s="14"/>
       <c r="AX43" s="13" t="s">
@@ -10597,15 +10763,15 @@
       <c r="AZ43" s="12"/>
       <c r="BA43" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-107</v>
       </c>
       <c r="BB43" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC43" s="11" t="e">
+        <v>-97992.380951889994</v>
+      </c>
+      <c r="BC43" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE43" s="14"/>
       <c r="BF43" s="13" t="s">
@@ -10815,18 +10981,23 @@
       <c r="AP44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR44" s="12"/>
+      <c r="AQ44" s="10">
+        <v>73</v>
+      </c>
+      <c r="AR44" s="12">
+        <v>85923.809523740012</v>
+      </c>
       <c r="AS44" s="10">
         <f t="shared" si="9"/>
-        <v>-89</v>
+        <v>-16</v>
       </c>
       <c r="AT44" s="12">
         <f t="shared" si="9"/>
-        <v>-79542.857142760011</v>
+        <v>6380.9523809800012</v>
       </c>
       <c r="AU44" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>8.0220306513855158E-2</v>
       </c>
       <c r="AW44" s="14"/>
       <c r="AX44" s="13" t="s">
@@ -10835,15 +11006,15 @@
       <c r="AZ44" s="12"/>
       <c r="BA44" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="BB44" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC44" s="11" t="e">
+        <v>-85923.809523740012</v>
+      </c>
+      <c r="BC44" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE44" s="14"/>
       <c r="BF44" s="13" t="s">
@@ -11053,18 +11224,23 @@
       <c r="AP45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR45" s="12"/>
+      <c r="AQ45" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR45" s="12">
+        <v>64190.476190469999</v>
+      </c>
       <c r="AS45" s="10">
         <f t="shared" si="9"/>
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="AT45" s="12">
         <f t="shared" si="9"/>
-        <v>-84152.380952370004</v>
+        <v>-19961.904761900005</v>
       </c>
       <c r="AU45" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.2372114078768417</v>
       </c>
       <c r="AW45" s="14"/>
       <c r="AX45" s="13" t="s">
@@ -11073,15 +11249,15 @@
       <c r="AZ45" s="12"/>
       <c r="BA45" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB45" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC45" s="11" t="e">
+        <v>-64190.476190469999</v>
+      </c>
+      <c r="BC45" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE45" s="14"/>
       <c r="BF45" s="13" t="s">
@@ -11291,18 +11467,23 @@
       <c r="AP46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR46" s="12"/>
+      <c r="AQ46" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR46" s="12">
+        <v>114285.71428568001</v>
+      </c>
       <c r="AS46" s="10">
         <f t="shared" si="9"/>
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="AT46" s="12">
         <f t="shared" si="9"/>
-        <v>-106761.90476187001</v>
+        <v>7523.8095238099922</v>
       </c>
       <c r="AU46" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>7.0472792149893521E-2</v>
       </c>
       <c r="AW46" s="14"/>
       <c r="AX46" s="13" t="s">
@@ -11311,15 +11492,15 @@
       <c r="AZ46" s="12"/>
       <c r="BA46" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB46" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC46" s="11" t="e">
+        <v>-114285.71428568001</v>
+      </c>
+      <c r="BC46" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE46" s="14"/>
       <c r="BF46" s="13" t="s">
@@ -11519,18 +11700,23 @@
       <c r="AP47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR47" s="12"/>
+      <c r="AQ47" s="10">
+        <v>1</v>
+      </c>
+      <c r="AR47" s="12">
+        <v>2657.1428571400002</v>
+      </c>
       <c r="AS47" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT47" s="12">
         <f t="shared" si="9"/>
-        <v>-5714.2857142800003</v>
+        <v>-3057.1428571400002</v>
       </c>
       <c r="AU47" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.535000000000035</v>
       </c>
       <c r="AW47" s="14"/>
       <c r="AX47" s="13" t="s">
@@ -11539,15 +11725,15 @@
       <c r="AZ47" s="12"/>
       <c r="BA47" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BB47" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC47" s="11" t="e">
+        <v>-2657.1428571400002</v>
+      </c>
+      <c r="BC47" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE47" s="14"/>
       <c r="BF47" s="13" t="s">
@@ -11752,18 +11938,23 @@
       <c r="AP48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR48" s="12"/>
+      <c r="AQ48" s="10">
+        <v>2</v>
+      </c>
+      <c r="AR48" s="12">
+        <v>15380</v>
+      </c>
       <c r="AS48" s="10">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT48" s="12">
         <f t="shared" si="9"/>
-        <v>-7290</v>
+        <v>8090</v>
       </c>
       <c r="AU48" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.1097393689986284</v>
       </c>
       <c r="AW48" s="14"/>
       <c r="AX48" s="13" t="s">
@@ -11772,15 +11963,15 @@
       <c r="AZ48" s="12"/>
       <c r="BA48" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BB48" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC48" s="11" t="e">
+        <v>-15380</v>
+      </c>
+      <c r="BC48" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE48" s="14"/>
       <c r="BF48" s="13" t="s">
@@ -11985,18 +12176,23 @@
       <c r="AP49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR49" s="12"/>
+      <c r="AQ49" s="10">
+        <v>4</v>
+      </c>
+      <c r="AR49" s="12">
+        <v>155101.90476190002</v>
+      </c>
       <c r="AS49" s="10">
         <f t="shared" si="9"/>
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="AT49" s="12">
         <f t="shared" si="9"/>
-        <v>-297597.14285711001</v>
+        <v>-142495.23809520999</v>
       </c>
       <c r="AU49" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.47881924109610308</v>
       </c>
       <c r="AW49" s="14"/>
       <c r="AX49" s="13" t="s">
@@ -12005,15 +12201,15 @@
       <c r="AZ49" s="12"/>
       <c r="BA49" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BB49" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC49" s="11" t="e">
+        <v>-155101.90476190002</v>
+      </c>
+      <c r="BC49" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE49" s="14"/>
       <c r="BF49" s="13" t="s">
@@ -12223,18 +12419,23 @@
       <c r="AP50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR50" s="12"/>
+      <c r="AQ50" s="10">
+        <v>15</v>
+      </c>
+      <c r="AR50" s="12">
+        <v>240285.71428568001</v>
+      </c>
       <c r="AS50" s="10">
         <f t="shared" si="9"/>
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="AT50" s="12">
         <f t="shared" si="9"/>
-        <v>-152285.71428568999</v>
+        <v>87999.999999990017</v>
       </c>
       <c r="AU50" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.57786116322704351</v>
       </c>
       <c r="AW50" s="14"/>
       <c r="AX50" s="13" t="s">
@@ -12243,15 +12444,15 @@
       <c r="AZ50" s="12"/>
       <c r="BA50" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BB50" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC50" s="11" t="e">
+        <v>-240285.71428568001</v>
+      </c>
+      <c r="BC50" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE50" s="14"/>
       <c r="BF50" s="13" t="s">
@@ -12461,18 +12662,23 @@
       <c r="AP51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR51" s="12"/>
+      <c r="AQ51" s="10">
+        <v>16</v>
+      </c>
+      <c r="AR51" s="12">
+        <v>496571.42857141001</v>
+      </c>
       <c r="AS51" s="10">
         <f t="shared" si="9"/>
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="AT51" s="12">
         <f t="shared" si="9"/>
-        <v>-681809.52380949003</v>
+        <v>-185238.09523808002</v>
       </c>
       <c r="AU51" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.27168598966335195</v>
       </c>
       <c r="AW51" s="14"/>
       <c r="AX51" s="13" t="s">
@@ -12481,15 +12687,15 @@
       <c r="AZ51" s="12"/>
       <c r="BA51" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BB51" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC51" s="11" t="e">
+        <v>-496571.42857141001</v>
+      </c>
+      <c r="BC51" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE51" s="14"/>
       <c r="BF51" s="13" t="s">
@@ -12700,19 +12906,23 @@
         <v>11</v>
       </c>
       <c r="AP52" s="9"/>
-      <c r="AQ52" s="8"/>
-      <c r="AR52" s="7"/>
+      <c r="AQ52" s="8">
+        <v>238</v>
+      </c>
+      <c r="AR52" s="7">
+        <v>1272388.5714279101</v>
+      </c>
       <c r="AS52" s="27">
         <f t="shared" si="9"/>
-        <v>-232</v>
+        <v>6</v>
       </c>
       <c r="AT52" s="28">
         <f t="shared" si="9"/>
-        <v>-1496061.42857081</v>
+        <v>-223672.85714289988</v>
       </c>
       <c r="AU52" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.14950780286914753</v>
       </c>
       <c r="AW52" s="9" t="s">
         <v>11</v>
@@ -12722,15 +12932,15 @@
       <c r="AZ52" s="7"/>
       <c r="BA52" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-238</v>
       </c>
       <c r="BB52" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC52" s="29" t="e">
+        <v>-1272388.5714279101</v>
+      </c>
+      <c r="BC52" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE52" s="9" t="s">
         <v>11</v>
@@ -13424,18 +13634,23 @@
       <c r="AP55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AR55" s="12"/>
+      <c r="AQ55" s="10">
+        <v>110</v>
+      </c>
+      <c r="AR55" s="12">
+        <v>108883.80952334993</v>
+      </c>
       <c r="AS55" s="10">
         <f t="shared" si="9"/>
-        <v>-128</v>
+        <v>-18</v>
       </c>
       <c r="AT55" s="12">
         <f t="shared" si="9"/>
-        <v>-119866.66666608992</v>
+        <v>-10982.857142739987</v>
       </c>
       <c r="AU55" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-9.1625615763010274E-2</v>
       </c>
       <c r="AW55" s="14"/>
       <c r="AX55" s="13" t="s">
@@ -13444,15 +13659,15 @@
       <c r="AZ55" s="12"/>
       <c r="BA55" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-110</v>
       </c>
       <c r="BB55" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC55" s="11" t="e">
+        <v>-108883.80952334993</v>
+      </c>
+      <c r="BC55" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE55" s="14"/>
       <c r="BF55" s="13" t="s">
@@ -13662,18 +13877,23 @@
       <c r="AP56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR56" s="12"/>
+      <c r="AQ56" s="10">
+        <v>76</v>
+      </c>
+      <c r="AR56" s="12">
+        <v>74323.809523749995</v>
+      </c>
       <c r="AS56" s="10">
         <f t="shared" si="9"/>
-        <v>-82</v>
+        <v>-6</v>
       </c>
       <c r="AT56" s="12">
         <f t="shared" si="9"/>
-        <v>-70076.190476100004</v>
+        <v>4247.6190476499905</v>
       </c>
       <c r="AU56" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>6.061429736393379E-2</v>
       </c>
       <c r="AW56" s="14"/>
       <c r="AX56" s="13" t="s">
@@ -13682,15 +13902,15 @@
       <c r="AZ56" s="12"/>
       <c r="BA56" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="BB56" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC56" s="11" t="e">
+        <v>-74323.809523749995</v>
+      </c>
+      <c r="BC56" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE56" s="14"/>
       <c r="BF56" s="13" t="s">
@@ -13900,18 +14120,23 @@
       <c r="AP57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR57" s="12"/>
+      <c r="AQ57" s="10">
+        <v>15</v>
+      </c>
+      <c r="AR57" s="12">
+        <v>106523.8095238</v>
+      </c>
       <c r="AS57" s="10">
         <f t="shared" si="9"/>
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="AT57" s="12">
         <f t="shared" si="9"/>
-        <v>-85580.952380939998</v>
+        <v>20942.857142859997</v>
       </c>
       <c r="AU57" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.24471399955493189</v>
       </c>
       <c r="AW57" s="14"/>
       <c r="AX57" s="13" t="s">
@@ -13920,15 +14145,15 @@
       <c r="AZ57" s="12"/>
       <c r="BA57" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BB57" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC57" s="11" t="e">
+        <v>-106523.8095238</v>
+      </c>
+      <c r="BC57" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE57" s="14"/>
       <c r="BF57" s="13" t="s">
@@ -14138,18 +14363,23 @@
       <c r="AP58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR58" s="12"/>
+      <c r="AQ58" s="10">
+        <v>20</v>
+      </c>
+      <c r="AR58" s="12">
+        <v>241523.80952376002</v>
+      </c>
       <c r="AS58" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>13</v>
       </c>
       <c r="AT58" s="12">
         <f t="shared" si="9"/>
-        <v>-105999.99999996999</v>
+        <v>135523.80952379003</v>
       </c>
       <c r="AU58" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.2785265049417773</v>
       </c>
       <c r="AW58" s="14"/>
       <c r="AX58" s="13" t="s">
@@ -14158,15 +14388,15 @@
       <c r="AZ58" s="12"/>
       <c r="BA58" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BB58" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC58" s="11" t="e">
+        <v>-241523.80952376002</v>
+      </c>
+      <c r="BC58" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE58" s="14"/>
       <c r="BF58" s="13" t="s">
@@ -14352,14 +14582,19 @@
       <c r="AP59" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR59" s="12"/>
+      <c r="AQ59" s="10">
+        <v>1</v>
+      </c>
+      <c r="AR59" s="12">
+        <v>2857.1428571400002</v>
+      </c>
       <c r="AS59" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT59" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2857.1428571400002</v>
       </c>
       <c r="AU59" s="11" t="e">
         <f t="shared" si="10"/>
@@ -14372,15 +14607,15 @@
       <c r="AZ59" s="12"/>
       <c r="BA59" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BB59" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC59" s="11" t="e">
+        <v>-2857.1428571400002</v>
+      </c>
+      <c r="BC59" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE59" s="14"/>
       <c r="BF59" s="13" t="s">
@@ -14590,18 +14825,23 @@
       <c r="AP60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR60" s="12"/>
+      <c r="AQ60" s="10">
+        <v>3</v>
+      </c>
+      <c r="AR60" s="12">
+        <v>8070</v>
+      </c>
       <c r="AS60" s="10">
         <f t="shared" si="9"/>
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="AT60" s="12">
         <f t="shared" si="9"/>
-        <v>-36520</v>
+        <v>-28450</v>
       </c>
       <c r="AU60" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.77902519167579409</v>
       </c>
       <c r="AW60" s="14"/>
       <c r="AX60" s="13" t="s">
@@ -14610,15 +14850,15 @@
       <c r="AZ60" s="12"/>
       <c r="BA60" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB60" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC60" s="11" t="e">
+        <v>-8070</v>
+      </c>
+      <c r="BC60" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE60" s="14"/>
       <c r="BF60" s="13" t="s">
@@ -14828,18 +15068,23 @@
       <c r="AP61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR61" s="12"/>
+      <c r="AQ61" s="10">
+        <v>2</v>
+      </c>
+      <c r="AR61" s="12">
+        <v>40761.904761900005</v>
+      </c>
       <c r="AS61" s="10">
         <f t="shared" si="9"/>
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AT61" s="12">
         <f t="shared" si="9"/>
-        <v>-397971.42857137998</v>
+        <v>-357209.52380947996</v>
       </c>
       <c r="AU61" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.89757580108646173</v>
       </c>
       <c r="AW61" s="14"/>
       <c r="AX61" s="13" t="s">
@@ -14848,15 +15093,15 @@
       <c r="AZ61" s="12"/>
       <c r="BA61" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BB61" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC61" s="11" t="e">
+        <v>-40761.904761900005</v>
+      </c>
+      <c r="BC61" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE61" s="14"/>
       <c r="BF61" s="13" t="s">
@@ -15066,18 +15311,23 @@
       <c r="AP62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR62" s="12"/>
+      <c r="AQ62" s="10">
+        <v>17</v>
+      </c>
+      <c r="AR62" s="12">
+        <v>311714.28571424005</v>
+      </c>
       <c r="AS62" s="10">
         <f t="shared" si="9"/>
-        <v>-20</v>
+        <v>-3</v>
       </c>
       <c r="AT62" s="12">
         <f t="shared" si="9"/>
-        <v>-407142.85714280012</v>
+        <v>-95428.57142856007</v>
       </c>
       <c r="AU62" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.23438596491228564</v>
       </c>
       <c r="AW62" s="14"/>
       <c r="AX62" s="13" t="s">
@@ -15086,15 +15336,15 @@
       <c r="AZ62" s="12"/>
       <c r="BA62" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BB62" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC62" s="11" t="e">
+        <v>-311714.28571424005</v>
+      </c>
+      <c r="BC62" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE62" s="14"/>
       <c r="BF62" s="13" t="s">
@@ -15304,18 +15554,23 @@
       <c r="AP63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR63" s="12"/>
+      <c r="AQ63" s="10">
+        <v>16</v>
+      </c>
+      <c r="AR63" s="12">
+        <v>560380.95238092996</v>
+      </c>
       <c r="AS63" s="10">
         <f t="shared" si="9"/>
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="AT63" s="12">
         <f t="shared" si="9"/>
-        <v>-510952.38095235999</v>
+        <v>49428.571428569965</v>
       </c>
       <c r="AU63" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>9.6738117427773704E-2</v>
       </c>
       <c r="AW63" s="14"/>
       <c r="AX63" s="13" t="s">
@@ -15324,15 +15579,15 @@
       <c r="AZ63" s="12"/>
       <c r="BA63" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BB63" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC63" s="11" t="e">
+        <v>-560380.95238092996</v>
+      </c>
+      <c r="BC63" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE63" s="14"/>
       <c r="BF63" s="13" t="s">
@@ -15543,19 +15798,23 @@
         <v>1</v>
       </c>
       <c r="AP64" s="9"/>
-      <c r="AQ64" s="8"/>
-      <c r="AR64" s="7"/>
+      <c r="AQ64" s="8">
+        <v>260</v>
+      </c>
+      <c r="AR64" s="7">
+        <v>1455039.52380887</v>
+      </c>
       <c r="AS64" s="27">
         <f t="shared" si="9"/>
-        <v>-286</v>
+        <v>-26</v>
       </c>
       <c r="AT64" s="28">
         <f t="shared" si="9"/>
-        <v>-1734110.4761896399</v>
+        <v>-279070.95238076989</v>
       </c>
       <c r="AU64" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.16093031915358263</v>
       </c>
       <c r="AW64" s="9" t="s">
         <v>1</v>
@@ -15565,15 +15824,15 @@
       <c r="AZ64" s="7"/>
       <c r="BA64" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="BB64" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC64" s="29" t="e">
+        <v>-1455039.52380887</v>
+      </c>
+      <c r="BC64" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE64" s="9" t="s">
         <v>1</v>
@@ -15790,19 +16049,23 @@
         <v>0</v>
       </c>
       <c r="AP65" s="4"/>
-      <c r="AQ65" s="3"/>
-      <c r="AR65" s="2"/>
+      <c r="AQ65" s="3">
+        <v>2062</v>
+      </c>
+      <c r="AR65" s="2">
+        <v>18647415.238091029</v>
+      </c>
       <c r="AS65" s="6">
         <f t="shared" si="9"/>
-        <v>-2341</v>
+        <v>-279</v>
       </c>
       <c r="AT65" s="5">
         <f t="shared" si="9"/>
-        <v>-20474951.904757049</v>
+        <v>-1827536.6666660197</v>
       </c>
       <c r="AU65" s="30">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-8.9257189719767732E-2</v>
       </c>
       <c r="AW65" s="4" t="s">
         <v>0</v>
@@ -15812,15 +16075,15 @@
       <c r="AZ65" s="2"/>
       <c r="BA65" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2062</v>
       </c>
       <c r="BB65" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC65" s="30" t="e">
+        <v>-18647415.238091029</v>
+      </c>
+      <c r="BC65" s="30">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FD10B9-911A-914F-B60C-EAC33B376122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A0BA5F-FD36-4443-B3FA-CD44AE65B7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7940" yWindow="700" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="11920" yWindow="1300" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -1750,10 +1750,13 @@
       <c r="AP6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AQ6" s="15">
+        <v>15</v>
+      </c>
       <c r="AR6" s="33"/>
       <c r="AS6" s="10">
         <f t="shared" si="9"/>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="AT6" s="12">
         <f t="shared" si="9"/>
@@ -1770,7 +1773,7 @@
       <c r="AZ6" s="33"/>
       <c r="BA6" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BB6" s="12">
         <f t="shared" si="12"/>
@@ -4674,10 +4677,13 @@
       <c r="AP18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AQ18" s="1">
+        <v>14</v>
+      </c>
       <c r="AR18" s="35"/>
       <c r="AS18" s="10">
         <f t="shared" si="9"/>
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="AT18" s="12">
         <f t="shared" si="9"/>
@@ -4694,7 +4700,7 @@
       <c r="AZ18" s="35"/>
       <c r="BA18" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BB18" s="12">
         <f t="shared" si="12"/>
@@ -7583,10 +7589,13 @@
       <c r="AP30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AQ30" s="1">
+        <v>3</v>
+      </c>
       <c r="AR30" s="35"/>
       <c r="AS30" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT30" s="12">
         <f t="shared" si="9"/>
@@ -7603,7 +7612,7 @@
       <c r="AZ30" s="35"/>
       <c r="BA30" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB30" s="12">
         <f t="shared" si="12"/>
@@ -10496,10 +10505,13 @@
       <c r="AP42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AQ42" s="1">
+        <v>3</v>
+      </c>
       <c r="AR42" s="35"/>
       <c r="AS42" s="10">
         <f t="shared" si="9"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AT42" s="12">
         <f t="shared" si="9"/>
@@ -10516,7 +10528,7 @@
       <c r="AZ42" s="35"/>
       <c r="BA42" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB42" s="12">
         <f t="shared" si="12"/>
@@ -13392,10 +13404,13 @@
       <c r="AP54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AQ54" s="1">
+        <v>2</v>
+      </c>
       <c r="AR54" s="35"/>
       <c r="AS54" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AT54" s="12">
         <f t="shared" si="9"/>
@@ -13412,7 +13427,7 @@
       <c r="AZ54" s="35"/>
       <c r="BA54" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BB54" s="12">
         <f t="shared" si="12"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A0BA5F-FD36-4443-B3FA-CD44AE65B7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5211C908-E5C9-D74A-82FB-6F45774AC60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11920" yWindow="1300" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="36">
   <si>
     <t>總計</t>
   </si>
@@ -192,6 +192,14 @@
   </si>
   <si>
     <t>05/03~05/09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/10~05/16</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1053,7 +1061,9 @@
       </c>
       <c r="AP1" s="26"/>
       <c r="AR1" s="25"/>
-      <c r="AW1" s="26"/>
+      <c r="AW1" s="26" t="s">
+        <v>34</v>
+      </c>
       <c r="AX1" s="26"/>
       <c r="AZ1" s="25"/>
       <c r="BE1" s="26"/>
@@ -1109,6 +1119,9 @@
       <c r="AQ2" s="22"/>
       <c r="AR2" s="22"/>
       <c r="AT2" s="21"/>
+      <c r="AW2" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="AY2" s="22"/>
       <c r="AZ2" s="22"/>
       <c r="BB2" s="21"/>
@@ -1513,11 +1526,13 @@
       <c r="AX5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AY5" s="40"/>
+      <c r="AY5" s="40">
+        <v>5761</v>
+      </c>
       <c r="AZ5" s="1"/>
       <c r="BA5" s="10">
         <f t="shared" ref="BA5:BA65" si="11">AY5-AQ5</f>
-        <v>-6004</v>
+        <v>-243</v>
       </c>
       <c r="BB5" s="12">
         <f t="shared" ref="BB5:BB65" si="12">AZ5-AR5</f>
@@ -1538,7 +1553,7 @@
       <c r="BH5" s="1"/>
       <c r="BI5" s="10">
         <f t="shared" ref="BI5:BI65" si="14">BG5-AY5</f>
-        <v>0</v>
+        <v>-5761</v>
       </c>
       <c r="BJ5" s="12">
         <f t="shared" ref="BJ5:BJ65" si="15">BH5-AZ5</f>
@@ -2013,18 +2028,23 @@
       <c r="AX7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AZ7" s="12"/>
+      <c r="AY7" s="10">
+        <v>143</v>
+      </c>
+      <c r="AZ7" s="12">
+        <v>188053.33333271995</v>
+      </c>
       <c r="BA7" s="10">
         <f t="shared" si="11"/>
-        <v>-202</v>
+        <v>-59</v>
       </c>
       <c r="BB7" s="12">
         <f t="shared" si="12"/>
-        <v>-198379.04761833997</v>
+        <v>-10325.714285620023</v>
       </c>
       <c r="BC7" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-5.2050427752257336E-2</v>
       </c>
       <c r="BE7" s="14"/>
       <c r="BF7" s="13" t="s">
@@ -2033,15 +2053,15 @@
       <c r="BH7" s="12"/>
       <c r="BI7" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-143</v>
       </c>
       <c r="BJ7" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK7" s="11" t="e">
+        <v>-188053.33333271995</v>
+      </c>
+      <c r="BK7" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM7" s="14"/>
       <c r="BN7" s="13" t="s">
@@ -2256,18 +2276,23 @@
       <c r="AX8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ8" s="12"/>
+      <c r="AY8" s="10">
+        <v>191</v>
+      </c>
+      <c r="AZ8" s="12">
+        <v>307257.14285700995</v>
+      </c>
       <c r="BA8" s="10">
         <f t="shared" si="11"/>
-        <v>-214</v>
+        <v>-23</v>
       </c>
       <c r="BB8" s="12">
         <f t="shared" si="12"/>
-        <v>-356401.90476171992</v>
+        <v>-49144.761904709972</v>
       </c>
       <c r="BC8" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.1378914120494579</v>
       </c>
       <c r="BE8" s="14"/>
       <c r="BF8" s="13" t="s">
@@ -2276,15 +2301,15 @@
       <c r="BH8" s="12"/>
       <c r="BI8" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-191</v>
       </c>
       <c r="BJ8" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK8" s="11" t="e">
+        <v>-307257.14285700995</v>
+      </c>
+      <c r="BK8" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM8" s="14"/>
       <c r="BN8" s="13" t="s">
@@ -2499,18 +2524,23 @@
       <c r="AX9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ9" s="12"/>
+      <c r="AY9" s="10">
+        <v>68</v>
+      </c>
+      <c r="AZ9" s="12">
+        <v>503638.09523805999</v>
+      </c>
       <c r="BA9" s="10">
         <f t="shared" si="11"/>
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="BB9" s="12">
         <f t="shared" si="12"/>
-        <v>-427923.80952379003</v>
+        <v>75714.285714269965</v>
       </c>
       <c r="BC9" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.17693403365082144</v>
       </c>
       <c r="BE9" s="14"/>
       <c r="BF9" s="13" t="s">
@@ -2519,15 +2549,15 @@
       <c r="BH9" s="12"/>
       <c r="BI9" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="BJ9" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK9" s="11" t="e">
+        <v>-503638.09523805999</v>
+      </c>
+      <c r="BK9" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM9" s="14"/>
       <c r="BN9" s="13" t="s">
@@ -2742,18 +2772,23 @@
       <c r="AX10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ10" s="12"/>
+      <c r="AY10" s="10">
+        <v>50</v>
+      </c>
+      <c r="AZ10" s="12">
+        <v>656190.47619036003</v>
+      </c>
       <c r="BA10" s="10">
         <f t="shared" si="11"/>
-        <v>-59</v>
+        <v>-9</v>
       </c>
       <c r="BB10" s="12">
         <f t="shared" si="12"/>
-        <v>-820004.76190469007</v>
+        <v>-163814.28571433004</v>
       </c>
       <c r="BC10" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.19977235904560556</v>
       </c>
       <c r="BE10" s="14"/>
       <c r="BF10" s="13" t="s">
@@ -2762,15 +2797,15 @@
       <c r="BH10" s="12"/>
       <c r="BI10" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="BJ10" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK10" s="11" t="e">
+        <v>-656190.47619036003</v>
+      </c>
+      <c r="BK10" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM10" s="14"/>
       <c r="BN10" s="13" t="s">
@@ -2980,18 +3015,23 @@
       <c r="AX11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ11" s="12"/>
+      <c r="AY11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="12">
+        <v>8857.1428571399993</v>
+      </c>
       <c r="BA11" s="10">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BB11" s="12">
         <f t="shared" si="12"/>
-        <v>-2657.1428571400002</v>
+        <v>6199.9999999999991</v>
       </c>
       <c r="BC11" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>2.3333333333358417</v>
       </c>
       <c r="BE11" s="14"/>
       <c r="BF11" s="13" t="s">
@@ -3000,15 +3040,15 @@
       <c r="BH11" s="12"/>
       <c r="BI11" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK11" s="11" t="e">
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="BK11" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM11" s="14"/>
       <c r="BN11" s="13" t="s">
@@ -3223,18 +3263,23 @@
       <c r="AX12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ12" s="12"/>
+      <c r="AY12" s="10">
+        <v>18</v>
+      </c>
+      <c r="AZ12" s="12">
+        <v>87850</v>
+      </c>
       <c r="BA12" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="BB12" s="12">
         <f t="shared" si="12"/>
-        <v>-40420</v>
+        <v>47430</v>
       </c>
       <c r="BC12" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>1.1734289955467589</v>
       </c>
       <c r="BE12" s="14"/>
       <c r="BF12" s="13" t="s">
@@ -3243,15 +3288,15 @@
       <c r="BH12" s="12"/>
       <c r="BI12" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK12" s="11" t="e">
+        <v>-87850</v>
+      </c>
+      <c r="BK12" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM12" s="14"/>
       <c r="BN12" s="13" t="s">
@@ -3466,18 +3511,23 @@
       <c r="AX13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ13" s="12"/>
+      <c r="AY13" s="10">
+        <v>27</v>
+      </c>
+      <c r="AZ13" s="12">
+        <v>1004395.2380951699</v>
+      </c>
       <c r="BA13" s="10">
         <f t="shared" si="11"/>
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="BB13" s="12">
         <f t="shared" si="12"/>
-        <v>-1014895.2380951601</v>
+        <v>-10499.999999990221</v>
       </c>
       <c r="BC13" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-1.0345895424337092E-2</v>
       </c>
       <c r="BE13" s="14"/>
       <c r="BF13" s="13" t="s">
@@ -3486,15 +3536,15 @@
       <c r="BH13" s="12"/>
       <c r="BI13" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="BJ13" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK13" s="11" t="e">
+        <v>-1004395.2380951699</v>
+      </c>
+      <c r="BK13" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM13" s="14"/>
       <c r="BN13" s="13" t="s">
@@ -3709,18 +3759,23 @@
       <c r="AX14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ14" s="12"/>
+      <c r="AY14" s="10">
+        <v>56</v>
+      </c>
+      <c r="AZ14" s="12">
+        <v>1272679.9999998901</v>
+      </c>
       <c r="BA14" s="10">
         <f t="shared" si="11"/>
-        <v>-80</v>
+        <v>-24</v>
       </c>
       <c r="BB14" s="12">
         <f t="shared" si="12"/>
-        <v>-1749238.0952379704</v>
+        <v>-476558.09523808025</v>
       </c>
       <c r="BC14" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.27243752381990527</v>
       </c>
       <c r="BE14" s="14"/>
       <c r="BF14" s="13" t="s">
@@ -3729,15 +3784,15 @@
       <c r="BH14" s="12"/>
       <c r="BI14" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="11" t="e">
+        <v>-1272679.9999998901</v>
+      </c>
+      <c r="BK14" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM14" s="14"/>
       <c r="BN14" s="13" t="s">
@@ -3952,18 +4007,23 @@
       <c r="AX15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ15" s="12"/>
+      <c r="AY15" s="10">
+        <v>58</v>
+      </c>
+      <c r="AZ15" s="12">
+        <v>2142095.2380951699</v>
+      </c>
       <c r="BA15" s="10">
         <f t="shared" si="11"/>
-        <v>-137</v>
+        <v>-79</v>
       </c>
       <c r="BB15" s="12">
         <f t="shared" si="12"/>
-        <v>-5078379.0476189293</v>
+        <v>-2936283.8095237594</v>
       </c>
       <c r="BC15" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.57819311673879048</v>
       </c>
       <c r="BE15" s="14"/>
       <c r="BF15" s="13" t="s">
@@ -3972,15 +4032,15 @@
       <c r="BH15" s="12"/>
       <c r="BI15" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK15" s="11" t="e">
+        <v>-2142095.2380951699</v>
+      </c>
+      <c r="BK15" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM15" s="14"/>
       <c r="BN15" s="13" t="s">
@@ -4196,19 +4256,23 @@
         <v>19</v>
       </c>
       <c r="AX16" s="9"/>
-      <c r="AY16" s="8"/>
-      <c r="AZ16" s="7"/>
+      <c r="AY16" s="8">
+        <v>612</v>
+      </c>
+      <c r="AZ16" s="7">
+        <v>6171016.6666655196</v>
+      </c>
       <c r="BA16" s="27">
         <f t="shared" si="11"/>
-        <v>-794</v>
+        <v>-182</v>
       </c>
       <c r="BB16" s="28">
         <f t="shared" si="12"/>
-        <v>-9688299.0476177391</v>
+        <v>-3517282.3809522195</v>
       </c>
       <c r="BC16" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.36304436554495972</v>
       </c>
       <c r="BE16" s="9" t="s">
         <v>19</v>
@@ -4218,15 +4282,15 @@
       <c r="BH16" s="7"/>
       <c r="BI16" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-612</v>
       </c>
       <c r="BJ16" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK16" s="29" t="e">
+        <v>-6171016.6666655196</v>
+      </c>
+      <c r="BK16" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM16" s="9" t="s">
         <v>19</v>
@@ -4449,10 +4513,13 @@
       <c r="AX17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AY17" s="1">
+        <v>4372</v>
+      </c>
       <c r="AZ17" s="35"/>
       <c r="BA17" s="10">
         <f t="shared" si="11"/>
-        <v>-4360</v>
+        <v>12</v>
       </c>
       <c r="BB17" s="12">
         <f t="shared" si="12"/>
@@ -4471,7 +4538,7 @@
       <c r="BH17" s="35"/>
       <c r="BI17" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-4372</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="15"/>
@@ -4944,18 +5011,23 @@
       <c r="AX19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AZ19" s="12"/>
+      <c r="AY19" s="10">
+        <v>158</v>
+      </c>
+      <c r="AZ19" s="12">
+        <v>186339.99999941007</v>
+      </c>
       <c r="BA19" s="10">
         <f t="shared" si="11"/>
-        <v>-157</v>
+        <v>1</v>
       </c>
       <c r="BB19" s="12">
         <f t="shared" si="12"/>
-        <v>-172610.47618982001</v>
+        <v>13729.523809590057</v>
       </c>
       <c r="BC19" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>7.9540501322131099E-2</v>
       </c>
       <c r="BE19" s="14"/>
       <c r="BF19" s="13" t="s">
@@ -4964,15 +5036,15 @@
       <c r="BH19" s="12"/>
       <c r="BI19" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-158</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK19" s="11" t="e">
+        <v>-186339.99999941007</v>
+      </c>
+      <c r="BK19" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM19" s="14"/>
       <c r="BN19" s="13" t="s">
@@ -5187,18 +5259,23 @@
       <c r="AX20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ20" s="12"/>
+      <c r="AY20" s="10">
+        <v>150</v>
+      </c>
+      <c r="AZ20" s="12">
+        <v>203866.66666649005</v>
+      </c>
       <c r="BA20" s="10">
         <f t="shared" si="11"/>
-        <v>-174</v>
+        <v>-24</v>
       </c>
       <c r="BB20" s="12">
         <f t="shared" si="12"/>
-        <v>-188534.28571418999</v>
+        <v>15332.380952300067</v>
       </c>
       <c r="BC20" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>8.1324099190867111E-2</v>
       </c>
       <c r="BE20" s="14"/>
       <c r="BF20" s="13" t="s">
@@ -5207,15 +5284,15 @@
       <c r="BH20" s="12"/>
       <c r="BI20" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK20" s="11" t="e">
+        <v>-203866.66666649005</v>
+      </c>
+      <c r="BK20" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM20" s="14"/>
       <c r="BN20" s="13" t="s">
@@ -5430,18 +5507,23 @@
       <c r="AX21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ21" s="12"/>
+      <c r="AY21" s="10">
+        <v>46</v>
+      </c>
+      <c r="AZ21" s="12">
+        <v>305752.38095235999</v>
+      </c>
       <c r="BA21" s="10">
         <f t="shared" si="11"/>
-        <v>-42</v>
+        <v>4</v>
       </c>
       <c r="BB21" s="12">
         <f t="shared" si="12"/>
-        <v>-262457.14285713003</v>
+        <v>43295.238095229957</v>
       </c>
       <c r="BC21" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.16496117279916422</v>
       </c>
       <c r="BE21" s="14"/>
       <c r="BF21" s="13" t="s">
@@ -5450,15 +5532,15 @@
       <c r="BH21" s="12"/>
       <c r="BI21" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK21" s="11" t="e">
+        <v>-305752.38095235999</v>
+      </c>
+      <c r="BK21" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM21" s="14"/>
       <c r="BN21" s="13" t="s">
@@ -5673,18 +5755,23 @@
       <c r="AX22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ22" s="12"/>
+      <c r="AY22" s="10">
+        <v>22</v>
+      </c>
+      <c r="AZ22" s="12">
+        <v>295047.61904756998</v>
+      </c>
       <c r="BA22" s="10">
         <f t="shared" si="11"/>
-        <v>-48</v>
+        <v>-26</v>
       </c>
       <c r="BB22" s="12">
         <f t="shared" si="12"/>
-        <v>-592190.47619040008</v>
+        <v>-297142.85714283009</v>
       </c>
       <c r="BC22" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.50176905757480172</v>
       </c>
       <c r="BE22" s="14"/>
       <c r="BF22" s="13" t="s">
@@ -5693,15 +5780,15 @@
       <c r="BH22" s="12"/>
       <c r="BI22" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK22" s="11" t="e">
+        <v>-295047.61904756998</v>
+      </c>
+      <c r="BK22" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM22" s="14"/>
       <c r="BN22" s="13" t="s">
@@ -5892,7 +5979,12 @@
       <c r="AX23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ23" s="12"/>
+      <c r="AY23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="12">
+        <v>0</v>
+      </c>
       <c r="BA23" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -6135,18 +6227,23 @@
       <c r="AX24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ24" s="12"/>
+      <c r="AY24" s="10">
+        <v>21</v>
+      </c>
+      <c r="AZ24" s="12">
+        <v>84960</v>
+      </c>
       <c r="BA24" s="10">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="BB24" s="12">
         <f t="shared" si="12"/>
-        <v>-71260</v>
+        <v>13700</v>
       </c>
       <c r="BC24" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.19225371877631209</v>
       </c>
       <c r="BE24" s="14"/>
       <c r="BF24" s="13" t="s">
@@ -6155,15 +6252,15 @@
       <c r="BH24" s="12"/>
       <c r="BI24" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK24" s="11" t="e">
+        <v>-84960</v>
+      </c>
+      <c r="BK24" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM24" s="14"/>
       <c r="BN24" s="13" t="s">
@@ -6378,18 +6475,23 @@
       <c r="AX25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ25" s="12"/>
+      <c r="AY25" s="10">
+        <v>29</v>
+      </c>
+      <c r="AZ25" s="12">
+        <v>923890.4761904201</v>
+      </c>
       <c r="BA25" s="10">
         <f t="shared" si="11"/>
-        <v>-11</v>
+        <v>18</v>
       </c>
       <c r="BB25" s="12">
         <f t="shared" si="12"/>
-        <v>-432152.38095233002</v>
+        <v>491738.09523809009</v>
       </c>
       <c r="BC25" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>1.1378812588153548</v>
       </c>
       <c r="BE25" s="14"/>
       <c r="BF25" s="13" t="s">
@@ -6398,15 +6500,15 @@
       <c r="BH25" s="12"/>
       <c r="BI25" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK25" s="11" t="e">
+        <v>-923890.4761904201</v>
+      </c>
+      <c r="BK25" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM25" s="14"/>
       <c r="BN25" s="13" t="s">
@@ -6621,18 +6723,23 @@
       <c r="AX26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ26" s="12"/>
+      <c r="AY26" s="10">
+        <v>39</v>
+      </c>
+      <c r="AZ26" s="12">
+        <v>694476.19047613</v>
+      </c>
       <c r="BA26" s="10">
         <f t="shared" si="11"/>
-        <v>-34</v>
+        <v>5</v>
       </c>
       <c r="BB26" s="12">
         <f t="shared" si="12"/>
-        <v>-635809.5238094501</v>
+        <v>58666.666666679899</v>
       </c>
       <c r="BC26" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>9.2270820850840374E-2</v>
       </c>
       <c r="BE26" s="14"/>
       <c r="BF26" s="13" t="s">
@@ -6641,15 +6748,15 @@
       <c r="BH26" s="12"/>
       <c r="BI26" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK26" s="11" t="e">
+        <v>-694476.19047613</v>
+      </c>
+      <c r="BK26" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM26" s="14"/>
       <c r="BN26" s="13" t="s">
@@ -6864,18 +6971,23 @@
       <c r="AX27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ27" s="12"/>
+      <c r="AY27" s="10">
+        <v>44</v>
+      </c>
+      <c r="AZ27" s="12">
+        <v>1570095.2380951999</v>
+      </c>
       <c r="BA27" s="10">
         <f t="shared" si="11"/>
-        <v>-74</v>
+        <v>-30</v>
       </c>
       <c r="BB27" s="12">
         <f t="shared" si="12"/>
-        <v>-2682476.1904761102</v>
+        <v>-1112380.9523809103</v>
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.41468437122771806</v>
       </c>
       <c r="BE27" s="14"/>
       <c r="BF27" s="13" t="s">
@@ -6884,15 +6996,15 @@
       <c r="BH27" s="12"/>
       <c r="BI27" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK27" s="11" t="e">
+        <v>-1570095.2380951999</v>
+      </c>
+      <c r="BK27" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM27" s="14"/>
       <c r="BN27" s="13" t="s">
@@ -7108,19 +7220,23 @@
         <v>13</v>
       </c>
       <c r="AX28" s="9"/>
-      <c r="AY28" s="8"/>
-      <c r="AZ28" s="7"/>
+      <c r="AY28" s="8">
+        <v>509</v>
+      </c>
+      <c r="AZ28" s="7">
+        <v>4264428.57142758</v>
+      </c>
       <c r="BA28" s="27">
         <f t="shared" si="11"/>
-        <v>-555</v>
+        <v>-46</v>
       </c>
       <c r="BB28" s="28">
         <f t="shared" si="12"/>
-        <v>-5037490.4761894308</v>
+        <v>-773061.90476185083</v>
       </c>
       <c r="BC28" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.15346171043218076</v>
       </c>
       <c r="BE28" s="9" t="s">
         <v>13</v>
@@ -7130,15 +7246,15 @@
       <c r="BH28" s="7"/>
       <c r="BI28" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-509</v>
       </c>
       <c r="BJ28" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK28" s="29" t="e">
+        <v>-4264428.57142758</v>
+      </c>
+      <c r="BK28" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM28" s="9" t="s">
         <v>13</v>
@@ -7361,10 +7477,13 @@
       <c r="AX29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AY29" s="1">
+        <v>3551</v>
+      </c>
       <c r="AZ29" s="35"/>
       <c r="BA29" s="10">
         <f t="shared" si="11"/>
-        <v>-3298</v>
+        <v>253</v>
       </c>
       <c r="BB29" s="12">
         <f t="shared" si="12"/>
@@ -7383,7 +7502,7 @@
       <c r="BH29" s="35"/>
       <c r="BI29" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3551</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="15"/>
@@ -7856,18 +7975,23 @@
       <c r="AX31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AZ31" s="12"/>
+      <c r="AY31" s="10">
+        <v>96</v>
+      </c>
+      <c r="AZ31" s="12">
+        <v>96162.857142399967</v>
+      </c>
       <c r="BA31" s="10">
         <f t="shared" si="11"/>
-        <v>-85</v>
+        <v>11</v>
       </c>
       <c r="BB31" s="12">
         <f t="shared" si="12"/>
-        <v>-74525.714285370021</v>
+        <v>21637.142857029947</v>
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.29033123754008067</v>
       </c>
       <c r="BE31" s="14"/>
       <c r="BF31" s="13" t="s">
@@ -7876,15 +8000,15 @@
       <c r="BH31" s="12"/>
       <c r="BI31" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK31" s="11" t="e">
+        <v>-96162.857142399967</v>
+      </c>
+      <c r="BK31" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM31" s="14"/>
       <c r="BN31" s="13" t="s">
@@ -8099,18 +8223,23 @@
       <c r="AX32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ32" s="12"/>
+      <c r="AY32" s="10">
+        <v>73</v>
+      </c>
+      <c r="AZ32" s="12">
+        <v>68838.09523803</v>
+      </c>
       <c r="BA32" s="10">
         <f t="shared" si="11"/>
-        <v>-67</v>
+        <v>6</v>
       </c>
       <c r="BB32" s="12">
         <f t="shared" si="12"/>
-        <v>-65083.80952372001</v>
+        <v>3754.28571430999</v>
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>5.7683865492565059E-2</v>
       </c>
       <c r="BE32" s="14"/>
       <c r="BF32" s="13" t="s">
@@ -8119,15 +8248,15 @@
       <c r="BH32" s="12"/>
       <c r="BI32" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK32" s="11" t="e">
+        <v>-68838.09523803</v>
+      </c>
+      <c r="BK32" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM32" s="14"/>
       <c r="BN32" s="13" t="s">
@@ -8342,18 +8471,23 @@
       <c r="AX33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ33" s="12"/>
+      <c r="AY33" s="10">
+        <v>16</v>
+      </c>
+      <c r="AZ33" s="12">
+        <v>99847.619047610002</v>
+      </c>
       <c r="BA33" s="10">
         <f t="shared" si="11"/>
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="BB33" s="12">
         <f t="shared" si="12"/>
-        <v>-79495.238095229986</v>
+        <v>20352.380952380016</v>
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.25602012699174787</v>
       </c>
       <c r="BE33" s="14"/>
       <c r="BF33" s="13" t="s">
@@ -8362,15 +8496,15 @@
       <c r="BH33" s="12"/>
       <c r="BI33" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK33" s="11" t="e">
+        <v>-99847.619047610002</v>
+      </c>
+      <c r="BK33" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM33" s="14"/>
       <c r="BN33" s="13" t="s">
@@ -8585,18 +8719,23 @@
       <c r="AX34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ34" s="12"/>
+      <c r="AY34" s="10">
+        <v>16</v>
+      </c>
+      <c r="AZ34" s="12">
+        <v>192761.90476186998</v>
+      </c>
       <c r="BA34" s="10">
         <f t="shared" si="11"/>
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="BB34" s="12">
         <f t="shared" si="12"/>
-        <v>-251714.28571425998</v>
+        <v>-58952.380952389998</v>
       </c>
       <c r="BC34" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.2342035565645699</v>
       </c>
       <c r="BE34" s="14"/>
       <c r="BF34" s="13" t="s">
@@ -8605,15 +8744,15 @@
       <c r="BH34" s="12"/>
       <c r="BI34" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ34" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK34" s="11" t="e">
+        <v>-192761.90476186998</v>
+      </c>
+      <c r="BK34" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM34" s="14"/>
       <c r="BN34" s="13" t="s">
@@ -9051,18 +9190,23 @@
       <c r="AX36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ36" s="12"/>
+      <c r="AY36" s="10">
+        <v>3</v>
+      </c>
+      <c r="AZ36" s="12">
+        <v>6470</v>
+      </c>
       <c r="BA36" s="10">
         <f t="shared" si="11"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="BB36" s="12">
         <f t="shared" si="12"/>
-        <v>-17950</v>
+        <v>-11480</v>
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.63955431754874648</v>
       </c>
       <c r="BE36" s="14"/>
       <c r="BF36" s="13" t="s">
@@ -9071,15 +9215,15 @@
       <c r="BH36" s="12"/>
       <c r="BI36" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK36" s="11" t="e">
+        <v>-6470</v>
+      </c>
+      <c r="BK36" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM36" s="14"/>
       <c r="BN36" s="13" t="s">
@@ -9294,18 +9438,23 @@
       <c r="AX37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ37" s="12"/>
+      <c r="AY37" s="10">
+        <v>2</v>
+      </c>
+      <c r="AZ37" s="12">
+        <v>55999.999999990003</v>
+      </c>
       <c r="BA37" s="10">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BB37" s="12">
         <f t="shared" si="12"/>
-        <v>-66476.190476179996</v>
+        <v>-10476.190476189993</v>
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.15759312320918664</v>
       </c>
       <c r="BE37" s="14"/>
       <c r="BF37" s="13" t="s">
@@ -9314,15 +9463,15 @@
       <c r="BH37" s="12"/>
       <c r="BI37" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK37" s="11" t="e">
+        <v>-55999.999999990003</v>
+      </c>
+      <c r="BK37" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM37" s="14"/>
       <c r="BN37" s="13" t="s">
@@ -9537,18 +9686,23 @@
       <c r="AX38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ38" s="12"/>
+      <c r="AY38" s="10">
+        <v>19</v>
+      </c>
+      <c r="AZ38" s="12">
+        <v>305333.33333328</v>
+      </c>
       <c r="BA38" s="10">
         <f t="shared" si="11"/>
-        <v>-14</v>
+        <v>5</v>
       </c>
       <c r="BB38" s="12">
         <f t="shared" si="12"/>
-        <v>-245809.52380949</v>
+        <v>59523.809523789998</v>
       </c>
       <c r="BC38" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.24215420379693178</v>
       </c>
       <c r="BE38" s="14"/>
       <c r="BF38" s="13" t="s">
@@ -9557,15 +9711,15 @@
       <c r="BH38" s="12"/>
       <c r="BI38" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK38" s="11" t="e">
+        <v>-305333.33333328</v>
+      </c>
+      <c r="BK38" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM38" s="14"/>
       <c r="BN38" s="13" t="s">
@@ -9780,18 +9934,23 @@
       <c r="AX39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ39" s="12"/>
+      <c r="AY39" s="10">
+        <v>15</v>
+      </c>
+      <c r="AZ39" s="12">
+        <v>517619.04761902994</v>
+      </c>
       <c r="BA39" s="10">
         <f t="shared" si="11"/>
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="BB39" s="12">
         <f t="shared" si="12"/>
-        <v>-393142.85714282992</v>
+        <v>124476.19047620002</v>
       </c>
       <c r="BC39" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.31661821705430976</v>
       </c>
       <c r="BE39" s="14"/>
       <c r="BF39" s="13" t="s">
@@ -9800,15 +9959,15 @@
       <c r="BH39" s="12"/>
       <c r="BI39" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BJ39" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK39" s="11" t="e">
+        <v>-517619.04761902994</v>
+      </c>
+      <c r="BK39" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM39" s="14"/>
       <c r="BN39" s="13" t="s">
@@ -10024,19 +10183,23 @@
         <v>12</v>
       </c>
       <c r="AX40" s="9"/>
-      <c r="AY40" s="8"/>
-      <c r="AZ40" s="7"/>
+      <c r="AY40" s="8">
+        <v>240</v>
+      </c>
+      <c r="AZ40" s="7">
+        <v>1343032.8571422098</v>
+      </c>
       <c r="BA40" s="27">
         <f t="shared" si="11"/>
-        <v>-215</v>
+        <v>25</v>
       </c>
       <c r="BB40" s="28">
         <f t="shared" si="12"/>
-        <v>-1194197.6190470799</v>
+        <v>148835.23809512984</v>
       </c>
       <c r="BC40" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.12463200036681883</v>
       </c>
       <c r="BE40" s="9" t="s">
         <v>12</v>
@@ -10046,15 +10209,15 @@
       <c r="BH40" s="7"/>
       <c r="BI40" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-240</v>
       </c>
       <c r="BJ40" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK40" s="29" t="e">
+        <v>-1343032.8571422098</v>
+      </c>
+      <c r="BK40" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM40" s="9" t="s">
         <v>12</v>
@@ -10277,10 +10440,13 @@
       <c r="AX41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AY41" s="1">
+        <v>1295</v>
+      </c>
       <c r="AZ41" s="35"/>
       <c r="BA41" s="10">
         <f t="shared" si="11"/>
-        <v>-1188</v>
+        <v>107</v>
       </c>
       <c r="BB41" s="12">
         <f t="shared" si="12"/>
@@ -10299,7 +10465,7 @@
       <c r="BH41" s="35"/>
       <c r="BI41" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1295</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="15"/>
@@ -10772,18 +10938,23 @@
       <c r="AX43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AZ43" s="12"/>
+      <c r="AY43" s="10">
+        <v>59</v>
+      </c>
+      <c r="AZ43" s="12">
+        <v>64087.619047350017</v>
+      </c>
       <c r="BA43" s="10">
         <f t="shared" si="11"/>
-        <v>-107</v>
+        <v>-48</v>
       </c>
       <c r="BB43" s="12">
         <f t="shared" si="12"/>
-        <v>-97992.380951889994</v>
+        <v>-33904.761904539977</v>
       </c>
       <c r="BC43" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.34599385763660284</v>
       </c>
       <c r="BE43" s="14"/>
       <c r="BF43" s="13" t="s">
@@ -10792,15 +10963,15 @@
       <c r="BH43" s="12"/>
       <c r="BI43" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK43" s="11" t="e">
+        <v>-64087.619047350017</v>
+      </c>
+      <c r="BK43" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM43" s="14"/>
       <c r="BN43" s="13" t="s">
@@ -11015,18 +11186,23 @@
       <c r="AX44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ44" s="12"/>
+      <c r="AY44" s="10">
+        <v>62</v>
+      </c>
+      <c r="AZ44" s="12">
+        <v>85239.047618909986</v>
+      </c>
       <c r="BA44" s="10">
         <f t="shared" si="11"/>
-        <v>-73</v>
+        <v>-11</v>
       </c>
       <c r="BB44" s="12">
         <f t="shared" si="12"/>
-        <v>-85923.809523740012</v>
+        <v>-684.76190483002574</v>
       </c>
       <c r="BC44" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-7.9694081142995862E-3</v>
       </c>
       <c r="BE44" s="14"/>
       <c r="BF44" s="13" t="s">
@@ -11035,15 +11211,15 @@
       <c r="BH44" s="12"/>
       <c r="BI44" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK44" s="11" t="e">
+        <v>-85239.047618909986</v>
+      </c>
+      <c r="BK44" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM44" s="14"/>
       <c r="BN44" s="13" t="s">
@@ -11258,18 +11434,23 @@
       <c r="AX45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ45" s="12"/>
+      <c r="AY45" s="10">
+        <v>20</v>
+      </c>
+      <c r="AZ45" s="12">
+        <v>125523.80952379</v>
+      </c>
       <c r="BA45" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="BB45" s="12">
         <f t="shared" si="12"/>
-        <v>-64190.476190469999</v>
+        <v>61333.333333319999</v>
       </c>
       <c r="BC45" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.95548961424320789</v>
       </c>
       <c r="BE45" s="14"/>
       <c r="BF45" s="13" t="s">
@@ -11278,15 +11459,15 @@
       <c r="BH45" s="12"/>
       <c r="BI45" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK45" s="11" t="e">
+        <v>-125523.80952379</v>
+      </c>
+      <c r="BK45" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM45" s="14"/>
       <c r="BN45" s="13" t="s">
@@ -11501,18 +11682,23 @@
       <c r="AX46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ46" s="12"/>
+      <c r="AY46" s="10">
+        <v>10</v>
+      </c>
+      <c r="AZ46" s="12">
+        <v>107619.04761902</v>
+      </c>
       <c r="BA46" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="BB46" s="12">
         <f t="shared" si="12"/>
-        <v>-114285.71428568001</v>
+        <v>-6666.6666666600067</v>
       </c>
       <c r="BC46" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-5.8333333333292554E-2</v>
       </c>
       <c r="BE46" s="14"/>
       <c r="BF46" s="13" t="s">
@@ -11521,15 +11707,15 @@
       <c r="BH46" s="12"/>
       <c r="BI46" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BJ46" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK46" s="11" t="e">
+        <v>-107619.04761902</v>
+      </c>
+      <c r="BK46" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM46" s="14"/>
       <c r="BN46" s="13" t="s">
@@ -11972,18 +12158,23 @@
       <c r="AX48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ48" s="12"/>
+      <c r="AY48" s="10">
+        <v>4</v>
+      </c>
+      <c r="AZ48" s="12">
+        <v>26360</v>
+      </c>
       <c r="BA48" s="10">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="BB48" s="12">
         <f t="shared" si="12"/>
-        <v>-15380</v>
+        <v>10980</v>
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.71391417425227566</v>
       </c>
       <c r="BE48" s="14"/>
       <c r="BF48" s="13" t="s">
@@ -11992,15 +12183,15 @@
       <c r="BH48" s="12"/>
       <c r="BI48" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK48" s="11" t="e">
+        <v>-26360</v>
+      </c>
+      <c r="BK48" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM48" s="14"/>
       <c r="BN48" s="13" t="s">
@@ -12210,18 +12401,23 @@
       <c r="AX49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ49" s="12"/>
+      <c r="AY49" s="10">
+        <v>4</v>
+      </c>
+      <c r="AZ49" s="12">
+        <v>138489.52380950999</v>
+      </c>
       <c r="BA49" s="10">
         <f t="shared" si="11"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BB49" s="12">
         <f t="shared" si="12"/>
-        <v>-155101.90476190002</v>
+        <v>-16612.380952390027</v>
       </c>
       <c r="BC49" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.10710623430377608</v>
       </c>
       <c r="BE49" s="14"/>
       <c r="BF49" s="13" t="s">
@@ -12230,15 +12426,15 @@
       <c r="BH49" s="12"/>
       <c r="BI49" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BJ49" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK49" s="11" t="e">
+        <v>-138489.52380950999</v>
+      </c>
+      <c r="BK49" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM49" s="14"/>
       <c r="BN49" s="13" t="s">
@@ -12453,18 +12649,23 @@
       <c r="AX50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ50" s="12"/>
+      <c r="AY50" s="10">
+        <v>9</v>
+      </c>
+      <c r="AZ50" s="12">
+        <v>141333.33333332001</v>
+      </c>
       <c r="BA50" s="10">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="BB50" s="12">
         <f t="shared" si="12"/>
-        <v>-240285.71428568001</v>
+        <v>-98952.380952359992</v>
       </c>
       <c r="BC50" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.41181133571142614</v>
       </c>
       <c r="BE50" s="14"/>
       <c r="BF50" s="13" t="s">
@@ -12473,15 +12674,15 @@
       <c r="BH50" s="12"/>
       <c r="BI50" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BJ50" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK50" s="11" t="e">
+        <v>-141333.33333332001</v>
+      </c>
+      <c r="BK50" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM50" s="14"/>
       <c r="BN50" s="13" t="s">
@@ -12696,18 +12897,23 @@
       <c r="AX51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ51" s="12"/>
+      <c r="AY51" s="10">
+        <v>14</v>
+      </c>
+      <c r="AZ51" s="12">
+        <v>514857.14285711991</v>
+      </c>
       <c r="BA51" s="10">
         <f t="shared" si="11"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="BB51" s="12">
         <f t="shared" si="12"/>
-        <v>-496571.42857141001</v>
+        <v>18285.714285709895</v>
       </c>
       <c r="BC51" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>3.6823935558105307E-2</v>
       </c>
       <c r="BE51" s="14"/>
       <c r="BF51" s="13" t="s">
@@ -12716,15 +12922,15 @@
       <c r="BH51" s="12"/>
       <c r="BI51" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BJ51" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK51" s="11" t="e">
+        <v>-514857.14285711991</v>
+      </c>
+      <c r="BK51" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM51" s="14"/>
       <c r="BN51" s="13" t="s">
@@ -12940,19 +13146,23 @@
         <v>11</v>
       </c>
       <c r="AX52" s="9"/>
-      <c r="AY52" s="8"/>
-      <c r="AZ52" s="7"/>
+      <c r="AY52" s="8">
+        <v>182</v>
+      </c>
+      <c r="AZ52" s="7">
+        <v>1203509.5238090199</v>
+      </c>
       <c r="BA52" s="27">
         <f t="shared" si="11"/>
-        <v>-238</v>
+        <v>-56</v>
       </c>
       <c r="BB52" s="28">
         <f t="shared" si="12"/>
-        <v>-1272388.5714279101</v>
+        <v>-68879.047618890181</v>
       </c>
       <c r="BC52" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-5.4133657882192529E-2</v>
       </c>
       <c r="BE52" s="9" t="s">
         <v>11</v>
@@ -12962,15 +13172,15 @@
       <c r="BH52" s="7"/>
       <c r="BI52" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-182</v>
       </c>
       <c r="BJ52" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK52" s="29" t="e">
+        <v>-1203509.5238090199</v>
+      </c>
+      <c r="BK52" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM52" s="9" t="s">
         <v>11</v>
@@ -13671,18 +13881,23 @@
       <c r="AX55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AZ55" s="12"/>
+      <c r="AY55" s="10">
+        <v>101</v>
+      </c>
+      <c r="AZ55" s="12">
+        <v>96124.761904319981</v>
+      </c>
       <c r="BA55" s="10">
         <f t="shared" si="11"/>
-        <v>-110</v>
+        <v>-9</v>
       </c>
       <c r="BB55" s="12">
         <f t="shared" si="12"/>
-        <v>-108883.80952334993</v>
+        <v>-12759.047619029952</v>
       </c>
       <c r="BC55" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.11718039325482819</v>
       </c>
       <c r="BE55" s="14"/>
       <c r="BF55" s="13" t="s">
@@ -13691,15 +13906,15 @@
       <c r="BH55" s="12"/>
       <c r="BI55" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-101</v>
       </c>
       <c r="BJ55" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK55" s="11" t="e">
+        <v>-96124.761904319981</v>
+      </c>
+      <c r="BK55" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM55" s="14"/>
       <c r="BN55" s="13" t="s">
@@ -13914,18 +14129,23 @@
       <c r="AX56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ56" s="12"/>
+      <c r="AY56" s="10">
+        <v>68</v>
+      </c>
+      <c r="AZ56" s="12">
+        <v>74685.714285630005</v>
+      </c>
       <c r="BA56" s="10">
         <f t="shared" si="11"/>
-        <v>-76</v>
+        <v>-8</v>
       </c>
       <c r="BB56" s="12">
         <f t="shared" si="12"/>
-        <v>-74323.809523749995</v>
+        <v>361.90476188001048</v>
       </c>
       <c r="BC56" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>4.8692977956729284E-3</v>
       </c>
       <c r="BE56" s="14"/>
       <c r="BF56" s="13" t="s">
@@ -13934,15 +14154,15 @@
       <c r="BH56" s="12"/>
       <c r="BI56" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="BJ56" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK56" s="11" t="e">
+        <v>-74685.714285630005</v>
+      </c>
+      <c r="BK56" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM56" s="14"/>
       <c r="BN56" s="13" t="s">
@@ -14157,18 +14377,23 @@
       <c r="AX57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ57" s="12"/>
+      <c r="AY57" s="10">
+        <v>12</v>
+      </c>
+      <c r="AZ57" s="12">
+        <v>97028.57142855</v>
+      </c>
       <c r="BA57" s="10">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="BB57" s="12">
         <f t="shared" si="12"/>
-        <v>-106523.8095238</v>
+        <v>-9495.2380952499952</v>
       </c>
       <c r="BC57" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-8.9137237371599343E-2</v>
       </c>
       <c r="BE57" s="14"/>
       <c r="BF57" s="13" t="s">
@@ -14177,15 +14402,15 @@
       <c r="BH57" s="12"/>
       <c r="BI57" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BJ57" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK57" s="11" t="e">
+        <v>-97028.57142855</v>
+      </c>
+      <c r="BK57" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM57" s="14"/>
       <c r="BN57" s="13" t="s">
@@ -14400,18 +14625,23 @@
       <c r="AX58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ58" s="12"/>
+      <c r="AY58" s="10">
+        <v>7</v>
+      </c>
+      <c r="AZ58" s="12">
+        <v>72666.66666665001</v>
+      </c>
       <c r="BA58" s="10">
         <f t="shared" si="11"/>
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="BB58" s="12">
         <f t="shared" si="12"/>
-        <v>-241523.80952376002</v>
+        <v>-168857.14285711001</v>
       </c>
       <c r="BC58" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.69913249211357198</v>
       </c>
       <c r="BE58" s="14"/>
       <c r="BF58" s="13" t="s">
@@ -14420,15 +14650,15 @@
       <c r="BH58" s="12"/>
       <c r="BI58" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BJ58" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK58" s="11" t="e">
+        <v>-72666.66666665001</v>
+      </c>
+      <c r="BK58" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM58" s="14"/>
       <c r="BN58" s="13" t="s">
@@ -14619,18 +14849,23 @@
       <c r="AX59" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ59" s="12"/>
+      <c r="AY59" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ59" s="12">
+        <v>8857.1428571399993</v>
+      </c>
       <c r="BA59" s="10">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BB59" s="12">
         <f t="shared" si="12"/>
-        <v>-2857.1428571400002</v>
+        <v>5999.9999999999991</v>
       </c>
       <c r="BC59" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>2.1000000000020997</v>
       </c>
       <c r="BE59" s="14"/>
       <c r="BF59" s="13" t="s">
@@ -14639,15 +14874,15 @@
       <c r="BH59" s="12"/>
       <c r="BI59" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ59" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK59" s="11" t="e">
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="BK59" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM59" s="14"/>
       <c r="BN59" s="13" t="s">
@@ -14862,18 +15097,23 @@
       <c r="AX60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ60" s="12"/>
+      <c r="AY60" s="10">
+        <v>2</v>
+      </c>
+      <c r="AZ60" s="12">
+        <v>4280</v>
+      </c>
       <c r="BA60" s="10">
         <f t="shared" si="11"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BB60" s="12">
         <f t="shared" si="12"/>
-        <v>-8070</v>
+        <v>-3790</v>
       </c>
       <c r="BC60" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.46964064436183395</v>
       </c>
       <c r="BE60" s="14"/>
       <c r="BF60" s="13" t="s">
@@ -14882,15 +15122,15 @@
       <c r="BH60" s="12"/>
       <c r="BI60" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ60" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK60" s="11" t="e">
+        <v>-4280</v>
+      </c>
+      <c r="BK60" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM60" s="14"/>
       <c r="BN60" s="13" t="s">
@@ -15105,18 +15345,23 @@
       <c r="AX61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ61" s="12"/>
+      <c r="AY61" s="10">
+        <v>3</v>
+      </c>
+      <c r="AZ61" s="12">
+        <v>78761.904761900005</v>
+      </c>
       <c r="BA61" s="10">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="BB61" s="12">
         <f t="shared" si="12"/>
-        <v>-40761.904761900005</v>
+        <v>38000</v>
       </c>
       <c r="BC61" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.93224299065431437</v>
       </c>
       <c r="BE61" s="14"/>
       <c r="BF61" s="13" t="s">
@@ -15125,15 +15370,15 @@
       <c r="BH61" s="12"/>
       <c r="BI61" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BJ61" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK61" s="11" t="e">
+        <v>-78761.904761900005</v>
+      </c>
+      <c r="BK61" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM61" s="14"/>
       <c r="BN61" s="13" t="s">
@@ -15348,18 +15593,23 @@
       <c r="AX62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ62" s="12"/>
+      <c r="AY62" s="10">
+        <v>22</v>
+      </c>
+      <c r="AZ62" s="12">
+        <v>430761.90476185014</v>
+      </c>
       <c r="BA62" s="10">
         <f t="shared" si="11"/>
-        <v>-17</v>
+        <v>5</v>
       </c>
       <c r="BB62" s="12">
         <f t="shared" si="12"/>
-        <v>-311714.28571424005</v>
+        <v>119047.61904761009</v>
       </c>
       <c r="BC62" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.38191261839293894</v>
       </c>
       <c r="BE62" s="14"/>
       <c r="BF62" s="13" t="s">
@@ -15368,15 +15618,15 @@
       <c r="BH62" s="12"/>
       <c r="BI62" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="BJ62" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK62" s="11" t="e">
+        <v>-430761.90476185014</v>
+      </c>
+      <c r="BK62" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM62" s="14"/>
       <c r="BN62" s="13" t="s">
@@ -15591,18 +15841,23 @@
       <c r="AX63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ63" s="12"/>
+      <c r="AY63" s="10">
+        <v>10</v>
+      </c>
+      <c r="AZ63" s="12">
+        <v>342857.14285711996</v>
+      </c>
       <c r="BA63" s="10">
         <f t="shared" si="11"/>
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="BB63" s="12">
         <f t="shared" si="12"/>
-        <v>-560380.95238092996</v>
+        <v>-217523.80952380999</v>
       </c>
       <c r="BC63" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.38817131203264721</v>
       </c>
       <c r="BE63" s="14"/>
       <c r="BF63" s="13" t="s">
@@ -15611,15 +15866,15 @@
       <c r="BH63" s="12"/>
       <c r="BI63" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BJ63" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK63" s="11" t="e">
+        <v>-342857.14285711996</v>
+      </c>
+      <c r="BK63" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM63" s="14"/>
       <c r="BN63" s="13" t="s">
@@ -15835,19 +16090,23 @@
         <v>1</v>
       </c>
       <c r="AX64" s="9"/>
-      <c r="AY64" s="8"/>
-      <c r="AZ64" s="7"/>
+      <c r="AY64" s="8">
+        <v>226</v>
+      </c>
+      <c r="AZ64" s="7">
+        <v>1206023.8095231601</v>
+      </c>
       <c r="BA64" s="27">
         <f t="shared" si="11"/>
-        <v>-260</v>
+        <v>-34</v>
       </c>
       <c r="BB64" s="28">
         <f t="shared" si="12"/>
-        <v>-1455039.52380887</v>
+        <v>-249015.7142857099</v>
       </c>
       <c r="BC64" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.171140171941075</v>
       </c>
       <c r="BE64" s="9" t="s">
         <v>1</v>
@@ -15857,15 +16116,15 @@
       <c r="BH64" s="7"/>
       <c r="BI64" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-226</v>
       </c>
       <c r="BJ64" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK64" s="29" t="e">
+        <v>-1206023.8095231601</v>
+      </c>
+      <c r="BK64" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM64" s="9" t="s">
         <v>1</v>
@@ -16086,19 +16345,23 @@
         <v>0</v>
       </c>
       <c r="AX65" s="4"/>
-      <c r="AY65" s="3"/>
-      <c r="AZ65" s="2"/>
+      <c r="AY65" s="3">
+        <v>1769</v>
+      </c>
+      <c r="AZ65" s="2">
+        <v>14188011.42856749</v>
+      </c>
       <c r="BA65" s="6">
         <f t="shared" si="11"/>
-        <v>-2062</v>
+        <v>-293</v>
       </c>
       <c r="BB65" s="5">
         <f t="shared" si="12"/>
-        <v>-18647415.238091029</v>
+        <v>-4459403.8095235396</v>
       </c>
       <c r="BC65" s="30">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.23914326744943859</v>
       </c>
       <c r="BE65" s="4" t="s">
         <v>0</v>
@@ -16108,15 +16371,15 @@
       <c r="BH65" s="2"/>
       <c r="BI65" s="6">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1769</v>
       </c>
       <c r="BJ65" s="5">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK65" s="30" t="e">
+        <v>-14188011.42856749</v>
+      </c>
+      <c r="BK65" s="30">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5211C908-E5C9-D74A-82FB-6F45774AC60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8091723D-3668-E54F-BD20-DC3ED91FB0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1785,10 +1785,13 @@
       <c r="AX6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AY6" s="15">
+        <v>16</v>
+      </c>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="10">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="BB6" s="12">
         <f t="shared" si="12"/>
@@ -1805,7 +1808,7 @@
       <c r="BH6" s="33"/>
       <c r="BI6" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ6" s="12">
         <f t="shared" si="15"/>
@@ -4764,10 +4767,13 @@
       <c r="AX18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AY18" s="1">
+        <v>9</v>
+      </c>
       <c r="AZ18" s="35"/>
       <c r="BA18" s="10">
         <f t="shared" si="11"/>
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="BB18" s="12">
         <f t="shared" si="12"/>
@@ -4784,7 +4790,7 @@
       <c r="BH18" s="35"/>
       <c r="BI18" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="15"/>
@@ -7728,10 +7734,13 @@
       <c r="AX30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AY30" s="1">
+        <v>2</v>
+      </c>
       <c r="AZ30" s="35"/>
       <c r="BA30" s="10">
         <f t="shared" si="11"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BB30" s="12">
         <f t="shared" si="12"/>
@@ -7748,7 +7757,7 @@
       <c r="BH30" s="35"/>
       <c r="BI30" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="15"/>
@@ -10691,10 +10700,13 @@
       <c r="AX42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AY42" s="1">
+        <v>2</v>
+      </c>
       <c r="AZ42" s="35"/>
       <c r="BA42" s="10">
         <f t="shared" si="11"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BB42" s="12">
         <f t="shared" si="12"/>
@@ -10711,7 +10723,7 @@
       <c r="BH42" s="35"/>
       <c r="BI42" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="15"/>
@@ -13634,10 +13646,13 @@
       <c r="AX54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="AY54" s="1">
+        <v>3</v>
+      </c>
       <c r="AZ54" s="35"/>
       <c r="BA54" s="10">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="BB54" s="12">
         <f t="shared" si="12"/>
@@ -13654,7 +13669,7 @@
       <c r="BH54" s="35"/>
       <c r="BI54" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BJ54" s="12">
         <f t="shared" si="15"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8091723D-3668-E54F-BD20-DC3ED91FB0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E033516-99E7-6541-B16B-A40458CB5B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20420" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="6960" yWindow="600" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="38">
   <si>
     <t>總計</t>
   </si>
@@ -200,6 +200,14 @@
   </si>
   <si>
     <t>05/10~05/16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/17~05/23</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1066,7 +1074,9 @@
       </c>
       <c r="AX1" s="26"/>
       <c r="AZ1" s="25"/>
-      <c r="BE1" s="26"/>
+      <c r="BE1" s="26" t="s">
+        <v>36</v>
+      </c>
       <c r="BF1" s="26"/>
       <c r="BH1" s="25"/>
       <c r="BM1" s="26"/>
@@ -1125,6 +1135,9 @@
       <c r="AY2" s="22"/>
       <c r="AZ2" s="22"/>
       <c r="BB2" s="21"/>
+      <c r="BE2" s="20" t="s">
+        <v>37</v>
+      </c>
       <c r="BG2" s="22"/>
       <c r="BH2" s="22"/>
       <c r="BJ2" s="21"/>
@@ -1549,11 +1562,13 @@
       <c r="BF5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BG5" s="40"/>
+      <c r="BG5" s="40">
+        <v>5642</v>
+      </c>
       <c r="BH5" s="1"/>
       <c r="BI5" s="10">
         <f t="shared" ref="BI5:BI65" si="14">BG5-AY5</f>
-        <v>-5761</v>
+        <v>-119</v>
       </c>
       <c r="BJ5" s="12">
         <f t="shared" ref="BJ5:BJ65" si="15">BH5-AZ5</f>
@@ -1574,7 +1589,7 @@
       <c r="BP5" s="1"/>
       <c r="BQ5" s="10">
         <f t="shared" ref="BQ5:BQ65" si="17">BO5-BG5</f>
-        <v>0</v>
+        <v>-5642</v>
       </c>
       <c r="BR5" s="12">
         <f t="shared" ref="BR5:BR65" si="18">BP5-BH5</f>
@@ -2053,18 +2068,23 @@
       <c r="BF7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BH7" s="12"/>
+      <c r="BG7" s="10">
+        <v>197</v>
+      </c>
+      <c r="BH7" s="12">
+        <v>247345.71428483998</v>
+      </c>
       <c r="BI7" s="10">
         <f t="shared" si="14"/>
-        <v>-143</v>
+        <v>54</v>
       </c>
       <c r="BJ7" s="12">
         <f t="shared" si="15"/>
-        <v>-188053.33333271995</v>
+        <v>59292.380952120031</v>
       </c>
       <c r="BK7" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.31529555951669791</v>
       </c>
       <c r="BM7" s="14"/>
       <c r="BN7" s="13" t="s">
@@ -2073,15 +2093,15 @@
       <c r="BP7" s="12"/>
       <c r="BQ7" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-197</v>
       </c>
       <c r="BR7" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS7" s="11" t="e">
+        <v>-247345.71428483998</v>
+      </c>
+      <c r="BS7" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU7" s="14"/>
       <c r="BV7" s="13" t="s">
@@ -2301,18 +2321,23 @@
       <c r="BF8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH8" s="12"/>
+      <c r="BG8" s="10">
+        <v>224</v>
+      </c>
+      <c r="BH8" s="12">
+        <v>321190.47619030986</v>
+      </c>
       <c r="BI8" s="10">
         <f t="shared" si="14"/>
-        <v>-191</v>
+        <v>33</v>
       </c>
       <c r="BJ8" s="12">
         <f t="shared" si="15"/>
-        <v>-307257.14285700995</v>
+        <v>13933.333333299903</v>
       </c>
       <c r="BK8" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>4.5347467608862518E-2</v>
       </c>
       <c r="BM8" s="14"/>
       <c r="BN8" s="13" t="s">
@@ -2321,15 +2346,15 @@
       <c r="BP8" s="12"/>
       <c r="BQ8" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-224</v>
       </c>
       <c r="BR8" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS8" s="11" t="e">
+        <v>-321190.47619030986</v>
+      </c>
+      <c r="BS8" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU8" s="14"/>
       <c r="BV8" s="13" t="s">
@@ -2549,18 +2574,23 @@
       <c r="BF9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH9" s="12"/>
+      <c r="BG9" s="10">
+        <v>55</v>
+      </c>
+      <c r="BH9" s="12">
+        <v>375190.47619045997</v>
+      </c>
       <c r="BI9" s="10">
         <f t="shared" si="14"/>
-        <v>-68</v>
+        <v>-13</v>
       </c>
       <c r="BJ9" s="12">
         <f t="shared" si="15"/>
-        <v>-503638.09523805999</v>
+        <v>-128447.61904760002</v>
       </c>
       <c r="BK9" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.25503952195452034</v>
       </c>
       <c r="BM9" s="14"/>
       <c r="BN9" s="13" t="s">
@@ -2569,15 +2599,15 @@
       <c r="BP9" s="12"/>
       <c r="BQ9" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="BR9" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS9" s="11" t="e">
+        <v>-375190.47619045997</v>
+      </c>
+      <c r="BS9" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="13" t="s">
@@ -2797,18 +2827,23 @@
       <c r="BF10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH10" s="12"/>
+      <c r="BG10" s="10">
+        <v>34</v>
+      </c>
+      <c r="BH10" s="12">
+        <v>411047.61904753</v>
+      </c>
       <c r="BI10" s="10">
         <f t="shared" si="14"/>
-        <v>-50</v>
+        <v>-16</v>
       </c>
       <c r="BJ10" s="12">
         <f t="shared" si="15"/>
-        <v>-656190.47619036003</v>
+        <v>-245142.85714283003</v>
       </c>
       <c r="BK10" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.3735849056604022</v>
       </c>
       <c r="BM10" s="14"/>
       <c r="BN10" s="13" t="s">
@@ -2817,15 +2852,15 @@
       <c r="BP10" s="12"/>
       <c r="BQ10" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="BR10" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS10" s="11" t="e">
+        <v>-411047.61904753</v>
+      </c>
+      <c r="BS10" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU10" s="14"/>
       <c r="BV10" s="13" t="s">
@@ -3040,18 +3075,23 @@
       <c r="BF11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH11" s="12"/>
+      <c r="BG11" s="10">
+        <v>1</v>
+      </c>
+      <c r="BH11" s="12">
+        <v>8857.1428571399993</v>
+      </c>
       <c r="BI11" s="10">
         <f t="shared" si="14"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" si="15"/>
-        <v>-8857.1428571399993</v>
+        <v>0</v>
       </c>
       <c r="BK11" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BM11" s="14"/>
       <c r="BN11" s="13" t="s">
@@ -3060,15 +3100,15 @@
       <c r="BP11" s="12"/>
       <c r="BQ11" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BR11" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS11" s="11" t="e">
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="BS11" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU11" s="14"/>
       <c r="BV11" s="13" t="s">
@@ -3288,18 +3328,23 @@
       <c r="BF12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH12" s="12"/>
+      <c r="BG12" s="10">
+        <v>7</v>
+      </c>
+      <c r="BH12" s="12">
+        <v>40030</v>
+      </c>
       <c r="BI12" s="10">
         <f t="shared" si="14"/>
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="15"/>
-        <v>-87850</v>
+        <v>-47820</v>
       </c>
       <c r="BK12" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.54433693796243598</v>
       </c>
       <c r="BM12" s="14"/>
       <c r="BN12" s="13" t="s">
@@ -3308,15 +3353,15 @@
       <c r="BP12" s="12"/>
       <c r="BQ12" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BR12" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS12" s="11" t="e">
+        <v>-40030</v>
+      </c>
+      <c r="BS12" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU12" s="14"/>
       <c r="BV12" s="13" t="s">
@@ -3536,18 +3581,23 @@
       <c r="BF13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH13" s="12"/>
+      <c r="BG13" s="10">
+        <v>38</v>
+      </c>
+      <c r="BH13" s="12">
+        <v>1349485.7142855995</v>
+      </c>
       <c r="BI13" s="10">
         <f t="shared" si="14"/>
-        <v>-27</v>
+        <v>11</v>
       </c>
       <c r="BJ13" s="12">
         <f t="shared" si="15"/>
-        <v>-1004395.2380951699</v>
+        <v>345090.47619042965</v>
       </c>
       <c r="BK13" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.34358035870907938</v>
       </c>
       <c r="BM13" s="14"/>
       <c r="BN13" s="13" t="s">
@@ -3556,15 +3606,15 @@
       <c r="BP13" s="12"/>
       <c r="BQ13" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="BR13" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS13" s="11" t="e">
+        <v>-1349485.7142855995</v>
+      </c>
+      <c r="BS13" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU13" s="14"/>
       <c r="BV13" s="13" t="s">
@@ -3784,18 +3834,23 @@
       <c r="BF14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH14" s="12"/>
+      <c r="BG14" s="10">
+        <v>51</v>
+      </c>
+      <c r="BH14" s="12">
+        <v>939619.04761893023</v>
+      </c>
       <c r="BI14" s="10">
         <f t="shared" si="14"/>
-        <v>-56</v>
+        <v>-5</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="15"/>
-        <v>-1272679.9999998901</v>
+        <v>-333060.95238095988</v>
       </c>
       <c r="BK14" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.26170046860246776</v>
       </c>
       <c r="BM14" s="14"/>
       <c r="BN14" s="13" t="s">
@@ -3804,15 +3859,15 @@
       <c r="BP14" s="12"/>
       <c r="BQ14" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-51</v>
       </c>
       <c r="BR14" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS14" s="11" t="e">
+        <v>-939619.04761893023</v>
+      </c>
+      <c r="BS14" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU14" s="14"/>
       <c r="BV14" s="13" t="s">
@@ -4032,18 +4087,23 @@
       <c r="BF15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH15" s="12"/>
+      <c r="BG15" s="10">
+        <v>84</v>
+      </c>
+      <c r="BH15" s="12">
+        <v>3233904.7619046797</v>
+      </c>
       <c r="BI15" s="10">
         <f t="shared" si="14"/>
-        <v>-58</v>
+        <v>26</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="15"/>
-        <v>-2142095.2380951699</v>
+        <v>1091809.5238095098</v>
       </c>
       <c r="BK15" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.5096923350524728</v>
       </c>
       <c r="BM15" s="14"/>
       <c r="BN15" s="13" t="s">
@@ -4052,15 +4112,15 @@
       <c r="BP15" s="12"/>
       <c r="BQ15" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-84</v>
       </c>
       <c r="BR15" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS15" s="11" t="e">
+        <v>-3233904.7619046797</v>
+      </c>
+      <c r="BS15" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU15" s="14"/>
       <c r="BV15" s="13" t="s">
@@ -4281,19 +4341,23 @@
         <v>19</v>
       </c>
       <c r="BF16" s="9"/>
-      <c r="BG16" s="8"/>
-      <c r="BH16" s="7"/>
+      <c r="BG16" s="8">
+        <v>691</v>
+      </c>
+      <c r="BH16" s="7">
+        <v>6926670.9523794893</v>
+      </c>
       <c r="BI16" s="27">
         <f t="shared" si="14"/>
-        <v>-612</v>
+        <v>79</v>
       </c>
       <c r="BJ16" s="28">
         <f t="shared" si="15"/>
-        <v>-6171016.6666655196</v>
+        <v>755654.28571396973</v>
       </c>
       <c r="BK16" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.1224521544068822</v>
       </c>
       <c r="BM16" s="9" t="s">
         <v>19</v>
@@ -4303,15 +4367,15 @@
       <c r="BP16" s="7"/>
       <c r="BQ16" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-691</v>
       </c>
       <c r="BR16" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS16" s="29" t="e">
+        <v>-6926670.9523794893</v>
+      </c>
+      <c r="BS16" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU16" s="9" t="s">
         <v>19</v>
@@ -4538,10 +4602,13 @@
       <c r="BF17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG17" s="1">
+        <v>4036</v>
+      </c>
       <c r="BH17" s="35"/>
       <c r="BI17" s="10">
         <f t="shared" si="14"/>
-        <v>-4372</v>
+        <v>-336</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="15"/>
@@ -4560,7 +4627,7 @@
       <c r="BP17" s="35"/>
       <c r="BQ17" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-4036</v>
       </c>
       <c r="BR17" s="12">
         <f t="shared" si="18"/>
@@ -5039,18 +5106,23 @@
       <c r="BF19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BH19" s="12"/>
+      <c r="BG19" s="10">
+        <v>119</v>
+      </c>
+      <c r="BH19" s="12">
+        <v>121252.38095184001</v>
+      </c>
       <c r="BI19" s="10">
         <f t="shared" si="14"/>
-        <v>-158</v>
+        <v>-39</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="15"/>
-        <v>-186339.99999941007</v>
+        <v>-65087.619047570057</v>
       </c>
       <c r="BK19" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.34929493961455466</v>
       </c>
       <c r="BM19" s="14"/>
       <c r="BN19" s="13" t="s">
@@ -5059,15 +5131,15 @@
       <c r="BP19" s="12"/>
       <c r="BQ19" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-119</v>
       </c>
       <c r="BR19" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS19" s="11" t="e">
+        <v>-121252.38095184001</v>
+      </c>
+      <c r="BS19" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU19" s="14"/>
       <c r="BV19" s="13" t="s">
@@ -5287,18 +5359,23 @@
       <c r="BF20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH20" s="12"/>
+      <c r="BG20" s="10">
+        <v>158</v>
+      </c>
+      <c r="BH20" s="12">
+        <v>167201.90476180997</v>
+      </c>
       <c r="BI20" s="10">
         <f t="shared" si="14"/>
-        <v>-150</v>
+        <v>8</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="15"/>
-        <v>-203866.66666649005</v>
+        <v>-36664.761904680083</v>
       </c>
       <c r="BK20" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.17984677193285731</v>
       </c>
       <c r="BM20" s="14"/>
       <c r="BN20" s="13" t="s">
@@ -5307,15 +5384,15 @@
       <c r="BP20" s="12"/>
       <c r="BQ20" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-158</v>
       </c>
       <c r="BR20" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS20" s="11" t="e">
+        <v>-167201.90476180997</v>
+      </c>
+      <c r="BS20" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU20" s="14"/>
       <c r="BV20" s="13" t="s">
@@ -5535,18 +5612,23 @@
       <c r="BF21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH21" s="12"/>
+      <c r="BG21" s="10">
+        <v>39</v>
+      </c>
+      <c r="BH21" s="12">
+        <v>258199.99999998001</v>
+      </c>
       <c r="BI21" s="10">
         <f t="shared" si="14"/>
-        <v>-46</v>
+        <v>-7</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="15"/>
-        <v>-305752.38095235999</v>
+        <v>-47552.380952379986</v>
       </c>
       <c r="BK21" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.15552579117867682</v>
       </c>
       <c r="BM21" s="14"/>
       <c r="BN21" s="13" t="s">
@@ -5555,15 +5637,15 @@
       <c r="BP21" s="12"/>
       <c r="BQ21" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="BR21" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS21" s="11" t="e">
+        <v>-258199.99999998001</v>
+      </c>
+      <c r="BS21" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU21" s="14"/>
       <c r="BV21" s="13" t="s">
@@ -5783,18 +5865,23 @@
       <c r="BF22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH22" s="12"/>
+      <c r="BG22" s="10">
+        <v>13</v>
+      </c>
+      <c r="BH22" s="12">
+        <v>152095.23809519003</v>
+      </c>
       <c r="BI22" s="10">
         <f t="shared" si="14"/>
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="15"/>
-        <v>-295047.61904756998</v>
+        <v>-142952.38095237996</v>
       </c>
       <c r="BK22" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.48450613298910239</v>
       </c>
       <c r="BM22" s="14"/>
       <c r="BN22" s="13" t="s">
@@ -5803,15 +5890,15 @@
       <c r="BP22" s="12"/>
       <c r="BQ22" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BR22" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS22" s="11" t="e">
+        <v>-152095.23809519003</v>
+      </c>
+      <c r="BS22" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU22" s="14"/>
       <c r="BV22" s="13" t="s">
@@ -6255,18 +6342,23 @@
       <c r="BF24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH24" s="12"/>
+      <c r="BG24" s="10">
+        <v>14</v>
+      </c>
+      <c r="BH24" s="12">
+        <v>74580</v>
+      </c>
       <c r="BI24" s="10">
         <f t="shared" si="14"/>
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="15"/>
-        <v>-84960</v>
+        <v>-10380</v>
       </c>
       <c r="BK24" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.12217514124293785</v>
       </c>
       <c r="BM24" s="14"/>
       <c r="BN24" s="13" t="s">
@@ -6275,15 +6367,15 @@
       <c r="BP24" s="12"/>
       <c r="BQ24" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BR24" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS24" s="11" t="e">
+        <v>-74580</v>
+      </c>
+      <c r="BS24" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU24" s="14"/>
       <c r="BV24" s="13" t="s">
@@ -6503,18 +6595,23 @@
       <c r="BF25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH25" s="12"/>
+      <c r="BG25" s="10">
+        <v>17</v>
+      </c>
+      <c r="BH25" s="12">
+        <v>685052.38095231005</v>
+      </c>
       <c r="BI25" s="10">
         <f t="shared" si="14"/>
-        <v>-29</v>
+        <v>-12</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="15"/>
-        <v>-923890.4761904201</v>
+        <v>-238838.09523811005</v>
       </c>
       <c r="BK25" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.25851342923561416</v>
       </c>
       <c r="BM25" s="14"/>
       <c r="BN25" s="13" t="s">
@@ -6523,15 +6620,15 @@
       <c r="BP25" s="12"/>
       <c r="BQ25" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BR25" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS25" s="11" t="e">
+        <v>-685052.38095231005</v>
+      </c>
+      <c r="BS25" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU25" s="14"/>
       <c r="BV25" s="13" t="s">
@@ -6751,18 +6848,23 @@
       <c r="BF26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH26" s="12"/>
+      <c r="BG26" s="10">
+        <v>22</v>
+      </c>
+      <c r="BH26" s="12">
+        <v>387999.99999995006</v>
+      </c>
       <c r="BI26" s="10">
         <f t="shared" si="14"/>
-        <v>-39</v>
+        <v>-17</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="15"/>
-        <v>-694476.19047613</v>
+        <v>-306476.19047617994</v>
       </c>
       <c r="BK26" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.44130554031818015</v>
       </c>
       <c r="BM26" s="14"/>
       <c r="BN26" s="13" t="s">
@@ -6771,15 +6873,15 @@
       <c r="BP26" s="12"/>
       <c r="BQ26" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="BR26" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS26" s="11" t="e">
+        <v>-387999.99999995006</v>
+      </c>
+      <c r="BS26" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU26" s="14"/>
       <c r="BV26" s="13" t="s">
@@ -6999,18 +7101,23 @@
       <c r="BF27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH27" s="12"/>
+      <c r="BG27" s="10">
+        <v>48</v>
+      </c>
+      <c r="BH27" s="12">
+        <v>1667809.52380947</v>
+      </c>
       <c r="BI27" s="10">
         <f t="shared" si="14"/>
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="15"/>
-        <v>-1570095.2380951999</v>
+        <v>97714.285714270081</v>
       </c>
       <c r="BK27" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>6.2234623316745168E-2</v>
       </c>
       <c r="BM27" s="14"/>
       <c r="BN27" s="13" t="s">
@@ -7019,15 +7126,15 @@
       <c r="BP27" s="12"/>
       <c r="BQ27" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="BR27" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS27" s="11" t="e">
+        <v>-1667809.52380947</v>
+      </c>
+      <c r="BS27" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU27" s="14"/>
       <c r="BV27" s="13" t="s">
@@ -7248,19 +7355,23 @@
         <v>13</v>
       </c>
       <c r="BF28" s="9"/>
-      <c r="BG28" s="8"/>
-      <c r="BH28" s="7"/>
+      <c r="BG28" s="8">
+        <v>430</v>
+      </c>
+      <c r="BH28" s="7">
+        <v>3514191.4285705499</v>
+      </c>
       <c r="BI28" s="27">
         <f t="shared" si="14"/>
-        <v>-509</v>
+        <v>-79</v>
       </c>
       <c r="BJ28" s="28">
         <f t="shared" si="15"/>
-        <v>-4264428.57142758</v>
+        <v>-750237.14285703003</v>
       </c>
       <c r="BK28" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.17592911460254032</v>
       </c>
       <c r="BM28" s="9" t="s">
         <v>13</v>
@@ -7270,15 +7381,15 @@
       <c r="BP28" s="7"/>
       <c r="BQ28" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-430</v>
       </c>
       <c r="BR28" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS28" s="29" t="e">
+        <v>-3514191.4285705499</v>
+      </c>
+      <c r="BS28" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU28" s="9" t="s">
         <v>13</v>
@@ -7505,10 +7616,13 @@
       <c r="BF29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG29" s="1">
+        <v>3581</v>
+      </c>
       <c r="BH29" s="35"/>
       <c r="BI29" s="10">
         <f t="shared" si="14"/>
-        <v>-3551</v>
+        <v>30</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="15"/>
@@ -7527,7 +7641,7 @@
       <c r="BP29" s="35"/>
       <c r="BQ29" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3581</v>
       </c>
       <c r="BR29" s="12">
         <f t="shared" si="18"/>
@@ -8006,18 +8120,23 @@
       <c r="BF31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BH31" s="12"/>
+      <c r="BG31" s="10">
+        <v>104</v>
+      </c>
+      <c r="BH31" s="12">
+        <v>104592.38095199002</v>
+      </c>
       <c r="BI31" s="10">
         <f t="shared" si="14"/>
-        <v>-96</v>
+        <v>8</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="15"/>
-        <v>-96162.857142399967</v>
+        <v>8429.5238095900568</v>
       </c>
       <c r="BK31" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>8.7658832735257042E-2</v>
       </c>
       <c r="BM31" s="14"/>
       <c r="BN31" s="13" t="s">
@@ -8026,15 +8145,15 @@
       <c r="BP31" s="12"/>
       <c r="BQ31" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="BR31" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS31" s="11" t="e">
+        <v>-104592.38095199002</v>
+      </c>
+      <c r="BS31" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU31" s="14"/>
       <c r="BV31" s="13" t="s">
@@ -8254,18 +8373,23 @@
       <c r="BF32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH32" s="12"/>
+      <c r="BG32" s="10">
+        <v>61</v>
+      </c>
+      <c r="BH32" s="12">
+        <v>63001.904761810008</v>
+      </c>
       <c r="BI32" s="10">
         <f t="shared" si="14"/>
-        <v>-73</v>
+        <v>-12</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="15"/>
-        <v>-68838.09523803</v>
+        <v>-5836.190476219992</v>
       </c>
       <c r="BK32" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-8.4781405645224114E-2</v>
       </c>
       <c r="BM32" s="14"/>
       <c r="BN32" s="13" t="s">
@@ -8274,15 +8398,15 @@
       <c r="BP32" s="12"/>
       <c r="BQ32" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="BR32" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS32" s="11" t="e">
+        <v>-63001.904761810008</v>
+      </c>
+      <c r="BS32" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU32" s="14"/>
       <c r="BV32" s="13" t="s">
@@ -8502,18 +8626,23 @@
       <c r="BF33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH33" s="12"/>
+      <c r="BG33" s="10">
+        <v>19</v>
+      </c>
+      <c r="BH33" s="12">
+        <v>119819.04761903</v>
+      </c>
       <c r="BI33" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>3</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="15"/>
-        <v>-99847.619047610002</v>
+        <v>19971.428571419994</v>
       </c>
       <c r="BK33" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.20001907668821914</v>
       </c>
       <c r="BM33" s="14"/>
       <c r="BN33" s="13" t="s">
@@ -8522,15 +8651,15 @@
       <c r="BP33" s="12"/>
       <c r="BQ33" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="BR33" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS33" s="11" t="e">
+        <v>-119819.04761903</v>
+      </c>
+      <c r="BS33" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU33" s="14"/>
       <c r="BV33" s="13" t="s">
@@ -8750,18 +8879,23 @@
       <c r="BF34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH34" s="12"/>
+      <c r="BG34" s="10">
+        <v>14</v>
+      </c>
+      <c r="BH34" s="12">
+        <v>163904.76190471998</v>
+      </c>
       <c r="BI34" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="BJ34" s="12">
         <f t="shared" si="15"/>
-        <v>-192761.90476186998</v>
+        <v>-28857.14285715</v>
       </c>
       <c r="BK34" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.14970355731231702</v>
       </c>
       <c r="BM34" s="14"/>
       <c r="BN34" s="13" t="s">
@@ -8770,15 +8904,15 @@
       <c r="BP34" s="12"/>
       <c r="BQ34" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BR34" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS34" s="11" t="e">
+        <v>-163904.76190471998</v>
+      </c>
+      <c r="BS34" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU34" s="14"/>
       <c r="BV34" s="13" t="s">
@@ -9221,18 +9355,23 @@
       <c r="BF36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH36" s="12"/>
+      <c r="BG36" s="10">
+        <v>7</v>
+      </c>
+      <c r="BH36" s="12">
+        <v>34530</v>
+      </c>
       <c r="BI36" s="10">
         <f t="shared" si="14"/>
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="15"/>
-        <v>-6470</v>
+        <v>28060</v>
       </c>
       <c r="BK36" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>4.3369397217928904</v>
       </c>
       <c r="BM36" s="14"/>
       <c r="BN36" s="13" t="s">
@@ -9241,15 +9380,15 @@
       <c r="BP36" s="12"/>
       <c r="BQ36" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BR36" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS36" s="11" t="e">
+        <v>-34530</v>
+      </c>
+      <c r="BS36" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU36" s="14"/>
       <c r="BV36" s="13" t="s">
@@ -9469,18 +9608,23 @@
       <c r="BF37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH37" s="12"/>
+      <c r="BG37" s="10">
+        <v>4</v>
+      </c>
+      <c r="BH37" s="12">
+        <v>110559.04761903</v>
+      </c>
       <c r="BI37" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="15"/>
-        <v>-55999.999999990003</v>
+        <v>54559.047619039993</v>
       </c>
       <c r="BK37" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.97426870748303096</v>
       </c>
       <c r="BM37" s="14"/>
       <c r="BN37" s="13" t="s">
@@ -9489,15 +9633,15 @@
       <c r="BP37" s="12"/>
       <c r="BQ37" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BR37" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS37" s="11" t="e">
+        <v>-110559.04761903</v>
+      </c>
+      <c r="BS37" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU37" s="14"/>
       <c r="BV37" s="13" t="s">
@@ -9717,18 +9861,23 @@
       <c r="BF38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH38" s="12"/>
+      <c r="BG38" s="10">
+        <v>12</v>
+      </c>
+      <c r="BH38" s="12">
+        <v>210285.71428568001</v>
+      </c>
       <c r="BI38" s="10">
         <f t="shared" si="14"/>
-        <v>-19</v>
+        <v>-7</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="15"/>
-        <v>-305333.33333328</v>
+        <v>-95047.61904759999</v>
       </c>
       <c r="BK38" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.31129132875856963</v>
       </c>
       <c r="BM38" s="14"/>
       <c r="BN38" s="13" t="s">
@@ -9737,15 +9886,15 @@
       <c r="BP38" s="12"/>
       <c r="BQ38" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BR38" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS38" s="11" t="e">
+        <v>-210285.71428568001</v>
+      </c>
+      <c r="BS38" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU38" s="14"/>
       <c r="BV38" s="13" t="s">
@@ -9965,18 +10114,23 @@
       <c r="BF39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH39" s="12"/>
+      <c r="BG39" s="10">
+        <v>16</v>
+      </c>
+      <c r="BH39" s="12">
+        <v>520380.95238091995</v>
+      </c>
       <c r="BI39" s="10">
         <f t="shared" si="14"/>
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="BJ39" s="12">
         <f t="shared" si="15"/>
-        <v>-517619.04761902994</v>
+        <v>2761.9047618900076</v>
       </c>
       <c r="BK39" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>5.3357865685089365E-3</v>
       </c>
       <c r="BM39" s="14"/>
       <c r="BN39" s="13" t="s">
@@ -9985,15 +10139,15 @@
       <c r="BP39" s="12"/>
       <c r="BQ39" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BR39" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS39" s="11" t="e">
+        <v>-520380.95238091995</v>
+      </c>
+      <c r="BS39" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU39" s="14"/>
       <c r="BV39" s="13" t="s">
@@ -10214,19 +10368,23 @@
         <v>12</v>
       </c>
       <c r="BF40" s="9"/>
-      <c r="BG40" s="8"/>
-      <c r="BH40" s="7"/>
+      <c r="BG40" s="8">
+        <v>237</v>
+      </c>
+      <c r="BH40" s="7">
+        <v>1327073.8095231799</v>
+      </c>
       <c r="BI40" s="27">
         <f t="shared" si="14"/>
-        <v>-240</v>
+        <v>-3</v>
       </c>
       <c r="BJ40" s="28">
         <f t="shared" si="15"/>
-        <v>-1343032.8571422098</v>
+        <v>-15959.04761902988</v>
       </c>
       <c r="BK40" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-1.1882842280559353E-2</v>
       </c>
       <c r="BM40" s="9" t="s">
         <v>12</v>
@@ -10236,15 +10394,15 @@
       <c r="BP40" s="7"/>
       <c r="BQ40" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-237</v>
       </c>
       <c r="BR40" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS40" s="29" t="e">
+        <v>-1327073.8095231799</v>
+      </c>
+      <c r="BS40" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU40" s="9" t="s">
         <v>12</v>
@@ -10471,10 +10629,13 @@
       <c r="BF41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG41" s="1">
+        <v>1157</v>
+      </c>
       <c r="BH41" s="35"/>
       <c r="BI41" s="10">
         <f t="shared" si="14"/>
-        <v>-1295</v>
+        <v>-138</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="15"/>
@@ -10493,7 +10654,7 @@
       <c r="BP41" s="35"/>
       <c r="BQ41" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1157</v>
       </c>
       <c r="BR41" s="12">
         <f t="shared" si="18"/>
@@ -10972,18 +11133,23 @@
       <c r="BF43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BH43" s="12"/>
+      <c r="BG43" s="10">
+        <v>106</v>
+      </c>
+      <c r="BH43" s="12">
+        <v>112294.28571382999</v>
+      </c>
       <c r="BI43" s="10">
         <f t="shared" si="14"/>
-        <v>-59</v>
+        <v>47</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="15"/>
-        <v>-64087.619047350017</v>
+        <v>48206.66666647997</v>
       </c>
       <c r="BK43" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.75219936991048642</v>
       </c>
       <c r="BM43" s="14"/>
       <c r="BN43" s="13" t="s">
@@ -10992,15 +11158,15 @@
       <c r="BP43" s="12"/>
       <c r="BQ43" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="BR43" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS43" s="11" t="e">
+        <v>-112294.28571382999</v>
+      </c>
+      <c r="BS43" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU43" s="14"/>
       <c r="BV43" s="13" t="s">
@@ -11220,18 +11386,23 @@
       <c r="BF44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH44" s="12"/>
+      <c r="BG44" s="10">
+        <v>50</v>
+      </c>
+      <c r="BH44" s="12">
+        <v>68229.523809420003</v>
+      </c>
       <c r="BI44" s="10">
         <f t="shared" si="14"/>
-        <v>-62</v>
+        <v>-12</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="15"/>
-        <v>-85239.047618909986</v>
+        <v>-17009.523809489983</v>
       </c>
       <c r="BK44" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.19955084300726605</v>
       </c>
       <c r="BM44" s="14"/>
       <c r="BN44" s="13" t="s">
@@ -11240,15 +11411,15 @@
       <c r="BP44" s="12"/>
       <c r="BQ44" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="BR44" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS44" s="11" t="e">
+        <v>-68229.523809420003</v>
+      </c>
+      <c r="BS44" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU44" s="14"/>
       <c r="BV44" s="13" t="s">
@@ -11468,18 +11639,23 @@
       <c r="BF45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH45" s="12"/>
+      <c r="BG45" s="10">
+        <v>13</v>
+      </c>
+      <c r="BH45" s="12">
+        <v>89876.190476179996</v>
+      </c>
       <c r="BI45" s="10">
         <f t="shared" si="14"/>
-        <v>-20</v>
+        <v>-7</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="15"/>
-        <v>-125523.80952379</v>
+        <v>-35647.619047610002</v>
       </c>
       <c r="BK45" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.28399089529587501</v>
       </c>
       <c r="BM45" s="14"/>
       <c r="BN45" s="13" t="s">
@@ -11488,15 +11664,15 @@
       <c r="BP45" s="12"/>
       <c r="BQ45" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BR45" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS45" s="11" t="e">
+        <v>-89876.190476179996</v>
+      </c>
+      <c r="BS45" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU45" s="14"/>
       <c r="BV45" s="13" t="s">
@@ -11716,18 +11892,23 @@
       <c r="BF46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH46" s="12"/>
+      <c r="BG46" s="10">
+        <v>6</v>
+      </c>
+      <c r="BH46" s="12">
+        <v>67047.619047600005</v>
+      </c>
       <c r="BI46" s="10">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="BJ46" s="12">
         <f t="shared" si="15"/>
-        <v>-107619.04761902</v>
+        <v>-40571.428571419994</v>
       </c>
       <c r="BK46" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.37699115044249493</v>
       </c>
       <c r="BM46" s="14"/>
       <c r="BN46" s="13" t="s">
@@ -11736,15 +11917,15 @@
       <c r="BP46" s="12"/>
       <c r="BQ46" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BR46" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS46" s="11" t="e">
+        <v>-67047.619047600005</v>
+      </c>
+      <c r="BS46" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU46" s="14"/>
       <c r="BV46" s="13" t="s">
@@ -12192,18 +12373,23 @@
       <c r="BF48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH48" s="12"/>
+      <c r="BG48" s="10">
+        <v>2</v>
+      </c>
+      <c r="BH48" s="12">
+        <v>8180</v>
+      </c>
       <c r="BI48" s="10">
         <f t="shared" si="14"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="15"/>
-        <v>-26360</v>
+        <v>-18180</v>
       </c>
       <c r="BK48" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.68968133535660092</v>
       </c>
       <c r="BM48" s="14"/>
       <c r="BN48" s="13" t="s">
@@ -12212,15 +12398,15 @@
       <c r="BP48" s="12"/>
       <c r="BQ48" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BR48" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS48" s="11" t="e">
+        <v>-8180</v>
+      </c>
+      <c r="BS48" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU48" s="14"/>
       <c r="BV48" s="13" t="s">
@@ -12435,18 +12621,23 @@
       <c r="BF49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH49" s="12"/>
+      <c r="BG49" s="10">
+        <v>4</v>
+      </c>
+      <c r="BH49" s="12">
+        <v>116466.66666665001</v>
+      </c>
       <c r="BI49" s="10">
         <f t="shared" si="14"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BJ49" s="12">
         <f t="shared" si="15"/>
-        <v>-138489.52380950999</v>
+        <v>-22022.857142859983</v>
       </c>
       <c r="BK49" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.15902182733440581</v>
       </c>
       <c r="BM49" s="14"/>
       <c r="BN49" s="13" t="s">
@@ -12455,15 +12646,15 @@
       <c r="BP49" s="12"/>
       <c r="BQ49" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BR49" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS49" s="11" t="e">
+        <v>-116466.66666665001</v>
+      </c>
+      <c r="BS49" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU49" s="14"/>
       <c r="BV49" s="13" t="s">
@@ -12683,18 +12874,23 @@
       <c r="BF50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH50" s="12"/>
+      <c r="BG50" s="10">
+        <v>13</v>
+      </c>
+      <c r="BH50" s="12">
+        <v>228285.71428568001</v>
+      </c>
       <c r="BI50" s="10">
         <f t="shared" si="14"/>
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="BJ50" s="12">
         <f t="shared" si="15"/>
-        <v>-141333.33333332001</v>
+        <v>86952.380952359992</v>
       </c>
       <c r="BK50" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.6152291105120391</v>
       </c>
       <c r="BM50" s="14"/>
       <c r="BN50" s="13" t="s">
@@ -12703,15 +12899,15 @@
       <c r="BP50" s="12"/>
       <c r="BQ50" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BR50" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS50" s="11" t="e">
+        <v>-228285.71428568001</v>
+      </c>
+      <c r="BS50" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU50" s="14"/>
       <c r="BV50" s="13" t="s">
@@ -12931,18 +13127,23 @@
       <c r="BF51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH51" s="12"/>
+      <c r="BG51" s="10">
+        <v>14</v>
+      </c>
+      <c r="BH51" s="12">
+        <v>454857.14285712002</v>
+      </c>
       <c r="BI51" s="10">
         <f t="shared" si="14"/>
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="BJ51" s="12">
         <f t="shared" si="15"/>
-        <v>-514857.14285711991</v>
+        <v>-59999.999999999884</v>
       </c>
       <c r="BK51" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.11653718091010486</v>
       </c>
       <c r="BM51" s="14"/>
       <c r="BN51" s="13" t="s">
@@ -12951,15 +13152,15 @@
       <c r="BP51" s="12"/>
       <c r="BQ51" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BR51" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS51" s="11" t="e">
+        <v>-454857.14285712002</v>
+      </c>
+      <c r="BS51" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU51" s="14"/>
       <c r="BV51" s="13" t="s">
@@ -13180,19 +13381,23 @@
         <v>11</v>
       </c>
       <c r="BF52" s="9"/>
-      <c r="BG52" s="8"/>
-      <c r="BH52" s="7"/>
+      <c r="BG52" s="8">
+        <v>208</v>
+      </c>
+      <c r="BH52" s="7">
+        <v>1145237.1428564801</v>
+      </c>
       <c r="BI52" s="27">
         <f t="shared" si="14"/>
-        <v>-182</v>
+        <v>26</v>
       </c>
       <c r="BJ52" s="28">
         <f t="shared" si="15"/>
-        <v>-1203509.5238090199</v>
+        <v>-58272.380952539854</v>
       </c>
       <c r="BK52" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-4.8418711941814983E-2</v>
       </c>
       <c r="BM52" s="9" t="s">
         <v>11</v>
@@ -13202,15 +13407,15 @@
       <c r="BP52" s="7"/>
       <c r="BQ52" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-208</v>
       </c>
       <c r="BR52" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS52" s="29" t="e">
+        <v>-1145237.1428564801</v>
+      </c>
+      <c r="BS52" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU52" s="9" t="s">
         <v>11</v>
@@ -13918,18 +14123,23 @@
       <c r="BF55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BH55" s="12"/>
+      <c r="BG55" s="10">
+        <v>102</v>
+      </c>
+      <c r="BH55" s="12">
+        <v>103464.76190425998</v>
+      </c>
       <c r="BI55" s="10">
         <f t="shared" si="14"/>
-        <v>-101</v>
+        <v>1</v>
       </c>
       <c r="BJ55" s="12">
         <f t="shared" si="15"/>
-        <v>-96124.761904319981</v>
+        <v>7339.9999999400025</v>
       </c>
       <c r="BK55" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>7.635909680843779E-2</v>
       </c>
       <c r="BM55" s="14"/>
       <c r="BN55" s="13" t="s">
@@ -13938,15 +14148,15 @@
       <c r="BP55" s="12"/>
       <c r="BQ55" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-102</v>
       </c>
       <c r="BR55" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS55" s="11" t="e">
+        <v>-103464.76190425998</v>
+      </c>
+      <c r="BS55" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU55" s="14"/>
       <c r="BV55" s="13" t="s">
@@ -14166,18 +14376,23 @@
       <c r="BF56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH56" s="12"/>
+      <c r="BG56" s="10">
+        <v>55</v>
+      </c>
+      <c r="BH56" s="12">
+        <v>61952.380952320003</v>
+      </c>
       <c r="BI56" s="10">
         <f t="shared" si="14"/>
-        <v>-68</v>
+        <v>-13</v>
       </c>
       <c r="BJ56" s="12">
         <f t="shared" si="15"/>
-        <v>-74685.714285630005</v>
+        <v>-12733.333333310002</v>
       </c>
       <c r="BK56" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.17049222137197895</v>
       </c>
       <c r="BM56" s="14"/>
       <c r="BN56" s="13" t="s">
@@ -14186,15 +14401,15 @@
       <c r="BP56" s="12"/>
       <c r="BQ56" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="BR56" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS56" s="11" t="e">
+        <v>-61952.380952320003</v>
+      </c>
+      <c r="BS56" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU56" s="14"/>
       <c r="BV56" s="13" t="s">
@@ -14414,18 +14629,23 @@
       <c r="BF57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH57" s="12"/>
+      <c r="BG57" s="10">
+        <v>16</v>
+      </c>
+      <c r="BH57" s="12">
+        <v>124133.33333332</v>
+      </c>
       <c r="BI57" s="10">
         <f t="shared" si="14"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="BJ57" s="12">
         <f t="shared" si="15"/>
-        <v>-97028.57142855</v>
+        <v>27104.761904769999</v>
       </c>
       <c r="BK57" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.27934825284663117</v>
       </c>
       <c r="BM57" s="14"/>
       <c r="BN57" s="13" t="s">
@@ -14434,15 +14654,15 @@
       <c r="BP57" s="12"/>
       <c r="BQ57" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BR57" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS57" s="11" t="e">
+        <v>-124133.33333332</v>
+      </c>
+      <c r="BS57" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU57" s="14"/>
       <c r="BV57" s="13" t="s">
@@ -14662,18 +14882,23 @@
       <c r="BF58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH58" s="12"/>
+      <c r="BG58" s="10">
+        <v>6</v>
+      </c>
+      <c r="BH58" s="12">
+        <v>61333.333333310002</v>
+      </c>
       <c r="BI58" s="10">
         <f t="shared" si="14"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="BJ58" s="12">
         <f t="shared" si="15"/>
-        <v>-72666.66666665001</v>
+        <v>-11333.333333340008</v>
       </c>
       <c r="BK58" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.15596330275242118</v>
       </c>
       <c r="BM58" s="14"/>
       <c r="BN58" s="13" t="s">
@@ -14682,15 +14907,15 @@
       <c r="BP58" s="12"/>
       <c r="BQ58" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BR58" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS58" s="11" t="e">
+        <v>-61333.333333310002</v>
+      </c>
+      <c r="BS58" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU58" s="14"/>
       <c r="BV58" s="13" t="s">
@@ -15134,18 +15359,23 @@
       <c r="BF60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH60" s="12"/>
+      <c r="BG60" s="10">
+        <v>7</v>
+      </c>
+      <c r="BH60" s="12">
+        <v>29130</v>
+      </c>
       <c r="BI60" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="BJ60" s="12">
         <f t="shared" si="15"/>
-        <v>-4280</v>
+        <v>24850</v>
       </c>
       <c r="BK60" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>5.80607476635514</v>
       </c>
       <c r="BM60" s="14"/>
       <c r="BN60" s="13" t="s">
@@ -15154,15 +15384,15 @@
       <c r="BP60" s="12"/>
       <c r="BQ60" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BR60" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS60" s="11" t="e">
+        <v>-29130</v>
+      </c>
+      <c r="BS60" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU60" s="14"/>
       <c r="BV60" s="13" t="s">
@@ -15382,18 +15612,23 @@
       <c r="BF61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH61" s="12"/>
+      <c r="BG61" s="10">
+        <v>3</v>
+      </c>
+      <c r="BH61" s="12">
+        <v>94242.857142840003</v>
+      </c>
       <c r="BI61" s="10">
         <f t="shared" si="14"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BJ61" s="12">
         <f t="shared" si="15"/>
-        <v>-78761.904761900005</v>
+        <v>15480.952380939998</v>
       </c>
       <c r="BK61" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.19655380894785948</v>
       </c>
       <c r="BM61" s="14"/>
       <c r="BN61" s="13" t="s">
@@ -15402,15 +15637,15 @@
       <c r="BP61" s="12"/>
       <c r="BQ61" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BR61" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS61" s="11" t="e">
+        <v>-94242.857142840003</v>
+      </c>
+      <c r="BS61" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU61" s="14"/>
       <c r="BV61" s="13" t="s">
@@ -15630,18 +15865,23 @@
       <c r="BF62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH62" s="12"/>
+      <c r="BG62" s="10">
+        <v>13</v>
+      </c>
+      <c r="BH62" s="12">
+        <v>247809.52380948002</v>
+      </c>
       <c r="BI62" s="10">
         <f t="shared" si="14"/>
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="BJ62" s="12">
         <f t="shared" si="15"/>
-        <v>-430761.90476185014</v>
+        <v>-182952.38095237012</v>
       </c>
       <c r="BK62" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.42471810745083571</v>
       </c>
       <c r="BM62" s="14"/>
       <c r="BN62" s="13" t="s">
@@ -15650,15 +15890,15 @@
       <c r="BP62" s="12"/>
       <c r="BQ62" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BR62" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS62" s="11" t="e">
+        <v>-247809.52380948002</v>
+      </c>
+      <c r="BS62" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU62" s="14"/>
       <c r="BV62" s="13" t="s">
@@ -15878,18 +16118,23 @@
       <c r="BF63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH63" s="12"/>
+      <c r="BG63" s="10">
+        <v>12</v>
+      </c>
+      <c r="BH63" s="12">
+        <v>383619.04761902994</v>
+      </c>
       <c r="BI63" s="10">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="BJ63" s="12">
         <f t="shared" si="15"/>
-        <v>-342857.14285711996</v>
+        <v>40761.904761909973</v>
       </c>
       <c r="BK63" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.11888888888891203</v>
       </c>
       <c r="BM63" s="14"/>
       <c r="BN63" s="13" t="s">
@@ -15898,15 +16143,15 @@
       <c r="BP63" s="12"/>
       <c r="BQ63" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BR63" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS63" s="11" t="e">
+        <v>-383619.04761902994</v>
+      </c>
+      <c r="BS63" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU63" s="14"/>
       <c r="BV63" s="13" t="s">
@@ -16127,19 +16372,23 @@
         <v>1</v>
       </c>
       <c r="BF64" s="9"/>
-      <c r="BG64" s="8"/>
-      <c r="BH64" s="7"/>
+      <c r="BG64" s="8">
+        <v>214</v>
+      </c>
+      <c r="BH64" s="7">
+        <v>1105685.2380945599</v>
+      </c>
       <c r="BI64" s="27">
         <f t="shared" si="14"/>
-        <v>-226</v>
+        <v>-12</v>
       </c>
       <c r="BJ64" s="28">
         <f t="shared" si="15"/>
-        <v>-1206023.8095231601</v>
+        <v>-100338.57142860023</v>
       </c>
       <c r="BK64" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-8.3197836258533137E-2</v>
       </c>
       <c r="BM64" s="9" t="s">
         <v>1</v>
@@ -16149,15 +16398,15 @@
       <c r="BP64" s="7"/>
       <c r="BQ64" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-214</v>
       </c>
       <c r="BR64" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS64" s="29" t="e">
+        <v>-1105685.2380945599</v>
+      </c>
+      <c r="BS64" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU64" s="9" t="s">
         <v>1</v>
@@ -16382,19 +16631,23 @@
         <v>0</v>
       </c>
       <c r="BF65" s="4"/>
-      <c r="BG65" s="3"/>
-      <c r="BH65" s="2"/>
+      <c r="BG65" s="3">
+        <v>1780</v>
+      </c>
+      <c r="BH65" s="2">
+        <v>14018858.571424255</v>
+      </c>
       <c r="BI65" s="6">
         <f t="shared" si="14"/>
-        <v>-1769</v>
+        <v>11</v>
       </c>
       <c r="BJ65" s="5">
         <f t="shared" si="15"/>
-        <v>-14188011.42856749</v>
+        <v>-169152.85714323446</v>
       </c>
       <c r="BK65" s="30">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-1.1922238574085586E-2</v>
       </c>
       <c r="BM65" s="4" t="s">
         <v>0</v>
@@ -16404,15 +16657,15 @@
       <c r="BP65" s="2"/>
       <c r="BQ65" s="6">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1780</v>
       </c>
       <c r="BR65" s="5">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS65" s="30" t="e">
+        <v>-14018858.571424255</v>
+      </c>
+      <c r="BS65" s="30">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E033516-99E7-6541-B16B-A40458CB5B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58179139-5F28-B847-A7E2-30B81F0358D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="600" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="7140" yWindow="3560" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -1820,10 +1820,13 @@
       <c r="BF6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BG6" s="15">
+        <v>11</v>
+      </c>
       <c r="BH6" s="33"/>
       <c r="BI6" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="BJ6" s="12">
         <f t="shared" si="15"/>
@@ -1840,7 +1843,7 @@
       <c r="BP6" s="33"/>
       <c r="BQ6" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BR6" s="12">
         <f t="shared" si="18"/>
@@ -4854,10 +4857,13 @@
       <c r="BF18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BG18" s="1">
+        <v>3</v>
+      </c>
       <c r="BH18" s="35"/>
       <c r="BI18" s="10">
         <f t="shared" si="14"/>
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="15"/>
@@ -4874,7 +4880,7 @@
       <c r="BP18" s="35"/>
       <c r="BQ18" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BR18" s="12">
         <f t="shared" si="18"/>
@@ -7868,10 +7874,13 @@
       <c r="BF30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BG30" s="1">
+        <v>2</v>
+      </c>
       <c r="BH30" s="35"/>
       <c r="BI30" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="15"/>
@@ -7888,7 +7897,7 @@
       <c r="BP30" s="35"/>
       <c r="BQ30" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BR30" s="12">
         <f t="shared" si="18"/>
@@ -10881,10 +10890,13 @@
       <c r="BF42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BG42" s="1">
+        <v>5</v>
+      </c>
       <c r="BH42" s="35"/>
       <c r="BI42" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="15"/>
@@ -10901,7 +10913,7 @@
       <c r="BP42" s="35"/>
       <c r="BQ42" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BR42" s="12">
         <f t="shared" si="18"/>
@@ -13870,6 +13882,9 @@
       <c r="BE54" s="14"/>
       <c r="BF54" s="32" t="s">
         <v>21</v>
+      </c>
+      <c r="BG54" s="1">
+        <v>0</v>
       </c>
       <c r="BH54" s="35"/>
       <c r="BI54" s="10">

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58179139-5F28-B847-A7E2-30B81F0358D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4059DEA3-341C-A749-AB3E-D3F4EE2237E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="3560" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="40">
   <si>
     <t>總計</t>
   </si>
@@ -208,6 +208,14 @@
   </si>
   <si>
     <t>05/17~05/23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/24~05/30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1079,7 +1087,9 @@
       </c>
       <c r="BF1" s="26"/>
       <c r="BH1" s="25"/>
-      <c r="BM1" s="26"/>
+      <c r="BM1" s="26" t="s">
+        <v>38</v>
+      </c>
       <c r="BU1" s="26"/>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
@@ -1141,6 +1151,9 @@
       <c r="BG2" s="22"/>
       <c r="BH2" s="22"/>
       <c r="BJ2" s="21"/>
+      <c r="BM2" s="20" t="s">
+        <v>39</v>
+      </c>
       <c r="BN2" s="21"/>
       <c r="BP2" s="21"/>
       <c r="BQ2" s="21"/>
@@ -1585,11 +1598,13 @@
       <c r="BN5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BO5" s="40"/>
+      <c r="BO5" s="40">
+        <v>5351</v>
+      </c>
       <c r="BP5" s="1"/>
       <c r="BQ5" s="10">
         <f t="shared" ref="BQ5:BQ65" si="17">BO5-BG5</f>
-        <v>-5642</v>
+        <v>-291</v>
       </c>
       <c r="BR5" s="12">
         <f t="shared" ref="BR5:BR65" si="18">BP5-BH5</f>
@@ -1610,7 +1625,7 @@
       <c r="BX5" s="33"/>
       <c r="BY5" s="10">
         <f t="shared" ref="BY5:BY36" si="20">BW5-BO5</f>
-        <v>0</v>
+        <v>-5351</v>
       </c>
       <c r="BZ5" s="12">
         <f t="shared" ref="BZ5:BZ65" si="21">BX5-BP5</f>
@@ -4627,10 +4642,13 @@
       <c r="BN17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BO17" s="1">
+        <v>3865</v>
+      </c>
       <c r="BP17" s="35"/>
       <c r="BQ17" s="10">
         <f t="shared" si="17"/>
-        <v>-4036</v>
+        <v>-171</v>
       </c>
       <c r="BR17" s="12">
         <f t="shared" si="18"/>
@@ -4650,7 +4668,7 @@
       <c r="BX17" s="33"/>
       <c r="BY17" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-3865</v>
       </c>
       <c r="BZ17" s="12">
         <f t="shared" si="21"/>
@@ -7644,10 +7662,13 @@
       <c r="BN29" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BO29" s="1">
+        <v>3127</v>
+      </c>
       <c r="BP29" s="35"/>
       <c r="BQ29" s="10">
         <f t="shared" si="17"/>
-        <v>-3581</v>
+        <v>-454</v>
       </c>
       <c r="BR29" s="12">
         <f t="shared" si="18"/>
@@ -7667,7 +7688,7 @@
       <c r="BX29" s="33"/>
       <c r="BY29" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-3127</v>
       </c>
       <c r="BZ29" s="12">
         <f t="shared" si="21"/>
@@ -10660,10 +10681,13 @@
       <c r="BN41" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BO41" s="1">
+        <v>1340</v>
+      </c>
       <c r="BP41" s="35"/>
       <c r="BQ41" s="10">
         <f t="shared" si="17"/>
-        <v>-1157</v>
+        <v>183</v>
       </c>
       <c r="BR41" s="12">
         <f t="shared" si="18"/>
@@ -10683,7 +10707,7 @@
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-1340</v>
       </c>
       <c r="BZ41" s="12">
         <f t="shared" si="21"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4059DEA3-341C-A749-AB3E-D3F4EE2237E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCAF389-5E03-7541-AC15-037C3232BDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="10400" yWindow="600" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -2108,18 +2108,23 @@
       <c r="BN7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BP7" s="12"/>
+      <c r="BO7" s="10">
+        <v>190</v>
+      </c>
+      <c r="BP7" s="12">
+        <v>236653.33333254</v>
+      </c>
       <c r="BQ7" s="10">
         <f t="shared" si="17"/>
-        <v>-197</v>
+        <v>-7</v>
       </c>
       <c r="BR7" s="12">
         <f t="shared" si="18"/>
-        <v>-247345.71428483998</v>
+        <v>-10692.38095229998</v>
       </c>
       <c r="BS7" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-4.3228486829518215E-2</v>
       </c>
       <c r="BU7" s="14"/>
       <c r="BV7" s="13" t="s">
@@ -2128,15 +2133,15 @@
       <c r="BX7" s="12"/>
       <c r="BY7" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-190</v>
       </c>
       <c r="BZ7" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA7" s="11" t="e">
+        <v>-236653.33333254</v>
+      </c>
+      <c r="CA7" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC7" s="14"/>
       <c r="CD7" s="13" t="s">
@@ -2361,18 +2366,23 @@
       <c r="BN8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP8" s="12"/>
+      <c r="BO8" s="10">
+        <v>145</v>
+      </c>
+      <c r="BP8" s="12">
+        <v>209325.71428555003</v>
+      </c>
       <c r="BQ8" s="10">
         <f t="shared" si="17"/>
-        <v>-224</v>
+        <v>-79</v>
       </c>
       <c r="BR8" s="12">
         <f t="shared" si="18"/>
-        <v>-321190.47619030986</v>
+        <v>-111864.76190475983</v>
       </c>
       <c r="BS8" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.34828169014101895</v>
       </c>
       <c r="BU8" s="14"/>
       <c r="BV8" s="13" t="s">
@@ -2381,15 +2391,15 @@
       <c r="BX8" s="12"/>
       <c r="BY8" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-145</v>
       </c>
       <c r="BZ8" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA8" s="11" t="e">
+        <v>-209325.71428555003</v>
+      </c>
+      <c r="CA8" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC8" s="14"/>
       <c r="CD8" s="13" t="s">
@@ -2614,18 +2624,23 @@
       <c r="BN9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP9" s="12"/>
+      <c r="BO9" s="10">
+        <v>58</v>
+      </c>
+      <c r="BP9" s="12">
+        <v>372304.76190474001</v>
+      </c>
       <c r="BQ9" s="10">
         <f t="shared" si="17"/>
-        <v>-55</v>
+        <v>3</v>
       </c>
       <c r="BR9" s="12">
         <f t="shared" si="18"/>
-        <v>-375190.47619045997</v>
+        <v>-2885.7142857199651</v>
       </c>
       <c r="BS9" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-7.6913313872473523E-3</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="13" t="s">
@@ -2634,15 +2649,15 @@
       <c r="BX9" s="12"/>
       <c r="BY9" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="BZ9" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA9" s="11" t="e">
+        <v>-372304.76190474001</v>
+      </c>
+      <c r="CA9" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC9" s="14"/>
       <c r="CD9" s="13" t="s">
@@ -2867,18 +2882,23 @@
       <c r="BN10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP10" s="12"/>
+      <c r="BO10" s="10">
+        <v>34</v>
+      </c>
+      <c r="BP10" s="12">
+        <v>491047.61904754001</v>
+      </c>
       <c r="BQ10" s="10">
         <f t="shared" si="17"/>
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="BR10" s="12">
         <f t="shared" si="18"/>
-        <v>-411047.61904753</v>
+        <v>80000.000000010012</v>
       </c>
       <c r="BS10" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.19462465245604427</v>
       </c>
       <c r="BU10" s="14"/>
       <c r="BV10" s="13" t="s">
@@ -2887,15 +2907,15 @@
       <c r="BX10" s="12"/>
       <c r="BY10" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="BZ10" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA10" s="11" t="e">
+        <v>-491047.61904754001</v>
+      </c>
+      <c r="CA10" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC10" s="14"/>
       <c r="CD10" s="13" t="s">
@@ -3368,18 +3388,23 @@
       <c r="BN12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP12" s="12"/>
+      <c r="BO12" s="10">
+        <v>9</v>
+      </c>
+      <c r="BP12" s="12">
+        <v>44230</v>
+      </c>
       <c r="BQ12" s="10">
         <f t="shared" si="17"/>
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="BR12" s="12">
         <f t="shared" si="18"/>
-        <v>-40030</v>
+        <v>4200</v>
       </c>
       <c r="BS12" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.10492130901823632</v>
       </c>
       <c r="BU12" s="14"/>
       <c r="BV12" s="13" t="s">
@@ -3388,15 +3413,15 @@
       <c r="BX12" s="12"/>
       <c r="BY12" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BZ12" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA12" s="11" t="e">
+        <v>-44230</v>
+      </c>
+      <c r="CA12" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC12" s="14"/>
       <c r="CD12" s="13" t="s">
@@ -3621,18 +3646,23 @@
       <c r="BN13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP13" s="12"/>
+      <c r="BO13" s="10">
+        <v>29</v>
+      </c>
+      <c r="BP13" s="12">
+        <v>1297114.28571422</v>
+      </c>
       <c r="BQ13" s="10">
         <f t="shared" si="17"/>
-        <v>-38</v>
+        <v>-9</v>
       </c>
       <c r="BR13" s="12">
         <f t="shared" si="18"/>
-        <v>-1349485.7142855995</v>
+        <v>-52371.428571379511</v>
       </c>
       <c r="BS13" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-3.8808434959316539E-2</v>
       </c>
       <c r="BU13" s="14"/>
       <c r="BV13" s="13" t="s">
@@ -3641,15 +3671,15 @@
       <c r="BX13" s="12"/>
       <c r="BY13" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="BZ13" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA13" s="11" t="e">
+        <v>-1297114.28571422</v>
+      </c>
+      <c r="CA13" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="13" t="s">
@@ -3874,18 +3904,23 @@
       <c r="BN14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP14" s="12"/>
+      <c r="BO14" s="10">
+        <v>56</v>
+      </c>
+      <c r="BP14" s="12">
+        <v>1051047.6190475204</v>
+      </c>
       <c r="BQ14" s="10">
         <f t="shared" si="17"/>
-        <v>-51</v>
+        <v>5</v>
       </c>
       <c r="BR14" s="12">
         <f t="shared" si="18"/>
-        <v>-939619.04761893023</v>
+        <v>111428.57142859022</v>
       </c>
       <c r="BS14" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.11858909385772791</v>
       </c>
       <c r="BU14" s="14"/>
       <c r="BV14" s="13" t="s">
@@ -3894,15 +3929,15 @@
       <c r="BX14" s="12"/>
       <c r="BY14" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="BZ14" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA14" s="11" t="e">
+        <v>-1051047.6190475204</v>
+      </c>
+      <c r="CA14" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC14" s="14"/>
       <c r="CD14" s="13" t="s">
@@ -4127,18 +4162,23 @@
       <c r="BN15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP15" s="12"/>
+      <c r="BO15" s="10">
+        <v>71</v>
+      </c>
+      <c r="BP15" s="12">
+        <v>2628476.1904761</v>
+      </c>
       <c r="BQ15" s="10">
         <f t="shared" si="17"/>
-        <v>-84</v>
+        <v>-13</v>
       </c>
       <c r="BR15" s="12">
         <f t="shared" si="18"/>
-        <v>-3233904.7619046797</v>
+        <v>-605428.57142857974</v>
       </c>
       <c r="BS15" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.18721286370597975</v>
       </c>
       <c r="BU15" s="14"/>
       <c r="BV15" s="13" t="s">
@@ -4147,15 +4187,15 @@
       <c r="BX15" s="12"/>
       <c r="BY15" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="BZ15" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA15" s="11" t="e">
+        <v>-2628476.1904761</v>
+      </c>
+      <c r="CA15" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC15" s="14"/>
       <c r="CD15" s="13" t="s">
@@ -4381,19 +4421,23 @@
         <v>19</v>
       </c>
       <c r="BN16" s="9"/>
-      <c r="BO16" s="8"/>
-      <c r="BP16" s="7"/>
+      <c r="BO16" s="8">
+        <v>592</v>
+      </c>
+      <c r="BP16" s="7">
+        <v>6330199.5238082111</v>
+      </c>
       <c r="BQ16" s="27">
         <f t="shared" si="17"/>
-        <v>-691</v>
+        <v>-99</v>
       </c>
       <c r="BR16" s="28">
         <f t="shared" si="18"/>
-        <v>-6926670.9523794893</v>
+        <v>-596471.42857127823</v>
       </c>
       <c r="BS16" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-8.6112280007522954E-2</v>
       </c>
       <c r="BU16" s="9" t="s">
         <v>19</v>
@@ -4403,15 +4447,15 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="27">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-592</v>
       </c>
       <c r="BZ16" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA16" s="29" t="e">
+        <v>-6330199.5238082111</v>
+      </c>
+      <c r="CA16" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC16" s="9" t="s">
         <v>19</v>
@@ -5152,18 +5196,23 @@
       <c r="BN19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BP19" s="12"/>
+      <c r="BO19" s="10">
+        <v>124</v>
+      </c>
+      <c r="BP19" s="12">
+        <v>131030.47618989997</v>
+      </c>
       <c r="BQ19" s="10">
         <f t="shared" si="17"/>
-        <v>-119</v>
+        <v>5</v>
       </c>
       <c r="BR19" s="12">
         <f t="shared" si="18"/>
-        <v>-121252.38095184001</v>
+        <v>9778.0952380599629</v>
       </c>
       <c r="BS19" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>8.0642500883703921E-2</v>
       </c>
       <c r="BU19" s="14"/>
       <c r="BV19" s="13" t="s">
@@ -5172,15 +5221,15 @@
       <c r="BX19" s="12"/>
       <c r="BY19" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="BZ19" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA19" s="11" t="e">
+        <v>-131030.47618989997</v>
+      </c>
+      <c r="CA19" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC19" s="14"/>
       <c r="CD19" s="13" t="s">
@@ -5405,18 +5454,23 @@
       <c r="BN20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP20" s="12"/>
+      <c r="BO20" s="10">
+        <v>124</v>
+      </c>
+      <c r="BP20" s="12">
+        <v>129352.38095226999</v>
+      </c>
       <c r="BQ20" s="10">
         <f t="shared" si="17"/>
-        <v>-158</v>
+        <v>-34</v>
       </c>
       <c r="BR20" s="12">
         <f t="shared" si="18"/>
-        <v>-167201.90476180997</v>
+        <v>-37849.523809539984</v>
       </c>
       <c r="BS20" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.22637017122178782</v>
       </c>
       <c r="BU20" s="14"/>
       <c r="BV20" s="13" t="s">
@@ -5425,15 +5479,15 @@
       <c r="BX20" s="12"/>
       <c r="BY20" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="BZ20" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA20" s="11" t="e">
+        <v>-129352.38095226999</v>
+      </c>
+      <c r="CA20" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC20" s="14"/>
       <c r="CD20" s="13" t="s">
@@ -5658,18 +5712,23 @@
       <c r="BN21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP21" s="12"/>
+      <c r="BO21" s="10">
+        <v>36</v>
+      </c>
+      <c r="BP21" s="12">
+        <v>249657.14285711999</v>
+      </c>
       <c r="BQ21" s="10">
         <f t="shared" si="17"/>
-        <v>-39</v>
+        <v>-3</v>
       </c>
       <c r="BR21" s="12">
         <f t="shared" si="18"/>
-        <v>-258199.99999998001</v>
+        <v>-8542.8571428600117</v>
       </c>
       <c r="BS21" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-3.3086201172969301E-2</v>
       </c>
       <c r="BU21" s="14"/>
       <c r="BV21" s="13" t="s">
@@ -5678,15 +5737,15 @@
       <c r="BX21" s="12"/>
       <c r="BY21" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="BZ21" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA21" s="11" t="e">
+        <v>-249657.14285711999</v>
+      </c>
+      <c r="CA21" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC21" s="14"/>
       <c r="CD21" s="13" t="s">
@@ -5911,18 +5970,23 @@
       <c r="BN22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP22" s="12"/>
+      <c r="BO22" s="10">
+        <v>18</v>
+      </c>
+      <c r="BP22" s="12">
+        <v>261142.85714278001</v>
+      </c>
       <c r="BQ22" s="10">
         <f t="shared" si="17"/>
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="BR22" s="12">
         <f t="shared" si="18"/>
-        <v>-152095.23809519003</v>
+        <v>109047.61904758998</v>
       </c>
       <c r="BS22" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.71696931747029224</v>
       </c>
       <c r="BU22" s="14"/>
       <c r="BV22" s="13" t="s">
@@ -5931,15 +5995,15 @@
       <c r="BX22" s="12"/>
       <c r="BY22" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BZ22" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA22" s="11" t="e">
+        <v>-261142.85714278001</v>
+      </c>
+      <c r="CA22" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC22" s="14"/>
       <c r="CD22" s="13" t="s">
@@ -6135,14 +6199,19 @@
       <c r="BN23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP23" s="12"/>
+      <c r="BO23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP23" s="12">
+        <v>2657.1428571400002</v>
+      </c>
       <c r="BQ23" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR23" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2657.1428571400002</v>
       </c>
       <c r="BS23" s="11" t="e">
         <f t="shared" si="19"/>
@@ -6155,15 +6224,15 @@
       <c r="BX23" s="12"/>
       <c r="BY23" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BZ23" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA23" s="11" t="e">
+        <v>-2657.1428571400002</v>
+      </c>
+      <c r="CA23" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC23" s="14"/>
       <c r="CD23" s="13" t="s">
@@ -6388,18 +6457,23 @@
       <c r="BN24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP24" s="12"/>
+      <c r="BO24" s="10">
+        <v>15</v>
+      </c>
+      <c r="BP24" s="12">
+        <v>73880</v>
+      </c>
       <c r="BQ24" s="10">
         <f t="shared" si="17"/>
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="BR24" s="12">
         <f t="shared" si="18"/>
-        <v>-74580</v>
+        <v>-700</v>
       </c>
       <c r="BS24" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-9.3858943416465536E-3</v>
       </c>
       <c r="BU24" s="14"/>
       <c r="BV24" s="13" t="s">
@@ -6408,15 +6482,15 @@
       <c r="BX24" s="12"/>
       <c r="BY24" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BZ24" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA24" s="11" t="e">
+        <v>-73880</v>
+      </c>
+      <c r="CA24" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC24" s="14"/>
       <c r="CD24" s="13" t="s">
@@ -6641,18 +6715,23 @@
       <c r="BN25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP25" s="12"/>
+      <c r="BO25" s="10">
+        <v>20</v>
+      </c>
+      <c r="BP25" s="12">
+        <v>865076.19047613011</v>
+      </c>
       <c r="BQ25" s="10">
         <f t="shared" si="17"/>
-        <v>-17</v>
+        <v>3</v>
       </c>
       <c r="BR25" s="12">
         <f t="shared" si="18"/>
-        <v>-685052.38095231005</v>
+        <v>180023.80952382006</v>
       </c>
       <c r="BS25" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.26278838601153981</v>
       </c>
       <c r="BU25" s="14"/>
       <c r="BV25" s="13" t="s">
@@ -6661,15 +6740,15 @@
       <c r="BX25" s="12"/>
       <c r="BY25" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BZ25" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA25" s="11" t="e">
+        <v>-865076.19047613011</v>
+      </c>
+      <c r="CA25" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC25" s="14"/>
       <c r="CD25" s="13" t="s">
@@ -6894,18 +6973,23 @@
       <c r="BN26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP26" s="12"/>
+      <c r="BO26" s="10">
+        <v>21</v>
+      </c>
+      <c r="BP26" s="12">
+        <v>340095.23809518002</v>
+      </c>
       <c r="BQ26" s="10">
         <f t="shared" si="17"/>
-        <v>-22</v>
+        <v>-1</v>
       </c>
       <c r="BR26" s="12">
         <f t="shared" si="18"/>
-        <v>-387999.99999995006</v>
+        <v>-47904.761904770043</v>
       </c>
       <c r="BS26" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.12346588119787683</v>
       </c>
       <c r="BU26" s="14"/>
       <c r="BV26" s="13" t="s">
@@ -6914,15 +6998,15 @@
       <c r="BX26" s="12"/>
       <c r="BY26" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="BZ26" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA26" s="11" t="e">
+        <v>-340095.23809518002</v>
+      </c>
+      <c r="CA26" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC26" s="14"/>
       <c r="CD26" s="13" t="s">
@@ -7147,18 +7231,23 @@
       <c r="BN27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP27" s="12"/>
+      <c r="BO27" s="10">
+        <v>46</v>
+      </c>
+      <c r="BP27" s="12">
+        <v>1654666.6666665899</v>
+      </c>
       <c r="BQ27" s="10">
         <f t="shared" si="17"/>
-        <v>-48</v>
+        <v>-2</v>
       </c>
       <c r="BR27" s="12">
         <f t="shared" si="18"/>
-        <v>-1667809.52380947</v>
+        <v>-13142.857142880093</v>
       </c>
       <c r="BS27" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-7.8803106441437554E-3</v>
       </c>
       <c r="BU27" s="14"/>
       <c r="BV27" s="13" t="s">
@@ -7167,15 +7256,15 @@
       <c r="BX27" s="12"/>
       <c r="BY27" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="BZ27" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA27" s="11" t="e">
+        <v>-1654666.6666665899</v>
+      </c>
+      <c r="CA27" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC27" s="14"/>
       <c r="CD27" s="13" t="s">
@@ -7401,19 +7490,23 @@
         <v>13</v>
       </c>
       <c r="BN28" s="9"/>
-      <c r="BO28" s="8"/>
-      <c r="BP28" s="7"/>
+      <c r="BO28" s="8">
+        <v>405</v>
+      </c>
+      <c r="BP28" s="7">
+        <v>3707558.0952371098</v>
+      </c>
       <c r="BQ28" s="27">
         <f t="shared" si="17"/>
-        <v>-430</v>
+        <v>-25</v>
       </c>
       <c r="BR28" s="28">
         <f t="shared" si="18"/>
-        <v>-3514191.4285705499</v>
+        <v>193366.66666655988</v>
       </c>
       <c r="BS28" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>5.5024511497717317E-2</v>
       </c>
       <c r="BU28" s="9" t="s">
         <v>13</v>
@@ -7423,15 +7516,15 @@
       <c r="BX28" s="7"/>
       <c r="BY28" s="27">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-405</v>
       </c>
       <c r="BZ28" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA28" s="29" t="e">
+        <v>-3707558.0952371098</v>
+      </c>
+      <c r="CA28" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC28" s="9" t="s">
         <v>13</v>
@@ -8172,18 +8265,23 @@
       <c r="BN31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BP31" s="12"/>
+      <c r="BO31" s="10">
+        <v>71</v>
+      </c>
+      <c r="BP31" s="12">
+        <v>83721.904761590064</v>
+      </c>
       <c r="BQ31" s="10">
         <f t="shared" si="17"/>
-        <v>-104</v>
+        <v>-33</v>
       </c>
       <c r="BR31" s="12">
         <f t="shared" si="18"/>
-        <v>-104592.38095199002</v>
+        <v>-20870.476190399961</v>
       </c>
       <c r="BS31" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.19954107555864822</v>
       </c>
       <c r="BU31" s="14"/>
       <c r="BV31" s="13" t="s">
@@ -8192,15 +8290,15 @@
       <c r="BX31" s="12"/>
       <c r="BY31" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="BZ31" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA31" s="11" t="e">
+        <v>-83721.904761590064</v>
+      </c>
+      <c r="CA31" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC31" s="14"/>
       <c r="CD31" s="13" t="s">
@@ -8425,18 +8523,23 @@
       <c r="BN32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP32" s="12"/>
+      <c r="BO32" s="10">
+        <v>49</v>
+      </c>
+      <c r="BP32" s="12">
+        <v>61971.428571330005</v>
+      </c>
       <c r="BQ32" s="10">
         <f t="shared" si="17"/>
-        <v>-61</v>
+        <v>-12</v>
       </c>
       <c r="BR32" s="12">
         <f t="shared" si="18"/>
-        <v>-63001.904761810008</v>
+        <v>-1030.4761904800034</v>
       </c>
       <c r="BS32" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-1.6356270407631379E-2</v>
       </c>
       <c r="BU32" s="14"/>
       <c r="BV32" s="13" t="s">
@@ -8445,15 +8548,15 @@
       <c r="BX32" s="12"/>
       <c r="BY32" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="BZ32" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA32" s="11" t="e">
+        <v>-61971.428571330005</v>
+      </c>
+      <c r="CA32" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC32" s="14"/>
       <c r="CD32" s="13" t="s">
@@ -8678,18 +8781,23 @@
       <c r="BN33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP33" s="12"/>
+      <c r="BO33" s="10">
+        <v>18</v>
+      </c>
+      <c r="BP33" s="12">
+        <v>144114.28571426001</v>
+      </c>
       <c r="BQ33" s="10">
         <f t="shared" si="17"/>
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="BR33" s="12">
         <f t="shared" si="18"/>
-        <v>-119819.04761903</v>
+        <v>24295.238095230015</v>
       </c>
       <c r="BS33" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.20276607582859285</v>
       </c>
       <c r="BU33" s="14"/>
       <c r="BV33" s="13" t="s">
@@ -8698,15 +8806,15 @@
       <c r="BX33" s="12"/>
       <c r="BY33" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BZ33" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA33" s="11" t="e">
+        <v>-144114.28571426001</v>
+      </c>
+      <c r="CA33" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC33" s="14"/>
       <c r="CD33" s="13" t="s">
@@ -8931,18 +9039,23 @@
       <c r="BN34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP34" s="12"/>
+      <c r="BO34" s="10">
+        <v>8</v>
+      </c>
+      <c r="BP34" s="12">
+        <v>83999.999999980006</v>
+      </c>
       <c r="BQ34" s="10">
         <f t="shared" si="17"/>
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="BR34" s="12">
         <f t="shared" si="18"/>
-        <v>-163904.76190471998</v>
+        <v>-79904.761904739978</v>
       </c>
       <c r="BS34" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.48750726321904958</v>
       </c>
       <c r="BU34" s="14"/>
       <c r="BV34" s="13" t="s">
@@ -8951,15 +9064,15 @@
       <c r="BX34" s="12"/>
       <c r="BY34" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ34" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA34" s="11" t="e">
+        <v>-83999.999999980006</v>
+      </c>
+      <c r="CA34" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC34" s="14"/>
       <c r="CD34" s="13" t="s">
@@ -9407,18 +9520,23 @@
       <c r="BN36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP36" s="12"/>
+      <c r="BO36" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP36" s="12">
+        <v>8280</v>
+      </c>
       <c r="BQ36" s="10">
         <f t="shared" si="17"/>
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="BR36" s="12">
         <f t="shared" si="18"/>
-        <v>-34530</v>
+        <v>-26250</v>
       </c>
       <c r="BS36" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.76020851433536052</v>
       </c>
       <c r="BU36" s="14"/>
       <c r="BV36" s="13" t="s">
@@ -9427,15 +9545,15 @@
       <c r="BX36" s="12"/>
       <c r="BY36" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BZ36" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA36" s="11" t="e">
+        <v>-8280</v>
+      </c>
+      <c r="CA36" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC36" s="14"/>
       <c r="CD36" s="13" t="s">
@@ -9660,18 +9778,23 @@
       <c r="BN37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP37" s="12"/>
+      <c r="BO37" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP37" s="12">
+        <v>104006.66666666001</v>
+      </c>
       <c r="BQ37" s="10">
         <f t="shared" si="17"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="BR37" s="12">
         <f t="shared" si="18"/>
-        <v>-110559.04761903</v>
+        <v>-6552.3809523699892</v>
       </c>
       <c r="BS37" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-5.9265895405941967E-2</v>
       </c>
       <c r="BU37" s="14"/>
       <c r="BV37" s="13" t="s">
@@ -9680,15 +9803,15 @@
       <c r="BX37" s="12"/>
       <c r="BY37" s="10">
         <f t="shared" ref="BY37:BY65" si="32">BW37-BO37</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BZ37" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA37" s="11" t="e">
+        <v>-104006.66666666001</v>
+      </c>
+      <c r="CA37" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC37" s="14"/>
       <c r="CD37" s="13" t="s">
@@ -9913,18 +10036,23 @@
       <c r="BN38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP38" s="12"/>
+      <c r="BO38" s="10">
+        <v>18</v>
+      </c>
+      <c r="BP38" s="12">
+        <v>311047.61904757994</v>
+      </c>
       <c r="BQ38" s="10">
         <f t="shared" si="17"/>
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="BR38" s="12">
         <f t="shared" si="18"/>
-        <v>-210285.71428568001</v>
+        <v>100761.90476189993</v>
       </c>
       <c r="BS38" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.47916666666672181</v>
       </c>
       <c r="BU38" s="14"/>
       <c r="BV38" s="13" t="s">
@@ -9933,15 +10061,15 @@
       <c r="BX38" s="12"/>
       <c r="BY38" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BZ38" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA38" s="11" t="e">
+        <v>-311047.61904757994</v>
+      </c>
+      <c r="CA38" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC38" s="14"/>
       <c r="CD38" s="13" t="s">
@@ -10166,18 +10294,23 @@
       <c r="BN39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP39" s="12"/>
+      <c r="BO39" s="10">
+        <v>15</v>
+      </c>
+      <c r="BP39" s="12">
+        <v>529047.61904759996</v>
+      </c>
       <c r="BQ39" s="10">
         <f t="shared" si="17"/>
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="BR39" s="12">
         <f t="shared" si="18"/>
-        <v>-520380.95238091995</v>
+        <v>8666.6666666800156</v>
       </c>
       <c r="BS39" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>1.6654465592998872E-2</v>
       </c>
       <c r="BU39" s="14"/>
       <c r="BV39" s="13" t="s">
@@ -10186,15 +10319,15 @@
       <c r="BX39" s="12"/>
       <c r="BY39" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BZ39" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA39" s="11" t="e">
+        <v>-529047.61904759996</v>
+      </c>
+      <c r="CA39" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC39" s="14"/>
       <c r="CD39" s="13" t="s">
@@ -10420,19 +10553,23 @@
         <v>12</v>
       </c>
       <c r="BN40" s="9"/>
-      <c r="BO40" s="8"/>
-      <c r="BP40" s="7"/>
+      <c r="BO40" s="8">
+        <v>185</v>
+      </c>
+      <c r="BP40" s="7">
+        <v>1326189.5238089999</v>
+      </c>
       <c r="BQ40" s="27">
         <f t="shared" si="17"/>
-        <v>-237</v>
+        <v>-52</v>
       </c>
       <c r="BR40" s="28">
         <f t="shared" si="18"/>
-        <v>-1327073.8095231799</v>
+        <v>-884.28571417997591</v>
       </c>
       <c r="BS40" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-6.6634252581452224E-4</v>
       </c>
       <c r="BU40" s="9" t="s">
         <v>12</v>
@@ -10442,15 +10579,15 @@
       <c r="BX40" s="7"/>
       <c r="BY40" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-185</v>
       </c>
       <c r="BZ40" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA40" s="29" t="e">
+        <v>-1326189.5238089999</v>
+      </c>
+      <c r="CA40" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC40" s="9" t="s">
         <v>12</v>
@@ -11191,18 +11328,23 @@
       <c r="BN43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BP43" s="12"/>
+      <c r="BO43" s="10">
+        <v>87</v>
+      </c>
+      <c r="BP43" s="12">
+        <v>104469.52380909999</v>
+      </c>
       <c r="BQ43" s="10">
         <f t="shared" si="17"/>
-        <v>-106</v>
+        <v>-19</v>
       </c>
       <c r="BR43" s="12">
         <f t="shared" si="18"/>
-        <v>-112294.28571382999</v>
+        <v>-7824.7619047299959</v>
       </c>
       <c r="BS43" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-6.9680855575060763E-2</v>
       </c>
       <c r="BU43" s="14"/>
       <c r="BV43" s="13" t="s">
@@ -11211,15 +11353,15 @@
       <c r="BX43" s="12"/>
       <c r="BY43" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-87</v>
       </c>
       <c r="BZ43" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA43" s="11" t="e">
+        <v>-104469.52380909999</v>
+      </c>
+      <c r="CA43" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC43" s="14"/>
       <c r="CD43" s="13" t="s">
@@ -11444,18 +11586,23 @@
       <c r="BN44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP44" s="12"/>
+      <c r="BO44" s="10">
+        <v>54</v>
+      </c>
+      <c r="BP44" s="12">
+        <v>67914.285714199999</v>
+      </c>
       <c r="BQ44" s="10">
         <f t="shared" si="17"/>
-        <v>-50</v>
+        <v>4</v>
       </c>
       <c r="BR44" s="12">
         <f t="shared" si="18"/>
-        <v>-68229.523809420003</v>
+        <v>-315.23809522000374</v>
       </c>
       <c r="BS44" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-4.6202593484388479E-3</v>
       </c>
       <c r="BU44" s="14"/>
       <c r="BV44" s="13" t="s">
@@ -11464,15 +11611,15 @@
       <c r="BX44" s="12"/>
       <c r="BY44" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="BZ44" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA44" s="11" t="e">
+        <v>-67914.285714199999</v>
+      </c>
+      <c r="CA44" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC44" s="14"/>
       <c r="CD44" s="13" t="s">
@@ -11697,18 +11844,23 @@
       <c r="BN45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP45" s="12"/>
+      <c r="BO45" s="10">
+        <v>9</v>
+      </c>
+      <c r="BP45" s="12">
+        <v>54199.999999990003</v>
+      </c>
       <c r="BQ45" s="10">
         <f t="shared" si="17"/>
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="BR45" s="12">
         <f t="shared" si="18"/>
-        <v>-89876.190476179996</v>
+        <v>-35676.190476189993</v>
       </c>
       <c r="BS45" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.39694818268521631</v>
       </c>
       <c r="BU45" s="14"/>
       <c r="BV45" s="13" t="s">
@@ -11717,15 +11869,15 @@
       <c r="BX45" s="12"/>
       <c r="BY45" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BZ45" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA45" s="11" t="e">
+        <v>-54199.999999990003</v>
+      </c>
+      <c r="CA45" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC45" s="14"/>
       <c r="CD45" s="13" t="s">
@@ -11950,18 +12102,23 @@
       <c r="BN46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP46" s="12"/>
+      <c r="BO46" s="10">
+        <v>12</v>
+      </c>
+      <c r="BP46" s="12">
+        <v>127428.57142853999</v>
+      </c>
       <c r="BQ46" s="10">
         <f t="shared" si="17"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="BR46" s="12">
         <f t="shared" si="18"/>
-        <v>-67047.619047600005</v>
+        <v>60380.952380939983</v>
       </c>
       <c r="BS46" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.90056818181825271</v>
       </c>
       <c r="BU46" s="14"/>
       <c r="BV46" s="13" t="s">
@@ -11970,15 +12127,15 @@
       <c r="BX46" s="12"/>
       <c r="BY46" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BZ46" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA46" s="11" t="e">
+        <v>-127428.57142853999</v>
+      </c>
+      <c r="CA46" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC46" s="14"/>
       <c r="CD46" s="13" t="s">
@@ -12431,18 +12588,23 @@
       <c r="BN48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP48" s="12"/>
+      <c r="BO48" s="10">
+        <v>4</v>
+      </c>
+      <c r="BP48" s="12">
+        <v>9170</v>
+      </c>
       <c r="BQ48" s="10">
         <f t="shared" si="17"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="BR48" s="12">
         <f t="shared" si="18"/>
-        <v>-8180</v>
+        <v>990</v>
       </c>
       <c r="BS48" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.12102689486552567</v>
       </c>
       <c r="BU48" s="14"/>
       <c r="BV48" s="13" t="s">
@@ -12451,15 +12613,15 @@
       <c r="BX48" s="12"/>
       <c r="BY48" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BZ48" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA48" s="11" t="e">
+        <v>-9170</v>
+      </c>
+      <c r="CA48" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC48" s="14"/>
       <c r="CD48" s="13" t="s">
@@ -12679,18 +12841,23 @@
       <c r="BN49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP49" s="12"/>
+      <c r="BO49" s="10">
+        <v>6</v>
+      </c>
+      <c r="BP49" s="12">
+        <v>145142.85714283999</v>
+      </c>
       <c r="BQ49" s="10">
         <f t="shared" si="17"/>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="BR49" s="12">
         <f t="shared" si="18"/>
-        <v>-116466.66666665001</v>
+        <v>28676.190476189979</v>
       </c>
       <c r="BS49" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.24621800637831207</v>
       </c>
       <c r="BU49" s="14"/>
       <c r="BV49" s="13" t="s">
@@ -12699,15 +12866,15 @@
       <c r="BX49" s="12"/>
       <c r="BY49" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BZ49" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA49" s="11" t="e">
+        <v>-145142.85714283999</v>
+      </c>
+      <c r="CA49" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC49" s="14"/>
       <c r="CD49" s="13" t="s">
@@ -12932,18 +13099,23 @@
       <c r="BN50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP50" s="12"/>
+      <c r="BO50" s="10">
+        <v>11</v>
+      </c>
+      <c r="BP50" s="12">
+        <v>194095.23809520999</v>
+      </c>
       <c r="BQ50" s="10">
         <f t="shared" si="17"/>
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="BR50" s="12">
         <f t="shared" si="18"/>
-        <v>-228285.71428568001</v>
+        <v>-34190.476190470014</v>
       </c>
       <c r="BS50" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.14977054651647437</v>
       </c>
       <c r="BU50" s="14"/>
       <c r="BV50" s="13" t="s">
@@ -12952,15 +13124,15 @@
       <c r="BX50" s="12"/>
       <c r="BY50" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BZ50" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA50" s="11" t="e">
+        <v>-194095.23809520999</v>
+      </c>
+      <c r="CA50" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC50" s="14"/>
       <c r="CD50" s="13" t="s">
@@ -13185,18 +13357,23 @@
       <c r="BN51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP51" s="12"/>
+      <c r="BO51" s="10">
+        <v>18</v>
+      </c>
+      <c r="BP51" s="12">
+        <v>639238.09523805999</v>
+      </c>
       <c r="BQ51" s="10">
         <f t="shared" si="17"/>
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="BR51" s="12">
         <f t="shared" si="18"/>
-        <v>-454857.14285712002</v>
+        <v>184380.95238093997</v>
       </c>
       <c r="BS51" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.40536013400334314</v>
       </c>
       <c r="BU51" s="14"/>
       <c r="BV51" s="13" t="s">
@@ -13205,15 +13382,15 @@
       <c r="BX51" s="12"/>
       <c r="BY51" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BZ51" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA51" s="11" t="e">
+        <v>-639238.09523805999</v>
+      </c>
+      <c r="CA51" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC51" s="14"/>
       <c r="CD51" s="13" t="s">
@@ -13439,19 +13616,23 @@
         <v>11</v>
       </c>
       <c r="BN52" s="9"/>
-      <c r="BO52" s="8"/>
-      <c r="BP52" s="7"/>
+      <c r="BO52" s="8">
+        <v>201</v>
+      </c>
+      <c r="BP52" s="7">
+        <v>1341658.5714279399</v>
+      </c>
       <c r="BQ52" s="27">
         <f t="shared" si="17"/>
-        <v>-208</v>
+        <v>-7</v>
       </c>
       <c r="BR52" s="28">
         <f t="shared" si="18"/>
-        <v>-1145237.1428564801</v>
+        <v>196421.42857145984</v>
       </c>
       <c r="BS52" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.17151157714073126</v>
       </c>
       <c r="BU52" s="9" t="s">
         <v>11</v>
@@ -13461,15 +13642,15 @@
       <c r="BX52" s="7"/>
       <c r="BY52" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-201</v>
       </c>
       <c r="BZ52" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA52" s="29" t="e">
+        <v>-1341658.5714279399</v>
+      </c>
+      <c r="CA52" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC52" s="9" t="s">
         <v>11</v>
@@ -14184,18 +14365,23 @@
       <c r="BN55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BP55" s="12"/>
+      <c r="BO55" s="10">
+        <v>91</v>
+      </c>
+      <c r="BP55" s="12">
+        <v>86616.190475760042</v>
+      </c>
       <c r="BQ55" s="10">
         <f t="shared" si="17"/>
-        <v>-102</v>
+        <v>-11</v>
       </c>
       <c r="BR55" s="12">
         <f t="shared" si="18"/>
-        <v>-103464.76190425998</v>
+        <v>-16848.571428499941</v>
       </c>
       <c r="BS55" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.16284357223081022</v>
       </c>
       <c r="BU55" s="14"/>
       <c r="BV55" s="13" t="s">
@@ -14204,15 +14390,15 @@
       <c r="BX55" s="12"/>
       <c r="BY55" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="BZ55" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA55" s="11" t="e">
+        <v>-86616.190475760042</v>
+      </c>
+      <c r="CA55" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC55" s="14"/>
       <c r="CD55" s="13" t="s">
@@ -14437,18 +14623,23 @@
       <c r="BN56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP56" s="12"/>
+      <c r="BO56" s="10">
+        <v>59</v>
+      </c>
+      <c r="BP56" s="12">
+        <v>56866.666666600002</v>
+      </c>
       <c r="BQ56" s="10">
         <f t="shared" si="17"/>
-        <v>-55</v>
+        <v>4</v>
       </c>
       <c r="BR56" s="12">
         <f t="shared" si="18"/>
-        <v>-61952.380952320003</v>
+        <v>-5085.7142857200015</v>
       </c>
       <c r="BS56" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-8.2090699462125369E-2</v>
       </c>
       <c r="BU56" s="14"/>
       <c r="BV56" s="13" t="s">
@@ -14457,15 +14648,15 @@
       <c r="BX56" s="12"/>
       <c r="BY56" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="BZ56" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA56" s="11" t="e">
+        <v>-56866.666666600002</v>
+      </c>
+      <c r="CA56" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC56" s="14"/>
       <c r="CD56" s="13" t="s">
@@ -14690,18 +14881,23 @@
       <c r="BN57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP57" s="12"/>
+      <c r="BO57" s="10">
+        <v>9</v>
+      </c>
+      <c r="BP57" s="12">
+        <v>57057.142857129998</v>
+      </c>
       <c r="BQ57" s="10">
         <f t="shared" si="17"/>
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="BR57" s="12">
         <f t="shared" si="18"/>
-        <v>-124133.33333332</v>
+        <v>-67076.190476190008</v>
       </c>
       <c r="BS57" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.54035599202092277</v>
       </c>
       <c r="BU57" s="14"/>
       <c r="BV57" s="13" t="s">
@@ -14710,15 +14906,15 @@
       <c r="BX57" s="12"/>
       <c r="BY57" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BZ57" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA57" s="11" t="e">
+        <v>-57057.142857129998</v>
+      </c>
+      <c r="CA57" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC57" s="14"/>
       <c r="CD57" s="13" t="s">
@@ -14943,18 +15139,23 @@
       <c r="BN58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP58" s="12"/>
+      <c r="BO58" s="10">
+        <v>12</v>
+      </c>
+      <c r="BP58" s="12">
+        <v>141714.28571425</v>
+      </c>
       <c r="BQ58" s="10">
         <f t="shared" si="17"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="BR58" s="12">
         <f t="shared" si="18"/>
-        <v>-61333.333333310002</v>
+        <v>80380.952380939998</v>
       </c>
       <c r="BS58" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>1.3105590062114767</v>
       </c>
       <c r="BU58" s="14"/>
       <c r="BV58" s="13" t="s">
@@ -14963,15 +15164,15 @@
       <c r="BX58" s="12"/>
       <c r="BY58" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BZ58" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA58" s="11" t="e">
+        <v>-141714.28571425</v>
+      </c>
+      <c r="CA58" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC58" s="14"/>
       <c r="CD58" s="13" t="s">
@@ -15420,18 +15621,23 @@
       <c r="BN60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP60" s="12"/>
+      <c r="BO60" s="10">
+        <v>7</v>
+      </c>
+      <c r="BP60" s="12">
+        <v>24830</v>
+      </c>
       <c r="BQ60" s="10">
         <f t="shared" si="17"/>
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="BR60" s="12">
         <f t="shared" si="18"/>
-        <v>-29130</v>
+        <v>-4300</v>
       </c>
       <c r="BS60" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.14761414349467902</v>
       </c>
       <c r="BU60" s="14"/>
       <c r="BV60" s="13" t="s">
@@ -15440,15 +15646,15 @@
       <c r="BX60" s="12"/>
       <c r="BY60" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BZ60" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA60" s="11" t="e">
+        <v>-24830</v>
+      </c>
+      <c r="CA60" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC60" s="14"/>
       <c r="CD60" s="13" t="s">
@@ -15673,18 +15879,23 @@
       <c r="BN61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP61" s="12"/>
+      <c r="BO61" s="10">
+        <v>4</v>
+      </c>
+      <c r="BP61" s="12">
+        <v>122476.19047618001</v>
+      </c>
       <c r="BQ61" s="10">
         <f t="shared" si="17"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="BR61" s="12">
         <f t="shared" si="18"/>
-        <v>-94242.857142840003</v>
+        <v>28233.333333340008</v>
       </c>
       <c r="BS61" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.29958061745250264</v>
       </c>
       <c r="BU61" s="14"/>
       <c r="BV61" s="13" t="s">
@@ -15693,15 +15904,15 @@
       <c r="BX61" s="12"/>
       <c r="BY61" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BZ61" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA61" s="11" t="e">
+        <v>-122476.19047618001</v>
+      </c>
+      <c r="CA61" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC61" s="14"/>
       <c r="CD61" s="13" t="s">
@@ -15926,18 +16137,23 @@
       <c r="BN62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP62" s="12"/>
+      <c r="BO62" s="10">
+        <v>13</v>
+      </c>
+      <c r="BP62" s="12">
+        <v>261619.04761899999</v>
+      </c>
       <c r="BQ62" s="10">
         <f t="shared" si="17"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="BR62" s="12">
         <f t="shared" si="18"/>
-        <v>-247809.52380948002</v>
+        <v>13809.523809519975</v>
       </c>
       <c r="BS62" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>5.5726364335121202E-2</v>
       </c>
       <c r="BU62" s="14"/>
       <c r="BV62" s="13" t="s">
@@ -15946,15 +16162,15 @@
       <c r="BX62" s="12"/>
       <c r="BY62" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BZ62" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA62" s="11" t="e">
+        <v>-261619.04761899999</v>
+      </c>
+      <c r="CA62" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC62" s="14"/>
       <c r="CD62" s="13" t="s">
@@ -16179,18 +16395,23 @@
       <c r="BN63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP63" s="12"/>
+      <c r="BO63" s="10">
+        <v>11</v>
+      </c>
+      <c r="BP63" s="12">
+        <v>395861.90476186998</v>
+      </c>
       <c r="BQ63" s="10">
         <f t="shared" si="17"/>
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="BR63" s="12">
         <f t="shared" si="18"/>
-        <v>-383619.04761902994</v>
+        <v>12242.857142840046</v>
       </c>
       <c r="BS63" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>3.1914101290920163E-2</v>
       </c>
       <c r="BU63" s="14"/>
       <c r="BV63" s="13" t="s">
@@ -16199,15 +16420,15 @@
       <c r="BX63" s="12"/>
       <c r="BY63" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BZ63" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA63" s="11" t="e">
+        <v>-395861.90476186998</v>
+      </c>
+      <c r="CA63" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC63" s="14"/>
       <c r="CD63" s="13" t="s">
@@ -16433,19 +16654,23 @@
         <v>1</v>
       </c>
       <c r="BN64" s="9"/>
-      <c r="BO64" s="8"/>
-      <c r="BP64" s="7"/>
+      <c r="BO64" s="8">
+        <v>206</v>
+      </c>
+      <c r="BP64" s="7">
+        <v>1147041.42857079</v>
+      </c>
       <c r="BQ64" s="27">
         <f t="shared" si="17"/>
-        <v>-214</v>
+        <v>-8</v>
       </c>
       <c r="BR64" s="28">
         <f t="shared" si="18"/>
-        <v>-1105685.2380945599</v>
+        <v>41356.190476230113</v>
       </c>
       <c r="BS64" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>3.7403222048527765E-2</v>
       </c>
       <c r="BU64" s="9" t="s">
         <v>1</v>
@@ -16455,15 +16680,15 @@
       <c r="BX64" s="7"/>
       <c r="BY64" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-206</v>
       </c>
       <c r="BZ64" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA64" s="29" t="e">
+        <v>-1147041.42857079</v>
+      </c>
+      <c r="CA64" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC64" s="9" t="s">
         <v>1</v>
@@ -16692,19 +16917,23 @@
         <v>0</v>
       </c>
       <c r="BN65" s="4"/>
-      <c r="BO65" s="3"/>
-      <c r="BP65" s="2"/>
+      <c r="BO65" s="3">
+        <v>1589</v>
+      </c>
+      <c r="BP65" s="2">
+        <v>13852647.142853051</v>
+      </c>
       <c r="BQ65" s="6">
         <f t="shared" si="17"/>
-        <v>-1780</v>
+        <v>-191</v>
       </c>
       <c r="BR65" s="5">
         <f t="shared" si="18"/>
-        <v>-14018858.571424255</v>
+        <v>-166211.42857120372</v>
       </c>
       <c r="BS65" s="30">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-1.1856274012921822E-2</v>
       </c>
       <c r="BU65" s="4" t="s">
         <v>0</v>
@@ -16714,15 +16943,15 @@
       <c r="BX65" s="2"/>
       <c r="BY65" s="6">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-1589</v>
       </c>
       <c r="BZ65" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA65" s="30" t="e">
+        <v>-13852647.142853051</v>
+      </c>
+      <c r="CA65" s="30">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCAF389-5E03-7541-AC15-037C3232BDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD86098-8F72-7A45-9A73-A32CAA44DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10400" yWindow="600" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="10400" yWindow="680" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="42">
   <si>
     <t>總計</t>
   </si>
@@ -216,6 +216,14 @@
   </si>
   <si>
     <t>05/24~05/30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/31~06/06</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1090,7 +1098,9 @@
       <c r="BM1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="BU1" s="26"/>
+      <c r="BU1" s="26" t="s">
+        <v>40</v>
+      </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
       <c r="CC1" s="26"/>
@@ -1159,6 +1169,9 @@
       <c r="BQ2" s="21"/>
       <c r="BR2" s="21"/>
       <c r="BS2" s="21"/>
+      <c r="BU2" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="BV2" s="21"/>
       <c r="BX2" s="21"/>
       <c r="BY2" s="21"/>
@@ -1621,11 +1634,13 @@
       <c r="BV5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BW5" s="15"/>
+      <c r="BW5" s="15">
+        <v>5525</v>
+      </c>
       <c r="BX5" s="33"/>
       <c r="BY5" s="10">
         <f t="shared" ref="BY5:BY36" si="20">BW5-BO5</f>
-        <v>-5351</v>
+        <v>174</v>
       </c>
       <c r="BZ5" s="12">
         <f t="shared" ref="BZ5:BZ65" si="21">BX5-BP5</f>
@@ -1646,7 +1661,7 @@
       <c r="CF5" s="33"/>
       <c r="CG5" s="10">
         <f t="shared" ref="CG5:CG65" si="23">CE5-BW5</f>
-        <v>0</v>
+        <v>-5525</v>
       </c>
       <c r="CH5" s="12">
         <f t="shared" ref="CH5:CH65" si="24">CF5-BX5</f>
@@ -1855,10 +1870,13 @@
       <c r="BN6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BO6" s="15">
+        <v>8</v>
+      </c>
       <c r="BP6" s="33"/>
       <c r="BQ6" s="10">
         <f t="shared" si="17"/>
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="BR6" s="12">
         <f t="shared" si="18"/>
@@ -1875,7 +1893,7 @@
       <c r="BX6" s="33"/>
       <c r="BY6" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ6" s="12">
         <f t="shared" si="21"/>
@@ -2130,18 +2148,23 @@
       <c r="BV7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BX7" s="12"/>
+      <c r="BW7" s="10">
+        <v>160</v>
+      </c>
+      <c r="BX7" s="12">
+        <v>192199.99999935</v>
+      </c>
       <c r="BY7" s="10">
         <f t="shared" si="20"/>
-        <v>-190</v>
+        <v>-30</v>
       </c>
       <c r="BZ7" s="12">
         <f t="shared" si="21"/>
-        <v>-236653.33333254</v>
+        <v>-44453.333333190007</v>
       </c>
       <c r="CA7" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.18784156853909667</v>
       </c>
       <c r="CC7" s="14"/>
       <c r="CD7" s="13" t="s">
@@ -2150,15 +2173,15 @@
       <c r="CF7" s="12"/>
       <c r="CG7" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="CH7" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI7" s="11" t="e">
+        <v>-192199.99999935</v>
+      </c>
+      <c r="CI7" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13" t="s">
@@ -2388,18 +2411,23 @@
       <c r="BV8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX8" s="12"/>
+      <c r="BW8" s="10">
+        <v>246</v>
+      </c>
+      <c r="BX8" s="12">
+        <v>345356.19047600986</v>
+      </c>
       <c r="BY8" s="10">
         <f t="shared" si="20"/>
-        <v>-145</v>
+        <v>101</v>
       </c>
       <c r="BZ8" s="12">
         <f t="shared" si="21"/>
-        <v>-209325.71428555003</v>
+        <v>136030.47619045983</v>
       </c>
       <c r="CA8" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.649850767999267</v>
       </c>
       <c r="CC8" s="14"/>
       <c r="CD8" s="13" t="s">
@@ -2408,15 +2436,15 @@
       <c r="CF8" s="12"/>
       <c r="CG8" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-246</v>
       </c>
       <c r="CH8" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI8" s="11" t="e">
+        <v>-345356.19047600986</v>
+      </c>
+      <c r="CI8" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13" t="s">
@@ -2646,18 +2674,23 @@
       <c r="BV9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX9" s="12"/>
+      <c r="BW9" s="10">
+        <v>54</v>
+      </c>
+      <c r="BX9" s="12">
+        <v>354723.80952379003</v>
+      </c>
       <c r="BY9" s="10">
         <f t="shared" si="20"/>
-        <v>-58</v>
+        <v>-4</v>
       </c>
       <c r="BZ9" s="12">
         <f t="shared" si="21"/>
-        <v>-372304.76190474001</v>
+        <v>-17580.952380949981</v>
       </c>
       <c r="CA9" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-4.7221937992424447E-2</v>
       </c>
       <c r="CC9" s="14"/>
       <c r="CD9" s="13" t="s">
@@ -2666,15 +2699,15 @@
       <c r="CF9" s="12"/>
       <c r="CG9" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="CH9" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI9" s="11" t="e">
+        <v>-354723.80952379003</v>
+      </c>
+      <c r="CI9" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13" t="s">
@@ -2904,18 +2937,23 @@
       <c r="BV10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX10" s="12"/>
+      <c r="BW10" s="10">
+        <v>42</v>
+      </c>
+      <c r="BX10" s="12">
+        <v>536290.47619040008</v>
+      </c>
       <c r="BY10" s="10">
         <f t="shared" si="20"/>
-        <v>-34</v>
+        <v>8</v>
       </c>
       <c r="BZ10" s="12">
         <f t="shared" si="21"/>
-        <v>-491047.61904754001</v>
+        <v>45242.85714286007</v>
       </c>
       <c r="CA10" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>9.2135376260687976E-2</v>
       </c>
       <c r="CC10" s="14"/>
       <c r="CD10" s="13" t="s">
@@ -2924,15 +2962,15 @@
       <c r="CF10" s="12"/>
       <c r="CG10" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="CH10" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI10" s="11" t="e">
+        <v>-536290.47619040008</v>
+      </c>
+      <c r="CI10" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK10" s="14"/>
       <c r="CL10" s="13" t="s">
@@ -3410,18 +3448,23 @@
       <c r="BV12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX12" s="12"/>
+      <c r="BW12" s="10">
+        <v>9</v>
+      </c>
+      <c r="BX12" s="12">
+        <v>64210</v>
+      </c>
       <c r="BY12" s="10">
         <f t="shared" si="20"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="BZ12" s="12">
         <f t="shared" si="21"/>
-        <v>-44230</v>
+        <v>19980</v>
       </c>
       <c r="CA12" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.45172959529730949</v>
       </c>
       <c r="CC12" s="14"/>
       <c r="CD12" s="13" t="s">
@@ -3430,15 +3473,15 @@
       <c r="CF12" s="12"/>
       <c r="CG12" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CH12" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI12" s="11" t="e">
+        <v>-64210</v>
+      </c>
+      <c r="CI12" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13" t="s">
@@ -3668,18 +3711,23 @@
       <c r="BV13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX13" s="12"/>
+      <c r="BW13" s="10">
+        <v>27</v>
+      </c>
+      <c r="BX13" s="12">
+        <v>1058461.9047618101</v>
+      </c>
       <c r="BY13" s="10">
         <f t="shared" si="20"/>
-        <v>-29</v>
+        <v>-2</v>
       </c>
       <c r="BZ13" s="12">
         <f t="shared" si="21"/>
-        <v>-1297114.28571422</v>
+        <v>-238652.38095240993</v>
       </c>
       <c r="CA13" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.18398716564978901</v>
       </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="13" t="s">
@@ -3688,15 +3736,15 @@
       <c r="CF13" s="12"/>
       <c r="CG13" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="CH13" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI13" s="11" t="e">
+        <v>-1058461.9047618101</v>
+      </c>
+      <c r="CI13" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13" t="s">
@@ -3926,18 +3974,23 @@
       <c r="BV14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX14" s="12"/>
+      <c r="BW14" s="10">
+        <v>42</v>
+      </c>
+      <c r="BX14" s="12">
+        <v>841809.52380944008</v>
+      </c>
       <c r="BY14" s="10">
         <f t="shared" si="20"/>
-        <v>-56</v>
+        <v>-14</v>
       </c>
       <c r="BZ14" s="12">
         <f t="shared" si="21"/>
-        <v>-1051047.6190475204</v>
+        <v>-209238.09523808036</v>
       </c>
       <c r="CA14" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.19907575208409295</v>
       </c>
       <c r="CC14" s="14"/>
       <c r="CD14" s="13" t="s">
@@ -3946,15 +3999,15 @@
       <c r="CF14" s="12"/>
       <c r="CG14" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="CH14" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI14" s="11" t="e">
+        <v>-841809.52380944008</v>
+      </c>
+      <c r="CI14" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13" t="s">
@@ -4184,18 +4237,23 @@
       <c r="BV15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX15" s="12"/>
+      <c r="BW15" s="10">
+        <v>79</v>
+      </c>
+      <c r="BX15" s="12">
+        <v>2778088.5714284801</v>
+      </c>
       <c r="BY15" s="10">
         <f t="shared" si="20"/>
-        <v>-71</v>
+        <v>8</v>
       </c>
       <c r="BZ15" s="12">
         <f t="shared" si="21"/>
-        <v>-2628476.1904761</v>
+        <v>149612.38095238013</v>
       </c>
       <c r="CA15" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>5.6919815935361627E-2</v>
       </c>
       <c r="CC15" s="14"/>
       <c r="CD15" s="13" t="s">
@@ -4204,15 +4262,15 @@
       <c r="CF15" s="12"/>
       <c r="CG15" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-79</v>
       </c>
       <c r="CH15" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI15" s="11" t="e">
+        <v>-2778088.5714284801</v>
+      </c>
+      <c r="CI15" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK15" s="14"/>
       <c r="CL15" s="13" t="s">
@@ -4443,19 +4501,23 @@
         <v>19</v>
       </c>
       <c r="BV16" s="9"/>
-      <c r="BW16" s="8"/>
-      <c r="BX16" s="7"/>
+      <c r="BW16" s="8">
+        <v>659</v>
+      </c>
+      <c r="BX16" s="7">
+        <v>6171140.4761892799</v>
+      </c>
       <c r="BY16" s="27">
         <f t="shared" si="20"/>
-        <v>-592</v>
+        <v>67</v>
       </c>
       <c r="BZ16" s="28">
         <f t="shared" si="21"/>
-        <v>-6330199.5238082111</v>
+        <v>-159059.04761893116</v>
       </c>
       <c r="CA16" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-2.5127019617739027E-2</v>
       </c>
       <c r="CC16" s="9" t="s">
         <v>19</v>
@@ -4465,15 +4527,15 @@
       <c r="CF16" s="7"/>
       <c r="CG16" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-659</v>
       </c>
       <c r="CH16" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI16" s="29" t="e">
+        <v>-6171140.4761892799</v>
+      </c>
+      <c r="CI16" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK16" s="9" t="s">
         <v>19</v>
@@ -4708,11 +4770,13 @@
       <c r="BV17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BW17" s="15"/>
+      <c r="BW17" s="15">
+        <v>3848</v>
+      </c>
       <c r="BX17" s="33"/>
       <c r="BY17" s="10">
         <f t="shared" si="20"/>
-        <v>-3865</v>
+        <v>-17</v>
       </c>
       <c r="BZ17" s="12">
         <f t="shared" si="21"/>
@@ -4732,7 +4796,7 @@
       <c r="CF17" s="33"/>
       <c r="CG17" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3848</v>
       </c>
       <c r="CH17" s="12">
         <f t="shared" si="24"/>
@@ -4939,10 +5003,13 @@
       <c r="BN18" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BO18" s="1">
+        <v>16</v>
+      </c>
       <c r="BP18" s="35"/>
       <c r="BQ18" s="10">
         <f t="shared" si="17"/>
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="BR18" s="12">
         <f t="shared" si="18"/>
@@ -4960,7 +5027,7 @@
       <c r="BX18" s="33"/>
       <c r="BY18" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BZ18" s="12">
         <f t="shared" si="21"/>
@@ -5218,18 +5285,23 @@
       <c r="BV19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BX19" s="12"/>
+      <c r="BW19" s="10">
+        <v>129</v>
+      </c>
+      <c r="BX19" s="12">
+        <v>147788.57142798993</v>
+      </c>
       <c r="BY19" s="10">
         <f t="shared" si="20"/>
-        <v>-124</v>
+        <v>5</v>
       </c>
       <c r="BZ19" s="12">
         <f t="shared" si="21"/>
-        <v>-131030.47618989997</v>
+        <v>16758.095238089954</v>
       </c>
       <c r="CA19" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.1278946373804119</v>
       </c>
       <c r="CC19" s="14"/>
       <c r="CD19" s="13" t="s">
@@ -5238,15 +5310,15 @@
       <c r="CF19" s="12"/>
       <c r="CG19" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="CH19" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI19" s="11" t="e">
+        <v>-147788.57142798993</v>
+      </c>
+      <c r="CI19" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13" t="s">
@@ -5476,18 +5548,23 @@
       <c r="BV20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX20" s="12"/>
+      <c r="BW20" s="10">
+        <v>177</v>
+      </c>
+      <c r="BX20" s="12">
+        <v>198124.76190461</v>
+      </c>
       <c r="BY20" s="10">
         <f t="shared" si="20"/>
-        <v>-124</v>
+        <v>53</v>
       </c>
       <c r="BZ20" s="12">
         <f t="shared" si="21"/>
-        <v>-129352.38095226999</v>
+        <v>68772.380952340012</v>
       </c>
       <c r="CA20" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.53166691208966987</v>
       </c>
       <c r="CC20" s="14"/>
       <c r="CD20" s="13" t="s">
@@ -5496,15 +5573,15 @@
       <c r="CF20" s="12"/>
       <c r="CG20" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-177</v>
       </c>
       <c r="CH20" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI20" s="11" t="e">
+        <v>-198124.76190461</v>
+      </c>
+      <c r="CI20" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13" t="s">
@@ -5734,18 +5811,23 @@
       <c r="BV21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX21" s="12"/>
+      <c r="BW21" s="10">
+        <v>36</v>
+      </c>
+      <c r="BX21" s="12">
+        <v>225371.42857140998</v>
+      </c>
       <c r="BY21" s="10">
         <f t="shared" si="20"/>
-        <v>-36</v>
+        <v>0</v>
       </c>
       <c r="BZ21" s="12">
         <f t="shared" si="21"/>
-        <v>-249657.14285711999</v>
+        <v>-24285.714285710012</v>
       </c>
       <c r="CA21" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-9.7276264591431474E-2</v>
       </c>
       <c r="CC21" s="14"/>
       <c r="CD21" s="13" t="s">
@@ -5754,15 +5836,15 @@
       <c r="CF21" s="12"/>
       <c r="CG21" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="CH21" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI21" s="11" t="e">
+        <v>-225371.42857140998</v>
+      </c>
+      <c r="CI21" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13" t="s">
@@ -5992,18 +6074,23 @@
       <c r="BV22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX22" s="12"/>
+      <c r="BW22" s="10">
+        <v>22</v>
+      </c>
+      <c r="BX22" s="12">
+        <v>235523.80952376002</v>
+      </c>
       <c r="BY22" s="10">
         <f t="shared" si="20"/>
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="BZ22" s="12">
         <f t="shared" si="21"/>
-        <v>-261142.85714278001</v>
+        <v>-25619.047619019984</v>
       </c>
       <c r="CA22" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-9.8103574033475305E-2</v>
       </c>
       <c r="CC22" s="14"/>
       <c r="CD22" s="13" t="s">
@@ -6012,15 +6099,15 @@
       <c r="CF22" s="12"/>
       <c r="CG22" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="CH22" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI22" s="11" t="e">
+        <v>-235523.80952376002</v>
+      </c>
+      <c r="CI22" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13" t="s">
@@ -6479,18 +6566,23 @@
       <c r="BV24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX24" s="12"/>
+      <c r="BW24" s="10">
+        <v>13</v>
+      </c>
+      <c r="BX24" s="12">
+        <v>37630</v>
+      </c>
       <c r="BY24" s="10">
         <f t="shared" si="20"/>
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="BZ24" s="12">
         <f t="shared" si="21"/>
-        <v>-73880</v>
+        <v>-36250</v>
       </c>
       <c r="CA24" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.49066053059014619</v>
       </c>
       <c r="CC24" s="14"/>
       <c r="CD24" s="13" t="s">
@@ -6499,15 +6591,15 @@
       <c r="CF24" s="12"/>
       <c r="CG24" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CH24" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI24" s="11" t="e">
+        <v>-37630</v>
+      </c>
+      <c r="CI24" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13" t="s">
@@ -6737,18 +6829,23 @@
       <c r="BV25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX25" s="12"/>
+      <c r="BW25" s="10">
+        <v>10</v>
+      </c>
+      <c r="BX25" s="12">
+        <v>399761.90476185997</v>
+      </c>
       <c r="BY25" s="10">
         <f t="shared" si="20"/>
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="BZ25" s="12">
         <f t="shared" si="21"/>
-        <v>-865076.19047613011</v>
+        <v>-465314.28571427014</v>
       </c>
       <c r="CA25" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.53788821243382667</v>
       </c>
       <c r="CC25" s="14"/>
       <c r="CD25" s="13" t="s">
@@ -6757,15 +6854,15 @@
       <c r="CF25" s="12"/>
       <c r="CG25" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CH25" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI25" s="11" t="e">
+        <v>-399761.90476185997</v>
+      </c>
+      <c r="CI25" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13" t="s">
@@ -6995,18 +7092,23 @@
       <c r="BV26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX26" s="12"/>
+      <c r="BW26" s="10">
+        <v>35</v>
+      </c>
+      <c r="BX26" s="12">
+        <v>695619.04761897004</v>
+      </c>
       <c r="BY26" s="10">
         <f t="shared" si="20"/>
-        <v>-21</v>
+        <v>14</v>
       </c>
       <c r="BZ26" s="12">
         <f t="shared" si="21"/>
-        <v>-340095.23809518002</v>
+        <v>355523.80952379003</v>
       </c>
       <c r="CA26" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.0453654438533835</v>
       </c>
       <c r="CC26" s="14"/>
       <c r="CD26" s="13" t="s">
@@ -7015,15 +7117,15 @@
       <c r="CF26" s="12"/>
       <c r="CG26" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="CH26" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI26" s="11" t="e">
+        <v>-695619.04761897004</v>
+      </c>
+      <c r="CI26" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK26" s="14"/>
       <c r="CL26" s="13" t="s">
@@ -7253,18 +7355,23 @@
       <c r="BV27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX27" s="12"/>
+      <c r="BW27" s="10">
+        <v>50</v>
+      </c>
+      <c r="BX27" s="12">
+        <v>1830476.19047613</v>
+      </c>
       <c r="BY27" s="10">
         <f t="shared" si="20"/>
-        <v>-46</v>
+        <v>4</v>
       </c>
       <c r="BZ27" s="12">
         <f t="shared" si="21"/>
-        <v>-1654666.6666665899</v>
+        <v>175809.52380954009</v>
       </c>
       <c r="CA27" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.1062507194658833</v>
       </c>
       <c r="CC27" s="14"/>
       <c r="CD27" s="13" t="s">
@@ -7273,15 +7380,15 @@
       <c r="CF27" s="12"/>
       <c r="CG27" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="CH27" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI27" s="11" t="e">
+        <v>-1830476.19047613</v>
+      </c>
+      <c r="CI27" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK27" s="14"/>
       <c r="CL27" s="13" t="s">
@@ -7512,19 +7619,23 @@
         <v>13</v>
       </c>
       <c r="BV28" s="9"/>
-      <c r="BW28" s="8"/>
-      <c r="BX28" s="7"/>
+      <c r="BW28" s="8">
+        <v>472</v>
+      </c>
+      <c r="BX28" s="7">
+        <v>3770295.7142847301</v>
+      </c>
       <c r="BY28" s="27">
         <f t="shared" si="20"/>
-        <v>-405</v>
+        <v>67</v>
       </c>
       <c r="BZ28" s="28">
         <f t="shared" si="21"/>
-        <v>-3707558.0952371098</v>
+        <v>62737.619047620334</v>
       </c>
       <c r="CA28" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.6921547130499669E-2</v>
       </c>
       <c r="CC28" s="9" t="s">
         <v>13</v>
@@ -7534,15 +7645,15 @@
       <c r="CF28" s="7"/>
       <c r="CG28" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-472</v>
       </c>
       <c r="CH28" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI28" s="29" t="e">
+        <v>-3770295.7142847301</v>
+      </c>
+      <c r="CI28" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK28" s="9" t="s">
         <v>13</v>
@@ -7777,11 +7888,13 @@
       <c r="BV29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BW29" s="15"/>
+      <c r="BW29" s="15">
+        <v>3070</v>
+      </c>
       <c r="BX29" s="33"/>
       <c r="BY29" s="10">
         <f t="shared" si="20"/>
-        <v>-3127</v>
+        <v>-57</v>
       </c>
       <c r="BZ29" s="12">
         <f t="shared" si="21"/>
@@ -7801,7 +7914,7 @@
       <c r="CF29" s="33"/>
       <c r="CG29" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3070</v>
       </c>
       <c r="CH29" s="12">
         <f t="shared" si="24"/>
@@ -8008,10 +8121,13 @@
       <c r="BN30" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BO30" s="1">
+        <v>4</v>
+      </c>
       <c r="BP30" s="35"/>
       <c r="BQ30" s="10">
         <f t="shared" si="17"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="BR30" s="12">
         <f t="shared" si="18"/>
@@ -8029,7 +8145,7 @@
       <c r="BX30" s="33"/>
       <c r="BY30" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BZ30" s="12">
         <f t="shared" si="21"/>
@@ -8287,18 +8403,23 @@
       <c r="BV31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BX31" s="12"/>
+      <c r="BW31" s="10">
+        <v>87</v>
+      </c>
+      <c r="BX31" s="12">
+        <v>81336.190475799987</v>
+      </c>
       <c r="BY31" s="10">
         <f t="shared" si="20"/>
-        <v>-71</v>
+        <v>16</v>
       </c>
       <c r="BZ31" s="12">
         <f t="shared" si="21"/>
-        <v>-83721.904761590064</v>
+        <v>-2385.7142857900762</v>
       </c>
       <c r="CA31" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-2.8495700051064703E-2</v>
       </c>
       <c r="CC31" s="14"/>
       <c r="CD31" s="13" t="s">
@@ -8307,15 +8428,15 @@
       <c r="CF31" s="12"/>
       <c r="CG31" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-87</v>
       </c>
       <c r="CH31" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI31" s="11" t="e">
+        <v>-81336.190475799987</v>
+      </c>
+      <c r="CI31" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13" t="s">
@@ -8545,18 +8666,23 @@
       <c r="BV32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX32" s="12"/>
+      <c r="BW32" s="10">
+        <v>73</v>
+      </c>
+      <c r="BX32" s="12">
+        <v>90666.666666549965</v>
+      </c>
       <c r="BY32" s="10">
         <f t="shared" si="20"/>
-        <v>-49</v>
+        <v>24</v>
       </c>
       <c r="BZ32" s="12">
         <f t="shared" si="21"/>
-        <v>-61971.428571330005</v>
+        <v>28695.23809521996</v>
       </c>
       <c r="CA32" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.46303980328920979</v>
       </c>
       <c r="CC32" s="14"/>
       <c r="CD32" s="13" t="s">
@@ -8565,15 +8691,15 @@
       <c r="CF32" s="12"/>
       <c r="CG32" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="CH32" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI32" s="11" t="e">
+        <v>-90666.666666549965</v>
+      </c>
+      <c r="CI32" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13" t="s">
@@ -8803,18 +8929,23 @@
       <c r="BV33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX33" s="12"/>
+      <c r="BW33" s="10">
+        <v>13</v>
+      </c>
+      <c r="BX33" s="12">
+        <v>81304.761904750005</v>
+      </c>
       <c r="BY33" s="10">
         <f t="shared" si="20"/>
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="BZ33" s="12">
         <f t="shared" si="21"/>
-        <v>-144114.28571426001</v>
+        <v>-62809.523809510007</v>
       </c>
       <c r="CA33" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.43583135077978635</v>
       </c>
       <c r="CC33" s="14"/>
       <c r="CD33" s="13" t="s">
@@ -8823,15 +8954,15 @@
       <c r="CF33" s="12"/>
       <c r="CG33" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CH33" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI33" s="11" t="e">
+        <v>-81304.761904750005</v>
+      </c>
+      <c r="CI33" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK33" s="14"/>
       <c r="CL33" s="13" t="s">
@@ -9061,18 +9192,23 @@
       <c r="BV34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX34" s="12"/>
+      <c r="BW34" s="10">
+        <v>15</v>
+      </c>
+      <c r="BX34" s="12">
+        <v>164147.61904758</v>
+      </c>
       <c r="BY34" s="10">
         <f t="shared" si="20"/>
-        <v>-8</v>
+        <v>7</v>
       </c>
       <c r="BZ34" s="12">
         <f t="shared" si="21"/>
-        <v>-83999.999999980006</v>
+        <v>80147.61904759999</v>
       </c>
       <c r="CA34" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.95413832199546511</v>
       </c>
       <c r="CC34" s="14"/>
       <c r="CD34" s="13" t="s">
@@ -9081,15 +9217,15 @@
       <c r="CF34" s="12"/>
       <c r="CG34" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="CH34" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI34" s="11" t="e">
+        <v>-164147.61904758</v>
+      </c>
+      <c r="CI34" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13" t="s">
@@ -9542,18 +9678,23 @@
       <c r="BV36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX36" s="12"/>
+      <c r="BW36" s="10">
+        <v>7</v>
+      </c>
+      <c r="BX36" s="12">
+        <v>32230</v>
+      </c>
       <c r="BY36" s="10">
         <f t="shared" si="20"/>
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="BZ36" s="12">
         <f t="shared" si="21"/>
-        <v>-8280</v>
+        <v>23950</v>
       </c>
       <c r="CA36" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>2.8925120772946862</v>
       </c>
       <c r="CC36" s="14"/>
       <c r="CD36" s="13" t="s">
@@ -9562,15 +9703,15 @@
       <c r="CF36" s="12"/>
       <c r="CG36" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CH36" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI36" s="11" t="e">
+        <v>-32230</v>
+      </c>
+      <c r="CI36" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13" t="s">
@@ -9800,18 +9941,23 @@
       <c r="BV37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX37" s="12"/>
+      <c r="BW37" s="10">
+        <v>5</v>
+      </c>
+      <c r="BX37" s="12">
+        <v>182375.23809522</v>
+      </c>
       <c r="BY37" s="10">
         <f t="shared" ref="BY37:BY65" si="32">BW37-BO37</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="BZ37" s="12">
         <f t="shared" si="21"/>
-        <v>-104006.66666666001</v>
+        <v>78368.571428559997</v>
       </c>
       <c r="CA37" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.7534956550403662</v>
       </c>
       <c r="CC37" s="14"/>
       <c r="CD37" s="13" t="s">
@@ -9820,15 +9966,15 @@
       <c r="CF37" s="12"/>
       <c r="CG37" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CH37" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI37" s="11" t="e">
+        <v>-182375.23809522</v>
+      </c>
+      <c r="CI37" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK37" s="14"/>
       <c r="CL37" s="13" t="s">
@@ -10058,18 +10204,23 @@
       <c r="BV38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX38" s="12"/>
+      <c r="BW38" s="10">
+        <v>10</v>
+      </c>
+      <c r="BX38" s="12">
+        <v>207619.04761901998</v>
+      </c>
       <c r="BY38" s="10">
         <f t="shared" si="32"/>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="BZ38" s="12">
         <f t="shared" si="21"/>
-        <v>-311047.61904757994</v>
+        <v>-103428.57142855995</v>
       </c>
       <c r="CA38" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.33251684017146849</v>
       </c>
       <c r="CC38" s="14"/>
       <c r="CD38" s="13" t="s">
@@ -10078,15 +10229,15 @@
       <c r="CF38" s="12"/>
       <c r="CG38" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CH38" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI38" s="11" t="e">
+        <v>-207619.04761901998</v>
+      </c>
+      <c r="CI38" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK38" s="14"/>
       <c r="CL38" s="13" t="s">
@@ -10316,18 +10467,23 @@
       <c r="BV39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX39" s="12"/>
+      <c r="BW39" s="10">
+        <v>18</v>
+      </c>
+      <c r="BX39" s="12">
+        <v>588761.90476187994</v>
+      </c>
       <c r="BY39" s="10">
         <f t="shared" si="32"/>
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="BZ39" s="12">
         <f t="shared" si="21"/>
-        <v>-529047.61904759996</v>
+        <v>59714.285714279977</v>
       </c>
       <c r="CA39" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.1128712871287061</v>
       </c>
       <c r="CC39" s="14"/>
       <c r="CD39" s="13" t="s">
@@ -10336,15 +10492,15 @@
       <c r="CF39" s="12"/>
       <c r="CG39" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CH39" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI39" s="11" t="e">
+        <v>-588761.90476187994</v>
+      </c>
+      <c r="CI39" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK39" s="14"/>
       <c r="CL39" s="13" t="s">
@@ -10575,19 +10731,23 @@
         <v>12</v>
       </c>
       <c r="BV40" s="9"/>
-      <c r="BW40" s="8"/>
-      <c r="BX40" s="7"/>
+      <c r="BW40" s="8">
+        <v>228</v>
+      </c>
+      <c r="BX40" s="7">
+        <v>1428441.4285708</v>
+      </c>
       <c r="BY40" s="27">
         <f t="shared" si="32"/>
-        <v>-185</v>
+        <v>43</v>
       </c>
       <c r="BZ40" s="28">
         <f t="shared" si="21"/>
-        <v>-1326189.5238089999</v>
+        <v>102251.90476180008</v>
       </c>
       <c r="CA40" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>7.7102030234802679E-2</v>
       </c>
       <c r="CC40" s="9" t="s">
         <v>12</v>
@@ -10597,15 +10757,15 @@
       <c r="CF40" s="7"/>
       <c r="CG40" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-228</v>
       </c>
       <c r="CH40" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI40" s="29" t="e">
+        <v>-1428441.4285708</v>
+      </c>
+      <c r="CI40" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK40" s="9" t="s">
         <v>12</v>
@@ -10840,11 +11000,13 @@
       <c r="BV41" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BW41" s="15"/>
+      <c r="BW41" s="15">
+        <v>1449</v>
+      </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
         <f t="shared" si="32"/>
-        <v>-1340</v>
+        <v>109</v>
       </c>
       <c r="BZ41" s="12">
         <f t="shared" si="21"/>
@@ -10864,7 +11026,7 @@
       <c r="CF41" s="33"/>
       <c r="CG41" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1449</v>
       </c>
       <c r="CH41" s="12">
         <f t="shared" si="24"/>
@@ -11071,10 +11233,13 @@
       <c r="BN42" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BO42" s="1">
+        <v>1</v>
+      </c>
       <c r="BP42" s="35"/>
       <c r="BQ42" s="10">
         <f t="shared" si="17"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="BR42" s="12">
         <f t="shared" si="18"/>
@@ -11092,7 +11257,7 @@
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BZ42" s="12">
         <f t="shared" si="21"/>
@@ -11350,18 +11515,23 @@
       <c r="BV43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BX43" s="12"/>
+      <c r="BW43" s="10">
+        <v>82</v>
+      </c>
+      <c r="BX43" s="12">
+        <v>77693.333332970011</v>
+      </c>
       <c r="BY43" s="10">
         <f t="shared" si="32"/>
-        <v>-87</v>
+        <v>-5</v>
       </c>
       <c r="BZ43" s="12">
         <f t="shared" si="21"/>
-        <v>-104469.52380909999</v>
+        <v>-26776.190476129981</v>
       </c>
       <c r="CA43" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.25630623649686435</v>
       </c>
       <c r="CC43" s="14"/>
       <c r="CD43" s="13" t="s">
@@ -11370,15 +11540,15 @@
       <c r="CF43" s="12"/>
       <c r="CG43" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="CH43" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI43" s="11" t="e">
+        <v>-77693.333332970011</v>
+      </c>
+      <c r="CI43" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13" t="s">
@@ -11608,18 +11778,23 @@
       <c r="BV44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX44" s="12"/>
+      <c r="BW44" s="10">
+        <v>70</v>
+      </c>
+      <c r="BX44" s="12">
+        <v>65399.999999930013</v>
+      </c>
       <c r="BY44" s="10">
         <f t="shared" si="32"/>
-        <v>-54</v>
+        <v>16</v>
       </c>
       <c r="BZ44" s="12">
         <f t="shared" si="21"/>
-        <v>-67914.285714199999</v>
+        <v>-2514.2857142699868</v>
       </c>
       <c r="CA44" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-3.7021455616138239E-2</v>
       </c>
       <c r="CC44" s="14"/>
       <c r="CD44" s="13" t="s">
@@ -11628,15 +11803,15 @@
       <c r="CF44" s="12"/>
       <c r="CG44" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="CH44" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI44" s="11" t="e">
+        <v>-65399.999999930013</v>
+      </c>
+      <c r="CI44" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13" t="s">
@@ -11866,18 +12041,23 @@
       <c r="BV45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX45" s="12"/>
+      <c r="BW45" s="10">
+        <v>9</v>
+      </c>
+      <c r="BX45" s="12">
+        <v>55628.571428559997</v>
+      </c>
       <c r="BY45" s="10">
         <f t="shared" si="32"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="BZ45" s="12">
         <f t="shared" si="21"/>
-        <v>-54199.999999990003</v>
+        <v>1428.5714285699942</v>
       </c>
       <c r="CA45" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>2.6357406431185566E-2</v>
       </c>
       <c r="CC45" s="14"/>
       <c r="CD45" s="13" t="s">
@@ -11886,15 +12066,15 @@
       <c r="CF45" s="12"/>
       <c r="CG45" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CH45" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI45" s="11" t="e">
+        <v>-55628.571428559997</v>
+      </c>
+      <c r="CI45" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13" t="s">
@@ -12124,18 +12304,23 @@
       <c r="BV46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX46" s="12"/>
+      <c r="BW46" s="10">
+        <v>13</v>
+      </c>
+      <c r="BX46" s="12">
+        <v>168285.71428568001</v>
+      </c>
       <c r="BY46" s="10">
         <f t="shared" si="32"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="BZ46" s="12">
         <f t="shared" si="21"/>
-        <v>-127428.57142853999</v>
+        <v>40857.142857140017</v>
       </c>
       <c r="CA46" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.32062780269063978</v>
       </c>
       <c r="CC46" s="14"/>
       <c r="CD46" s="13" t="s">
@@ -12144,15 +12329,15 @@
       <c r="CF46" s="12"/>
       <c r="CG46" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CH46" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI46" s="11" t="e">
+        <v>-168285.71428568001</v>
+      </c>
+      <c r="CI46" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13" t="s">
@@ -12610,18 +12795,23 @@
       <c r="BV48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX48" s="12"/>
+      <c r="BW48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX48" s="12">
+        <v>6290</v>
+      </c>
       <c r="BY48" s="10">
         <f t="shared" si="32"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="BZ48" s="12">
         <f t="shared" si="21"/>
-        <v>-9170</v>
+        <v>-2880</v>
       </c>
       <c r="CA48" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.31406761177753545</v>
       </c>
       <c r="CC48" s="14"/>
       <c r="CD48" s="13" t="s">
@@ -12630,15 +12820,15 @@
       <c r="CF48" s="12"/>
       <c r="CG48" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CH48" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI48" s="11" t="e">
+        <v>-6290</v>
+      </c>
+      <c r="CI48" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK48" s="14"/>
       <c r="CL48" s="13" t="s">
@@ -12863,18 +13053,23 @@
       <c r="BV49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX49" s="12"/>
+      <c r="BW49" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX49" s="12">
+        <v>122933.33333332</v>
+      </c>
       <c r="BY49" s="10">
         <f t="shared" si="32"/>
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="BZ49" s="12">
         <f t="shared" si="21"/>
-        <v>-145142.85714283999</v>
+        <v>-22209.523809519989</v>
       </c>
       <c r="CA49" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.15301837270340385</v>
       </c>
       <c r="CC49" s="14"/>
       <c r="CD49" s="13" t="s">
@@ -12883,15 +13078,15 @@
       <c r="CF49" s="12"/>
       <c r="CG49" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CH49" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI49" s="11" t="e">
+        <v>-122933.33333332</v>
+      </c>
+      <c r="CI49" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK49" s="14"/>
       <c r="CL49" s="13" t="s">
@@ -13121,18 +13316,23 @@
       <c r="BV50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX50" s="12"/>
+      <c r="BW50" s="10">
+        <v>13</v>
+      </c>
+      <c r="BX50" s="12">
+        <v>216857.14285710998</v>
+      </c>
       <c r="BY50" s="10">
         <f t="shared" si="32"/>
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="BZ50" s="12">
         <f t="shared" si="21"/>
-        <v>-194095.23809520999</v>
+        <v>22761.90476189999</v>
       </c>
       <c r="CA50" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.11727183513247522</v>
       </c>
       <c r="CC50" s="14"/>
       <c r="CD50" s="13" t="s">
@@ -13141,15 +13341,15 @@
       <c r="CF50" s="12"/>
       <c r="CG50" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CH50" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI50" s="11" t="e">
+        <v>-216857.14285710998</v>
+      </c>
+      <c r="CI50" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK50" s="14"/>
       <c r="CL50" s="13" t="s">
@@ -13379,18 +13579,23 @@
       <c r="BV51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX51" s="12"/>
+      <c r="BW51" s="10">
+        <v>17</v>
+      </c>
+      <c r="BX51" s="12">
+        <v>630761.90476187994</v>
+      </c>
       <c r="BY51" s="10">
         <f t="shared" si="32"/>
-        <v>-18</v>
+        <v>-1</v>
       </c>
       <c r="BZ51" s="12">
         <f t="shared" si="21"/>
-        <v>-639238.09523805999</v>
+        <v>-8476.1904761800542</v>
       </c>
       <c r="CA51" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-1.3259833134668575E-2</v>
       </c>
       <c r="CC51" s="14"/>
       <c r="CD51" s="13" t="s">
@@ -13399,15 +13604,15 @@
       <c r="CF51" s="12"/>
       <c r="CG51" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="CH51" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI51" s="11" t="e">
+        <v>-630761.90476187994</v>
+      </c>
+      <c r="CI51" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13" t="s">
@@ -13638,19 +13843,23 @@
         <v>11</v>
       </c>
       <c r="BV52" s="9"/>
-      <c r="BW52" s="8"/>
-      <c r="BX52" s="7"/>
+      <c r="BW52" s="8">
+        <v>208</v>
+      </c>
+      <c r="BX52" s="7">
+        <v>1343849.9999994501</v>
+      </c>
       <c r="BY52" s="27">
         <f t="shared" si="32"/>
-        <v>-201</v>
+        <v>7</v>
       </c>
       <c r="BZ52" s="28">
         <f t="shared" si="21"/>
-        <v>-1341658.5714279399</v>
+        <v>2191.4285715101287</v>
       </c>
       <c r="CA52" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.6333727657534885E-3</v>
       </c>
       <c r="CC52" s="9" t="s">
         <v>11</v>
@@ -13660,15 +13869,15 @@
       <c r="CF52" s="7"/>
       <c r="CG52" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-208</v>
       </c>
       <c r="CH52" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI52" s="29" t="e">
+        <v>-1343849.9999994501</v>
+      </c>
+      <c r="CI52" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK52" s="9" t="s">
         <v>11</v>
@@ -14108,6 +14317,9 @@
       <c r="BN54" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BO54" s="1">
+        <v>0</v>
+      </c>
       <c r="BP54" s="35"/>
       <c r="BQ54" s="10">
         <f t="shared" si="17"/>
@@ -14387,18 +14599,23 @@
       <c r="BV55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="BX55" s="12"/>
+      <c r="BW55" s="10">
+        <v>113</v>
+      </c>
+      <c r="BX55" s="12">
+        <v>119877.14285659992</v>
+      </c>
       <c r="BY55" s="10">
         <f t="shared" si="32"/>
-        <v>-91</v>
+        <v>22</v>
       </c>
       <c r="BZ55" s="12">
         <f t="shared" si="21"/>
-        <v>-86616.190475760042</v>
+        <v>33260.952380839881</v>
       </c>
       <c r="CA55" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.38400387038665845</v>
       </c>
       <c r="CC55" s="14"/>
       <c r="CD55" s="13" t="s">
@@ -14407,15 +14624,15 @@
       <c r="CF55" s="12"/>
       <c r="CG55" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-113</v>
       </c>
       <c r="CH55" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI55" s="11" t="e">
+        <v>-119877.14285659992</v>
+      </c>
+      <c r="CI55" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13" t="s">
@@ -14645,18 +14862,23 @@
       <c r="BV56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX56" s="12"/>
+      <c r="BW56" s="10">
+        <v>51</v>
+      </c>
+      <c r="BX56" s="12">
+        <v>67355.238095140012</v>
+      </c>
       <c r="BY56" s="10">
         <f t="shared" si="32"/>
-        <v>-59</v>
+        <v>-8</v>
       </c>
       <c r="BZ56" s="12">
         <f t="shared" si="21"/>
-        <v>-56866.666666600002</v>
+        <v>10488.57142854001</v>
       </c>
       <c r="CA56" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.18444146709060327</v>
       </c>
       <c r="CC56" s="14"/>
       <c r="CD56" s="13" t="s">
@@ -14665,15 +14887,15 @@
       <c r="CF56" s="12"/>
       <c r="CG56" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-51</v>
       </c>
       <c r="CH56" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI56" s="11" t="e">
+        <v>-67355.238095140012</v>
+      </c>
+      <c r="CI56" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13" t="s">
@@ -14903,18 +15125,23 @@
       <c r="BV57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX57" s="12"/>
+      <c r="BW57" s="10">
+        <v>12</v>
+      </c>
+      <c r="BX57" s="12">
+        <v>77028.571428569994</v>
+      </c>
       <c r="BY57" s="10">
         <f t="shared" si="32"/>
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="BZ57" s="12">
         <f t="shared" si="21"/>
-        <v>-57057.142857129998</v>
+        <v>19971.428571439996</v>
       </c>
       <c r="CA57" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.35002503755661363</v>
       </c>
       <c r="CC57" s="14"/>
       <c r="CD57" s="13" t="s">
@@ -14923,15 +15150,15 @@
       <c r="CF57" s="12"/>
       <c r="CG57" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CH57" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI57" s="11" t="e">
+        <v>-77028.571428569994</v>
+      </c>
+      <c r="CI57" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13" t="s">
@@ -15161,18 +15388,23 @@
       <c r="BV58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX58" s="12"/>
+      <c r="BW58" s="10">
+        <v>13</v>
+      </c>
+      <c r="BX58" s="12">
+        <v>155904.76190472004</v>
+      </c>
       <c r="BY58" s="10">
         <f t="shared" si="32"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="BZ58" s="12">
         <f t="shared" si="21"/>
-        <v>-141714.28571425</v>
+        <v>14190.476190470043</v>
       </c>
       <c r="CA58" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.10013440860213239</v>
       </c>
       <c r="CC58" s="14"/>
       <c r="CD58" s="13" t="s">
@@ -15181,15 +15413,15 @@
       <c r="CF58" s="12"/>
       <c r="CG58" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CH58" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI58" s="11" t="e">
+        <v>-155904.76190472004</v>
+      </c>
+      <c r="CI58" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13" t="s">
@@ -15643,18 +15875,23 @@
       <c r="BV60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX60" s="12"/>
+      <c r="BW60" s="10">
+        <v>6</v>
+      </c>
+      <c r="BX60" s="12">
+        <v>18550</v>
+      </c>
       <c r="BY60" s="10">
         <f t="shared" si="32"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="BZ60" s="12">
         <f t="shared" si="21"/>
-        <v>-24830</v>
+        <v>-6280</v>
       </c>
       <c r="CA60" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.25291985501409586</v>
       </c>
       <c r="CC60" s="14"/>
       <c r="CD60" s="13" t="s">
@@ -15663,15 +15900,15 @@
       <c r="CF60" s="12"/>
       <c r="CG60" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CH60" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI60" s="11" t="e">
+        <v>-18550</v>
+      </c>
+      <c r="CI60" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK60" s="14"/>
       <c r="CL60" s="13" t="s">
@@ -15901,18 +16138,23 @@
       <c r="BV61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX61" s="12"/>
+      <c r="BW61" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX61" s="12">
+        <v>126861.90476189001</v>
+      </c>
       <c r="BY61" s="10">
         <f t="shared" si="32"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="BZ61" s="12">
         <f t="shared" si="21"/>
-        <v>-122476.19047618001</v>
+        <v>4385.7142857099971</v>
       </c>
       <c r="CA61" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>3.580870917570677E-2</v>
       </c>
       <c r="CC61" s="14"/>
       <c r="CD61" s="13" t="s">
@@ -15921,15 +16163,15 @@
       <c r="CF61" s="12"/>
       <c r="CG61" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CH61" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI61" s="11" t="e">
+        <v>-126861.90476189001</v>
+      </c>
+      <c r="CI61" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK61" s="14"/>
       <c r="CL61" s="13" t="s">
@@ -16159,18 +16401,23 @@
       <c r="BV62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX62" s="12"/>
+      <c r="BW62" s="10">
+        <v>11</v>
+      </c>
+      <c r="BX62" s="12">
+        <v>208952.38095234003</v>
+      </c>
       <c r="BY62" s="10">
         <f t="shared" si="32"/>
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="BZ62" s="12">
         <f t="shared" si="21"/>
-        <v>-261619.04761899999</v>
+        <v>-52666.666666659963</v>
       </c>
       <c r="CA62" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.20131052056790327</v>
       </c>
       <c r="CC62" s="14"/>
       <c r="CD62" s="13" t="s">
@@ -16179,15 +16426,15 @@
       <c r="CF62" s="12"/>
       <c r="CG62" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CH62" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI62" s="11" t="e">
+        <v>-208952.38095234003</v>
+      </c>
+      <c r="CI62" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK62" s="14"/>
       <c r="CL62" s="13" t="s">
@@ -16417,18 +16664,23 @@
       <c r="BV63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX63" s="12"/>
+      <c r="BW63" s="10">
+        <v>11</v>
+      </c>
+      <c r="BX63" s="12">
+        <v>348476.19047617994</v>
+      </c>
       <c r="BY63" s="10">
         <f t="shared" si="32"/>
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="BZ63" s="12">
         <f t="shared" si="21"/>
-        <v>-395861.90476186998</v>
+        <v>-47385.714285690046</v>
       </c>
       <c r="CA63" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.11970263800502561</v>
       </c>
       <c r="CC63" s="14"/>
       <c r="CD63" s="13" t="s">
@@ -16437,15 +16689,15 @@
       <c r="CF63" s="12"/>
       <c r="CG63" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CH63" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI63" s="11" t="e">
+        <v>-348476.19047617994</v>
+      </c>
+      <c r="CI63" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK63" s="14"/>
       <c r="CL63" s="13" t="s">
@@ -16676,19 +16928,23 @@
         <v>1</v>
       </c>
       <c r="BV64" s="9"/>
-      <c r="BW64" s="8"/>
-      <c r="BX64" s="7"/>
+      <c r="BW64" s="8">
+        <v>220</v>
+      </c>
+      <c r="BX64" s="7">
+        <v>1123006.1904754401</v>
+      </c>
       <c r="BY64" s="27">
         <f t="shared" si="32"/>
-        <v>-206</v>
+        <v>14</v>
       </c>
       <c r="BZ64" s="28">
         <f t="shared" si="21"/>
-        <v>-1147041.42857079</v>
+        <v>-24035.238095349865</v>
       </c>
       <c r="CA64" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-2.0954115079607628E-2</v>
       </c>
       <c r="CC64" s="9" t="s">
         <v>1</v>
@@ -16698,15 +16954,15 @@
       <c r="CF64" s="7"/>
       <c r="CG64" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="CH64" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI64" s="29" t="e">
+        <v>-1123006.1904754401</v>
+      </c>
+      <c r="CI64" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK64" s="9" t="s">
         <v>1</v>
@@ -16939,19 +17195,23 @@
         <v>0</v>
       </c>
       <c r="BV65" s="4"/>
-      <c r="BW65" s="3"/>
-      <c r="BX65" s="2"/>
+      <c r="BW65" s="3">
+        <v>1787</v>
+      </c>
+      <c r="BX65" s="2">
+        <v>13836733.809519703</v>
+      </c>
       <c r="BY65" s="6">
         <f t="shared" si="32"/>
-        <v>-1589</v>
+        <v>198</v>
       </c>
       <c r="BZ65" s="5">
         <f t="shared" si="21"/>
-        <v>-13852647.142853051</v>
+        <v>-15913.333333348855</v>
       </c>
       <c r="CA65" s="30">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-1.1487575745808964E-3</v>
       </c>
       <c r="CC65" s="4" t="s">
         <v>0</v>
@@ -16961,15 +17221,15 @@
       <c r="CF65" s="2"/>
       <c r="CG65" s="6">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1787</v>
       </c>
       <c r="CH65" s="5">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI65" s="30" t="e">
+        <v>-13836733.809519703</v>
+      </c>
+      <c r="CI65" s="30">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD86098-8F72-7A45-9A73-A32CAA44DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734466CF-CC75-344D-B422-FA09D5080FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10400" yWindow="680" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="17300" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -1890,10 +1890,13 @@
       <c r="BV6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="BW6" s="15">
+        <v>14</v>
+      </c>
       <c r="BX6" s="33"/>
       <c r="BY6" s="10">
         <f t="shared" si="20"/>
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="BZ6" s="12">
         <f t="shared" si="21"/>
@@ -1910,7 +1913,7 @@
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -5023,11 +5026,13 @@
       <c r="BV18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="BW18" s="15"/>
+      <c r="BW18" s="15">
+        <v>16</v>
+      </c>
       <c r="BX18" s="33"/>
       <c r="BY18" s="10">
         <f t="shared" si="20"/>
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="BZ18" s="12">
         <f t="shared" si="21"/>
@@ -5045,7 +5050,7 @@
       <c r="CF18" s="33"/>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
@@ -8141,11 +8146,13 @@
       <c r="BV30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="BW30" s="15"/>
+      <c r="BW30" s="15">
+        <v>4</v>
+      </c>
       <c r="BX30" s="33"/>
       <c r="BY30" s="10">
         <f t="shared" si="20"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BZ30" s="12">
         <f t="shared" si="21"/>
@@ -8163,7 +8170,7 @@
       <c r="CF30" s="33"/>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
@@ -11253,11 +11260,13 @@
       <c r="BV42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="BW42" s="15"/>
+      <c r="BW42" s="15">
+        <v>4</v>
+      </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BZ42" s="12">
         <f t="shared" si="21"/>
@@ -11275,7 +11284,7 @@
       <c r="CF42" s="33"/>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
@@ -14337,7 +14346,9 @@
       <c r="BV54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="BW54" s="15"/>
+      <c r="BW54" s="15">
+        <v>0</v>
+      </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
         <f t="shared" si="32"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734466CF-CC75-344D-B422-FA09D5080FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9ECBCAE-5B4A-B74A-A511-5953E846577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17300" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q3" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="44">
   <si>
     <t>總計</t>
   </si>
@@ -224,6 +224,14 @@
   </si>
   <si>
     <t>05/31~06/06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06/07~06/13</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -425,7 +433,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -577,6 +585,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1103,7 +1117,9 @@
       </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
-      <c r="CC1" s="26"/>
+      <c r="CC1" s="26" t="s">
+        <v>42</v>
+      </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
       <c r="CK1" s="26"/>
@@ -1177,6 +1193,9 @@
       <c r="BY2" s="21"/>
       <c r="BZ2" s="21"/>
       <c r="CA2" s="21"/>
+      <c r="CC2" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="CD2" s="21"/>
       <c r="CF2" s="21"/>
       <c r="CG2" s="21"/>
@@ -1657,11 +1676,13 @@
       <c r="CD5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CE5" s="15"/>
+      <c r="CE5" s="15">
+        <v>5735</v>
+      </c>
       <c r="CF5" s="33"/>
       <c r="CG5" s="10">
         <f t="shared" ref="CG5:CG65" si="23">CE5-BW5</f>
-        <v>-5525</v>
+        <v>210</v>
       </c>
       <c r="CH5" s="12">
         <f t="shared" ref="CH5:CH65" si="24">CF5-BX5</f>
@@ -1682,7 +1703,7 @@
       <c r="CN5" s="33"/>
       <c r="CO5" s="10">
         <f t="shared" ref="CO5:CO65" si="26">CM5-CE5</f>
-        <v>0</v>
+        <v>-5735</v>
       </c>
       <c r="CP5" s="12">
         <f t="shared" ref="CP5:CP65" si="27">CN5-CF5</f>
@@ -2173,18 +2194,23 @@
       <c r="CD7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CF7" s="12"/>
+      <c r="CE7" s="10">
+        <v>188</v>
+      </c>
+      <c r="CF7" s="12">
+        <v>238791.42857063009</v>
+      </c>
       <c r="CG7" s="10">
         <f t="shared" si="23"/>
-        <v>-160</v>
+        <v>28</v>
       </c>
       <c r="CH7" s="12">
         <f t="shared" si="24"/>
-        <v>-192199.99999935</v>
+        <v>46591.428571280092</v>
       </c>
       <c r="CI7" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.24241117883162155</v>
       </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13" t="s">
@@ -2193,15 +2219,15 @@
       <c r="CN7" s="12"/>
       <c r="CO7" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-188</v>
       </c>
       <c r="CP7" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ7" s="11" t="e">
+        <v>-238791.42857063009</v>
+      </c>
+      <c r="CQ7" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13" t="s">
@@ -2436,18 +2462,23 @@
       <c r="CD8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF8" s="12"/>
+      <c r="CE8" s="10">
+        <v>248</v>
+      </c>
+      <c r="CF8" s="12">
+        <v>401064.76190457988</v>
+      </c>
       <c r="CG8" s="10">
         <f t="shared" si="23"/>
-        <v>-246</v>
+        <v>2</v>
       </c>
       <c r="CH8" s="12">
         <f t="shared" si="24"/>
-        <v>-345356.19047600986</v>
+        <v>55708.571428570023</v>
       </c>
       <c r="CI8" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.16130758030364542</v>
       </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13" t="s">
@@ -2456,15 +2487,15 @@
       <c r="CN8" s="12"/>
       <c r="CO8" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-248</v>
       </c>
       <c r="CP8" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ8" s="11" t="e">
+        <v>-401064.76190457988</v>
+      </c>
+      <c r="CQ8" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13" t="s">
@@ -2699,18 +2730,23 @@
       <c r="CD9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF9" s="12"/>
+      <c r="CE9" s="10">
+        <v>75</v>
+      </c>
+      <c r="CF9" s="12">
+        <v>487572.38095234998</v>
+      </c>
       <c r="CG9" s="10">
         <f t="shared" si="23"/>
-        <v>-54</v>
+        <v>21</v>
       </c>
       <c r="CH9" s="12">
         <f t="shared" si="24"/>
-        <v>-354723.80952379003</v>
+        <v>132848.57142855995</v>
       </c>
       <c r="CI9" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.37451269935025405</v>
       </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13" t="s">
@@ -2719,15 +2755,15 @@
       <c r="CN9" s="12"/>
       <c r="CO9" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="CP9" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ9" s="11" t="e">
+        <v>-487572.38095234998</v>
+      </c>
+      <c r="CQ9" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13" t="s">
@@ -2962,18 +2998,23 @@
       <c r="CD10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF10" s="12"/>
+      <c r="CE10" s="10">
+        <v>45</v>
+      </c>
+      <c r="CF10" s="12">
+        <v>569999.99999992002</v>
+      </c>
       <c r="CG10" s="10">
         <f t="shared" si="23"/>
-        <v>-42</v>
+        <v>3</v>
       </c>
       <c r="CH10" s="12">
         <f t="shared" si="24"/>
-        <v>-536290.47619040008</v>
+        <v>33709.523809519946</v>
       </c>
       <c r="CI10" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>6.285683842267599E-2</v>
       </c>
       <c r="CK10" s="14"/>
       <c r="CL10" s="13" t="s">
@@ -2982,15 +3023,15 @@
       <c r="CN10" s="12"/>
       <c r="CO10" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="CP10" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ10" s="11" t="e">
+        <v>-569999.99999992002</v>
+      </c>
+      <c r="CQ10" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS10" s="14"/>
       <c r="CT10" s="13" t="s">
@@ -3473,18 +3514,23 @@
       <c r="CD12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF12" s="12"/>
+      <c r="CE12" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF12" s="12">
+        <v>84420</v>
+      </c>
       <c r="CG12" s="10">
         <f t="shared" si="23"/>
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="CH12" s="12">
         <f t="shared" si="24"/>
-        <v>-64210</v>
+        <v>20210</v>
       </c>
       <c r="CI12" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.31474848154493068</v>
       </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13" t="s">
@@ -3493,15 +3539,15 @@
       <c r="CN12" s="12"/>
       <c r="CO12" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="CP12" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ12" s="11" t="e">
+        <v>-84420</v>
+      </c>
+      <c r="CQ12" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13" t="s">
@@ -3736,18 +3782,23 @@
       <c r="CD13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF13" s="12"/>
+      <c r="CE13" s="10">
+        <v>33</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>1255690.47619037</v>
+      </c>
       <c r="CG13" s="10">
         <f t="shared" si="23"/>
-        <v>-27</v>
+        <v>6</v>
       </c>
       <c r="CH13" s="12">
         <f t="shared" si="24"/>
-        <v>-1058461.9047618101</v>
+        <v>197228.57142855995</v>
       </c>
       <c r="CI13" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.18633506840564384</v>
       </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13" t="s">
@@ -3756,15 +3807,15 @@
       <c r="CN13" s="12"/>
       <c r="CO13" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="CP13" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ13" s="11" t="e">
+        <v>-1255690.47619037</v>
+      </c>
+      <c r="CQ13" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13" t="s">
@@ -3999,18 +4050,23 @@
       <c r="CD14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF14" s="12"/>
+      <c r="CE14" s="10">
+        <v>66</v>
+      </c>
+      <c r="CF14" s="12">
+        <v>1463238.0952379603</v>
+      </c>
       <c r="CG14" s="10">
         <f t="shared" si="23"/>
-        <v>-42</v>
+        <v>24</v>
       </c>
       <c r="CH14" s="12">
         <f t="shared" si="24"/>
-        <v>-841809.52380944008</v>
+        <v>621428.57142852026</v>
       </c>
       <c r="CI14" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.73820567937550763</v>
       </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13" t="s">
@@ -4019,15 +4075,15 @@
       <c r="CN14" s="12"/>
       <c r="CO14" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="CP14" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ14" s="11" t="e">
+        <v>-1463238.0952379603</v>
+      </c>
+      <c r="CQ14" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13" t="s">
@@ -4262,18 +4318,23 @@
       <c r="CD15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF15" s="12"/>
+      <c r="CE15" s="10">
+        <v>91</v>
+      </c>
+      <c r="CF15" s="12">
+        <v>3423385.7142856503</v>
+      </c>
       <c r="CG15" s="10">
         <f t="shared" si="23"/>
-        <v>-79</v>
+        <v>12</v>
       </c>
       <c r="CH15" s="12">
         <f t="shared" si="24"/>
-        <v>-2778088.5714284801</v>
+        <v>645297.1428571702</v>
       </c>
       <c r="CI15" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.23228098250494636</v>
       </c>
       <c r="CK15" s="14"/>
       <c r="CL15" s="13" t="s">
@@ -4282,15 +4343,15 @@
       <c r="CN15" s="12"/>
       <c r="CO15" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="CP15" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ15" s="11" t="e">
+        <v>-3423385.7142856503</v>
+      </c>
+      <c r="CQ15" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS15" s="14"/>
       <c r="CT15" s="13" t="s">
@@ -4526,19 +4587,23 @@
         <v>19</v>
       </c>
       <c r="CD16" s="9"/>
-      <c r="CE16" s="8"/>
-      <c r="CF16" s="7"/>
+      <c r="CE16" s="8">
+        <v>765</v>
+      </c>
+      <c r="CF16" s="7">
+        <v>7924162.8571414603</v>
+      </c>
       <c r="CG16" s="27">
         <f t="shared" si="23"/>
-        <v>-659</v>
+        <v>106</v>
       </c>
       <c r="CH16" s="28">
         <f t="shared" si="24"/>
-        <v>-6171140.4761892799</v>
+        <v>1753022.3809521804</v>
       </c>
       <c r="CI16" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.28406781335087727</v>
       </c>
       <c r="CK16" s="9" t="s">
         <v>19</v>
@@ -4548,15 +4613,15 @@
       <c r="CN16" s="7"/>
       <c r="CO16" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-765</v>
       </c>
       <c r="CP16" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ16" s="29" t="e">
+        <v>-7924162.8571414603</v>
+      </c>
+      <c r="CQ16" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS16" s="9" t="s">
         <v>19</v>
@@ -4795,11 +4860,13 @@
       <c r="CD17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CE17" s="15"/>
+      <c r="CE17" s="15">
+        <v>2719</v>
+      </c>
       <c r="CF17" s="33"/>
       <c r="CG17" s="10">
         <f t="shared" si="23"/>
-        <v>-3848</v>
+        <v>-1129</v>
       </c>
       <c r="CH17" s="12">
         <f t="shared" si="24"/>
@@ -4819,7 +4886,7 @@
       <c r="CN17" s="33"/>
       <c r="CO17" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2719</v>
       </c>
       <c r="CP17" s="12">
         <f t="shared" si="27"/>
@@ -5312,18 +5379,23 @@
       <c r="CD19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CF19" s="12"/>
+      <c r="CE19" s="10">
+        <v>121</v>
+      </c>
+      <c r="CF19" s="12">
+        <v>135971.42857091996</v>
+      </c>
       <c r="CG19" s="10">
         <f t="shared" si="23"/>
-        <v>-129</v>
+        <v>-8</v>
       </c>
       <c r="CH19" s="12">
         <f t="shared" si="24"/>
-        <v>-147788.57142798993</v>
+        <v>-11817.142857069965</v>
       </c>
       <c r="CI19" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-7.9959788114115943E-2</v>
       </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13" t="s">
@@ -5332,15 +5404,15 @@
       <c r="CN19" s="12"/>
       <c r="CO19" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-121</v>
       </c>
       <c r="CP19" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ19" s="11" t="e">
+        <v>-135971.42857091996</v>
+      </c>
+      <c r="CQ19" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13" t="s">
@@ -5575,18 +5647,23 @@
       <c r="CD20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF20" s="12"/>
+      <c r="CE20" s="10">
+        <v>205</v>
+      </c>
+      <c r="CF20" s="12">
+        <v>239438.09523798001</v>
+      </c>
       <c r="CG20" s="10">
         <f t="shared" si="23"/>
-        <v>-177</v>
+        <v>28</v>
       </c>
       <c r="CH20" s="12">
         <f t="shared" si="24"/>
-        <v>-198124.76190461</v>
+        <v>41313.333333370014</v>
       </c>
       <c r="CI20" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.20852180684644006</v>
       </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13" t="s">
@@ -5595,15 +5672,15 @@
       <c r="CN20" s="12"/>
       <c r="CO20" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-205</v>
       </c>
       <c r="CP20" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ20" s="11" t="e">
+        <v>-239438.09523798001</v>
+      </c>
+      <c r="CQ20" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13" t="s">
@@ -5838,18 +5915,23 @@
       <c r="CD21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF21" s="12"/>
+      <c r="CE21" s="10">
+        <v>28</v>
+      </c>
+      <c r="CF21" s="12">
+        <v>172114.28571427002</v>
+      </c>
       <c r="CG21" s="10">
         <f t="shared" si="23"/>
-        <v>-36</v>
+        <v>-8</v>
       </c>
       <c r="CH21" s="12">
         <f t="shared" si="24"/>
-        <v>-225371.42857140998</v>
+        <v>-53257.142857139959</v>
       </c>
       <c r="CI21" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.23630831643002692</v>
       </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13" t="s">
@@ -5858,15 +5940,15 @@
       <c r="CN21" s="12"/>
       <c r="CO21" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="CP21" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ21" s="11" t="e">
+        <v>-172114.28571427002</v>
+      </c>
+      <c r="CQ21" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13" t="s">
@@ -6101,18 +6183,23 @@
       <c r="CD22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF22" s="12"/>
+      <c r="CE22" s="10">
+        <v>20</v>
+      </c>
+      <c r="CF22" s="12">
+        <v>240476.19047615997</v>
+      </c>
       <c r="CG22" s="10">
         <f t="shared" si="23"/>
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="CH22" s="12">
         <f t="shared" si="24"/>
-        <v>-235523.80952376002</v>
+        <v>4952.3809523999516</v>
       </c>
       <c r="CI22" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>2.1027092600165963E-2</v>
       </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13" t="s">
@@ -6121,15 +6208,15 @@
       <c r="CN22" s="12"/>
       <c r="CO22" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CP22" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ22" s="11" t="e">
+        <v>-240476.19047615997</v>
+      </c>
+      <c r="CQ22" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13" t="s">
@@ -6593,18 +6680,23 @@
       <c r="CD24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF24" s="12"/>
+      <c r="CE24" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF24" s="12">
+        <v>65780</v>
+      </c>
       <c r="CG24" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="CH24" s="12">
         <f t="shared" si="24"/>
-        <v>-37630</v>
+        <v>28150</v>
       </c>
       <c r="CI24" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.74807334573478612</v>
       </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13" t="s">
@@ -6613,15 +6705,15 @@
       <c r="CN24" s="12"/>
       <c r="CO24" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CP24" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ24" s="11" t="e">
+        <v>-65780</v>
+      </c>
+      <c r="CQ24" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13" t="s">
@@ -6856,18 +6948,23 @@
       <c r="CD25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF25" s="12"/>
+      <c r="CE25" s="10">
+        <v>14</v>
+      </c>
+      <c r="CF25" s="12">
+        <v>481090.47619045002</v>
+      </c>
       <c r="CG25" s="10">
         <f t="shared" si="23"/>
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="CH25" s="12">
         <f t="shared" si="24"/>
-        <v>-399761.90476185997</v>
+        <v>81328.571428590047</v>
       </c>
       <c r="CI25" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.2034425253127555</v>
       </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13" t="s">
@@ -6876,15 +6973,15 @@
       <c r="CN25" s="12"/>
       <c r="CO25" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CP25" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ25" s="11" t="e">
+        <v>-481090.47619045002</v>
+      </c>
+      <c r="CQ25" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13" t="s">
@@ -7119,18 +7216,23 @@
       <c r="CD26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF26" s="12"/>
+      <c r="CE26" s="10">
+        <v>30</v>
+      </c>
+      <c r="CF26" s="12">
+        <v>642285.71428565006</v>
+      </c>
       <c r="CG26" s="10">
         <f t="shared" si="23"/>
-        <v>-35</v>
+        <v>-5</v>
       </c>
       <c r="CH26" s="12">
         <f t="shared" si="24"/>
-        <v>-695619.04761897004</v>
+        <v>-53333.333333319984</v>
       </c>
       <c r="CI26" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-7.6670317634162419E-2</v>
       </c>
       <c r="CK26" s="14"/>
       <c r="CL26" s="13" t="s">
@@ -7139,15 +7241,15 @@
       <c r="CN26" s="12"/>
       <c r="CO26" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="CP26" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ26" s="11" t="e">
+        <v>-642285.71428565006</v>
+      </c>
+      <c r="CQ26" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS26" s="14"/>
       <c r="CT26" s="13" t="s">
@@ -7382,18 +7484,23 @@
       <c r="CD27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF27" s="12"/>
+      <c r="CE27" s="10">
+        <v>39</v>
+      </c>
+      <c r="CF27" s="12">
+        <v>1315333.3333332802</v>
+      </c>
       <c r="CG27" s="10">
         <f t="shared" si="23"/>
-        <v>-50</v>
+        <v>-11</v>
       </c>
       <c r="CH27" s="12">
         <f t="shared" si="24"/>
-        <v>-1830476.19047613</v>
+        <v>-515142.85714284983</v>
       </c>
       <c r="CI27" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.28142559833507291</v>
       </c>
       <c r="CK27" s="14"/>
       <c r="CL27" s="13" t="s">
@@ -7402,15 +7509,15 @@
       <c r="CN27" s="12"/>
       <c r="CO27" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="CP27" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ27" s="11" t="e">
+        <v>-1315333.3333332802</v>
+      </c>
+      <c r="CQ27" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS27" s="14"/>
       <c r="CT27" s="13" t="s">
@@ -7646,19 +7753,23 @@
         <v>13</v>
       </c>
       <c r="CD28" s="9"/>
-      <c r="CE28" s="8"/>
-      <c r="CF28" s="7"/>
+      <c r="CE28" s="8">
+        <v>475</v>
+      </c>
+      <c r="CF28" s="7">
+        <v>3292489.5238087103</v>
+      </c>
       <c r="CG28" s="27">
         <f t="shared" si="23"/>
-        <v>-472</v>
+        <v>3</v>
       </c>
       <c r="CH28" s="28">
         <f t="shared" si="24"/>
-        <v>-3770295.7142847301</v>
+        <v>-477806.19047601987</v>
       </c>
       <c r="CI28" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.12672910208759722</v>
       </c>
       <c r="CK28" s="9" t="s">
         <v>13</v>
@@ -7668,15 +7779,15 @@
       <c r="CN28" s="7"/>
       <c r="CO28" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-475</v>
       </c>
       <c r="CP28" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ28" s="29" t="e">
+        <v>-3292489.5238087103</v>
+      </c>
+      <c r="CQ28" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS28" s="9" t="s">
         <v>13</v>
@@ -7915,11 +8026,13 @@
       <c r="CD29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CE29" s="15"/>
+      <c r="CE29" s="15">
+        <v>2988</v>
+      </c>
       <c r="CF29" s="33"/>
       <c r="CG29" s="10">
         <f t="shared" si="23"/>
-        <v>-3070</v>
+        <v>-82</v>
       </c>
       <c r="CH29" s="12">
         <f t="shared" si="24"/>
@@ -7939,7 +8052,7 @@
       <c r="CN29" s="33"/>
       <c r="CO29" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2988</v>
       </c>
       <c r="CP29" s="12">
         <f t="shared" si="27"/>
@@ -8432,18 +8545,23 @@
       <c r="CD31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CF31" s="12"/>
+      <c r="CE31" s="10">
+        <v>61</v>
+      </c>
+      <c r="CF31" s="12">
+        <v>53934.285714040001</v>
+      </c>
       <c r="CG31" s="10">
         <f t="shared" si="23"/>
-        <v>-87</v>
+        <v>-26</v>
       </c>
       <c r="CH31" s="12">
         <f t="shared" si="24"/>
-        <v>-81336.190475799987</v>
+        <v>-27401.904761759986</v>
       </c>
       <c r="CI31" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.33689683032195727</v>
       </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13" t="s">
@@ -8452,15 +8570,15 @@
       <c r="CN31" s="12"/>
       <c r="CO31" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="CP31" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ31" s="11" t="e">
+        <v>-53934.285714040001</v>
+      </c>
+      <c r="CQ31" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13" t="s">
@@ -8695,18 +8813,23 @@
       <c r="CD32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF32" s="12"/>
+      <c r="CE32" s="10">
+        <v>72</v>
+      </c>
+      <c r="CF32" s="12">
+        <v>63057.142857050007</v>
+      </c>
       <c r="CG32" s="10">
         <f t="shared" si="23"/>
-        <v>-73</v>
+        <v>-1</v>
       </c>
       <c r="CH32" s="12">
         <f t="shared" si="24"/>
-        <v>-90666.666666549965</v>
+        <v>-27609.523809499959</v>
       </c>
       <c r="CI32" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.30451680672281795</v>
       </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13" t="s">
@@ -8715,15 +8838,15 @@
       <c r="CN32" s="12"/>
       <c r="CO32" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="CP32" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ32" s="11" t="e">
+        <v>-63057.142857050007</v>
+      </c>
+      <c r="CQ32" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13" t="s">
@@ -8958,18 +9081,23 @@
       <c r="CD33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF33" s="12"/>
+      <c r="CE33" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF33" s="12">
+        <v>130962.85714283999</v>
+      </c>
       <c r="CG33" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>6</v>
       </c>
       <c r="CH33" s="12">
         <f t="shared" si="24"/>
-        <v>-81304.761904750005</v>
+        <v>49658.095238089983</v>
       </c>
       <c r="CI33" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.61076490570460484</v>
       </c>
       <c r="CK33" s="14"/>
       <c r="CL33" s="13" t="s">
@@ -8978,15 +9106,15 @@
       <c r="CN33" s="12"/>
       <c r="CO33" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="CP33" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ33" s="11" t="e">
+        <v>-130962.85714283999</v>
+      </c>
+      <c r="CQ33" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13" t="s">
@@ -9221,18 +9349,23 @@
       <c r="CD34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF34" s="12"/>
+      <c r="CE34" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF34" s="12">
+        <v>204476.19047614001</v>
+      </c>
       <c r="CG34" s="10">
         <f t="shared" si="23"/>
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="CH34" s="12">
         <f t="shared" si="24"/>
-        <v>-164147.61904758</v>
+        <v>40328.571428560012</v>
       </c>
       <c r="CI34" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.24568477850946063</v>
       </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13" t="s">
@@ -9241,15 +9374,15 @@
       <c r="CN34" s="12"/>
       <c r="CO34" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CP34" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ34" s="11" t="e">
+        <v>-204476.19047614001</v>
+      </c>
+      <c r="CQ34" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13" t="s">
@@ -9707,18 +9840,23 @@
       <c r="CD36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF36" s="12"/>
+      <c r="CE36" s="10">
+        <v>3</v>
+      </c>
+      <c r="CF36" s="12">
+        <v>9670</v>
+      </c>
       <c r="CG36" s="10">
         <f t="shared" si="23"/>
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="CH36" s="12">
         <f t="shared" si="24"/>
-        <v>-32230</v>
+        <v>-22560</v>
       </c>
       <c r="CI36" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.69996897300651562</v>
       </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13" t="s">
@@ -9727,15 +9865,15 @@
       <c r="CN36" s="12"/>
       <c r="CO36" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CP36" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ36" s="11" t="e">
+        <v>-9670</v>
+      </c>
+      <c r="CQ36" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13" t="s">
@@ -9970,18 +10108,23 @@
       <c r="CD37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF37" s="12"/>
+      <c r="CE37" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF37" s="12">
+        <v>62666.666666660007</v>
+      </c>
       <c r="CG37" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="CH37" s="12">
         <f t="shared" si="24"/>
-        <v>-182375.23809522</v>
+        <v>-119708.57142856</v>
       </c>
       <c r="CI37" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.6563861008700036</v>
       </c>
       <c r="CK37" s="14"/>
       <c r="CL37" s="13" t="s">
@@ -9990,15 +10133,15 @@
       <c r="CN37" s="12"/>
       <c r="CO37" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP37" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ37" s="11" t="e">
+        <v>-62666.666666660007</v>
+      </c>
+      <c r="CQ37" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS37" s="14"/>
       <c r="CT37" s="13" t="s">
@@ -10233,18 +10376,23 @@
       <c r="CD38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF38" s="12"/>
+      <c r="CE38" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF38" s="12">
+        <v>141333.33333329999</v>
+      </c>
       <c r="CG38" s="10">
         <f t="shared" si="23"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="CH38" s="12">
         <f t="shared" si="24"/>
-        <v>-207619.04761901998</v>
+        <v>-66285.714285719994</v>
       </c>
       <c r="CI38" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.31926605504594158</v>
       </c>
       <c r="CK38" s="14"/>
       <c r="CL38" s="13" t="s">
@@ -10253,15 +10401,15 @@
       <c r="CN38" s="12"/>
       <c r="CO38" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CP38" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ38" s="11" t="e">
+        <v>-141333.33333329999</v>
+      </c>
+      <c r="CQ38" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS38" s="14"/>
       <c r="CT38" s="13" t="s">
@@ -10496,18 +10644,23 @@
       <c r="CD39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF39" s="12"/>
+      <c r="CE39" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF39" s="12">
+        <v>312476.19047616998</v>
+      </c>
       <c r="CG39" s="10">
         <f t="shared" si="23"/>
-        <v>-18</v>
+        <v>-9</v>
       </c>
       <c r="CH39" s="12">
         <f t="shared" si="24"/>
-        <v>-588761.90476187994</v>
+        <v>-276285.71428570995</v>
       </c>
       <c r="CI39" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.46926560983501731</v>
       </c>
       <c r="CK39" s="14"/>
       <c r="CL39" s="13" t="s">
@@ -10516,15 +10669,15 @@
       <c r="CN39" s="12"/>
       <c r="CO39" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CP39" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ39" s="11" t="e">
+        <v>-312476.19047616998</v>
+      </c>
+      <c r="CQ39" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS39" s="14"/>
       <c r="CT39" s="13" t="s">
@@ -10760,19 +10913,23 @@
         <v>12</v>
       </c>
       <c r="CD40" s="9"/>
-      <c r="CE40" s="8"/>
-      <c r="CF40" s="7"/>
+      <c r="CE40" s="8">
+        <v>193</v>
+      </c>
+      <c r="CF40" s="7">
+        <v>978576.66666619992</v>
+      </c>
       <c r="CG40" s="27">
         <f t="shared" si="23"/>
-        <v>-228</v>
+        <v>-35</v>
       </c>
       <c r="CH40" s="28">
         <f t="shared" si="24"/>
-        <v>-1428441.4285708</v>
+        <v>-449864.76190460008</v>
       </c>
       <c r="CI40" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.31493399232666036</v>
       </c>
       <c r="CK40" s="9" t="s">
         <v>12</v>
@@ -10782,15 +10939,15 @@
       <c r="CN40" s="7"/>
       <c r="CO40" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-193</v>
       </c>
       <c r="CP40" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ40" s="29" t="e">
+        <v>-978576.66666619992</v>
+      </c>
+      <c r="CQ40" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS40" s="9" t="s">
         <v>12</v>
@@ -11029,11 +11186,13 @@
       <c r="CD41" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CE41" s="15"/>
+      <c r="CE41" s="15">
+        <v>1557</v>
+      </c>
       <c r="CF41" s="33"/>
       <c r="CG41" s="10">
         <f t="shared" si="23"/>
-        <v>-1449</v>
+        <v>108</v>
       </c>
       <c r="CH41" s="12">
         <f t="shared" si="24"/>
@@ -11053,7 +11212,7 @@
       <c r="CN41" s="33"/>
       <c r="CO41" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1557</v>
       </c>
       <c r="CP41" s="12">
         <f t="shared" si="27"/>
@@ -11546,18 +11705,23 @@
       <c r="CD43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CF43" s="12"/>
+      <c r="CE43" s="10">
+        <v>90</v>
+      </c>
+      <c r="CF43" s="12">
+        <v>81430.476190019996</v>
+      </c>
       <c r="CG43" s="10">
         <f t="shared" si="23"/>
-        <v>-82</v>
+        <v>8</v>
       </c>
       <c r="CH43" s="12">
         <f t="shared" si="24"/>
-        <v>-77693.333332970011</v>
+        <v>3737.1428570499847</v>
       </c>
       <c r="CI43" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>4.8101203754944151E-2</v>
       </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13" t="s">
@@ -11566,15 +11730,15 @@
       <c r="CN43" s="12"/>
       <c r="CO43" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="CP43" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ43" s="11" t="e">
+        <v>-81430.476190019996</v>
+      </c>
+      <c r="CQ43" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13" t="s">
@@ -11809,18 +11973,23 @@
       <c r="CD44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF44" s="12"/>
+      <c r="CE44" s="10">
+        <v>67</v>
+      </c>
+      <c r="CF44" s="12">
+        <v>75810.476190389993</v>
+      </c>
       <c r="CG44" s="10">
         <f t="shared" si="23"/>
-        <v>-70</v>
+        <v>-3</v>
       </c>
       <c r="CH44" s="12">
         <f t="shared" si="24"/>
-        <v>-65399.999999930013</v>
+        <v>10410.47619045998</v>
       </c>
       <c r="CI44" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.15918159312646973</v>
       </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13" t="s">
@@ -11829,15 +11998,15 @@
       <c r="CN44" s="12"/>
       <c r="CO44" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-67</v>
       </c>
       <c r="CP44" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ44" s="11" t="e">
+        <v>-75810.476190389993</v>
+      </c>
+      <c r="CQ44" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13" t="s">
@@ -12072,18 +12241,23 @@
       <c r="CD45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF45" s="12"/>
+      <c r="CE45" s="10">
+        <v>7</v>
+      </c>
+      <c r="CF45" s="12">
+        <v>44219.04761904</v>
+      </c>
       <c r="CG45" s="10">
         <f t="shared" si="23"/>
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="CH45" s="12">
         <f t="shared" si="24"/>
-        <v>-55628.571428559997</v>
+        <v>-11409.523809519997</v>
       </c>
       <c r="CI45" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.20510186611878889</v>
       </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13" t="s">
@@ -12092,15 +12266,15 @@
       <c r="CN45" s="12"/>
       <c r="CO45" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CP45" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ45" s="11" t="e">
+        <v>-44219.04761904</v>
+      </c>
+      <c r="CQ45" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13" t="s">
@@ -12335,18 +12509,23 @@
       <c r="CD46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF46" s="12"/>
+      <c r="CE46" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF46" s="12">
+        <v>212571.42857138999</v>
+      </c>
       <c r="CG46" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="CH46" s="12">
         <f t="shared" si="24"/>
-        <v>-168285.71428568001</v>
+        <v>44285.714285709983</v>
       </c>
       <c r="CI46" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.26315789473687012</v>
       </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13" t="s">
@@ -12355,15 +12534,15 @@
       <c r="CN46" s="12"/>
       <c r="CO46" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CP46" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ46" s="11" t="e">
+        <v>-212571.42857138999</v>
+      </c>
+      <c r="CQ46" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13" t="s">
@@ -12826,10 +13005,15 @@
       <c r="CD48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF48" s="12"/>
+      <c r="CE48" s="51">
+        <v>2</v>
+      </c>
+      <c r="CF48" s="51">
+        <v>0</v>
+      </c>
       <c r="CG48" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CH48" s="12">
         <f t="shared" si="24"/>
@@ -12846,7 +13030,7 @@
       <c r="CN48" s="12"/>
       <c r="CO48" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP48" s="12">
         <f t="shared" si="27"/>
@@ -13084,18 +13268,23 @@
       <c r="CD49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF49" s="12"/>
+      <c r="CE49" s="51">
+        <v>6</v>
+      </c>
+      <c r="CF49" s="51">
+        <v>175492.38095235999</v>
+      </c>
       <c r="CG49" s="10">
         <f t="shared" si="23"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="CH49" s="12">
         <f t="shared" si="24"/>
-        <v>-122933.33333332</v>
+        <v>52559.047619039993</v>
       </c>
       <c r="CI49" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.42754105980785545</v>
       </c>
       <c r="CK49" s="14"/>
       <c r="CL49" s="13" t="s">
@@ -13104,15 +13293,15 @@
       <c r="CN49" s="12"/>
       <c r="CO49" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CP49" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ49" s="11" t="e">
+        <v>-175492.38095235999</v>
+      </c>
+      <c r="CQ49" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS49" s="14"/>
       <c r="CT49" s="13" t="s">
@@ -13347,18 +13536,23 @@
       <c r="CD50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF50" s="12"/>
+      <c r="CE50" s="51">
+        <v>17</v>
+      </c>
+      <c r="CF50" s="51">
+        <v>334285.71428567002</v>
+      </c>
       <c r="CG50" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>4</v>
       </c>
       <c r="CH50" s="12">
         <f t="shared" si="24"/>
-        <v>-216857.14285710998</v>
+        <v>117428.57142856004</v>
       </c>
       <c r="CI50" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.54150197628461461</v>
       </c>
       <c r="CK50" s="14"/>
       <c r="CL50" s="13" t="s">
@@ -13367,15 +13561,15 @@
       <c r="CN50" s="12"/>
       <c r="CO50" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="CP50" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ50" s="11" t="e">
+        <v>-334285.71428567002</v>
+      </c>
+      <c r="CQ50" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS50" s="14"/>
       <c r="CT50" s="13" t="s">
@@ -13610,18 +13804,23 @@
       <c r="CD51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF51" s="12"/>
+      <c r="CE51" s="51">
+        <v>11</v>
+      </c>
+      <c r="CF51" s="51">
+        <v>358952.38095235999</v>
+      </c>
       <c r="CG51" s="10">
         <f t="shared" si="23"/>
-        <v>-17</v>
+        <v>-6</v>
       </c>
       <c r="CH51" s="12">
         <f t="shared" si="24"/>
-        <v>-630761.90476187994</v>
+        <v>-271809.52380951995</v>
       </c>
       <c r="CI51" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.43092254265439706</v>
       </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13" t="s">
@@ -13630,15 +13829,15 @@
       <c r="CN51" s="12"/>
       <c r="CO51" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CP51" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ51" s="11" t="e">
+        <v>-358952.38095235999</v>
+      </c>
+      <c r="CQ51" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13" t="s">
@@ -13874,19 +14073,23 @@
         <v>11</v>
       </c>
       <c r="CD52" s="9"/>
-      <c r="CE52" s="8"/>
-      <c r="CF52" s="7"/>
+      <c r="CE52" s="52">
+        <v>218</v>
+      </c>
+      <c r="CF52" s="52">
+        <v>1282761.9047612301</v>
+      </c>
       <c r="CG52" s="27">
         <f t="shared" si="23"/>
-        <v>-208</v>
+        <v>10</v>
       </c>
       <c r="CH52" s="28">
         <f t="shared" si="24"/>
-        <v>-1343849.9999994501</v>
+        <v>-61088.095238219947</v>
       </c>
       <c r="CI52" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-4.5457525198679127E-2</v>
       </c>
       <c r="CK52" s="9" t="s">
         <v>11</v>
@@ -13896,15 +14099,15 @@
       <c r="CN52" s="7"/>
       <c r="CO52" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-218</v>
       </c>
       <c r="CP52" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ52" s="29" t="e">
+        <v>-1282761.9047612301</v>
+      </c>
+      <c r="CQ52" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS52" s="9" t="s">
         <v>11</v>
@@ -14632,18 +14835,23 @@
       <c r="CD55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CF55" s="12"/>
+      <c r="CE55" s="10">
+        <v>113</v>
+      </c>
+      <c r="CF55" s="12">
+        <v>121799.04761848997</v>
+      </c>
       <c r="CG55" s="10">
         <f t="shared" si="23"/>
-        <v>-113</v>
+        <v>0</v>
       </c>
       <c r="CH55" s="12">
         <f t="shared" si="24"/>
-        <v>-119877.14285659992</v>
+        <v>1921.9047618900513</v>
       </c>
       <c r="CI55" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>1.603228702396655E-2</v>
       </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13" t="s">
@@ -14652,15 +14860,15 @@
       <c r="CN55" s="12"/>
       <c r="CO55" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-113</v>
       </c>
       <c r="CP55" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ55" s="11" t="e">
+        <v>-121799.04761848997</v>
+      </c>
+      <c r="CQ55" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13" t="s">
@@ -14895,18 +15103,23 @@
       <c r="CD56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF56" s="12"/>
+      <c r="CE56" s="10">
+        <v>59</v>
+      </c>
+      <c r="CF56" s="12">
+        <v>70390.476190379995</v>
+      </c>
       <c r="CG56" s="10">
         <f t="shared" si="23"/>
-        <v>-51</v>
+        <v>8</v>
       </c>
       <c r="CH56" s="12">
         <f t="shared" si="24"/>
-        <v>-67355.238095140012</v>
+        <v>3035.2380952399835</v>
       </c>
       <c r="CI56" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>4.5063133634130677E-2</v>
       </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13" t="s">
@@ -14915,15 +15128,15 @@
       <c r="CN56" s="12"/>
       <c r="CO56" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="CP56" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ56" s="11" t="e">
+        <v>-70390.476190379995</v>
+      </c>
+      <c r="CQ56" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13" t="s">
@@ -15158,18 +15371,23 @@
       <c r="CD57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF57" s="12"/>
+      <c r="CE57" s="10">
+        <v>14</v>
+      </c>
+      <c r="CF57" s="12">
+        <v>102723.80952379</v>
+      </c>
       <c r="CG57" s="10">
         <f t="shared" si="23"/>
-        <v>-12</v>
+        <v>2</v>
       </c>
       <c r="CH57" s="12">
         <f t="shared" si="24"/>
-        <v>-77028.571428569994</v>
+        <v>25695.238095220004</v>
       </c>
       <c r="CI57" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.33358061325397509</v>
       </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13" t="s">
@@ -15178,15 +15396,15 @@
       <c r="CN57" s="12"/>
       <c r="CO57" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CP57" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ57" s="11" t="e">
+        <v>-102723.80952379</v>
+      </c>
+      <c r="CQ57" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13" t="s">
@@ -15421,18 +15639,23 @@
       <c r="CD58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF58" s="12"/>
+      <c r="CE58" s="10">
+        <v>13</v>
+      </c>
+      <c r="CF58" s="12">
+        <v>156857.1428571</v>
+      </c>
       <c r="CG58" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="CH58" s="12">
         <f t="shared" si="24"/>
-        <v>-155904.76190472004</v>
+        <v>952.38095237995731</v>
       </c>
       <c r="CI58" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>6.1087354917484646E-3</v>
       </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13" t="s">
@@ -15441,15 +15664,15 @@
       <c r="CN58" s="12"/>
       <c r="CO58" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CP58" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ58" s="11" t="e">
+        <v>-156857.1428571</v>
+      </c>
+      <c r="CQ58" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13" t="s">
@@ -15908,18 +16131,23 @@
       <c r="CD60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF60" s="12"/>
+      <c r="CE60" s="51">
+        <v>5</v>
+      </c>
+      <c r="CF60" s="51">
+        <v>27150</v>
+      </c>
       <c r="CG60" s="10">
         <f t="shared" si="23"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="CH60" s="12">
         <f t="shared" si="24"/>
-        <v>-18550</v>
+        <v>8600</v>
       </c>
       <c r="CI60" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.46361185983827491</v>
       </c>
       <c r="CK60" s="14"/>
       <c r="CL60" s="13" t="s">
@@ -15928,15 +16156,15 @@
       <c r="CN60" s="12"/>
       <c r="CO60" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CP60" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ60" s="11" t="e">
+        <v>-27150</v>
+      </c>
+      <c r="CQ60" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS60" s="14"/>
       <c r="CT60" s="13" t="s">
@@ -16171,18 +16399,23 @@
       <c r="CD61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF61" s="12"/>
+      <c r="CE61" s="51">
+        <v>7</v>
+      </c>
+      <c r="CF61" s="51">
+        <v>261295.23809520996</v>
+      </c>
       <c r="CG61" s="10">
         <f t="shared" si="23"/>
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="CH61" s="12">
         <f t="shared" si="24"/>
-        <v>-126861.90476189001</v>
+        <v>134433.33333331996</v>
       </c>
       <c r="CI61" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>1.0596824443527073</v>
       </c>
       <c r="CK61" s="14"/>
       <c r="CL61" s="13" t="s">
@@ -16191,15 +16424,15 @@
       <c r="CN61" s="12"/>
       <c r="CO61" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CP61" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ61" s="11" t="e">
+        <v>-261295.23809520996</v>
+      </c>
+      <c r="CQ61" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS61" s="14"/>
       <c r="CT61" s="13" t="s">
@@ -16434,18 +16667,23 @@
       <c r="CD62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF62" s="12"/>
+      <c r="CE62" s="51">
+        <v>13</v>
+      </c>
+      <c r="CF62" s="51">
+        <v>277809.52380949003</v>
+      </c>
       <c r="CG62" s="10">
         <f t="shared" si="23"/>
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="CH62" s="12">
         <f t="shared" si="24"/>
-        <v>-208952.38095234003</v>
+        <v>68857.14285715</v>
       </c>
       <c r="CI62" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.32953509571568668</v>
       </c>
       <c r="CK62" s="14"/>
       <c r="CL62" s="13" t="s">
@@ -16454,15 +16692,15 @@
       <c r="CN62" s="12"/>
       <c r="CO62" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CP62" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ62" s="11" t="e">
+        <v>-277809.52380949003</v>
+      </c>
+      <c r="CQ62" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS62" s="14"/>
       <c r="CT62" s="13" t="s">
@@ -16697,18 +16935,23 @@
       <c r="CD63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF63" s="12"/>
+      <c r="CE63" s="51">
+        <v>18</v>
+      </c>
+      <c r="CF63" s="51">
+        <v>655428.57142853993</v>
+      </c>
       <c r="CG63" s="10">
         <f t="shared" si="23"/>
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="CH63" s="12">
         <f t="shared" si="24"/>
-        <v>-348476.19047617994</v>
+        <v>306952.38095235999</v>
       </c>
       <c r="CI63" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.8808417600436943</v>
       </c>
       <c r="CK63" s="14"/>
       <c r="CL63" s="13" t="s">
@@ -16717,15 +16960,15 @@
       <c r="CN63" s="12"/>
       <c r="CO63" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CP63" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ63" s="11" t="e">
+        <v>-655428.57142853993</v>
+      </c>
+      <c r="CQ63" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS63" s="14"/>
       <c r="CT63" s="13" t="s">
@@ -16961,19 +17204,23 @@
         <v>1</v>
       </c>
       <c r="CD64" s="9"/>
-      <c r="CE64" s="8"/>
-      <c r="CF64" s="7"/>
+      <c r="CE64" s="52">
+        <v>242</v>
+      </c>
+      <c r="CF64" s="52">
+        <v>1673453.8095229999</v>
+      </c>
       <c r="CG64" s="27">
         <f t="shared" si="23"/>
-        <v>-220</v>
+        <v>22</v>
       </c>
       <c r="CH64" s="28">
         <f t="shared" si="24"/>
-        <v>-1123006.1904754401</v>
+        <v>550447.6190475598</v>
       </c>
       <c r="CI64" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.49015546282475986</v>
       </c>
       <c r="CK64" s="9" t="s">
         <v>1</v>
@@ -16983,15 +17230,15 @@
       <c r="CN64" s="7"/>
       <c r="CO64" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-242</v>
       </c>
       <c r="CP64" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ64" s="29" t="e">
+        <v>-1673453.8095229999</v>
+      </c>
+      <c r="CQ64" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS64" s="9" t="s">
         <v>1</v>
@@ -17228,19 +17475,23 @@
         <v>0</v>
       </c>
       <c r="CD65" s="4"/>
-      <c r="CE65" s="3"/>
-      <c r="CF65" s="2"/>
+      <c r="CE65" s="3">
+        <v>1893</v>
+      </c>
+      <c r="CF65" s="2">
+        <v>15151444.7619006</v>
+      </c>
       <c r="CG65" s="6">
         <f t="shared" si="23"/>
-        <v>-1787</v>
+        <v>106</v>
       </c>
       <c r="CH65" s="5">
         <f t="shared" si="24"/>
-        <v>-13836733.809519703</v>
+        <v>1314710.9523808975</v>
       </c>
       <c r="CI65" s="30">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>9.501598935699504E-2</v>
       </c>
       <c r="CK65" s="4" t="s">
         <v>0</v>
@@ -17250,15 +17501,15 @@
       <c r="CN65" s="2"/>
       <c r="CO65" s="6">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1893</v>
       </c>
       <c r="CP65" s="5">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ65" s="30" t="e">
+        <v>-15151444.7619006</v>
+      </c>
+      <c r="CQ65" s="30">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS65" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9ECBCAE-5B4A-B74A-A511-5953E846577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C656A1-C9B0-5349-B197-4F70595FEDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1931,10 +1931,13 @@
       <c r="CD6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CE6" s="15">
+        <v>8</v>
+      </c>
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -1951,7 +1954,7 @@
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -5113,11 +5116,13 @@
       <c r="CD18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE18" s="15"/>
+      <c r="CE18" s="15">
+        <v>7</v>
+      </c>
       <c r="CF18" s="33"/>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
@@ -5135,7 +5140,7 @@
       <c r="CN18" s="33"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
@@ -8279,11 +8284,13 @@
       <c r="CD30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE30" s="15"/>
+      <c r="CE30" s="15">
+        <v>2</v>
+      </c>
       <c r="CF30" s="33"/>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
@@ -8301,7 +8308,7 @@
       <c r="CN30" s="33"/>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
@@ -11439,11 +11446,13 @@
       <c r="CD42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE42" s="15"/>
+      <c r="CE42" s="15">
+        <v>2</v>
+      </c>
       <c r="CF42" s="33"/>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
@@ -11461,7 +11470,7 @@
       <c r="CN42" s="33"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
@@ -14569,11 +14578,13 @@
       <c r="CD54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE54" s="15"/>
+      <c r="CE54" s="15">
+        <v>1</v>
+      </c>
       <c r="CF54" s="33"/>
       <c r="CG54" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH54" s="12">
         <f t="shared" si="24"/>
@@ -14591,7 +14602,7 @@
       <c r="CN54" s="33"/>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C656A1-C9B0-5349-B197-4F70595FEDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F2AE45-3CBD-124A-A494-F0D4BB1BD09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="46">
   <si>
     <t>總計</t>
   </si>
@@ -232,6 +232,14 @@
   </si>
   <si>
     <t>06/07~06/13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06/14~06/20</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1122,7 +1130,9 @@
       </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
-      <c r="CK1" s="26"/>
+      <c r="CK1" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
       <c r="CS1" s="26"/>
@@ -1201,6 +1211,9 @@
       <c r="CG2" s="21"/>
       <c r="CH2" s="21"/>
       <c r="CI2" s="21"/>
+      <c r="CK2" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="CL2" s="21"/>
       <c r="CN2" s="21"/>
       <c r="CO2" s="21"/>
@@ -1699,11 +1712,13 @@
       <c r="CL5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CM5" s="15"/>
+      <c r="CM5" s="15">
+        <v>6416</v>
+      </c>
       <c r="CN5" s="33"/>
       <c r="CO5" s="10">
         <f t="shared" ref="CO5:CO65" si="26">CM5-CE5</f>
-        <v>-5735</v>
+        <v>681</v>
       </c>
       <c r="CP5" s="12">
         <f t="shared" ref="CP5:CP65" si="27">CN5-CF5</f>
@@ -1724,7 +1739,7 @@
       <c r="CV5" s="33"/>
       <c r="CW5" s="10">
         <f t="shared" ref="CW5:CW65" si="29">CU5-CM5</f>
-        <v>0</v>
+        <v>-6416</v>
       </c>
       <c r="CX5" s="12">
         <f t="shared" ref="CX5:CX65" si="30">CV5-CN5</f>
@@ -2219,18 +2234,23 @@
       <c r="CL7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CN7" s="12"/>
+      <c r="CM7" s="10">
+        <v>181</v>
+      </c>
+      <c r="CN7" s="12">
+        <v>215959.04761827007</v>
+      </c>
       <c r="CO7" s="10">
         <f t="shared" si="26"/>
-        <v>-188</v>
+        <v>-7</v>
       </c>
       <c r="CP7" s="12">
         <f t="shared" si="27"/>
-        <v>-238791.42857063009</v>
+        <v>-22832.380952360021</v>
       </c>
       <c r="CQ7" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-9.5616417595184439E-2</v>
       </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13" t="s">
@@ -2239,15 +2259,15 @@
       <c r="CV7" s="12"/>
       <c r="CW7" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-181</v>
       </c>
       <c r="CX7" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY7" s="11" t="e">
+        <v>-215959.04761827007</v>
+      </c>
+      <c r="CY7" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2487,18 +2507,23 @@
       <c r="CL8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN8" s="12"/>
+      <c r="CM8" s="10">
+        <v>277</v>
+      </c>
+      <c r="CN8" s="12">
+        <v>357247.61904741998</v>
+      </c>
       <c r="CO8" s="10">
         <f t="shared" si="26"/>
-        <v>-248</v>
+        <v>29</v>
       </c>
       <c r="CP8" s="12">
         <f t="shared" si="27"/>
-        <v>-401064.76190457988</v>
+        <v>-43817.142857159895</v>
       </c>
       <c r="CQ8" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.10925203862109616</v>
       </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13" t="s">
@@ -2507,15 +2532,15 @@
       <c r="CV8" s="12"/>
       <c r="CW8" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-277</v>
       </c>
       <c r="CX8" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY8" s="11" t="e">
+        <v>-357247.61904741998</v>
+      </c>
+      <c r="CY8" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2755,18 +2780,23 @@
       <c r="CL9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN9" s="12"/>
+      <c r="CM9" s="10">
+        <v>61</v>
+      </c>
+      <c r="CN9" s="12">
+        <v>388849.52380950999</v>
+      </c>
       <c r="CO9" s="10">
         <f t="shared" si="26"/>
-        <v>-75</v>
+        <v>-14</v>
       </c>
       <c r="CP9" s="12">
         <f t="shared" si="27"/>
-        <v>-487572.38095234998</v>
+        <v>-98722.857142839988</v>
       </c>
       <c r="CQ9" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.20247836218698387</v>
       </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13" t="s">
@@ -2775,15 +2805,15 @@
       <c r="CV9" s="12"/>
       <c r="CW9" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="CX9" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY9" s="11" t="e">
+        <v>-388849.52380950999</v>
+      </c>
+      <c r="CY9" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3023,18 +3053,23 @@
       <c r="CL10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN10" s="12"/>
+      <c r="CM10" s="10">
+        <v>39</v>
+      </c>
+      <c r="CN10" s="12">
+        <v>491523.80952373007</v>
+      </c>
       <c r="CO10" s="10">
         <f t="shared" si="26"/>
-        <v>-45</v>
+        <v>-6</v>
       </c>
       <c r="CP10" s="12">
         <f t="shared" si="27"/>
-        <v>-569999.99999992002</v>
+        <v>-78476.19047618995</v>
       </c>
       <c r="CQ10" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.13767752715122974</v>
       </c>
       <c r="CS10" s="14"/>
       <c r="CT10" s="13" t="s">
@@ -3043,15 +3078,15 @@
       <c r="CV10" s="12"/>
       <c r="CW10" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="CX10" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY10" s="11" t="e">
+        <v>-491523.80952373007</v>
+      </c>
+      <c r="CY10" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3539,18 +3574,23 @@
       <c r="CL12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN12" s="12"/>
+      <c r="CM12" s="10">
+        <v>12</v>
+      </c>
+      <c r="CN12" s="12">
+        <v>80780</v>
+      </c>
       <c r="CO12" s="10">
         <f t="shared" si="26"/>
-        <v>-19</v>
+        <v>-7</v>
       </c>
       <c r="CP12" s="12">
         <f t="shared" si="27"/>
-        <v>-84420</v>
+        <v>-3640</v>
       </c>
       <c r="CQ12" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-4.3117744610281922E-2</v>
       </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13" t="s">
@@ -3559,15 +3599,15 @@
       <c r="CV12" s="12"/>
       <c r="CW12" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CX12" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY12" s="11" t="e">
+        <v>-80780</v>
+      </c>
+      <c r="CY12" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3807,18 +3847,23 @@
       <c r="CL13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN13" s="12"/>
+      <c r="CM13" s="10">
+        <v>46</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>1416838.0952379801</v>
+      </c>
       <c r="CO13" s="10">
         <f t="shared" si="26"/>
-        <v>-33</v>
+        <v>13</v>
       </c>
       <c r="CP13" s="12">
         <f t="shared" si="27"/>
-        <v>-1255690.47619037</v>
+        <v>161147.61904761009</v>
       </c>
       <c r="CQ13" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.12833387057017001</v>
       </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13" t="s">
@@ -3827,15 +3872,15 @@
       <c r="CV13" s="12"/>
       <c r="CW13" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="CX13" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY13" s="11" t="e">
+        <v>-1416838.0952379801</v>
+      </c>
+      <c r="CY13" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4075,18 +4120,23 @@
       <c r="CL14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN14" s="12"/>
+      <c r="CM14" s="10">
+        <v>51</v>
+      </c>
+      <c r="CN14" s="12">
+        <v>1142380.9523808402</v>
+      </c>
       <c r="CO14" s="10">
         <f t="shared" si="26"/>
-        <v>-66</v>
+        <v>-15</v>
       </c>
       <c r="CP14" s="12">
         <f t="shared" si="27"/>
-        <v>-1463238.0952379603</v>
+        <v>-320857.14285712014</v>
       </c>
       <c r="CQ14" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.21927883363707837</v>
       </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13" t="s">
@@ -4095,15 +4145,15 @@
       <c r="CV14" s="12"/>
       <c r="CW14" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-51</v>
       </c>
       <c r="CX14" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY14" s="11" t="e">
+        <v>-1142380.9523808402</v>
+      </c>
+      <c r="CY14" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4343,18 +4393,23 @@
       <c r="CL15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN15" s="12"/>
+      <c r="CM15" s="10">
+        <v>82</v>
+      </c>
+      <c r="CN15" s="12">
+        <v>2929333.3333332599</v>
+      </c>
       <c r="CO15" s="10">
         <f t="shared" si="26"/>
-        <v>-91</v>
+        <v>-9</v>
       </c>
       <c r="CP15" s="12">
         <f t="shared" si="27"/>
-        <v>-3423385.7142856503</v>
+        <v>-494052.38095239038</v>
       </c>
       <c r="CQ15" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.14431689040785844</v>
       </c>
       <c r="CS15" s="14"/>
       <c r="CT15" s="13" t="s">
@@ -4363,15 +4418,15 @@
       <c r="CV15" s="12"/>
       <c r="CW15" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="CX15" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY15" s="11" t="e">
+        <v>-2929333.3333332599</v>
+      </c>
+      <c r="CY15" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4612,19 +4667,23 @@
         <v>19</v>
       </c>
       <c r="CL16" s="9"/>
-      <c r="CM16" s="8"/>
-      <c r="CN16" s="7"/>
+      <c r="CM16" s="8">
+        <v>749</v>
+      </c>
+      <c r="CN16" s="7">
+        <v>7022912.3809510106</v>
+      </c>
       <c r="CO16" s="27">
         <f t="shared" si="26"/>
-        <v>-765</v>
+        <v>-16</v>
       </c>
       <c r="CP16" s="28">
         <f t="shared" si="27"/>
-        <v>-7924162.8571414603</v>
+        <v>-901250.47619044967</v>
       </c>
       <c r="CQ16" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.11373447169605044</v>
       </c>
       <c r="CS16" s="9" t="s">
         <v>19</v>
@@ -4634,15 +4693,15 @@
       <c r="CV16" s="7"/>
       <c r="CW16" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-749</v>
       </c>
       <c r="CX16" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY16" s="29" t="e">
+        <v>-7022912.3809510106</v>
+      </c>
+      <c r="CY16" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4885,11 +4944,13 @@
       <c r="CL17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CM17" s="15"/>
+      <c r="CM17" s="15">
+        <v>4430</v>
+      </c>
       <c r="CN17" s="33"/>
       <c r="CO17" s="10">
         <f t="shared" si="26"/>
-        <v>-2719</v>
+        <v>1711</v>
       </c>
       <c r="CP17" s="12">
         <f t="shared" si="27"/>
@@ -4909,7 +4970,7 @@
       <c r="CV17" s="33"/>
       <c r="CW17" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-4430</v>
       </c>
       <c r="CX17" s="12">
         <f t="shared" si="30"/>
@@ -5406,18 +5467,23 @@
       <c r="CL19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CN19" s="12"/>
+      <c r="CM19" s="10">
+        <v>152</v>
+      </c>
+      <c r="CN19" s="12">
+        <v>188762.85714221009</v>
+      </c>
       <c r="CO19" s="10">
         <f t="shared" si="26"/>
-        <v>-121</v>
+        <v>31</v>
       </c>
       <c r="CP19" s="12">
         <f t="shared" si="27"/>
-        <v>-135971.42857091996</v>
+        <v>52791.428571290133</v>
       </c>
       <c r="CQ19" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.38825383483968606</v>
       </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13" t="s">
@@ -5426,15 +5492,15 @@
       <c r="CV19" s="12"/>
       <c r="CW19" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-152</v>
       </c>
       <c r="CX19" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY19" s="11" t="e">
+        <v>-188762.85714221009</v>
+      </c>
+      <c r="CY19" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5674,18 +5740,23 @@
       <c r="CL20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN20" s="12"/>
+      <c r="CM20" s="10">
+        <v>189</v>
+      </c>
+      <c r="CN20" s="12">
+        <v>199820.95238083001</v>
+      </c>
       <c r="CO20" s="10">
         <f t="shared" si="26"/>
-        <v>-205</v>
+        <v>-16</v>
       </c>
       <c r="CP20" s="12">
         <f t="shared" si="27"/>
-        <v>-239438.09523798001</v>
+        <v>-39617.14285715</v>
       </c>
       <c r="CQ20" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.16545881229874515</v>
       </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13" t="s">
@@ -5694,15 +5765,15 @@
       <c r="CV20" s="12"/>
       <c r="CW20" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-189</v>
       </c>
       <c r="CX20" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY20" s="11" t="e">
+        <v>-199820.95238083001</v>
+      </c>
+      <c r="CY20" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5942,18 +6013,23 @@
       <c r="CL21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN21" s="12"/>
+      <c r="CM21" s="10">
+        <v>37</v>
+      </c>
+      <c r="CN21" s="12">
+        <v>220862.85714285</v>
+      </c>
       <c r="CO21" s="10">
         <f t="shared" si="26"/>
-        <v>-28</v>
+        <v>9</v>
       </c>
       <c r="CP21" s="12">
         <f t="shared" si="27"/>
-        <v>-172114.28571427002</v>
+        <v>48748.571428579977</v>
       </c>
       <c r="CQ21" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.28323373173978333</v>
       </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13" t="s">
@@ -5962,15 +6038,15 @@
       <c r="CV21" s="12"/>
       <c r="CW21" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="CX21" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY21" s="11" t="e">
+        <v>-220862.85714285</v>
+      </c>
+      <c r="CY21" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6210,18 +6286,23 @@
       <c r="CL22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN22" s="12"/>
+      <c r="CM22" s="10">
+        <v>29</v>
+      </c>
+      <c r="CN22" s="12">
+        <v>370095.23809517</v>
+      </c>
       <c r="CO22" s="10">
         <f t="shared" si="26"/>
-        <v>-20</v>
+        <v>9</v>
       </c>
       <c r="CP22" s="12">
         <f t="shared" si="27"/>
-        <v>-240476.19047615997</v>
+        <v>129619.04761901003</v>
       </c>
       <c r="CQ22" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.53900990099001111</v>
       </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13" t="s">
@@ -6230,15 +6311,15 @@
       <c r="CV22" s="12"/>
       <c r="CW22" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="CX22" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY22" s="11" t="e">
+        <v>-370095.23809517</v>
+      </c>
+      <c r="CY22" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6707,18 +6788,23 @@
       <c r="CL24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN24" s="12"/>
+      <c r="CM24" s="10">
+        <v>25</v>
+      </c>
+      <c r="CN24" s="12">
+        <v>69870</v>
+      </c>
       <c r="CO24" s="10">
         <f t="shared" si="26"/>
-        <v>-18</v>
+        <v>7</v>
       </c>
       <c r="CP24" s="12">
         <f t="shared" si="27"/>
-        <v>-65780</v>
+        <v>4090</v>
       </c>
       <c r="CQ24" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>6.2176953481301304E-2</v>
       </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13" t="s">
@@ -6727,15 +6813,15 @@
       <c r="CV24" s="12"/>
       <c r="CW24" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="CX24" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY24" s="11" t="e">
+        <v>-69870</v>
+      </c>
+      <c r="CY24" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6975,18 +7061,23 @@
       <c r="CL25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN25" s="12"/>
+      <c r="CM25" s="10">
+        <v>34</v>
+      </c>
+      <c r="CN25" s="12">
+        <v>944399.99999992002</v>
+      </c>
       <c r="CO25" s="10">
         <f t="shared" si="26"/>
-        <v>-14</v>
+        <v>20</v>
       </c>
       <c r="CP25" s="12">
         <f t="shared" si="27"/>
-        <v>-481090.47619045002</v>
+        <v>463309.52380947</v>
       </c>
       <c r="CQ25" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.96304031515697464</v>
       </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13" t="s">
@@ -6995,15 +7086,15 @@
       <c r="CV25" s="12"/>
       <c r="CW25" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="CX25" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY25" s="11" t="e">
+        <v>-944399.99999992002</v>
+      </c>
+      <c r="CY25" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7243,18 +7334,23 @@
       <c r="CL26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN26" s="12"/>
+      <c r="CM26" s="10">
+        <v>40</v>
+      </c>
+      <c r="CN26" s="12">
+        <v>759238.09523802018</v>
+      </c>
       <c r="CO26" s="10">
         <f t="shared" si="26"/>
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="CP26" s="12">
         <f t="shared" si="27"/>
-        <v>-642285.71428565006</v>
+        <v>116952.38095237012</v>
       </c>
       <c r="CQ26" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.1820877817319112</v>
       </c>
       <c r="CS26" s="14"/>
       <c r="CT26" s="13" t="s">
@@ -7263,15 +7359,15 @@
       <c r="CV26" s="12"/>
       <c r="CW26" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="CX26" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY26" s="11" t="e">
+        <v>-759238.09523802018</v>
+      </c>
+      <c r="CY26" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7511,18 +7607,23 @@
       <c r="CL27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN27" s="12"/>
+      <c r="CM27" s="10">
+        <v>50</v>
+      </c>
+      <c r="CN27" s="12">
+        <v>1803809.5238094598</v>
+      </c>
       <c r="CO27" s="10">
         <f t="shared" si="26"/>
-        <v>-39</v>
+        <v>11</v>
       </c>
       <c r="CP27" s="12">
         <f t="shared" si="27"/>
-        <v>-1315333.3333332802</v>
+        <v>488476.19047617959</v>
       </c>
       <c r="CQ27" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.37137064658606134</v>
       </c>
       <c r="CS27" s="14"/>
       <c r="CT27" s="13" t="s">
@@ -7531,15 +7632,15 @@
       <c r="CV27" s="12"/>
       <c r="CW27" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="CX27" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY27" s="11" t="e">
+        <v>-1803809.5238094598</v>
+      </c>
+      <c r="CY27" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7780,19 +7881,23 @@
         <v>13</v>
       </c>
       <c r="CL28" s="9"/>
-      <c r="CM28" s="8"/>
-      <c r="CN28" s="7"/>
+      <c r="CM28" s="8">
+        <v>556</v>
+      </c>
+      <c r="CN28" s="7">
+        <v>4556859.5238084598</v>
+      </c>
       <c r="CO28" s="27">
         <f t="shared" si="26"/>
-        <v>-475</v>
+        <v>81</v>
       </c>
       <c r="CP28" s="28">
         <f t="shared" si="27"/>
-        <v>-3292489.5238087103</v>
+        <v>1264369.9999997495</v>
       </c>
       <c r="CQ28" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.3840164079055724</v>
       </c>
       <c r="CS28" s="9" t="s">
         <v>13</v>
@@ -7802,15 +7907,15 @@
       <c r="CV28" s="7"/>
       <c r="CW28" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-556</v>
       </c>
       <c r="CX28" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY28" s="29" t="e">
+        <v>-4556859.5238084598</v>
+      </c>
+      <c r="CY28" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -8053,11 +8158,13 @@
       <c r="CL29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CM29" s="15"/>
+      <c r="CM29" s="15">
+        <v>4006</v>
+      </c>
       <c r="CN29" s="33"/>
       <c r="CO29" s="10">
         <f t="shared" si="26"/>
-        <v>-2988</v>
+        <v>1018</v>
       </c>
       <c r="CP29" s="12">
         <f t="shared" si="27"/>
@@ -8077,7 +8184,7 @@
       <c r="CV29" s="33"/>
       <c r="CW29" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-4006</v>
       </c>
       <c r="CX29" s="12">
         <f t="shared" si="30"/>
@@ -8574,18 +8681,23 @@
       <c r="CL31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CN31" s="12"/>
+      <c r="CM31" s="10">
+        <v>81</v>
+      </c>
+      <c r="CN31" s="12">
+        <v>74516.190475820025</v>
+      </c>
       <c r="CO31" s="10">
         <f t="shared" si="26"/>
-        <v>-61</v>
+        <v>20</v>
       </c>
       <c r="CP31" s="12">
         <f t="shared" si="27"/>
-        <v>-53934.285714040001</v>
+        <v>20581.904761780024</v>
       </c>
       <c r="CQ31" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.38161077854827713</v>
       </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13" t="s">
@@ -8594,15 +8706,15 @@
       <c r="CV31" s="12"/>
       <c r="CW31" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-81</v>
       </c>
       <c r="CX31" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY31" s="11" t="e">
+        <v>-74516.190475820025</v>
+      </c>
+      <c r="CY31" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8842,18 +8954,23 @@
       <c r="CL32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN32" s="12"/>
+      <c r="CM32" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN32" s="12">
+        <v>71185.714285619993</v>
+      </c>
       <c r="CO32" s="10">
         <f t="shared" si="26"/>
-        <v>-72</v>
+        <v>3</v>
       </c>
       <c r="CP32" s="12">
         <f t="shared" si="27"/>
-        <v>-63057.142857050007</v>
+        <v>8128.5714285699869</v>
       </c>
       <c r="CQ32" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.12890801993673243</v>
       </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13" t="s">
@@ -8862,15 +8979,15 @@
       <c r="CV32" s="12"/>
       <c r="CW32" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="CX32" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY32" s="11" t="e">
+        <v>-71185.714285619993</v>
+      </c>
+      <c r="CY32" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9110,18 +9227,23 @@
       <c r="CL33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN33" s="12"/>
+      <c r="CM33" s="10">
+        <v>27</v>
+      </c>
+      <c r="CN33" s="12">
+        <v>182315.23809522</v>
+      </c>
       <c r="CO33" s="10">
         <f t="shared" si="26"/>
-        <v>-19</v>
+        <v>8</v>
       </c>
       <c r="CP33" s="12">
         <f t="shared" si="27"/>
-        <v>-130962.85714283999</v>
+        <v>51352.380952380016</v>
       </c>
       <c r="CQ33" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.39211408541866527</v>
       </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13" t="s">
@@ -9130,15 +9252,15 @@
       <c r="CV33" s="12"/>
       <c r="CW33" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="CX33" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY33" s="11" t="e">
+        <v>-182315.23809522</v>
+      </c>
+      <c r="CY33" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9378,18 +9500,23 @@
       <c r="CL34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN34" s="12"/>
+      <c r="CM34" s="10">
+        <v>19</v>
+      </c>
+      <c r="CN34" s="12">
+        <v>213719.04761903</v>
+      </c>
       <c r="CO34" s="10">
         <f t="shared" si="26"/>
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="CP34" s="12">
         <f t="shared" si="27"/>
-        <v>-204476.19047614001</v>
+        <v>9242.8571428899886</v>
       </c>
       <c r="CQ34" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>4.5202608290809888E-2</v>
       </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13" t="s">
@@ -9398,15 +9525,15 @@
       <c r="CV34" s="12"/>
       <c r="CW34" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="CX34" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY34" s="11" t="e">
+        <v>-213719.04761903</v>
+      </c>
+      <c r="CY34" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9869,18 +9996,23 @@
       <c r="CL36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN36" s="12"/>
+      <c r="CM36" s="10">
+        <v>2</v>
+      </c>
+      <c r="CN36" s="12">
+        <v>7480</v>
+      </c>
       <c r="CO36" s="10">
         <f t="shared" si="26"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="CP36" s="12">
         <f t="shared" si="27"/>
-        <v>-9670</v>
+        <v>-2190</v>
       </c>
       <c r="CQ36" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.2264736297828335</v>
       </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13" t="s">
@@ -9889,15 +10021,15 @@
       <c r="CV36" s="12"/>
       <c r="CW36" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CX36" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY36" s="11" t="e">
+        <v>-7480</v>
+      </c>
+      <c r="CY36" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10137,18 +10269,23 @@
       <c r="CL37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN37" s="12"/>
+      <c r="CM37" s="10">
+        <v>2</v>
+      </c>
+      <c r="CN37" s="12">
+        <v>43619.04761904</v>
+      </c>
       <c r="CO37" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="CP37" s="12">
         <f t="shared" si="27"/>
-        <v>-62666.666666660007</v>
+        <v>-19047.619047620006</v>
       </c>
       <c r="CQ37" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.30395136778120263</v>
       </c>
       <c r="CS37" s="14"/>
       <c r="CT37" s="13" t="s">
@@ -10157,15 +10294,15 @@
       <c r="CV37" s="12"/>
       <c r="CW37" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CX37" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY37" s="11" t="e">
+        <v>-43619.04761904</v>
+      </c>
+      <c r="CY37" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10405,18 +10542,23 @@
       <c r="CL38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN38" s="12"/>
+      <c r="CM38" s="10">
+        <v>12</v>
+      </c>
+      <c r="CN38" s="12">
+        <v>196476.19047616998</v>
+      </c>
       <c r="CO38" s="10">
         <f t="shared" si="26"/>
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="CP38" s="12">
         <f t="shared" si="27"/>
-        <v>-141333.33333329999</v>
+        <v>55142.857142869994</v>
       </c>
       <c r="CQ38" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.39016172506756841</v>
       </c>
       <c r="CS38" s="14"/>
       <c r="CT38" s="13" t="s">
@@ -10425,15 +10567,15 @@
       <c r="CV38" s="12"/>
       <c r="CW38" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CX38" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY38" s="11" t="e">
+        <v>-196476.19047616998</v>
+      </c>
+      <c r="CY38" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10673,18 +10815,23 @@
       <c r="CL39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN39" s="12"/>
+      <c r="CM39" s="10">
+        <v>18</v>
+      </c>
+      <c r="CN39" s="12">
+        <v>606857.14285711991</v>
+      </c>
       <c r="CO39" s="10">
         <f t="shared" si="26"/>
-        <v>-9</v>
+        <v>9</v>
       </c>
       <c r="CP39" s="12">
         <f t="shared" si="27"/>
-        <v>-312476.19047616998</v>
+        <v>294380.95238094992</v>
       </c>
       <c r="CQ39" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.94209082596774674</v>
       </c>
       <c r="CS39" s="14"/>
       <c r="CT39" s="13" t="s">
@@ -10693,15 +10840,15 @@
       <c r="CV39" s="12"/>
       <c r="CW39" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CX39" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY39" s="11" t="e">
+        <v>-606857.14285711991</v>
+      </c>
+      <c r="CY39" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -10942,19 +11089,23 @@
         <v>12</v>
       </c>
       <c r="CL40" s="9"/>
-      <c r="CM40" s="8"/>
-      <c r="CN40" s="7"/>
+      <c r="CM40" s="8">
+        <v>236</v>
+      </c>
+      <c r="CN40" s="7">
+        <v>1396168.5714280198</v>
+      </c>
       <c r="CO40" s="27">
         <f t="shared" si="26"/>
-        <v>-193</v>
+        <v>43</v>
       </c>
       <c r="CP40" s="28">
         <f t="shared" si="27"/>
-        <v>-978576.66666619992</v>
+        <v>417591.90476181987</v>
       </c>
       <c r="CQ40" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.42673396882072162</v>
       </c>
       <c r="CS40" s="9" t="s">
         <v>12</v>
@@ -10964,15 +11115,15 @@
       <c r="CV40" s="7"/>
       <c r="CW40" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-236</v>
       </c>
       <c r="CX40" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY40" s="29" t="e">
+        <v>-1396168.5714280198</v>
+      </c>
+      <c r="CY40" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -11215,11 +11366,13 @@
       <c r="CL41" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CM41" s="15"/>
+      <c r="CM41" s="15">
+        <v>1907</v>
+      </c>
       <c r="CN41" s="33"/>
       <c r="CO41" s="10">
         <f t="shared" si="26"/>
-        <v>-1557</v>
+        <v>350</v>
       </c>
       <c r="CP41" s="12">
         <f t="shared" si="27"/>
@@ -11239,7 +11392,7 @@
       <c r="CV41" s="33"/>
       <c r="CW41" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1907</v>
       </c>
       <c r="CX41" s="12">
         <f t="shared" si="30"/>
@@ -11736,18 +11889,23 @@
       <c r="CL43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CN43" s="12"/>
+      <c r="CM43" s="10">
+        <v>116</v>
+      </c>
+      <c r="CN43" s="12">
+        <v>117830.47619000993</v>
+      </c>
       <c r="CO43" s="10">
         <f t="shared" si="26"/>
-        <v>-90</v>
+        <v>26</v>
       </c>
       <c r="CP43" s="12">
         <f t="shared" si="27"/>
-        <v>-81430.476190019996</v>
+        <v>36399.99999998993</v>
       </c>
       <c r="CQ43" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.44700708755588808</v>
       </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13" t="s">
@@ -11756,15 +11914,15 @@
       <c r="CV43" s="12"/>
       <c r="CW43" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-116</v>
       </c>
       <c r="CX43" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY43" s="11" t="e">
+        <v>-117830.47619000993</v>
+      </c>
+      <c r="CY43" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12004,18 +12162,23 @@
       <c r="CL44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN44" s="12"/>
+      <c r="CM44" s="10">
+        <v>109</v>
+      </c>
+      <c r="CN44" s="12">
+        <v>104896.19047608</v>
+      </c>
       <c r="CO44" s="10">
         <f t="shared" si="26"/>
-        <v>-67</v>
+        <v>42</v>
       </c>
       <c r="CP44" s="12">
         <f t="shared" si="27"/>
-        <v>-75810.476190389993</v>
+        <v>29085.714285690003</v>
       </c>
       <c r="CQ44" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.3836635218151685</v>
       </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13" t="s">
@@ -12024,15 +12187,15 @@
       <c r="CV44" s="12"/>
       <c r="CW44" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="CX44" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY44" s="11" t="e">
+        <v>-104896.19047608</v>
+      </c>
+      <c r="CY44" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12272,18 +12435,23 @@
       <c r="CL45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN45" s="12"/>
+      <c r="CM45" s="10">
+        <v>9</v>
+      </c>
+      <c r="CN45" s="12">
+        <v>57057.142857129998</v>
+      </c>
       <c r="CO45" s="10">
         <f t="shared" si="26"/>
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="CP45" s="12">
         <f t="shared" si="27"/>
-        <v>-44219.04761904</v>
+        <v>12838.095238089998</v>
       </c>
       <c r="CQ45" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.29032952832213699</v>
       </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13" t="s">
@@ -12292,15 +12460,15 @@
       <c r="CV45" s="12"/>
       <c r="CW45" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CX45" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY45" s="11" t="e">
+        <v>-57057.142857129998</v>
+      </c>
+      <c r="CY45" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12540,18 +12708,23 @@
       <c r="CL46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN46" s="12"/>
+      <c r="CM46" s="10">
+        <v>13</v>
+      </c>
+      <c r="CN46" s="12">
+        <v>140004.76190474001</v>
+      </c>
       <c r="CO46" s="10">
         <f t="shared" si="26"/>
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="CP46" s="12">
         <f t="shared" si="27"/>
-        <v>-212571.42857138999</v>
+        <v>-72566.66666664998</v>
       </c>
       <c r="CQ46" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.34137544802865732</v>
       </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13" t="s">
@@ -12560,15 +12733,15 @@
       <c r="CV46" s="12"/>
       <c r="CW46" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CX46" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY46" s="11" t="e">
+        <v>-140004.76190474001</v>
+      </c>
+      <c r="CY46" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13036,14 +13209,19 @@
       <c r="CL48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN48" s="12"/>
+      <c r="CM48" s="10">
+        <v>3</v>
+      </c>
+      <c r="CN48" s="12">
+        <v>20770</v>
+      </c>
       <c r="CO48" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="CP48" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>20770</v>
       </c>
       <c r="CQ48" s="11" t="e">
         <f t="shared" si="28"/>
@@ -13056,15 +13234,15 @@
       <c r="CV48" s="12"/>
       <c r="CW48" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CX48" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY48" s="11" t="e">
+        <v>-20770</v>
+      </c>
+      <c r="CY48" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13299,18 +13477,23 @@
       <c r="CL49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN49" s="12"/>
+      <c r="CM49" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN49" s="12">
+        <v>290060.95238092</v>
+      </c>
       <c r="CO49" s="10">
         <f t="shared" si="26"/>
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="CP49" s="12">
         <f t="shared" si="27"/>
-        <v>-175492.38095235999</v>
+        <v>114568.57142856001</v>
       </c>
       <c r="CQ49" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.65284071483229433</v>
       </c>
       <c r="CS49" s="14"/>
       <c r="CT49" s="13" t="s">
@@ -13319,15 +13502,15 @@
       <c r="CV49" s="12"/>
       <c r="CW49" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CX49" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY49" s="11" t="e">
+        <v>-290060.95238092</v>
+      </c>
+      <c r="CY49" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13567,18 +13750,23 @@
       <c r="CL50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN50" s="12"/>
+      <c r="CM50" s="10">
+        <v>14</v>
+      </c>
+      <c r="CN50" s="12">
+        <v>293047.61904758</v>
+      </c>
       <c r="CO50" s="10">
         <f t="shared" si="26"/>
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="CP50" s="12">
         <f t="shared" si="27"/>
-        <v>-334285.71428567002</v>
+        <v>-41238.095238090027</v>
       </c>
       <c r="CQ50" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.12336182336182411</v>
       </c>
       <c r="CS50" s="14"/>
       <c r="CT50" s="13" t="s">
@@ -13587,15 +13775,15 @@
       <c r="CV50" s="12"/>
       <c r="CW50" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CX50" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY50" s="11" t="e">
+        <v>-293047.61904758</v>
+      </c>
+      <c r="CY50" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13835,18 +14023,23 @@
       <c r="CL51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN51" s="12"/>
+      <c r="CM51" s="10">
+        <v>18</v>
+      </c>
+      <c r="CN51" s="12">
+        <v>628761.90476186003</v>
+      </c>
       <c r="CO51" s="10">
         <f t="shared" si="26"/>
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="CP51" s="12">
         <f t="shared" si="27"/>
-        <v>-358952.38095235999</v>
+        <v>269809.52380950004</v>
       </c>
       <c r="CQ51" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.75165826479169962</v>
       </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13" t="s">
@@ -13855,15 +14048,15 @@
       <c r="CV51" s="12"/>
       <c r="CW51" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CX51" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY51" s="11" t="e">
+        <v>-628761.90476186003</v>
+      </c>
+      <c r="CY51" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -14104,19 +14297,23 @@
         <v>11</v>
       </c>
       <c r="CL52" s="9"/>
-      <c r="CM52" s="8"/>
-      <c r="CN52" s="7"/>
+      <c r="CM52" s="8">
+        <v>293</v>
+      </c>
+      <c r="CN52" s="7">
+        <v>1652429.0476183197</v>
+      </c>
       <c r="CO52" s="27">
         <f t="shared" si="26"/>
-        <v>-218</v>
+        <v>75</v>
       </c>
       <c r="CP52" s="28">
         <f t="shared" si="27"/>
-        <v>-1282761.9047612301</v>
+        <v>369667.14285708964</v>
       </c>
       <c r="CQ52" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.28818063701844848</v>
       </c>
       <c r="CS52" s="9" t="s">
         <v>11</v>
@@ -14126,15 +14323,15 @@
       <c r="CV52" s="7"/>
       <c r="CW52" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-293</v>
       </c>
       <c r="CX52" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY52" s="29" t="e">
+        <v>-1652429.0476183197</v>
+      </c>
+      <c r="CY52" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -14868,18 +15065,23 @@
       <c r="CL55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CN55" s="12"/>
+      <c r="CM55" s="10">
+        <v>89</v>
+      </c>
+      <c r="CN55" s="12">
+        <v>85134.285713899968</v>
+      </c>
       <c r="CO55" s="10">
         <f t="shared" si="26"/>
-        <v>-113</v>
+        <v>-24</v>
       </c>
       <c r="CP55" s="12">
         <f t="shared" si="27"/>
-        <v>-121799.04761848997</v>
+        <v>-36664.761904590006</v>
       </c>
       <c r="CQ55" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.3010266715667162</v>
       </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13" t="s">
@@ -14888,15 +15090,15 @@
       <c r="CV55" s="12"/>
       <c r="CW55" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="CX55" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY55" s="11" t="e">
+        <v>-85134.285713899968</v>
+      </c>
+      <c r="CY55" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15136,18 +15338,23 @@
       <c r="CL56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN56" s="12"/>
+      <c r="CM56" s="10">
+        <v>63</v>
+      </c>
+      <c r="CN56" s="12">
+        <v>57885.714285640017</v>
+      </c>
       <c r="CO56" s="10">
         <f t="shared" si="26"/>
-        <v>-59</v>
+        <v>4</v>
       </c>
       <c r="CP56" s="12">
         <f t="shared" si="27"/>
-        <v>-70390.476190379995</v>
+        <v>-12504.761904739978</v>
       </c>
       <c r="CQ56" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.17764849140840103</v>
       </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13" t="s">
@@ -15156,15 +15363,15 @@
       <c r="CV56" s="12"/>
       <c r="CW56" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="CX56" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY56" s="11" t="e">
+        <v>-57885.714285640017</v>
+      </c>
+      <c r="CY56" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15404,18 +15611,23 @@
       <c r="CL57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN57" s="12"/>
+      <c r="CM57" s="10">
+        <v>22</v>
+      </c>
+      <c r="CN57" s="12">
+        <v>175504.76190475002</v>
+      </c>
       <c r="CO57" s="10">
         <f t="shared" si="26"/>
-        <v>-14</v>
+        <v>8</v>
       </c>
       <c r="CP57" s="12">
         <f t="shared" si="27"/>
-        <v>-102723.80952379</v>
+        <v>72780.952380960021</v>
       </c>
       <c r="CQ57" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.70851103282053174</v>
       </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13" t="s">
@@ -15424,15 +15636,15 @@
       <c r="CV57" s="12"/>
       <c r="CW57" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="CX57" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY57" s="11" t="e">
+        <v>-175504.76190475002</v>
+      </c>
+      <c r="CY57" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15672,18 +15884,23 @@
       <c r="CL58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN58" s="12"/>
+      <c r="CM58" s="10">
+        <v>12</v>
+      </c>
+      <c r="CN58" s="12">
+        <v>143619.04761902001</v>
+      </c>
       <c r="CO58" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="CP58" s="12">
         <f t="shared" si="27"/>
-        <v>-156857.1428571</v>
+        <v>-13238.095238079986</v>
       </c>
       <c r="CQ58" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-8.4395871281043006E-2</v>
       </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13" t="s">
@@ -15692,15 +15909,15 @@
       <c r="CV58" s="12"/>
       <c r="CW58" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CX58" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY58" s="11" t="e">
+        <v>-143619.04761902001</v>
+      </c>
+      <c r="CY58" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16164,18 +16381,23 @@
       <c r="CL60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN60" s="12"/>
+      <c r="CM60" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN60" s="12">
+        <v>2590</v>
+      </c>
       <c r="CO60" s="10">
         <f t="shared" si="26"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="CP60" s="12">
         <f t="shared" si="27"/>
-        <v>-27150</v>
+        <v>-24560</v>
       </c>
       <c r="CQ60" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.90460405156537749</v>
       </c>
       <c r="CS60" s="14"/>
       <c r="CT60" s="13" t="s">
@@ -16184,15 +16406,15 @@
       <c r="CV60" s="12"/>
       <c r="CW60" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CX60" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY60" s="11" t="e">
+        <v>-2590</v>
+      </c>
+      <c r="CY60" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16432,18 +16654,23 @@
       <c r="CL61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN61" s="12"/>
+      <c r="CM61" s="10">
+        <v>7</v>
+      </c>
+      <c r="CN61" s="12">
+        <v>267904.76190473</v>
+      </c>
       <c r="CO61" s="10">
         <f t="shared" si="26"/>
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="CP61" s="12">
         <f t="shared" si="27"/>
-        <v>-261295.23809520996</v>
+        <v>6609.523809520033</v>
       </c>
       <c r="CQ61" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>2.5295232541175033E-2</v>
       </c>
       <c r="CS61" s="14"/>
       <c r="CT61" s="13" t="s">
@@ -16452,15 +16679,15 @@
       <c r="CV61" s="12"/>
       <c r="CW61" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CX61" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY61" s="11" t="e">
+        <v>-267904.76190473</v>
+      </c>
+      <c r="CY61" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16700,18 +16927,23 @@
       <c r="CL62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN62" s="12"/>
+      <c r="CM62" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN62" s="12">
+        <v>159523.80952377999</v>
+      </c>
       <c r="CO62" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="CP62" s="12">
         <f t="shared" si="27"/>
-        <v>-277809.52380949003</v>
+        <v>-118285.71428571004</v>
       </c>
       <c r="CQ62" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.42577991086736594</v>
       </c>
       <c r="CS62" s="14"/>
       <c r="CT62" s="13" t="s">
@@ -16720,15 +16952,15 @@
       <c r="CV62" s="12"/>
       <c r="CW62" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CX62" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY62" s="11" t="e">
+        <v>-159523.80952377999</v>
+      </c>
+      <c r="CY62" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16968,18 +17200,23 @@
       <c r="CL63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN63" s="12"/>
+      <c r="CM63" s="10">
+        <v>12</v>
+      </c>
+      <c r="CN63" s="12">
+        <v>430707.61904758995</v>
+      </c>
       <c r="CO63" s="10">
         <f t="shared" si="26"/>
-        <v>-18</v>
+        <v>-6</v>
       </c>
       <c r="CP63" s="12">
         <f t="shared" si="27"/>
-        <v>-655428.57142853993</v>
+        <v>-224720.95238094998</v>
       </c>
       <c r="CQ63" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.34286108689335776</v>
       </c>
       <c r="CS63" s="14"/>
       <c r="CT63" s="13" t="s">
@@ -16988,15 +17225,15 @@
       <c r="CV63" s="12"/>
       <c r="CW63" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CX63" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY63" s="11" t="e">
+        <v>-430707.61904758995</v>
+      </c>
+      <c r="CY63" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -17237,19 +17474,23 @@
         <v>1</v>
       </c>
       <c r="CL64" s="9"/>
-      <c r="CM64" s="8"/>
-      <c r="CN64" s="7"/>
+      <c r="CM64" s="8">
+        <v>216</v>
+      </c>
+      <c r="CN64" s="7">
+        <v>1322869.99999941</v>
+      </c>
       <c r="CO64" s="27">
         <f t="shared" si="26"/>
-        <v>-242</v>
+        <v>-26</v>
       </c>
       <c r="CP64" s="28">
         <f t="shared" si="27"/>
-        <v>-1673453.8095229999</v>
+        <v>-350583.80952358991</v>
       </c>
       <c r="CQ64" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.20949715344908149</v>
       </c>
       <c r="CS64" s="9" t="s">
         <v>1</v>
@@ -17259,15 +17500,15 @@
       <c r="CV64" s="7"/>
       <c r="CW64" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-216</v>
       </c>
       <c r="CX64" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY64" s="29" t="e">
+        <v>-1322869.99999941</v>
+      </c>
+      <c r="CY64" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -17508,19 +17749,23 @@
         <v>0</v>
       </c>
       <c r="CL65" s="4"/>
-      <c r="CM65" s="3"/>
-      <c r="CN65" s="2"/>
+      <c r="CM65" s="3">
+        <v>2050</v>
+      </c>
+      <c r="CN65" s="2">
+        <v>15951239.52380522</v>
+      </c>
       <c r="CO65" s="6">
         <f t="shared" si="26"/>
-        <v>-1893</v>
+        <v>157</v>
       </c>
       <c r="CP65" s="5">
         <f t="shared" si="27"/>
-        <v>-15151444.7619006</v>
+        <v>799794.76190461963</v>
       </c>
       <c r="CQ65" s="30">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>5.2786699517643441E-2</v>
       </c>
       <c r="CS65" s="4" t="s">
         <v>0</v>
@@ -17530,15 +17775,15 @@
       <c r="CV65" s="2"/>
       <c r="CW65" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-2050</v>
       </c>
       <c r="CX65" s="5">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY65" s="30" t="e">
+        <v>-15951239.52380522</v>
+      </c>
+      <c r="CY65" s="30">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F2AE45-3CBD-124A-A494-F0D4BB1BD09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83EA91F-2C62-1E4A-977C-FDA85A8FA20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="48">
   <si>
     <t>總計</t>
   </si>
@@ -240,6 +240,14 @@
   </si>
   <si>
     <t>06/14~06/20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3W13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06/21~06/27</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1135,7 +1143,9 @@
       </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
-      <c r="CS1" s="26"/>
+      <c r="CS1" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="CT1" s="26"/>
       <c r="CV1" s="25"/>
     </row>
@@ -1219,6 +1229,9 @@
       <c r="CO2" s="21"/>
       <c r="CP2" s="21"/>
       <c r="CQ2" s="21"/>
+      <c r="CS2" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="CT2" s="21"/>
       <c r="CV2" s="21"/>
       <c r="CW2" s="21"/>
@@ -1735,11 +1748,13 @@
       <c r="CT5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CU5" s="15"/>
+      <c r="CU5" s="15">
+        <v>5170</v>
+      </c>
       <c r="CV5" s="33"/>
       <c r="CW5" s="10">
         <f t="shared" ref="CW5:CW65" si="29">CU5-CM5</f>
-        <v>-6416</v>
+        <v>-1246</v>
       </c>
       <c r="CX5" s="12">
         <f t="shared" ref="CX5:CX65" si="30">CV5-CN5</f>
@@ -1966,10 +1981,13 @@
       <c r="CL6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CM6" s="15">
+        <v>5</v>
+      </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -1986,7 +2004,7 @@
       <c r="CV6" s="33"/>
       <c r="CW6" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CX6" s="12">
         <f t="shared" si="30"/>
@@ -2256,18 +2274,23 @@
       <c r="CT7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CV7" s="12"/>
+      <c r="CU7" s="10">
+        <v>171</v>
+      </c>
+      <c r="CV7" s="12">
+        <v>199022.85714212016</v>
+      </c>
       <c r="CW7" s="10">
         <f t="shared" si="29"/>
-        <v>-181</v>
+        <v>-10</v>
       </c>
       <c r="CX7" s="12">
         <f t="shared" si="30"/>
-        <v>-215959.04761827007</v>
+        <v>-16936.190476149903</v>
       </c>
       <c r="CY7" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-7.8423157829841744E-2</v>
       </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2529,18 +2552,23 @@
       <c r="CT8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV8" s="12"/>
+      <c r="CU8" s="10">
+        <v>246</v>
+      </c>
+      <c r="CV8" s="12">
+        <v>409514.28571404982</v>
+      </c>
       <c r="CW8" s="10">
         <f t="shared" si="29"/>
-        <v>-277</v>
+        <v>-31</v>
       </c>
       <c r="CX8" s="12">
         <f t="shared" si="30"/>
-        <v>-357247.61904741998</v>
+        <v>52266.666666629841</v>
       </c>
       <c r="CY8" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.14630375089971451</v>
       </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2802,18 +2830,23 @@
       <c r="CT9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV9" s="12"/>
+      <c r="CU9" s="10">
+        <v>60</v>
+      </c>
+      <c r="CV9" s="12">
+        <v>436215.23809520004</v>
+      </c>
       <c r="CW9" s="10">
         <f t="shared" si="29"/>
-        <v>-61</v>
+        <v>-1</v>
       </c>
       <c r="CX9" s="12">
         <f t="shared" si="30"/>
-        <v>-388849.52380950999</v>
+        <v>47365.714285690046</v>
       </c>
       <c r="CY9" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.12180988116342303</v>
       </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3075,18 +3108,23 @@
       <c r="CT10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV10" s="12"/>
+      <c r="CU10" s="10">
+        <v>39</v>
+      </c>
+      <c r="CV10" s="12">
+        <v>481619.04761899001</v>
+      </c>
       <c r="CW10" s="10">
         <f t="shared" si="29"/>
-        <v>-39</v>
+        <v>0</v>
       </c>
       <c r="CX10" s="12">
         <f t="shared" si="30"/>
-        <v>-491523.80952373007</v>
+        <v>-9904.7619047400658</v>
       </c>
       <c r="CY10" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-2.0151133501218273E-2</v>
       </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3596,18 +3634,23 @@
       <c r="CT12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV12" s="12"/>
+      <c r="CU12" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV12" s="12">
+        <v>62080</v>
+      </c>
       <c r="CW12" s="10">
         <f t="shared" si="29"/>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="CX12" s="12">
         <f t="shared" si="30"/>
-        <v>-80780</v>
+        <v>-18700</v>
       </c>
       <c r="CY12" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.23149294379796981</v>
       </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3869,18 +3912,23 @@
       <c r="CT13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV13" s="12"/>
+      <c r="CU13" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV13" s="12">
+        <v>602380.95238092006</v>
+      </c>
       <c r="CW13" s="10">
         <f t="shared" si="29"/>
-        <v>-46</v>
+        <v>-34</v>
       </c>
       <c r="CX13" s="12">
         <f t="shared" si="30"/>
-        <v>-1416838.0952379801</v>
+        <v>-814457.14285706007</v>
       </c>
       <c r="CY13" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.57484136373412464</v>
       </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4142,18 +4190,23 @@
       <c r="CT14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV14" s="12"/>
+      <c r="CU14" s="10">
+        <v>48</v>
+      </c>
+      <c r="CV14" s="12">
+        <v>925904.76190467994</v>
+      </c>
       <c r="CW14" s="10">
         <f t="shared" si="29"/>
-        <v>-51</v>
+        <v>-3</v>
       </c>
       <c r="CX14" s="12">
         <f t="shared" si="30"/>
-        <v>-1142380.9523808402</v>
+        <v>-216476.19047616026</v>
       </c>
       <c r="CY14" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.18949562317631563</v>
       </c>
     </row>
     <row r="15" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4415,18 +4468,23 @@
       <c r="CT15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV15" s="12"/>
+      <c r="CU15" s="10">
+        <v>71</v>
+      </c>
+      <c r="CV15" s="12">
+        <v>2685619.04761896</v>
+      </c>
       <c r="CW15" s="10">
         <f t="shared" si="29"/>
-        <v>-82</v>
+        <v>-11</v>
       </c>
       <c r="CX15" s="12">
         <f t="shared" si="30"/>
-        <v>-2929333.3333332599</v>
+        <v>-243714.28571429988</v>
       </c>
       <c r="CY15" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-8.3197867221542779E-2</v>
       </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4689,19 +4747,23 @@
         <v>19</v>
       </c>
       <c r="CT16" s="9"/>
-      <c r="CU16" s="8"/>
-      <c r="CV16" s="7"/>
+      <c r="CU16" s="8">
+        <v>659</v>
+      </c>
+      <c r="CV16" s="7">
+        <v>5802356.19047492</v>
+      </c>
       <c r="CW16" s="27">
         <f t="shared" si="29"/>
-        <v>-749</v>
+        <v>-90</v>
       </c>
       <c r="CX16" s="28">
         <f t="shared" si="30"/>
-        <v>-7022912.3809510106</v>
+        <v>-1220556.1904760906</v>
       </c>
       <c r="CY16" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.17379630049019756</v>
       </c>
     </row>
     <row r="17" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4966,11 +5028,13 @@
       <c r="CT17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CU17" s="15"/>
+      <c r="CU17" s="15">
+        <v>3643</v>
+      </c>
       <c r="CV17" s="33"/>
       <c r="CW17" s="10">
         <f t="shared" si="29"/>
-        <v>-4430</v>
+        <v>-787</v>
       </c>
       <c r="CX17" s="12">
         <f t="shared" si="30"/>
@@ -5197,11 +5261,13 @@
       <c r="CL18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM18" s="15"/>
+      <c r="CM18" s="15">
+        <v>5</v>
+      </c>
       <c r="CN18" s="33"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
@@ -5219,7 +5285,7 @@
       <c r="CV18" s="33"/>
       <c r="CW18" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CX18" s="12">
         <f t="shared" si="30"/>
@@ -5489,18 +5555,23 @@
       <c r="CT19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CV19" s="12"/>
+      <c r="CU19" s="10">
+        <v>105</v>
+      </c>
+      <c r="CV19" s="12">
+        <v>103399.04761858996</v>
+      </c>
       <c r="CW19" s="10">
         <f t="shared" si="29"/>
-        <v>-152</v>
+        <v>-47</v>
       </c>
       <c r="CX19" s="12">
         <f t="shared" si="30"/>
-        <v>-188762.85714221009</v>
+        <v>-85363.809523620133</v>
       </c>
       <c r="CY19" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.4522277889622574</v>
       </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5762,18 +5833,23 @@
       <c r="CT20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV20" s="12"/>
+      <c r="CU20" s="10">
+        <v>168</v>
+      </c>
+      <c r="CV20" s="12">
+        <v>153828.57142846001</v>
+      </c>
       <c r="CW20" s="10">
         <f t="shared" si="29"/>
-        <v>-189</v>
+        <v>-21</v>
       </c>
       <c r="CX20" s="12">
         <f t="shared" si="30"/>
-        <v>-199820.95238083001</v>
+        <v>-45992.380952370004</v>
       </c>
       <c r="CY20" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.2301679598879858</v>
       </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6035,18 +6111,23 @@
       <c r="CT21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV21" s="12"/>
+      <c r="CU21" s="10">
+        <v>35</v>
+      </c>
+      <c r="CV21" s="12">
+        <v>233952.38095235999</v>
+      </c>
       <c r="CW21" s="10">
         <f t="shared" si="29"/>
-        <v>-37</v>
+        <v>-2</v>
       </c>
       <c r="CX21" s="12">
         <f t="shared" si="30"/>
-        <v>-220862.85714285</v>
+        <v>13089.523809509992</v>
       </c>
       <c r="CY21" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>5.926539201222019E-2</v>
       </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6308,18 +6389,23 @@
       <c r="CT22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV22" s="12"/>
+      <c r="CU22" s="10">
+        <v>29</v>
+      </c>
+      <c r="CV22" s="12">
+        <v>411809.52380948007</v>
+      </c>
       <c r="CW22" s="10">
         <f t="shared" si="29"/>
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="CX22" s="12">
         <f t="shared" si="30"/>
-        <v>-370095.23809517</v>
+        <v>41714.28571431007</v>
       </c>
       <c r="CY22" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.11271230056622139</v>
       </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6810,18 +6896,23 @@
       <c r="CT24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV24" s="12"/>
+      <c r="CU24" s="10">
+        <v>16</v>
+      </c>
+      <c r="CV24" s="12">
+        <v>40730</v>
+      </c>
       <c r="CW24" s="10">
         <f t="shared" si="29"/>
-        <v>-25</v>
+        <v>-9</v>
       </c>
       <c r="CX24" s="12">
         <f t="shared" si="30"/>
-        <v>-69870</v>
+        <v>-29140</v>
       </c>
       <c r="CY24" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.41706025475883785</v>
       </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7083,18 +7174,23 @@
       <c r="CT25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV25" s="12"/>
+      <c r="CU25" s="10">
+        <v>3</v>
+      </c>
+      <c r="CV25" s="12">
+        <v>107333.33333332</v>
+      </c>
       <c r="CW25" s="10">
         <f t="shared" si="29"/>
-        <v>-34</v>
+        <v>-31</v>
       </c>
       <c r="CX25" s="12">
         <f t="shared" si="30"/>
-        <v>-944399.99999992002</v>
+        <v>-837066.66666660004</v>
       </c>
       <c r="CY25" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.88634759282790232</v>
       </c>
     </row>
     <row r="26" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7356,18 +7452,23 @@
       <c r="CT26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV26" s="12"/>
+      <c r="CU26" s="10">
+        <v>24</v>
+      </c>
+      <c r="CV26" s="12">
+        <v>405904.76190470997</v>
+      </c>
       <c r="CW26" s="10">
         <f t="shared" si="29"/>
-        <v>-40</v>
+        <v>-16</v>
       </c>
       <c r="CX26" s="12">
         <f t="shared" si="30"/>
-        <v>-759238.09523802018</v>
+        <v>-353333.33333331021</v>
       </c>
       <c r="CY26" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.46537882589063273</v>
       </c>
     </row>
     <row r="27" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7629,18 +7730,23 @@
       <c r="CT27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV27" s="12"/>
+      <c r="CU27" s="10">
+        <v>42</v>
+      </c>
+      <c r="CV27" s="12">
+        <v>1423619.0476189998</v>
+      </c>
       <c r="CW27" s="10">
         <f t="shared" si="29"/>
-        <v>-50</v>
+        <v>-8</v>
       </c>
       <c r="CX27" s="12">
         <f t="shared" si="30"/>
-        <v>-1803809.5238094598</v>
+        <v>-380190.47619045991</v>
       </c>
       <c r="CY27" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.21077085533262782</v>
       </c>
     </row>
     <row r="28" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7903,19 +8009,23 @@
         <v>13</v>
       </c>
       <c r="CT28" s="9"/>
-      <c r="CU28" s="8"/>
-      <c r="CV28" s="7"/>
+      <c r="CU28" s="8">
+        <v>422</v>
+      </c>
+      <c r="CV28" s="7">
+        <v>2880576.6666659201</v>
+      </c>
       <c r="CW28" s="27">
         <f t="shared" si="29"/>
-        <v>-556</v>
+        <v>-134</v>
       </c>
       <c r="CX28" s="28">
         <f t="shared" si="30"/>
-        <v>-4556859.5238084598</v>
+        <v>-1676282.8571425397</v>
       </c>
       <c r="CY28" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.36785923471732623</v>
       </c>
     </row>
     <row r="29" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -8180,11 +8290,13 @@
       <c r="CT29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CU29" s="15"/>
+      <c r="CU29" s="15">
+        <v>2776</v>
+      </c>
       <c r="CV29" s="33"/>
       <c r="CW29" s="10">
         <f t="shared" si="29"/>
-        <v>-4006</v>
+        <v>-1230</v>
       </c>
       <c r="CX29" s="12">
         <f t="shared" si="30"/>
@@ -8411,11 +8523,13 @@
       <c r="CL30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM30" s="15"/>
+      <c r="CM30" s="15">
+        <v>1</v>
+      </c>
       <c r="CN30" s="33"/>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
@@ -8433,7 +8547,7 @@
       <c r="CV30" s="33"/>
       <c r="CW30" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CX30" s="12">
         <f t="shared" si="30"/>
@@ -8703,18 +8817,23 @@
       <c r="CT31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CV31" s="12"/>
+      <c r="CU31" s="10">
+        <v>100</v>
+      </c>
+      <c r="CV31" s="12">
+        <v>101870.47619005997</v>
+      </c>
       <c r="CW31" s="10">
         <f t="shared" si="29"/>
-        <v>-81</v>
+        <v>19</v>
       </c>
       <c r="CX31" s="12">
         <f t="shared" si="30"/>
-        <v>-74516.190475820025</v>
+        <v>27354.285714239944</v>
       </c>
       <c r="CY31" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.36709184325675126</v>
       </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8976,18 +9095,23 @@
       <c r="CT32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV32" s="12"/>
+      <c r="CU32" s="10">
+        <v>60</v>
+      </c>
+      <c r="CV32" s="12">
+        <v>67135.238095150009</v>
+      </c>
       <c r="CW32" s="10">
         <f t="shared" si="29"/>
-        <v>-75</v>
+        <v>-15</v>
       </c>
       <c r="CX32" s="12">
         <f t="shared" si="30"/>
-        <v>-71185.714285619993</v>
+        <v>-4050.4761904699844</v>
       </c>
       <c r="CY32" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-5.6900127098790783E-2</v>
       </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9249,18 +9373,23 @@
       <c r="CT33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV33" s="12"/>
+      <c r="CU33" s="10">
+        <v>16</v>
+      </c>
+      <c r="CV33" s="12">
+        <v>126874.28571427001</v>
+      </c>
       <c r="CW33" s="10">
         <f t="shared" si="29"/>
-        <v>-27</v>
+        <v>-11</v>
       </c>
       <c r="CX33" s="12">
         <f t="shared" si="30"/>
-        <v>-182315.23809522</v>
+        <v>-55440.952380949995</v>
       </c>
       <c r="CY33" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.30409390328631869</v>
       </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9522,18 +9651,23 @@
       <c r="CT34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV34" s="12"/>
+      <c r="CU34" s="10">
+        <v>11</v>
+      </c>
+      <c r="CV34" s="12">
+        <v>106571.42857140001</v>
+      </c>
       <c r="CW34" s="10">
         <f t="shared" si="29"/>
-        <v>-19</v>
+        <v>-8</v>
       </c>
       <c r="CX34" s="12">
         <f t="shared" si="30"/>
-        <v>-213719.04761903</v>
+        <v>-107147.61904762998</v>
       </c>
       <c r="CY34" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.50134800917992361</v>
       </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10018,18 +10152,23 @@
       <c r="CT36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV36" s="12"/>
+      <c r="CU36" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV36" s="12">
+        <v>2590</v>
+      </c>
       <c r="CW36" s="10">
         <f t="shared" si="29"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CX36" s="12">
         <f t="shared" si="30"/>
-        <v>-7480</v>
+        <v>-4890</v>
       </c>
       <c r="CY36" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.65374331550802134</v>
       </c>
     </row>
     <row r="37" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10291,18 +10430,23 @@
       <c r="CT37" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV37" s="12"/>
+      <c r="CU37" s="10">
+        <v>4</v>
+      </c>
+      <c r="CV37" s="12">
+        <v>103428.57142856001</v>
+      </c>
       <c r="CW37" s="10">
         <f t="shared" si="29"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="CX37" s="12">
         <f t="shared" si="30"/>
-        <v>-43619.04761904</v>
+        <v>59809.523809520011</v>
       </c>
       <c r="CY37" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.3711790393014625</v>
       </c>
     </row>
     <row r="38" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10564,18 +10708,23 @@
       <c r="CT38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV38" s="12"/>
+      <c r="CU38" s="10">
+        <v>20</v>
+      </c>
+      <c r="CV38" s="12">
+        <v>377904.76190471998</v>
+      </c>
       <c r="CW38" s="10">
         <f t="shared" si="29"/>
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="CX38" s="12">
         <f t="shared" si="30"/>
-        <v>-196476.19047616998</v>
+        <v>181428.57142855</v>
       </c>
       <c r="CY38" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.92341250605912439</v>
       </c>
     </row>
     <row r="39" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10837,18 +10986,23 @@
       <c r="CT39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV39" s="12"/>
+      <c r="CU39" s="10">
+        <v>19</v>
+      </c>
+      <c r="CV39" s="12">
+        <v>784857.14285709988</v>
+      </c>
       <c r="CW39" s="10">
         <f t="shared" si="29"/>
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="CX39" s="12">
         <f t="shared" si="30"/>
-        <v>-606857.14285711991</v>
+        <v>177999.99999997998</v>
       </c>
       <c r="CY39" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.29331450094159767</v>
       </c>
     </row>
     <row r="40" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -11111,19 +11265,23 @@
         <v>12</v>
       </c>
       <c r="CT40" s="9"/>
-      <c r="CU40" s="8"/>
-      <c r="CV40" s="7"/>
+      <c r="CU40" s="8">
+        <v>231</v>
+      </c>
+      <c r="CV40" s="7">
+        <v>1671231.9047612599</v>
+      </c>
       <c r="CW40" s="27">
         <f t="shared" si="29"/>
-        <v>-236</v>
+        <v>-5</v>
       </c>
       <c r="CX40" s="28">
         <f t="shared" si="30"/>
-        <v>-1396168.5714280198</v>
+        <v>275063.33333324012</v>
       </c>
       <c r="CY40" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.19701298178621918</v>
       </c>
     </row>
     <row r="41" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -11388,11 +11546,13 @@
       <c r="CT41" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="CU41" s="15"/>
+      <c r="CU41" s="15">
+        <v>1614</v>
+      </c>
       <c r="CV41" s="33"/>
       <c r="CW41" s="10">
         <f t="shared" si="29"/>
-        <v>-1907</v>
+        <v>-293</v>
       </c>
       <c r="CX41" s="12">
         <f t="shared" si="30"/>
@@ -11619,11 +11779,13 @@
       <c r="CL42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM42" s="15"/>
+      <c r="CM42" s="15">
+        <v>1</v>
+      </c>
       <c r="CN42" s="33"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
@@ -11641,7 +11803,7 @@
       <c r="CV42" s="33"/>
       <c r="CW42" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CX42" s="12">
         <f t="shared" si="30"/>
@@ -11911,18 +12073,23 @@
       <c r="CT43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CV43" s="12"/>
+      <c r="CU43" s="10">
+        <v>97</v>
+      </c>
+      <c r="CV43" s="12">
+        <v>97424.76190433999</v>
+      </c>
       <c r="CW43" s="10">
         <f t="shared" si="29"/>
-        <v>-116</v>
+        <v>-19</v>
       </c>
       <c r="CX43" s="12">
         <f t="shared" si="30"/>
-        <v>-117830.47619000993</v>
+        <v>-20405.714285669936</v>
       </c>
       <c r="CY43" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.17317857777952358</v>
       </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12184,18 +12351,23 @@
       <c r="CT44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV44" s="12"/>
+      <c r="CU44" s="10">
+        <v>92</v>
+      </c>
+      <c r="CV44" s="12">
+        <v>84857.14285702999</v>
+      </c>
       <c r="CW44" s="10">
         <f t="shared" si="29"/>
-        <v>-109</v>
+        <v>-17</v>
       </c>
       <c r="CX44" s="12">
         <f t="shared" si="30"/>
-        <v>-104896.19047608</v>
+        <v>-20039.047619050005</v>
       </c>
       <c r="CY44" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.19103694355439543</v>
       </c>
     </row>
     <row r="45" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12457,18 +12629,23 @@
       <c r="CT45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV45" s="12"/>
+      <c r="CU45" s="10">
+        <v>10</v>
+      </c>
+      <c r="CV45" s="12">
+        <v>77047.619047610002</v>
+      </c>
       <c r="CW45" s="10">
         <f t="shared" si="29"/>
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="CX45" s="12">
         <f t="shared" si="30"/>
-        <v>-57057.142857129998</v>
+        <v>19990.476190480003</v>
       </c>
       <c r="CY45" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.35035887164094032</v>
       </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12730,18 +12907,23 @@
       <c r="CT46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV46" s="12"/>
+      <c r="CU46" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV46" s="12">
+        <v>90666.66666665001</v>
+      </c>
       <c r="CW46" s="10">
         <f t="shared" si="29"/>
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="CX46" s="12">
         <f t="shared" si="30"/>
-        <v>-140004.76190474001</v>
+        <v>-49338.095238089998</v>
       </c>
       <c r="CY46" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.35240297949051119</v>
       </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13231,18 +13413,23 @@
       <c r="CT48" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV48" s="12"/>
+      <c r="CU48" s="10">
+        <v>2</v>
+      </c>
+      <c r="CV48" s="12">
+        <v>7290</v>
+      </c>
       <c r="CW48" s="10">
         <f t="shared" si="29"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="CX48" s="12">
         <f t="shared" si="30"/>
-        <v>-20770</v>
+        <v>-13480</v>
       </c>
       <c r="CY48" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.6490129995185363</v>
       </c>
     </row>
     <row r="49" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13499,18 +13686,23 @@
       <c r="CT49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV49" s="12"/>
+      <c r="CU49" s="10">
+        <v>3</v>
+      </c>
+      <c r="CV49" s="12">
+        <v>103711.42857142001</v>
+      </c>
       <c r="CW49" s="10">
         <f t="shared" si="29"/>
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="CX49" s="12">
         <f t="shared" si="30"/>
-        <v>-290060.95238092</v>
+        <v>-186349.52380949998</v>
       </c>
       <c r="CY49" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.64244953441640118</v>
       </c>
     </row>
     <row r="50" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13772,18 +13964,23 @@
       <c r="CT50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV50" s="12"/>
+      <c r="CU50" s="10">
+        <v>11</v>
+      </c>
+      <c r="CV50" s="12">
+        <v>249904.76190471</v>
+      </c>
       <c r="CW50" s="10">
         <f t="shared" si="29"/>
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="CX50" s="12">
         <f t="shared" si="30"/>
-        <v>-293047.61904758</v>
+        <v>-43142.857142869994</v>
       </c>
       <c r="CY50" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.14722131946707681</v>
       </c>
     </row>
     <row r="51" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14045,18 +14242,23 @@
       <c r="CT51" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV51" s="12"/>
+      <c r="CU51" s="10">
+        <v>18</v>
+      </c>
+      <c r="CV51" s="12">
+        <v>619238.09523804998</v>
+      </c>
       <c r="CW51" s="10">
         <f t="shared" si="29"/>
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="CX51" s="12">
         <f t="shared" si="30"/>
-        <v>-628761.90476186003</v>
+        <v>-9523.8095238100505</v>
       </c>
       <c r="CY51" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-1.5146925174191554E-2</v>
       </c>
     </row>
     <row r="52" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -14319,19 +14521,23 @@
         <v>11</v>
       </c>
       <c r="CT52" s="9"/>
-      <c r="CU52" s="8"/>
-      <c r="CV52" s="7"/>
+      <c r="CU52" s="8">
+        <v>241</v>
+      </c>
+      <c r="CV52" s="7">
+        <v>1330140.4761898099</v>
+      </c>
       <c r="CW52" s="27">
         <f t="shared" si="29"/>
-        <v>-293</v>
+        <v>-52</v>
       </c>
       <c r="CX52" s="28">
         <f t="shared" si="30"/>
-        <v>-1652429.0476183197</v>
+        <v>-322288.57142850989</v>
       </c>
       <c r="CY52" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.19503927983657215</v>
       </c>
     </row>
     <row r="53" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -14795,11 +15001,13 @@
       <c r="CL54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM54" s="15"/>
+      <c r="CM54" s="15">
+        <v>2</v>
+      </c>
       <c r="CN54" s="33"/>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>
@@ -14817,7 +15025,7 @@
       <c r="CV54" s="33"/>
       <c r="CW54" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CX54" s="12">
         <f t="shared" si="30"/>
@@ -15087,18 +15295,23 @@
       <c r="CT55" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="CV55" s="12"/>
+      <c r="CU55" s="10">
+        <v>104</v>
+      </c>
+      <c r="CV55" s="12">
+        <v>95000.952380499963</v>
+      </c>
       <c r="CW55" s="10">
         <f t="shared" si="29"/>
-        <v>-89</v>
+        <v>15</v>
       </c>
       <c r="CX55" s="12">
         <f t="shared" si="30"/>
-        <v>-85134.285713899968</v>
+        <v>9866.6666665999946</v>
       </c>
       <c r="CY55" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.11589533621927192</v>
       </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15360,18 +15573,23 @@
       <c r="CT56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV56" s="12"/>
+      <c r="CU56" s="10">
+        <v>60</v>
+      </c>
+      <c r="CV56" s="12">
+        <v>74285.714285630005</v>
+      </c>
       <c r="CW56" s="10">
         <f t="shared" si="29"/>
-        <v>-63</v>
+        <v>-3</v>
       </c>
       <c r="CX56" s="12">
         <f t="shared" si="30"/>
-        <v>-57885.714285640017</v>
+        <v>16399.999999989988</v>
       </c>
       <c r="CY56" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.28331688055300397</v>
       </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15633,18 +15851,23 @@
       <c r="CT57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV57" s="12"/>
+      <c r="CU57" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV57" s="12">
+        <v>88428.571428560012</v>
+      </c>
       <c r="CW57" s="10">
         <f t="shared" si="29"/>
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="CX57" s="12">
         <f t="shared" si="30"/>
-        <v>-175504.76190475002</v>
+        <v>-87076.190476190008</v>
       </c>
       <c r="CY57" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.49614716735405739</v>
       </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15906,18 +16129,23 @@
       <c r="CT58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV58" s="12"/>
+      <c r="CU58" s="10">
+        <v>11</v>
+      </c>
+      <c r="CV58" s="12">
+        <v>131333.33333330002</v>
+      </c>
       <c r="CW58" s="10">
         <f t="shared" si="29"/>
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="CX58" s="12">
         <f t="shared" si="30"/>
-        <v>-143619.04761902001</v>
+        <v>-12285.714285719994</v>
       </c>
       <c r="CY58" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-8.5543766578305522E-2</v>
       </c>
     </row>
     <row r="59" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16403,18 +16631,23 @@
       <c r="CT60" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV60" s="12"/>
+      <c r="CU60" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV60" s="12">
+        <v>20720</v>
+      </c>
       <c r="CW60" s="10">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CX60" s="12">
         <f t="shared" si="30"/>
-        <v>-2590</v>
+        <v>18130</v>
       </c>
       <c r="CY60" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16676,18 +16909,23 @@
       <c r="CT61" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV61" s="12"/>
+      <c r="CU61" s="10">
+        <v>5</v>
+      </c>
+      <c r="CV61" s="12">
+        <v>125238.09523808002</v>
+      </c>
       <c r="CW61" s="10">
         <f t="shared" si="29"/>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="CX61" s="12">
         <f t="shared" si="30"/>
-        <v>-267904.76190473</v>
+        <v>-142666.66666664998</v>
       </c>
       <c r="CY61" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.532527550657662</v>
       </c>
     </row>
     <row r="62" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16949,18 +17187,23 @@
       <c r="CT62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV62" s="12"/>
+      <c r="CU62" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV62" s="12">
+        <v>265238.09523804998</v>
+      </c>
       <c r="CW62" s="10">
         <f t="shared" si="29"/>
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="CX62" s="12">
         <f t="shared" si="30"/>
-        <v>-159523.80952377999</v>
+        <v>105714.28571426999</v>
       </c>
       <c r="CY62" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.66268656716420327</v>
       </c>
     </row>
     <row r="63" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -17222,18 +17465,23 @@
       <c r="CT63" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV63" s="12"/>
+      <c r="CU63" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV63" s="12">
+        <v>466190.47619046003</v>
+      </c>
       <c r="CW63" s="10">
         <f t="shared" si="29"/>
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="CX63" s="12">
         <f t="shared" si="30"/>
-        <v>-430707.61904758995</v>
+        <v>35482.857142870082</v>
       </c>
       <c r="CY63" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>8.2382701335379657E-2</v>
       </c>
     </row>
     <row r="64" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -17496,19 +17744,23 @@
         <v>1</v>
       </c>
       <c r="CT64" s="9"/>
-      <c r="CU64" s="8"/>
-      <c r="CV64" s="7"/>
+      <c r="CU64" s="8">
+        <v>233</v>
+      </c>
+      <c r="CV64" s="7">
+        <v>1266435.2380945799</v>
+      </c>
       <c r="CW64" s="27">
         <f t="shared" si="29"/>
-        <v>-216</v>
+        <v>17</v>
       </c>
       <c r="CX64" s="28">
         <f t="shared" si="30"/>
-        <v>-1322869.99999941</v>
+        <v>-56434.761904830113</v>
       </c>
       <c r="CY64" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-4.2660852468387127E-2</v>
       </c>
     </row>
     <row r="65" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -17771,19 +18023,23 @@
         <v>0</v>
       </c>
       <c r="CT65" s="4"/>
-      <c r="CU65" s="3"/>
-      <c r="CV65" s="2"/>
+      <c r="CU65" s="3">
+        <v>1786</v>
+      </c>
+      <c r="CV65" s="2">
+        <v>12950740.476186495</v>
+      </c>
       <c r="CW65" s="6">
         <f t="shared" si="29"/>
-        <v>-2050</v>
+        <v>-264</v>
       </c>
       <c r="CX65" s="5">
         <f t="shared" si="30"/>
-        <v>-15951239.52380522</v>
+        <v>-3000499.0476187244</v>
       </c>
       <c r="CY65" s="30">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.18810444436878129</v>
       </c>
     </row>
   </sheetData>

--- a/data/FY26Q3.xlsx
+++ b/data/FY26Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83EA91F-2C62-1E4A-977C-FDA85A8FA20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856A3A0D-00AF-6D4C-B10C-F1E33B9D1172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1982,12 +1982,12 @@
         <v>21</v>
       </c>
       <c r="CM6" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -2001,10 +2001,13 @@
       <c r="CT6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CU6" s="15">
+        <v>7</v>
+      </c>
       <c r="CV6" s="33"/>
       <c r="CW6" s="10">
         <f t="shared" si="29"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="CX6" s="12">
         <f t="shared" si="30"/>
@@ -5262,12 +5265,12 @@
         <v>21</v>
       </c>
       <c r="CM18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CN18" s="33"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
@@ -5281,11 +5284,13 @@
       <c r="CT18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU18" s="15"/>
+      <c r="CU18" s="15">
+        <v>8</v>
+      </c>
       <c r="CV18" s="33"/>
       <c r="CW18" s="10">
         <f t="shared" si="29"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="CX18" s="12">
         <f t="shared" si="30"/>
@@ -8543,11 +8548,13 @@
       <c r="CT30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU30" s="15"/>
+      <c r="CU30" s="15">
+        <v>4</v>
+      </c>
       <c r="CV30" s="33"/>
       <c r="CW30" s="10">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CX30" s="12">
         <f t="shared" si="30"/>
@@ -11780,12 +11787,12 @@
         <v>21</v>
       </c>
       <c r="CM42" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN42" s="33"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
@@ -11799,11 +11806,13 @@
       <c r="CT42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU42" s="15"/>
+      <c r="CU42" s="15">
+        <v>4</v>
+      </c>
       <c r="CV42" s="33"/>
       <c r="CW42" s="10">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CX42" s="12">
         <f t="shared" si="30"/>
@@ -15021,7 +15030,9 @@
       <c r="CT54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU54" s="15"/>
+      <c r="CU54" s="15">
+        <v>0</v>
+      </c>
       <c r="CV54" s="33"/>
       <c r="CW54" s="10">
         <f t="shared" si="29"/>
